--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -1900,7 +1900,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>h</v>
+            <v>Decision limit h — crossing it is the signal</v>
           </tx>
           <spPr>
             <a:ln w="16000">

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -174,6 +174,7 @@
     <xf numFmtId="167" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,7 +522,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>Average</v>
+            <v>Mean</v>
           </tx>
           <spPr>
             <a:ln w="28000">
@@ -551,6 +552,74 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Median</v>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'t and g (rare events)'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'t and g (rare events)'!$N$14:$N$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>UCL</v>
+          </tx>
+          <spPr>
+            <a:ln w="16000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'t and g (rare events)'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'t and g (rare events)'!$M$14:$M$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -573,7 +642,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="62590"/>
+          <max val="133760"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2038,7 +2107,7 @@
           <idx val="1"/>
           <order val="1"/>
           <tx>
-            <v>Average</v>
+            <v>Centre line (back-transformed)</v>
           </tx>
           <spPr>
             <a:ln w="28000">
@@ -2411,7 +2480,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>16</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>
@@ -10654,7 +10723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10719,7 +10788,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Average days between (t-chart)</t>
@@ -10731,7 +10800,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Rising over time is the improvement you want.</t>
+          <t>Rising over time is the improvement you want. This is the arithmetic mean and is deliberately NOT the chart's centre line — these gaps are right-skewed, so the mean sits above the middle of the limits.</t>
         </is>
       </c>
     </row>
@@ -10865,6 +10934,16 @@
           <t>Signal</t>
         </is>
       </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>g UCL</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>g median</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10903,7 +10982,15 @@
         <v/>
       </c>
       <c r="L14" s="33">
-        <f>IF(B14="","",$B$6)</f>
+        <f>IF(B14="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M14" s="34">
+        <f>IF(F14="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N14" s="34">
+        <f>IF(F14="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -10948,7 +11035,15 @@
         <v/>
       </c>
       <c r="L15" s="33">
-        <f>IF(B15="","",$B$6)</f>
+        <f>IF(B15="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M15" s="34">
+        <f>IF(F15="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N15" s="34">
+        <f>IF(F15="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -10993,7 +11088,15 @@
         <v/>
       </c>
       <c r="L16" s="33">
-        <f>IF(B16="","",$B$6)</f>
+        <f>IF(B16="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M16" s="34">
+        <f>IF(F16="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N16" s="34">
+        <f>IF(F16="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11038,7 +11141,15 @@
         <v/>
       </c>
       <c r="L17" s="33">
-        <f>IF(B17="","",$B$6)</f>
+        <f>IF(B17="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M17" s="34">
+        <f>IF(F17="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N17" s="34">
+        <f>IF(F17="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11083,7 +11194,15 @@
         <v/>
       </c>
       <c r="L18" s="33">
-        <f>IF(B18="","",$B$6)</f>
+        <f>IF(B18="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M18" s="34">
+        <f>IF(F18="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N18" s="34">
+        <f>IF(F18="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11128,7 +11247,15 @@
         <v/>
       </c>
       <c r="L19" s="33">
-        <f>IF(B19="","",$B$6)</f>
+        <f>IF(B19="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M19" s="34">
+        <f>IF(F19="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N19" s="34">
+        <f>IF(F19="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11173,7 +11300,15 @@
         <v/>
       </c>
       <c r="L20" s="33">
-        <f>IF(B20="","",$B$6)</f>
+        <f>IF(B20="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M20" s="34">
+        <f>IF(F20="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N20" s="34">
+        <f>IF(F20="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11218,7 +11353,15 @@
         <v/>
       </c>
       <c r="L21" s="33">
-        <f>IF(B21="","",$B$6)</f>
+        <f>IF(B21="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M21" s="34">
+        <f>IF(F21="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N21" s="34">
+        <f>IF(F21="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11263,7 +11406,15 @@
         <v/>
       </c>
       <c r="L22" s="33">
-        <f>IF(B22="","",$B$6)</f>
+        <f>IF(B22="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M22" s="34">
+        <f>IF(F22="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N22" s="34">
+        <f>IF(F22="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11308,7 +11459,15 @@
         <v/>
       </c>
       <c r="L23" s="33">
-        <f>IF(B23="","",$B$6)</f>
+        <f>IF(B23="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M23" s="34">
+        <f>IF(F23="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N23" s="34">
+        <f>IF(F23="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11353,7 +11512,15 @@
         <v/>
       </c>
       <c r="L24" s="33">
-        <f>IF(B24="","",$B$6)</f>
+        <f>IF(B24="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M24" s="34">
+        <f>IF(F24="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N24" s="34">
+        <f>IF(F24="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11398,7 +11565,15 @@
         <v/>
       </c>
       <c r="L25" s="33">
-        <f>IF(B25="","",$B$6)</f>
+        <f>IF(B25="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M25" s="34">
+        <f>IF(F25="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N25" s="34">
+        <f>IF(F25="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11443,7 +11618,15 @@
         <v/>
       </c>
       <c r="L26" s="33">
-        <f>IF(B26="","",$B$6)</f>
+        <f>IF(B26="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M26" s="34">
+        <f>IF(F26="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N26" s="34">
+        <f>IF(F26="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11488,7 +11671,15 @@
         <v/>
       </c>
       <c r="L27" s="33">
-        <f>IF(B27="","",$B$6)</f>
+        <f>IF(B27="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M27" s="34">
+        <f>IF(F27="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N27" s="34">
+        <f>IF(F27="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11533,7 +11724,15 @@
         <v/>
       </c>
       <c r="L28" s="33">
-        <f>IF(B28="","",$B$6)</f>
+        <f>IF(B28="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M28" s="34">
+        <f>IF(F28="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N28" s="34">
+        <f>IF(F28="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11578,7 +11777,15 @@
         <v/>
       </c>
       <c r="L29" s="33">
-        <f>IF(B29="","",$B$6)</f>
+        <f>IF(B29="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M29" s="34">
+        <f>IF(F29="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N29" s="34">
+        <f>IF(F29="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11623,7 +11830,15 @@
         <v/>
       </c>
       <c r="L30" s="33">
-        <f>IF(B30="","",$B$6)</f>
+        <f>IF(B30="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M30" s="34">
+        <f>IF(F30="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N30" s="34">
+        <f>IF(F30="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11668,7 +11883,15 @@
         <v/>
       </c>
       <c r="L31" s="33">
-        <f>IF(B31="","",$B$6)</f>
+        <f>IF(B31="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M31" s="34">
+        <f>IF(F31="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N31" s="34">
+        <f>IF(F31="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11713,7 +11936,15 @@
         <v/>
       </c>
       <c r="L32" s="33">
-        <f>IF(B32="","",$B$6)</f>
+        <f>IF(B32="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M32" s="34">
+        <f>IF(F32="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N32" s="34">
+        <f>IF(F32="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11758,7 +11989,15 @@
         <v/>
       </c>
       <c r="L33" s="33">
-        <f>IF(B33="","",$B$6)</f>
+        <f>IF(B33="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M33" s="34">
+        <f>IF(F33="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N33" s="34">
+        <f>IF(F33="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11803,7 +12042,15 @@
         <v/>
       </c>
       <c r="L34" s="33">
-        <f>IF(B34="","",$B$6)</f>
+        <f>IF(B34="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M34" s="34">
+        <f>IF(F34="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N34" s="34">
+        <f>IF(F34="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11848,7 +12095,15 @@
         <v/>
       </c>
       <c r="L35" s="33">
-        <f>IF(B35="","",$B$6)</f>
+        <f>IF(B35="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M35" s="34">
+        <f>IF(F35="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N35" s="34">
+        <f>IF(F35="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11893,7 +12148,15 @@
         <v/>
       </c>
       <c r="L36" s="33">
-        <f>IF(B36="","",$B$6)</f>
+        <f>IF(B36="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M36" s="34">
+        <f>IF(F36="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N36" s="34">
+        <f>IF(F36="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>
@@ -11938,7 +12201,15 @@
         <v/>
       </c>
       <c r="L37" s="33">
-        <f>IF(B37="","",$B$6)</f>
+        <f>IF(B37="","",$B$7^3.6)</f>
+        <v/>
+      </c>
+      <c r="M37" s="34">
+        <f>IF(F37="","",$B$11)</f>
+        <v/>
+      </c>
+      <c r="N37" s="34">
+        <f>IF(F37="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
     </row>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +61,10 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -125,12 +129,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,6 +162,7 @@
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -278,6 +283,84 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Out of control</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'I-MR'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'I-MR'!$AD$14:$AD$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>8 in a row one side — shift</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="B45309"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'I-MR'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'I-MR'!$AE$14:$AE$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
             <v>Value</v>
           </tx>
           <spPr>
@@ -313,8 +396,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>Centre line</v>
           </tx>
@@ -347,8 +430,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <v>UCL</v>
           </tx>
@@ -381,8 +464,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <v>LCL</v>
           </tx>
@@ -484,6 +567,84 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Above the UCL</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'t and g (rare events)'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'t and g (rare events)'!$AF$14:$AF$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>8 in a row above the median — sustained improvement</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="B45309"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'t and g (rare events)'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'t and g (rare events)'!$AG$14:$AG$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
             <v>Contacts between</v>
           </tx>
           <spPr>
@@ -519,8 +680,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>Mean</v>
           </tx>
@@ -553,8 +714,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <v>Median</v>
           </tx>
@@ -587,8 +748,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <v>UCL</v>
           </tx>
@@ -690,6 +851,45 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Out of control</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'I-MR'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'I-MR'!$AF$14:$AF$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
             <v>Moving range</v>
           </tx>
           <spPr>
@@ -725,8 +925,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <v>MR centre line</v>
           </tx>
@@ -759,8 +959,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>MR UCL</v>
           </tx>
@@ -862,6 +1062,84 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Out of control</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Laney p-prime'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Laney p-prime'!$AD$14:$AD$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>8 in a row one side — shift</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="B45309"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Laney p-prime'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Laney p-prime'!$AE$14:$AE$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
             <v>Proportion</v>
           </tx>
           <spPr>
@@ -897,8 +1175,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>Centre line</v>
           </tx>
@@ -931,8 +1209,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <v>UCL</v>
           </tx>
@@ -965,8 +1243,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <v>LCL</v>
           </tx>
@@ -1069,6 +1347,84 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Out of control</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Laney u-prime'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Laney u-prime'!$AD$14:$AD$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>8 in a row one side — shift</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="B45309"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Laney u-prime'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Laney u-prime'!$AE$14:$AE$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
             <v>Rate</v>
           </tx>
           <spPr>
@@ -1104,8 +1460,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>Centre line</v>
           </tx>
@@ -1138,8 +1494,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <v>UCL</v>
           </tx>
@@ -1172,8 +1528,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <v>LCL</v>
           </tx>
@@ -1275,6 +1631,84 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Out of control</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Xbar-R'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Xbar-R'!$AD$14:$AD$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>8 in a row one side — shift</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="B45309"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Xbar-R'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Xbar-R'!$AE$14:$AE$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
             <v>Subgroup average</v>
           </tx>
           <spPr>
@@ -1310,8 +1744,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>Centre line</v>
           </tx>
@@ -1344,8 +1778,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <v>UCL</v>
           </tx>
@@ -1378,8 +1812,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <v>LCL</v>
           </tx>
@@ -1481,6 +1915,45 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Out of control</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Xbar-R'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Xbar-R'!$AF$14:$AF$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
             <v>Subgroup range</v>
           </tx>
           <spPr>
@@ -1516,8 +1989,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <v>R centre line</v>
           </tx>
@@ -1550,8 +2023,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>R UCL</v>
           </tx>
@@ -1584,8 +2057,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <v>R LCL</v>
           </tx>
@@ -1687,6 +2160,45 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Signal — the process has drifted</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'EWMA'!$A$16:$A$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'EWMA'!$AD$16:$AD$39</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
             <v>EWMA</v>
           </tx>
           <spPr>
@@ -1722,8 +2234,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <v>Target</v>
           </tx>
@@ -1756,8 +2268,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>UCL</v>
           </tx>
@@ -1790,8 +2302,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <v>LCL</v>
           </tx>
@@ -1893,6 +2405,45 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Crossed the decision limit</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'CUSUM'!$A$16:$A$39</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'CUSUM'!$AD$16:$AD$39</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
             <v>SH (evidence it went up)</v>
           </tx>
           <spPr>
@@ -1928,8 +2479,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <v>SL (evidence it went down)</v>
           </tx>
@@ -1966,8 +2517,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>Decision limit h — crossing it is the signal</v>
           </tx>
@@ -2069,6 +2620,84 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
+            <v>Out of control</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="C0392B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'t and g (rare events)'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'t and g (rare events)'!$AD$14:$AD$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>8 in a row one side — sustained change</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="B45309"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'t and g (rare events)'!$A$14:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'t and g (rare events)'!$AE$14:$AE$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
             <v>Days between</v>
           </tx>
           <spPr>
@@ -2104,8 +2733,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="1"/>
-          <order val="1"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <v>Centre line (back-transformed)</v>
           </tx>
@@ -2138,8 +2767,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <v>UCL</v>
           </tx>
@@ -2172,8 +2801,8 @@
           <smooth val="0"/>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="5"/>
+          <order val="5"/>
           <tx>
             <v>LCL</v>
           </tx>
@@ -3160,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3172,6 +3801,9 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3385,6 +4017,21 @@
           <t>Signal</t>
         </is>
       </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>out of control</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>8 in a row one side</t>
+        </is>
+      </c>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>MR out of control</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3419,6 +4066,18 @@
         <f>IF(B14="","",IF(OR(B14&gt;$B$9,B14&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
+      <c r="AD14" s="18">
+        <f>IF($B14="",NA(),IF(OR($B14&gt;$B$9,$B14&lt;$B$10),$B14,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF14" s="18">
+        <f>IF($C14="",NA(),IF($C14&gt;$B$11,$C14,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3426,7 +4085,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C15" s="15">
@@ -3457,6 +4116,18 @@
         <f>IF(B15="","",IF(OR(B15&gt;$B$9,B15&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
+      <c r="AD15" s="18">
+        <f>IF($B15="",NA(),IF(OR($B15&gt;$B$9,$B15&lt;$B$10),$B15,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF15" s="18">
+        <f>IF($C15="",NA(),IF($C15&gt;$B$11,$C15,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3464,7 +4135,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C16" s="15">
@@ -3495,6 +4166,18 @@
         <f>IF(B16="","",IF(OR(B16&gt;$B$9,B16&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
+      <c r="AD16" s="18">
+        <f>IF($B16="",NA(),IF(OR($B16&gt;$B$9,$B16&lt;$B$10),$B16,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF16" s="18">
+        <f>IF($C16="",NA(),IF($C16&gt;$B$11,$C16,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3502,7 +4185,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C17" s="15">
@@ -3533,6 +4216,18 @@
         <f>IF(B17="","",IF(OR(B17&gt;$B$9,B17&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
+      <c r="AD17" s="18">
+        <f>IF($B17="",NA(),IF(OR($B17&gt;$B$9,$B17&lt;$B$10),$B17,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF17" s="18">
+        <f>IF($C17="",NA(),IF($C17&gt;$B$11,$C17,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3540,7 +4235,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C18" s="15">
@@ -3571,6 +4266,18 @@
         <f>IF(B18="","",IF(OR(B18&gt;$B$9,B18&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
+      <c r="AD18" s="18">
+        <f>IF($B18="",NA(),IF(OR($B18&gt;$B$9,$B18&lt;$B$10),$B18,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF18" s="18">
+        <f>IF($C18="",NA(),IF($C18&gt;$B$11,$C18,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3578,7 +4285,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C19" s="15">
@@ -3609,6 +4316,18 @@
         <f>IF(B19="","",IF(OR(B19&gt;$B$9,B19&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
+      <c r="AD19" s="18">
+        <f>IF($B19="",NA(),IF(OR($B19&gt;$B$9,$B19&lt;$B$10),$B19,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF19" s="18">
+        <f>IF($C19="",NA(),IF($C19&gt;$B$11,$C19,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3616,7 +4335,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C20" s="15">
@@ -3647,6 +4366,18 @@
         <f>IF(B20="","",IF(OR(B20&gt;$B$9,B20&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
+      <c r="AD20" s="18">
+        <f>IF($B20="",NA(),IF(OR($B20&gt;$B$9,$B20&lt;$B$10),$B20,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF20" s="18">
+        <f>IF($C20="",NA(),IF($C20&gt;$B$11,$C20,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3654,7 +4385,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C21" s="15">
@@ -3685,6 +4416,18 @@
         <f>IF(B21="","",IF(OR(B21&gt;$B$9,B21&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B14:B21)=8,OR(MIN(B14:B21)&gt;$B$6,MAX(B14:B21)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD21" s="18">
+        <f>IF($B21="",NA(),IF(OR($B21&gt;$B$9,$B21&lt;$B$10),$B21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="18">
+        <f>IF(COUNT($B14:$B21)&lt;8,NA(),IF(OR(MIN($B14:$B21)&gt;$B$6,MAX($B14:$B21)&lt;$B$6),$B21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="18">
+        <f>IF($C21="",NA(),IF($C21&gt;$B$11,$C21,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3692,7 +4435,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C22" s="15">
@@ -3723,6 +4466,18 @@
         <f>IF(B22="","",IF(OR(B22&gt;$B$9,B22&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B15:B22)=8,OR(MIN(B15:B22)&gt;$B$6,MAX(B15:B22)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD22" s="18">
+        <f>IF($B22="",NA(),IF(OR($B22&gt;$B$9,$B22&lt;$B$10),$B22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="18">
+        <f>IF(COUNT($B15:$B22)&lt;8,NA(),IF(OR(MIN($B15:$B22)&gt;$B$6,MAX($B15:$B22)&lt;$B$6),$B22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="18">
+        <f>IF($C22="",NA(),IF($C22&gt;$B$11,$C22,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3730,7 +4485,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C23" s="15">
@@ -3761,6 +4516,18 @@
         <f>IF(B23="","",IF(OR(B23&gt;$B$9,B23&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B16:B23)=8,OR(MIN(B16:B23)&gt;$B$6,MAX(B16:B23)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD23" s="18">
+        <f>IF($B23="",NA(),IF(OR($B23&gt;$B$9,$B23&lt;$B$10),$B23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="18">
+        <f>IF(COUNT($B16:$B23)&lt;8,NA(),IF(OR(MIN($B16:$B23)&gt;$B$6,MAX($B16:$B23)&lt;$B$6),$B23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="18">
+        <f>IF($C23="",NA(),IF($C23&gt;$B$11,$C23,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3768,7 +4535,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C24" s="15">
@@ -3799,6 +4566,18 @@
         <f>IF(B24="","",IF(OR(B24&gt;$B$9,B24&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B17:B24)=8,OR(MIN(B17:B24)&gt;$B$6,MAX(B17:B24)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD24" s="18">
+        <f>IF($B24="",NA(),IF(OR($B24&gt;$B$9,$B24&lt;$B$10),$B24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="18">
+        <f>IF(COUNT($B17:$B24)&lt;8,NA(),IF(OR(MIN($B17:$B24)&gt;$B$6,MAX($B17:$B24)&lt;$B$6),$B24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="18">
+        <f>IF($C24="",NA(),IF($C24&gt;$B$11,$C24,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3806,7 +4585,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C25" s="15">
@@ -3837,6 +4616,18 @@
         <f>IF(B25="","",IF(OR(B25&gt;$B$9,B25&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B18:B25)=8,OR(MIN(B18:B25)&gt;$B$6,MAX(B18:B25)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD25" s="18">
+        <f>IF($B25="",NA(),IF(OR($B25&gt;$B$9,$B25&lt;$B$10),$B25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="18">
+        <f>IF(COUNT($B18:$B25)&lt;8,NA(),IF(OR(MIN($B18:$B25)&gt;$B$6,MAX($B18:$B25)&lt;$B$6),$B25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="18">
+        <f>IF($C25="",NA(),IF($C25&gt;$B$11,$C25,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3844,7 +4635,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>401</v>
       </c>
       <c r="C26" s="15">
@@ -3875,6 +4666,18 @@
         <f>IF(B26="","",IF(OR(B26&gt;$B$9,B26&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B19:B26)=8,OR(MIN(B19:B26)&gt;$B$6,MAX(B19:B26)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD26" s="18">
+        <f>IF($B26="",NA(),IF(OR($B26&gt;$B$9,$B26&lt;$B$10),$B26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="18">
+        <f>IF(COUNT($B19:$B26)&lt;8,NA(),IF(OR(MIN($B19:$B26)&gt;$B$6,MAX($B19:$B26)&lt;$B$6),$B26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="18">
+        <f>IF($C26="",NA(),IF($C26&gt;$B$11,$C26,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3882,7 +4685,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="19" t="n">
         <v>422</v>
       </c>
       <c r="C27" s="15">
@@ -3913,6 +4716,18 @@
         <f>IF(B27="","",IF(OR(B27&gt;$B$9,B27&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B20:B27)=8,OR(MIN(B20:B27)&gt;$B$6,MAX(B20:B27)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD27" s="18">
+        <f>IF($B27="",NA(),IF(OR($B27&gt;$B$9,$B27&lt;$B$10),$B27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="18">
+        <f>IF(COUNT($B20:$B27)&lt;8,NA(),IF(OR(MIN($B20:$B27)&gt;$B$6,MAX($B20:$B27)&lt;$B$6),$B27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="18">
+        <f>IF($C27="",NA(),IF($C27&gt;$B$11,$C27,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3920,7 +4735,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="19" t="n">
         <v>413</v>
       </c>
       <c r="C28" s="15">
@@ -3951,6 +4766,18 @@
         <f>IF(B28="","",IF(OR(B28&gt;$B$9,B28&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B21:B28)=8,OR(MIN(B21:B28)&gt;$B$6,MAX(B21:B28)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD28" s="18">
+        <f>IF($B28="",NA(),IF(OR($B28&gt;$B$9,$B28&lt;$B$10),$B28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="18">
+        <f>IF(COUNT($B21:$B28)&lt;8,NA(),IF(OR(MIN($B21:$B28)&gt;$B$6,MAX($B21:$B28)&lt;$B$6),$B28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="18">
+        <f>IF($C28="",NA(),IF($C28&gt;$B$11,$C28,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3958,7 +4785,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="19" t="n">
         <v>407</v>
       </c>
       <c r="C29" s="15">
@@ -3989,6 +4816,18 @@
         <f>IF(B29="","",IF(OR(B29&gt;$B$9,B29&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B22:B29)=8,OR(MIN(B22:B29)&gt;$B$6,MAX(B22:B29)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD29" s="18">
+        <f>IF($B29="",NA(),IF(OR($B29&gt;$B$9,$B29&lt;$B$10),$B29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="18">
+        <f>IF(COUNT($B22:$B29)&lt;8,NA(),IF(OR(MIN($B22:$B29)&gt;$B$6,MAX($B22:$B29)&lt;$B$6),$B29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF29" s="18">
+        <f>IF($C29="",NA(),IF($C29&gt;$B$11,$C29,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3996,7 +4835,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="19" t="n">
         <v>435</v>
       </c>
       <c r="C30" s="15">
@@ -4027,6 +4866,18 @@
         <f>IF(B30="","",IF(OR(B30&gt;$B$9,B30&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B23:B30)=8,OR(MIN(B23:B30)&gt;$B$6,MAX(B23:B30)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD30" s="18">
+        <f>IF($B30="",NA(),IF(OR($B30&gt;$B$9,$B30&lt;$B$10),$B30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="18">
+        <f>IF(COUNT($B23:$B30)&lt;8,NA(),IF(OR(MIN($B23:$B30)&gt;$B$6,MAX($B23:$B30)&lt;$B$6),$B30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF30" s="18">
+        <f>IF($C30="",NA(),IF($C30&gt;$B$11,$C30,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4034,7 +4885,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="19" t="n">
         <v>398</v>
       </c>
       <c r="C31" s="15">
@@ -4065,6 +4916,18 @@
         <f>IF(B31="","",IF(OR(B31&gt;$B$9,B31&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B24:B31)=8,OR(MIN(B24:B31)&gt;$B$6,MAX(B24:B31)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD31" s="18">
+        <f>IF($B31="",NA(),IF(OR($B31&gt;$B$9,$B31&lt;$B$10),$B31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="18">
+        <f>IF(COUNT($B24:$B31)&lt;8,NA(),IF(OR(MIN($B24:$B31)&gt;$B$6,MAX($B24:$B31)&lt;$B$6),$B31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF31" s="18">
+        <f>IF($C31="",NA(),IF($C31&gt;$B$11,$C31,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4072,7 +4935,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="19" t="n">
         <v>420</v>
       </c>
       <c r="C32" s="15">
@@ -4103,6 +4966,18 @@
         <f>IF(B32="","",IF(OR(B32&gt;$B$9,B32&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B25:B32)=8,OR(MIN(B25:B32)&gt;$B$6,MAX(B25:B32)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD32" s="18">
+        <f>IF($B32="",NA(),IF(OR($B32&gt;$B$9,$B32&lt;$B$10),$B32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="18">
+        <f>IF(COUNT($B25:$B32)&lt;8,NA(),IF(OR(MIN($B25:$B32)&gt;$B$6,MAX($B25:$B32)&lt;$B$6),$B32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF32" s="18">
+        <f>IF($C32="",NA(),IF($C32&gt;$B$11,$C32,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4110,7 +4985,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="19" t="n">
         <v>411</v>
       </c>
       <c r="C33" s="15">
@@ -4141,6 +5016,18 @@
         <f>IF(B33="","",IF(OR(B33&gt;$B$9,B33&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B26:B33)=8,OR(MIN(B26:B33)&gt;$B$6,MAX(B26:B33)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD33" s="18">
+        <f>IF($B33="",NA(),IF(OR($B33&gt;$B$9,$B33&lt;$B$10),$B33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="18">
+        <f>IF(COUNT($B26:$B33)&lt;8,NA(),IF(OR(MIN($B26:$B33)&gt;$B$6,MAX($B26:$B33)&lt;$B$6),$B33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF33" s="18">
+        <f>IF($C33="",NA(),IF($C33&gt;$B$11,$C33,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4148,7 +5035,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="19" t="n">
         <v>442</v>
       </c>
       <c r="C34" s="15">
@@ -4179,6 +5066,18 @@
         <f>IF(B34="","",IF(OR(B34&gt;$B$9,B34&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B27:B34)=8,OR(MIN(B27:B34)&gt;$B$6,MAX(B27:B34)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD34" s="18">
+        <f>IF($B34="",NA(),IF(OR($B34&gt;$B$9,$B34&lt;$B$10),$B34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="18">
+        <f>IF(COUNT($B27:$B34)&lt;8,NA(),IF(OR(MIN($B27:$B34)&gt;$B$6,MAX($B27:$B34)&lt;$B$6),$B34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF34" s="18">
+        <f>IF($C34="",NA(),IF($C34&gt;$B$11,$C34,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4186,7 +5085,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="19" t="n">
         <v>404</v>
       </c>
       <c r="C35" s="15">
@@ -4217,6 +5116,18 @@
         <f>IF(B35="","",IF(OR(B35&gt;$B$9,B35&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B28:B35)=8,OR(MIN(B28:B35)&gt;$B$6,MAX(B28:B35)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD35" s="18">
+        <f>IF($B35="",NA(),IF(OR($B35&gt;$B$9,$B35&lt;$B$10),$B35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="18">
+        <f>IF(COUNT($B28:$B35)&lt;8,NA(),IF(OR(MIN($B28:$B35)&gt;$B$6,MAX($B28:$B35)&lt;$B$6),$B35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF35" s="18">
+        <f>IF($C35="",NA(),IF($C35&gt;$B$11,$C35,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4224,7 +5135,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="19" t="n">
         <v>416</v>
       </c>
       <c r="C36" s="15">
@@ -4255,6 +5166,18 @@
         <f>IF(B36="","",IF(OR(B36&gt;$B$9,B36&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B29:B36)=8,OR(MIN(B29:B36)&gt;$B$6,MAX(B29:B36)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="AD36" s="18">
+        <f>IF($B36="",NA(),IF(OR($B36&gt;$B$9,$B36&lt;$B$10),$B36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="18">
+        <f>IF(COUNT($B29:$B36)&lt;8,NA(),IF(OR(MIN($B29:$B36)&gt;$B$6,MAX($B29:$B36)&lt;$B$6),$B36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF36" s="18">
+        <f>IF($C36="",NA(),IF($C36&gt;$B$11,$C36,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4262,7 +5185,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="19" t="n">
         <v>428</v>
       </c>
       <c r="C37" s="15">
@@ -4291,6 +5214,18 @@
       </c>
       <c r="I37" s="17">
         <f>IF(B37="","",IF(OR(B37&gt;$B$9,B37&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B30:B37)=8,OR(MIN(B30:B37)&gt;$B$6,MAX(B30:B37)&lt;$B$6)),"8 in a row one side — shift","")))</f>
+        <v/>
+      </c>
+      <c r="AD37" s="18">
+        <f>IF($B37="",NA(),IF(OR($B37&gt;$B$9,$B37&lt;$B$10),$B37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="18">
+        <f>IF(COUNT($B30:$B37)&lt;8,NA(),IF(OR(MIN($B30:$B37)&gt;$B$6,MAX($B30:$B37)&lt;$B$6),$B37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF37" s="18">
+        <f>IF($C37="",NA(),IF($C37&gt;$B$11,$C37,NA()))</f>
         <v/>
       </c>
     </row>
@@ -4321,7 +5256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4333,6 +5268,8 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4379,7 +5316,7 @@
           <t>Overall proportion (p-bar)</t>
         </is>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="20">
         <f>SUM(C14:C37)/SUM(B14:B37)</f>
         <v/>
       </c>
@@ -4395,7 +5332,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <f>AVERAGE(G15:G37)</f>
         <v/>
       </c>
@@ -4411,7 +5348,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="21">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -4427,7 +5364,7 @@
           <t>Ordinary p-chart limits would be</t>
         </is>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="22">
         <f>"±"&amp;TEXT(3*SQRT(B5*(1-B5)/AVERAGE(B14:B37)),"0.00%")</f>
         <v/>
       </c>
@@ -4497,19 +5434,29 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>CL</t>
+        </is>
+      </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>out of control</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>8 in a row one side</t>
         </is>
       </c>
     </row>
@@ -4519,17 +5466,17 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>7820</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="24" t="n">
         <v>5610</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <f>IF(B14="","",SQRT($B$5*(1-$B$5)/B14))</f>
         <v/>
       </c>
@@ -4541,16 +5488,24 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="26">
         <f>IF(B14="","",MIN(1,$B$5+3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="26">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="25">
+      <c r="M14" s="26">
         <f>IF(B14="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="18">
+        <f>IF($D14="",NA(),IF(OR($D14&gt;$K14,$D14&lt;$L14),$D14,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -4560,17 +5515,17 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>8140</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>5990</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <f>IF(B15="","",SQRT($B$5*(1-$B$5)/B15))</f>
         <v/>
       </c>
@@ -4586,16 +5541,24 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="26">
         <f>IF(B15="","",MIN(1,$B$5+3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="26">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="26">
         <f>IF(B15="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="18">
+        <f>IF($D15="",NA(),IF(OR($D15&gt;$K15,$D15&lt;$L15),$D15,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -4605,17 +5568,17 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>7960</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>5570</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>IF(B16="","",SQRT($B$5*(1-$B$5)/B16))</f>
         <v/>
       </c>
@@ -4631,16 +5594,24 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="26">
         <f>IF(B16="","",MIN(1,$B$5+3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="26">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="26">
         <f>IF(B16="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="18">
+        <f>IF($D16="",NA(),IF(OR($D16&gt;$K16,$D16&lt;$L16),$D16,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -4650,17 +5621,17 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>8310</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>6120</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <f>IF(B17="","",SQRT($B$5*(1-$B$5)/B17))</f>
         <v/>
       </c>
@@ -4676,16 +5647,24 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="26">
         <f>IF(B17="","",MIN(1,$B$5+3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="26">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="26">
         <f>IF(B17="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="18">
+        <f>IF($D17="",NA(),IF(OR($D17&gt;$K17,$D17&lt;$L17),$D17,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -4695,17 +5674,17 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>7690</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>5410</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <f>IF(B18="","",SQRT($B$5*(1-$B$5)/B18))</f>
         <v/>
       </c>
@@ -4721,16 +5700,24 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="26">
         <f>IF(B18="","",MIN(1,$B$5+3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="L18" s="25">
+      <c r="L18" s="26">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="25">
+      <c r="M18" s="26">
         <f>IF(B18="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="18">
+        <f>IF($D18="",NA(),IF(OR($D18&gt;$K18,$D18&lt;$L18),$D18,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -4740,17 +5727,17 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>8020</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>5880</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <f>IF(B19="","",SQRT($B$5*(1-$B$5)/B19))</f>
         <v/>
       </c>
@@ -4766,16 +5753,24 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="26">
         <f>IF(B19="","",MIN(1,$B$5+3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="L19" s="25">
+      <c r="L19" s="26">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="25">
+      <c r="M19" s="26">
         <f>IF(B19="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="18">
+        <f>IF($D19="",NA(),IF(OR($D19&gt;$K19,$D19&lt;$L19),$D19,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -4785,17 +5780,17 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>8450</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>6210</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <f>IF(B20="","",SQRT($B$5*(1-$B$5)/B20))</f>
         <v/>
       </c>
@@ -4811,16 +5806,24 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="26">
         <f>IF(B20="","",MIN(1,$B$5+3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="L20" s="25">
+      <c r="L20" s="26">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="25">
+      <c r="M20" s="26">
         <f>IF(B20="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="18">
+        <f>IF($D20="",NA(),IF(OR($D20&gt;$K20,$D20&lt;$L20),$D20,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -4830,17 +5833,17 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>7880</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>5490</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <f>IF(B21="","",SQRT($B$5*(1-$B$5)/B21))</f>
         <v/>
       </c>
@@ -4856,16 +5859,24 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="26">
         <f>IF(B21="","",MIN(1,$B$5+3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="L21" s="25">
+      <c r="L21" s="26">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="25">
+      <c r="M21" s="26">
         <f>IF(B21="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="18">
+        <f>IF($D21="",NA(),IF(OR($D21&gt;$K21,$D21&lt;$L21),$D21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="18">
+        <f>IF(COUNT($D14:$D21)&lt;8,NA(),IF(OR(MIN($D14:$D21)&gt;$B$5,MAX($D14:$D21)&lt;$B$5),$D21,NA()))</f>
         <v/>
       </c>
     </row>
@@ -4875,17 +5886,17 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>8210</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>6050</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="25">
         <f>IF(B22="","",SQRT($B$5*(1-$B$5)/B22))</f>
         <v/>
       </c>
@@ -4901,16 +5912,24 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="26">
         <f>IF(B22="","",MIN(1,$B$5+3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="26">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="25">
+      <c r="M22" s="26">
         <f>IF(B22="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="18">
+        <f>IF($D22="",NA(),IF(OR($D22&gt;$K22,$D22&lt;$L22),$D22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="18">
+        <f>IF(COUNT($D15:$D22)&lt;8,NA(),IF(OR(MIN($D15:$D22)&gt;$B$5,MAX($D15:$D22)&lt;$B$5),$D22,NA()))</f>
         <v/>
       </c>
     </row>
@@ -4920,17 +5939,17 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>7740</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>5380</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <f>IF(B23="","",SQRT($B$5*(1-$B$5)/B23))</f>
         <v/>
       </c>
@@ -4946,16 +5965,24 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="25">
+      <c r="K23" s="26">
         <f>IF(B23="","",MIN(1,$B$5+3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="L23" s="25">
+      <c r="L23" s="26">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="25">
+      <c r="M23" s="26">
         <f>IF(B23="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="18">
+        <f>IF($D23="",NA(),IF(OR($D23&gt;$K23,$D23&lt;$L23),$D23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="18">
+        <f>IF(COUNT($D16:$D23)&lt;8,NA(),IF(OR(MIN($D16:$D23)&gt;$B$5,MAX($D16:$D23)&lt;$B$5),$D23,NA()))</f>
         <v/>
       </c>
     </row>
@@ -4965,17 +5992,17 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>8090</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>5940</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="25">
         <f>IF(B24="","",SQRT($B$5*(1-$B$5)/B24))</f>
         <v/>
       </c>
@@ -4991,16 +6018,24 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="25">
+      <c r="K24" s="26">
         <f>IF(B24="","",MIN(1,$B$5+3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="L24" s="25">
+      <c r="L24" s="26">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="26">
         <f>IF(B24="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="18">
+        <f>IF($D24="",NA(),IF(OR($D24&gt;$K24,$D24&lt;$L24),$D24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="18">
+        <f>IF(COUNT($D17:$D24)&lt;8,NA(),IF(OR(MIN($D17:$D24)&gt;$B$5,MAX($D17:$D24)&lt;$B$5),$D24,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5010,17 +6045,17 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>8380</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>6180</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="25">
         <f>IF(B25="","",SQRT($B$5*(1-$B$5)/B25))</f>
         <v/>
       </c>
@@ -5036,16 +6071,24 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="25">
+      <c r="K25" s="26">
         <f>IF(B25="","",MIN(1,$B$5+3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="L25" s="25">
+      <c r="L25" s="26">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="25">
+      <c r="M25" s="26">
         <f>IF(B25="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="18">
+        <f>IF($D25="",NA(),IF(OR($D25&gt;$K25,$D25&lt;$L25),$D25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="18">
+        <f>IF(COUNT($D18:$D25)&lt;8,NA(),IF(OR(MIN($D18:$D25)&gt;$B$5,MAX($D18:$D25)&lt;$B$5),$D25,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5055,17 +6098,17 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>7930</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <v>5520</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="25">
         <f>IF(B26="","",SQRT($B$5*(1-$B$5)/B26))</f>
         <v/>
       </c>
@@ -5081,16 +6124,24 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="25">
+      <c r="K26" s="26">
         <f>IF(B26="","",MIN(1,$B$5+3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="L26" s="25">
+      <c r="L26" s="26">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="25">
+      <c r="M26" s="26">
         <f>IF(B26="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="18">
+        <f>IF($D26="",NA(),IF(OR($D26&gt;$K26,$D26&lt;$L26),$D26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="18">
+        <f>IF(COUNT($D19:$D26)&lt;8,NA(),IF(OR(MIN($D19:$D26)&gt;$B$5,MAX($D19:$D26)&lt;$B$5),$D26,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5100,17 +6151,17 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>8260</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>6010</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <f>IF(B27="","",SQRT($B$5*(1-$B$5)/B27))</f>
         <v/>
       </c>
@@ -5126,16 +6177,24 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="25">
+      <c r="K27" s="26">
         <f>IF(B27="","",MIN(1,$B$5+3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="L27" s="25">
+      <c r="L27" s="26">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="25">
+      <c r="M27" s="26">
         <f>IF(B27="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="18">
+        <f>IF($D27="",NA(),IF(OR($D27&gt;$K27,$D27&lt;$L27),$D27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="18">
+        <f>IF(COUNT($D20:$D27)&lt;8,NA(),IF(OR(MIN($D20:$D27)&gt;$B$5,MAX($D20:$D27)&lt;$B$5),$D27,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5145,17 +6204,17 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>7810</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>5480</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="25">
         <f>IF(B28="","",SQRT($B$5*(1-$B$5)/B28))</f>
         <v/>
       </c>
@@ -5171,16 +6230,24 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="26">
         <f>IF(B28="","",MIN(1,$B$5+3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="L28" s="25">
+      <c r="L28" s="26">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="25">
+      <c r="M28" s="26">
         <f>IF(B28="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="18">
+        <f>IF($D28="",NA(),IF(OR($D28&gt;$K28,$D28&lt;$L28),$D28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="18">
+        <f>IF(COUNT($D21:$D28)&lt;8,NA(),IF(OR(MIN($D21:$D28)&gt;$B$5,MAX($D21:$D28)&lt;$B$5),$D28,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5190,17 +6257,17 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>8150</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>5860</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="20">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="25">
         <f>IF(B29="","",SQRT($B$5*(1-$B$5)/B29))</f>
         <v/>
       </c>
@@ -5216,16 +6283,24 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="25">
+      <c r="K29" s="26">
         <f>IF(B29="","",MIN(1,$B$5+3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="L29" s="25">
+      <c r="L29" s="26">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="25">
+      <c r="M29" s="26">
         <f>IF(B29="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="18">
+        <f>IF($D29="",NA(),IF(OR($D29&gt;$K29,$D29&lt;$L29),$D29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="18">
+        <f>IF(COUNT($D22:$D29)&lt;8,NA(),IF(OR(MIN($D22:$D29)&gt;$B$5,MAX($D22:$D29)&lt;$B$5),$D29,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5235,17 +6310,17 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>8470</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>6240</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="20">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="25">
         <f>IF(B30="","",SQRT($B$5*(1-$B$5)/B30))</f>
         <v/>
       </c>
@@ -5261,16 +6336,24 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="25">
+      <c r="K30" s="26">
         <f>IF(B30="","",MIN(1,$B$5+3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="L30" s="25">
+      <c r="L30" s="26">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="25">
+      <c r="M30" s="26">
         <f>IF(B30="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD30" s="18">
+        <f>IF($D30="",NA(),IF(OR($D30&gt;$K30,$D30&lt;$L30),$D30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="18">
+        <f>IF(COUNT($D23:$D30)&lt;8,NA(),IF(OR(MIN($D23:$D30)&gt;$B$5,MAX($D23:$D30)&lt;$B$5),$D30,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5280,17 +6363,17 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <v>7860</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <v>5600</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="20">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <f>IF(B31="","",SQRT($B$5*(1-$B$5)/B31))</f>
         <v/>
       </c>
@@ -5306,16 +6389,24 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="25">
+      <c r="K31" s="26">
         <f>IF(B31="","",MIN(1,$B$5+3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="L31" s="25">
+      <c r="L31" s="26">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="25">
+      <c r="M31" s="26">
         <f>IF(B31="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="18">
+        <f>IF($D31="",NA(),IF(OR($D31&gt;$K31,$D31&lt;$L31),$D31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="18">
+        <f>IF(COUNT($D24:$D31)&lt;8,NA(),IF(OR(MIN($D24:$D31)&gt;$B$5,MAX($D24:$D31)&lt;$B$5),$D31,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5325,17 +6416,17 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>8030</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="27" t="n">
         <v>5760</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="20">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="25">
         <f>IF(B32="","",SQRT($B$5*(1-$B$5)/B32))</f>
         <v/>
       </c>
@@ -5351,16 +6442,24 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="25">
+      <c r="K32" s="26">
         <f>IF(B32="","",MIN(1,$B$5+3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="L32" s="25">
+      <c r="L32" s="26">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="25">
+      <c r="M32" s="26">
         <f>IF(B32="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD32" s="18">
+        <f>IF($D32="",NA(),IF(OR($D32&gt;$K32,$D32&lt;$L32),$D32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="18">
+        <f>IF(COUNT($D25:$D32)&lt;8,NA(),IF(OR(MIN($D25:$D32)&gt;$B$5,MAX($D25:$D32)&lt;$B$5),$D32,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5370,17 +6469,17 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>8340</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
         <v>6090</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="20">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="25">
         <f>IF(B33="","",SQRT($B$5*(1-$B$5)/B33))</f>
         <v/>
       </c>
@@ -5396,16 +6495,24 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="25">
+      <c r="K33" s="26">
         <f>IF(B33="","",MIN(1,$B$5+3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="L33" s="25">
+      <c r="L33" s="26">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="25">
+      <c r="M33" s="26">
         <f>IF(B33="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="18">
+        <f>IF($D33="",NA(),IF(OR($D33&gt;$K33,$D33&lt;$L33),$D33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="18">
+        <f>IF(COUNT($D26:$D33)&lt;8,NA(),IF(OR(MIN($D26:$D33)&gt;$B$5,MAX($D26:$D33)&lt;$B$5),$D33,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5415,17 +6522,17 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <v>7900</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <v>5710</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="20">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="25">
         <f>IF(B34="","",SQRT($B$5*(1-$B$5)/B34))</f>
         <v/>
       </c>
@@ -5441,16 +6548,24 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="25">
+      <c r="K34" s="26">
         <f>IF(B34="","",MIN(1,$B$5+3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="L34" s="25">
+      <c r="L34" s="26">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="25">
+      <c r="M34" s="26">
         <f>IF(B34="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="18">
+        <f>IF($D34="",NA(),IF(OR($D34&gt;$K34,$D34&lt;$L34),$D34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="18">
+        <f>IF(COUNT($D27:$D34)&lt;8,NA(),IF(OR(MIN($D27:$D34)&gt;$B$5,MAX($D27:$D34)&lt;$B$5),$D34,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5460,17 +6575,17 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>8180</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="27" t="n">
         <v>5900</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="20">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="25">
         <f>IF(B35="","",SQRT($B$5*(1-$B$5)/B35))</f>
         <v/>
       </c>
@@ -5486,16 +6601,24 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="25">
+      <c r="K35" s="26">
         <f>IF(B35="","",MIN(1,$B$5+3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="L35" s="25">
+      <c r="L35" s="26">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="25">
+      <c r="M35" s="26">
         <f>IF(B35="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD35" s="18">
+        <f>IF($D35="",NA(),IF(OR($D35&gt;$K35,$D35&lt;$L35),$D35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="18">
+        <f>IF(COUNT($D28:$D35)&lt;8,NA(),IF(OR(MIN($D28:$D35)&gt;$B$5,MAX($D28:$D35)&lt;$B$5),$D35,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5505,17 +6628,17 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>7770</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="27" t="n">
         <v>5450</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="20">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="25">
         <f>IF(B36="","",SQRT($B$5*(1-$B$5)/B36))</f>
         <v/>
       </c>
@@ -5531,16 +6654,24 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="26">
         <f>IF(B36="","",MIN(1,$B$5+3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="L36" s="25">
+      <c r="L36" s="26">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="25">
+      <c r="M36" s="26">
         <f>IF(B36="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD36" s="18">
+        <f>IF($D36="",NA(),IF(OR($D36&gt;$K36,$D36&lt;$L36),$D36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="18">
+        <f>IF(COUNT($D29:$D36)&lt;8,NA(),IF(OR(MIN($D29:$D36)&gt;$B$5,MAX($D29:$D36)&lt;$B$5),$D36,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5550,17 +6681,17 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <v>8240</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="27" t="n">
         <v>6020</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="20">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="25">
         <f>IF(B37="","",SQRT($B$5*(1-$B$5)/B37))</f>
         <v/>
       </c>
@@ -5576,16 +6707,24 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="26">
         <f>IF(B37="","",MIN(1,$B$5+3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="L37" s="25">
+      <c r="L37" s="26">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="25">
+      <c r="M37" s="26">
         <f>IF(B37="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD37" s="18">
+        <f>IF($D37="",NA(),IF(OR($D37&gt;$K37,$D37&lt;$L37),$D37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="18">
+        <f>IF(COUNT($D30:$D37)&lt;8,NA(),IF(OR(MIN($D30:$D37)&gt;$B$5,MAX($D30:$D37)&lt;$B$5),$D37,NA()))</f>
         <v/>
       </c>
     </row>
@@ -5613,7 +6752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5625,6 +6764,8 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -5671,7 +6812,7 @@
           <t>Overall rate (u-bar)</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>SUM(C14:C37)/SUM(B14:B37)</f>
         <v/>
       </c>
@@ -5687,7 +6828,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <f>AVERAGE(G15:G37)</f>
         <v/>
       </c>
@@ -5703,7 +6844,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="21">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -5789,19 +6930,29 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>CL</t>
+        </is>
+      </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>out of control</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>8 in a row one side</t>
         </is>
       </c>
     </row>
@@ -5811,17 +6962,17 @@
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>1240</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="24" t="n">
         <v>38</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <f>IF(B14="","",SQRT($B$5/B14))</f>
         <v/>
       </c>
@@ -5833,16 +6984,24 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="29">
         <f>IF(B14="","",$B$5+3*E14*$B$7)</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="29">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="29">
         <f>IF(B14="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="18">
+        <f>IF($D14="",NA(),IF(OR($D14&gt;$K14,$D14&lt;$L14),$D14,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -5852,17 +7011,17 @@
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>1310</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>68</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <f>IF(B15="","",SQRT($B$5/B15))</f>
         <v/>
       </c>
@@ -5878,16 +7037,24 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="29">
         <f>IF(B15="","",$B$5+3*E15*$B$7)</f>
         <v/>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="29">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="29">
         <f>IF(B15="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="18">
+        <f>IF($D15="",NA(),IF(OR($D15&gt;$K15,$D15&lt;$L15),$D15,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -5897,17 +7064,17 @@
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>1180</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>IF(B16="","",SQRT($B$5/B16))</f>
         <v/>
       </c>
@@ -5923,16 +7090,24 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>IF(B16="","",$B$5+3*E16*$B$7)</f>
         <v/>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>IF(B16="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="18">
+        <f>IF($D16="",NA(),IF(OR($D16&gt;$K16,$D16&lt;$L16),$D16,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -5942,17 +7117,17 @@
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>1420</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <f>IF(B17="","",SQRT($B$5/B17))</f>
         <v/>
       </c>
@@ -5968,16 +7143,24 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="29">
         <f>IF(B17="","",$B$5+3*E17*$B$7)</f>
         <v/>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="29">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="29">
         <f>IF(B17="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="18">
+        <f>IF($D17="",NA(),IF(OR($D17&gt;$K17,$D17&lt;$L17),$D17,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -5987,17 +7170,17 @@
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>1275</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <f>IF(B18="","",SQRT($B$5/B18))</f>
         <v/>
       </c>
@@ -6013,16 +7196,24 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="29">
         <f>IF(B18="","",$B$5+3*E18*$B$7)</f>
         <v/>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="29">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="28">
+      <c r="M18" s="29">
         <f>IF(B18="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="18">
+        <f>IF($D18="",NA(),IF(OR($D18&gt;$K18,$D18&lt;$L18),$D18,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -6032,17 +7223,17 @@
           <t>Week 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>1195</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>59</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <f>IF(B19="","",SQRT($B$5/B19))</f>
         <v/>
       </c>
@@ -6058,16 +7249,24 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="29">
         <f>IF(B19="","",$B$5+3*E19*$B$7)</f>
         <v/>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="29">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="28">
+      <c r="M19" s="29">
         <f>IF(B19="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="18">
+        <f>IF($D19="",NA(),IF(OR($D19&gt;$K19,$D19&lt;$L19),$D19,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -6077,17 +7276,17 @@
           <t>Week 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>1360</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <f>IF(B20="","",SQRT($B$5/B20))</f>
         <v/>
       </c>
@@ -6103,16 +7302,24 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="29">
         <f>IF(B20="","",$B$5+3*E20*$B$7)</f>
         <v/>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="29">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="28">
+      <c r="M20" s="29">
         <f>IF(B20="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="18">
+        <f>IF($D20="",NA(),IF(OR($D20&gt;$K20,$D20&lt;$L20),$D20,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -6122,17 +7329,17 @@
           <t>Week 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>1230</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>69</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <f>IF(B21="","",SQRT($B$5/B21))</f>
         <v/>
       </c>
@@ -6148,16 +7355,24 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>IF(B21="","",$B$5+3*E21*$B$7)</f>
         <v/>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>IF(B21="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="18">
+        <f>IF($D21="",NA(),IF(OR($D21&gt;$K21,$D21&lt;$L21),$D21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="18">
+        <f>IF(COUNT($D14:$D21)&lt;8,NA(),IF(OR(MIN($D14:$D21)&gt;$B$5,MAX($D14:$D21)&lt;$B$5),$D21,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6167,17 +7382,17 @@
           <t>Week 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>1405</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="25">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="25">
         <f>IF(B22="","",SQRT($B$5/B22))</f>
         <v/>
       </c>
@@ -6193,16 +7408,24 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="29">
         <f>IF(B22="","",$B$5+3*E22*$B$7)</f>
         <v/>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="29">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="28">
+      <c r="M22" s="29">
         <f>IF(B22="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="18">
+        <f>IF($D22="",NA(),IF(OR($D22&gt;$K22,$D22&lt;$L22),$D22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="18">
+        <f>IF(COUNT($D15:$D22)&lt;8,NA(),IF(OR(MIN($D15:$D22)&gt;$B$5,MAX($D15:$D22)&lt;$B$5),$D22,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6212,17 +7435,17 @@
           <t>Week 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>1150</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>54</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="25">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <f>IF(B23="","",SQRT($B$5/B23))</f>
         <v/>
       </c>
@@ -6238,16 +7461,24 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>IF(B23="","",$B$5+3*E23*$B$7)</f>
         <v/>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>IF(B23="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="18">
+        <f>IF($D23="",NA(),IF(OR($D23&gt;$K23,$D23&lt;$L23),$D23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="18">
+        <f>IF(COUNT($D16:$D23)&lt;8,NA(),IF(OR(MIN($D16:$D23)&gt;$B$5,MAX($D16:$D23)&lt;$B$5),$D23,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6257,17 +7488,17 @@
           <t>Week 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>1290</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="25">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="25">
         <f>IF(B24="","",SQRT($B$5/B24))</f>
         <v/>
       </c>
@@ -6283,16 +7514,24 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="29">
         <f>IF(B24="","",$B$5+3*E24*$B$7)</f>
         <v/>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="29">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="28">
+      <c r="M24" s="29">
         <f>IF(B24="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="18">
+        <f>IF($D24="",NA(),IF(OR($D24&gt;$K24,$D24&lt;$L24),$D24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="18">
+        <f>IF(COUNT($D17:$D24)&lt;8,NA(),IF(OR(MIN($D17:$D24)&gt;$B$5,MAX($D17:$D24)&lt;$B$5),$D24,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6302,17 +7541,17 @@
           <t>Week 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>1375</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>74</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="25">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="25">
         <f>IF(B25="","",SQRT($B$5/B25))</f>
         <v/>
       </c>
@@ -6328,16 +7567,24 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="29">
         <f>IF(B25="","",$B$5+3*E25*$B$7)</f>
         <v/>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="29">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="28">
+      <c r="M25" s="29">
         <f>IF(B25="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="18">
+        <f>IF($D25="",NA(),IF(OR($D25&gt;$K25,$D25&lt;$L25),$D25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="18">
+        <f>IF(COUNT($D18:$D25)&lt;8,NA(),IF(OR(MIN($D18:$D25)&gt;$B$5,MAX($D18:$D25)&lt;$B$5),$D25,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6347,17 +7594,17 @@
           <t>Week 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>1215</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <v>39</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="25">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="25">
         <f>IF(B26="","",SQRT($B$5/B26))</f>
         <v/>
       </c>
@@ -6373,16 +7620,24 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="28">
+      <c r="K26" s="29">
         <f>IF(B26="","",$B$5+3*E26*$B$7)</f>
         <v/>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="29">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="28">
+      <c r="M26" s="29">
         <f>IF(B26="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="18">
+        <f>IF($D26="",NA(),IF(OR($D26&gt;$K26,$D26&lt;$L26),$D26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="18">
+        <f>IF(COUNT($D19:$D26)&lt;8,NA(),IF(OR(MIN($D19:$D26)&gt;$B$5,MAX($D19:$D26)&lt;$B$5),$D26,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6392,17 +7647,17 @@
           <t>Week 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>1330</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>66</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="25">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <f>IF(B27="","",SQRT($B$5/B27))</f>
         <v/>
       </c>
@@ -6418,16 +7673,24 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="28">
+      <c r="K27" s="29">
         <f>IF(B27="","",$B$5+3*E27*$B$7)</f>
         <v/>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="29">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="28">
+      <c r="M27" s="29">
         <f>IF(B27="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="18">
+        <f>IF($D27="",NA(),IF(OR($D27&gt;$K27,$D27&lt;$L27),$D27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="18">
+        <f>IF(COUNT($D20:$D27)&lt;8,NA(),IF(OR(MIN($D20:$D27)&gt;$B$5,MAX($D20:$D27)&lt;$B$5),$D27,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6437,17 +7700,17 @@
           <t>Week 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>1185</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>41</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="25">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="25">
         <f>IF(B28="","",SQRT($B$5/B28))</f>
         <v/>
       </c>
@@ -6463,16 +7726,24 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="29">
         <f>IF(B28="","",$B$5+3*E28*$B$7)</f>
         <v/>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="29">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="28">
+      <c r="M28" s="29">
         <f>IF(B28="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="18">
+        <f>IF($D28="",NA(),IF(OR($D28&gt;$K28,$D28&lt;$L28),$D28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="18">
+        <f>IF(COUNT($D21:$D28)&lt;8,NA(),IF(OR(MIN($D21:$D28)&gt;$B$5,MAX($D21:$D28)&lt;$B$5),$D28,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6482,17 +7753,17 @@
           <t>Week 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>1265</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>72</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="25">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="25">
         <f>IF(B29="","",SQRT($B$5/B29))</f>
         <v/>
       </c>
@@ -6508,16 +7779,24 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="28">
+      <c r="K29" s="29">
         <f>IF(B29="","",$B$5+3*E29*$B$7)</f>
         <v/>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="29">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="28">
+      <c r="M29" s="29">
         <f>IF(B29="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="18">
+        <f>IF($D29="",NA(),IF(OR($D29&gt;$K29,$D29&lt;$L29),$D29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="18">
+        <f>IF(COUNT($D22:$D29)&lt;8,NA(),IF(OR(MIN($D22:$D29)&gt;$B$5,MAX($D22:$D29)&lt;$B$5),$D29,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6527,17 +7806,17 @@
           <t>Week 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>1440</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="25">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="25">
         <f>IF(B30="","",SQRT($B$5/B30))</f>
         <v/>
       </c>
@@ -6553,16 +7832,24 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="28">
+      <c r="K30" s="29">
         <f>IF(B30="","",$B$5+3*E30*$B$7)</f>
         <v/>
       </c>
-      <c r="L30" s="28">
+      <c r="L30" s="29">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="28">
+      <c r="M30" s="29">
         <f>IF(B30="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD30" s="18">
+        <f>IF($D30="",NA(),IF(OR($D30&gt;$K30,$D30&lt;$L30),$D30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="18">
+        <f>IF(COUNT($D23:$D30)&lt;8,NA(),IF(OR(MIN($D23:$D30)&gt;$B$5,MAX($D23:$D30)&lt;$B$5),$D30,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6572,17 +7859,17 @@
           <t>Week 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <v>1205</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <v>54</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <f>IF(B31="","",SQRT($B$5/B31))</f>
         <v/>
       </c>
@@ -6598,16 +7885,24 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="28">
+      <c r="K31" s="29">
         <f>IF(B31="","",$B$5+3*E31*$B$7)</f>
         <v/>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="29">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="28">
+      <c r="M31" s="29">
         <f>IF(B31="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="18">
+        <f>IF($D31="",NA(),IF(OR($D31&gt;$K31,$D31&lt;$L31),$D31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="18">
+        <f>IF(COUNT($D24:$D31)&lt;8,NA(),IF(OR(MIN($D24:$D31)&gt;$B$5,MAX($D24:$D31)&lt;$B$5),$D31,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6617,17 +7912,17 @@
           <t>Week 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>1300</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="25">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="25">
         <f>IF(B32="","",SQRT($B$5/B32))</f>
         <v/>
       </c>
@@ -6643,16 +7938,24 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="28">
+      <c r="K32" s="29">
         <f>IF(B32="","",$B$5+3*E32*$B$7)</f>
         <v/>
       </c>
-      <c r="L32" s="28">
+      <c r="L32" s="29">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="28">
+      <c r="M32" s="29">
         <f>IF(B32="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD32" s="18">
+        <f>IF($D32="",NA(),IF(OR($D32&gt;$K32,$D32&lt;$L32),$D32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="18">
+        <f>IF(COUNT($D25:$D32)&lt;8,NA(),IF(OR(MIN($D25:$D32)&gt;$B$5,MAX($D25:$D32)&lt;$B$5),$D32,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6662,17 +7965,17 @@
           <t>Week 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>1355</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
         <v>72</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="25">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="25">
         <f>IF(B33="","",SQRT($B$5/B33))</f>
         <v/>
       </c>
@@ -6688,16 +7991,24 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="28">
+      <c r="K33" s="29">
         <f>IF(B33="","",$B$5+3*E33*$B$7)</f>
         <v/>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="29">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="28">
+      <c r="M33" s="29">
         <f>IF(B33="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="18">
+        <f>IF($D33="",NA(),IF(OR($D33&gt;$K33,$D33&lt;$L33),$D33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="18">
+        <f>IF(COUNT($D26:$D33)&lt;8,NA(),IF(OR(MIN($D26:$D33)&gt;$B$5,MAX($D26:$D33)&lt;$B$5),$D33,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6707,17 +8018,17 @@
           <t>Week 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <v>1170</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <v>43</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="25">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="25">
         <f>IF(B34="","",SQRT($B$5/B34))</f>
         <v/>
       </c>
@@ -6733,16 +8044,24 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="28">
+      <c r="K34" s="29">
         <f>IF(B34="","",$B$5+3*E34*$B$7)</f>
         <v/>
       </c>
-      <c r="L34" s="28">
+      <c r="L34" s="29">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="28">
+      <c r="M34" s="29">
         <f>IF(B34="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="18">
+        <f>IF($D34="",NA(),IF(OR($D34&gt;$K34,$D34&lt;$L34),$D34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="18">
+        <f>IF(COUNT($D27:$D34)&lt;8,NA(),IF(OR(MIN($D27:$D34)&gt;$B$5,MAX($D27:$D34)&lt;$B$5),$D34,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6752,17 +8071,17 @@
           <t>Week 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>1285</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="27" t="n">
         <v>62</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="25">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="25">
         <f>IF(B35="","",SQRT($B$5/B35))</f>
         <v/>
       </c>
@@ -6778,16 +8097,24 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="28">
+      <c r="K35" s="29">
         <f>IF(B35="","",$B$5+3*E35*$B$7)</f>
         <v/>
       </c>
-      <c r="L35" s="28">
+      <c r="L35" s="29">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="28">
+      <c r="M35" s="29">
         <f>IF(B35="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD35" s="18">
+        <f>IF($D35="",NA(),IF(OR($D35&gt;$K35,$D35&lt;$L35),$D35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="18">
+        <f>IF(COUNT($D28:$D35)&lt;8,NA(),IF(OR(MIN($D28:$D35)&gt;$B$5,MAX($D28:$D35)&lt;$B$5),$D35,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6797,17 +8124,17 @@
           <t>Week 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>1225</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="25">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="25">
         <f>IF(B36="","",SQRT($B$5/B36))</f>
         <v/>
       </c>
@@ -6823,16 +8150,24 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="28">
+      <c r="K36" s="29">
         <f>IF(B36="","",$B$5+3*E36*$B$7)</f>
         <v/>
       </c>
-      <c r="L36" s="28">
+      <c r="L36" s="29">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="28">
+      <c r="M36" s="29">
         <f>IF(B36="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD36" s="18">
+        <f>IF($D36="",NA(),IF(OR($D36&gt;$K36,$D36&lt;$L36),$D36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="18">
+        <f>IF(COUNT($D29:$D36)&lt;8,NA(),IF(OR(MIN($D29:$D36)&gt;$B$5,MAX($D29:$D36)&lt;$B$5),$D36,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6842,17 +8177,17 @@
           <t>Week 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <v>1390</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="27" t="n">
         <v>76</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="25">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="25">
         <f>IF(B37="","",SQRT($B$5/B37))</f>
         <v/>
       </c>
@@ -6868,16 +8203,24 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="28">
+      <c r="K37" s="29">
         <f>IF(B37="","",$B$5+3*E37*$B$7)</f>
         <v/>
       </c>
-      <c r="L37" s="28">
+      <c r="L37" s="29">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="28">
+      <c r="M37" s="29">
         <f>IF(B37="","",$B$5)</f>
+        <v/>
+      </c>
+      <c r="AD37" s="18">
+        <f>IF($D37="",NA(),IF(OR($D37&gt;$K37,$D37&lt;$L37),$D37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="18">
+        <f>IF(COUNT($D30:$D37)&lt;8,NA(),IF(OR(MIN($D30:$D37)&gt;$B$5,MAX($D30:$D37)&lt;$B$5),$D37,NA()))</f>
         <v/>
       </c>
     </row>
@@ -6905,7 +8248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6920,6 +8263,9 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7020,7 +8366,7 @@
           <t>A2 for this n</t>
         </is>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{1.880;1.023;0.729;0.577;0.483;0.419;0.373;0.337;0.308}),"n out of range")</f>
         <v/>
       </c>
@@ -7036,7 +8382,7 @@
           <t>D4 for this n</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="21">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{3.267;2.574;2.282;2.114;2.004;1.924;1.864;1.816;1.777}),"n out of range")</f>
         <v/>
       </c>
@@ -7047,7 +8393,7 @@
           <t>D3 for this n</t>
         </is>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="21">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{0;0;0;0;0;0.076;0.136;0.184;0.223}),"n out of range")</f>
         <v/>
       </c>
@@ -7063,7 +8409,7 @@
           <t>Xbar UCL / LCL</t>
         </is>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="22">
         <f>TEXT(B6+B8*B7,"#,##0.00")&amp;"  /  "&amp;TEXT(B6-B8*B7,"#,##0.00")</f>
         <v/>
       </c>
@@ -7152,6 +8498,21 @@
           <t>Signal</t>
         </is>
       </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>out of control</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>8 in a row one side</t>
+        </is>
+      </c>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>R out of control</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7159,19 +8520,19 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>400</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="24" t="n">
         <v>419</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="24" t="n">
         <v>381</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="24" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="24" t="n">
         <v>419</v>
       </c>
       <c r="G14" s="15">
@@ -7198,16 +8559,28 @@
         <f>IF(G14="","",IF(OR(G14&gt;J14,G14&lt;K14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N14" s="29">
+      <c r="N14" s="30">
         <f>IF(H14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="29">
+      <c r="O14" s="30">
         <f>IF(H14="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P14" s="29">
+      <c r="P14" s="30">
         <f>IF(H14="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD14" s="18">
+        <f>IF($G14="",NA(),IF(OR($G14&gt;$J14,$G14&lt;$K14),$G14,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF14" s="18">
+        <f>IF($H14="",NA(),IF($H14&gt;$O14,$H14,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7217,19 +8590,19 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>430</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>395</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="27" t="n">
         <v>430</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="27" t="n">
         <v>395</v>
       </c>
       <c r="G15" s="15">
@@ -7256,16 +8629,28 @@
         <f>IF(G15="","",IF(OR(G15&gt;J15,G15&lt;K15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N15" s="29">
+      <c r="N15" s="30">
         <f>IF(H15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="29">
+      <c r="O15" s="30">
         <f>IF(H15="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P15" s="29">
+      <c r="P15" s="30">
         <f>IF(H15="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD15" s="18">
+        <f>IF($G15="",NA(),IF(OR($G15&gt;$J15,$G15&lt;$K15),$G15,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF15" s="18">
+        <f>IF($H15="",NA(),IF($H15&gt;$O15,$H15,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7275,19 +8660,19 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>411</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>401</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="27" t="n">
         <v>438</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="27" t="n">
         <v>410</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="27" t="n">
         <v>401</v>
       </c>
       <c r="G16" s="15">
@@ -7314,16 +8699,28 @@
         <f>IF(G16="","",IF(OR(G16&gt;J16,G16&lt;K16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N16" s="29">
+      <c r="N16" s="30">
         <f>IF(H16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O16" s="29">
+      <c r="O16" s="30">
         <f>IF(H16="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P16" s="29">
+      <c r="P16" s="30">
         <f>IF(H16="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="18">
+        <f>IF($G16="",NA(),IF(OR($G16&gt;$J16,$G16&lt;$K16),$G16,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF16" s="18">
+        <f>IF($H16="",NA(),IF($H16&gt;$O16,$H16,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7333,19 +8730,19 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>402</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>440</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="27" t="n">
         <v>425</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="27" t="n">
         <v>402</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="27" t="n">
         <v>440</v>
       </c>
       <c r="G17" s="15">
@@ -7372,16 +8769,28 @@
         <f>IF(G17="","",IF(OR(G17&gt;J17,G17&lt;K17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N17" s="29">
+      <c r="N17" s="30">
         <f>IF(H17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O17" s="29">
+      <c r="O17" s="30">
         <f>IF(H17="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P17" s="29">
+      <c r="P17" s="30">
         <f>IF(H17="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD17" s="18">
+        <f>IF($G17="",NA(),IF(OR($G17&gt;$J17,$G17&lt;$K17),$G17,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF17" s="18">
+        <f>IF($H17="",NA(),IF($H17&gt;$O17,$H17,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7391,19 +8800,19 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>437</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>437</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="27" t="n">
         <v>404</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="27" t="n">
         <v>437</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="27" t="n">
         <v>437</v>
       </c>
       <c r="G18" s="15">
@@ -7430,16 +8839,28 @@
         <f>IF(G18="","",IF(OR(G18&gt;J18,G18&lt;K18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N18" s="29">
+      <c r="N18" s="30">
         <f>IF(H18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O18" s="29">
+      <c r="O18" s="30">
         <f>IF(H18="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P18" s="29">
+      <c r="P18" s="30">
         <f>IF(H18="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD18" s="18">
+        <f>IF($G18="",NA(),IF(OR($G18&gt;$J18,$G18&lt;$K18),$G18,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF18" s="18">
+        <f>IF($H18="",NA(),IF($H18&gt;$O18,$H18,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7449,19 +8870,19 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>430</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>392</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="27" t="n">
         <v>415</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="27" t="n">
         <v>430</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="27" t="n">
         <v>392</v>
       </c>
       <c r="G19" s="15">
@@ -7488,16 +8909,28 @@
         <f>IF(G19="","",IF(OR(G19&gt;J19,G19&lt;K19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N19" s="29">
+      <c r="N19" s="30">
         <f>IF(H19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="29">
+      <c r="O19" s="30">
         <f>IF(H19="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P19" s="29">
+      <c r="P19" s="30">
         <f>IF(H19="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD19" s="18">
+        <f>IF($G19="",NA(),IF(OR($G19&gt;$J19,$G19&lt;$K19),$G19,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF19" s="18">
+        <f>IF($H19="",NA(),IF($H19&gt;$O19,$H19,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7507,19 +8940,19 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>396</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>406</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="27" t="n">
         <v>433</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="27" t="n">
         <v>396</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="27" t="n">
         <v>406</v>
       </c>
       <c r="G20" s="15">
@@ -7546,16 +8979,28 @@
         <f>IF(G20="","",IF(OR(G20&gt;J20,G20&lt;K20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N20" s="29">
+      <c r="N20" s="30">
         <f>IF(H20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="29">
+      <c r="O20" s="30">
         <f>IF(H20="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P20" s="29">
+      <c r="P20" s="30">
         <f>IF(H20="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD20" s="18">
+        <f>IF($G20="",NA(),IF(OR($G20&gt;$J20,$G20&lt;$K20),$G20,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF20" s="18">
+        <f>IF($H20="",NA(),IF($H20&gt;$O20,$H20,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7565,19 +9010,19 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>396</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>431</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="27" t="n">
         <v>401</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="27" t="n">
         <v>396</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="27" t="n">
         <v>431</v>
       </c>
       <c r="G21" s="15">
@@ -7604,16 +9049,28 @@
         <f>IF(G21="","",IF(OR(G21&gt;J21,G21&lt;K21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="30">
         <f>IF(H21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="30">
         <f>IF(H21="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="30">
         <f>IF(H21="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="18">
+        <f>IF($G21="",NA(),IF(OR($G21&gt;$J21,$G21&lt;$K21),$G21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="18">
+        <f>IF(COUNT($G14:$G21)&lt;8,NA(),IF(OR(MIN($G14:$G21)&gt;$B$6,MAX($G14:$G21)&lt;$B$6),$G21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="18">
+        <f>IF($H21="",NA(),IF($H21&gt;$O21,$H21,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7623,19 +9080,19 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>425</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>407</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="27" t="n">
         <v>387</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="27" t="n">
         <v>425</v>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="27" t="n">
         <v>406</v>
       </c>
       <c r="G22" s="15">
@@ -7662,16 +9119,28 @@
         <f>IF(G22="","",IF(OR(G22&gt;J22,G22&lt;K22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="30">
         <f>IF(H22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="29">
+      <c r="O22" s="30">
         <f>IF(H22="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P22" s="29">
+      <c r="P22" s="30">
         <f>IF(H22="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="18">
+        <f>IF($G22="",NA(),IF(OR($G22&gt;$J22,$G22&lt;$K22),$G22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="18">
+        <f>IF(COUNT($G15:$G22)&lt;8,NA(),IF(OR(MIN($G15:$G22)&gt;$B$6,MAX($G15:$G22)&lt;$B$6),$G22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="18">
+        <f>IF($H22="",NA(),IF($H22&gt;$O22,$H22,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7681,19 +9150,19 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>413</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>382</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="27" t="n">
         <v>417</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="27" t="n">
         <v>412</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="27" t="n">
         <v>382</v>
       </c>
       <c r="G23" s="15">
@@ -7720,16 +9189,28 @@
         <f>IF(G23="","",IF(OR(G23&gt;J23,G23&lt;K23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N23" s="29">
+      <c r="N23" s="30">
         <f>IF(H23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="29">
+      <c r="O23" s="30">
         <f>IF(H23="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P23" s="29">
+      <c r="P23" s="30">
         <f>IF(H23="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="18">
+        <f>IF($G23="",NA(),IF(OR($G23&gt;$J23,$G23&lt;$K23),$G23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="18">
+        <f>IF(COUNT($G16:$G23)&lt;8,NA(),IF(OR(MIN($G16:$G23)&gt;$B$6,MAX($G16:$G23)&lt;$B$6),$G23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="18">
+        <f>IF($H23="",NA(),IF($H23&gt;$O23,$H23,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7739,19 +9220,19 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>367</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>393</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="27" t="n">
         <v>404</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="27" t="n">
         <v>367</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="27" t="n">
         <v>394</v>
       </c>
       <c r="G24" s="15">
@@ -7778,16 +9259,28 @@
         <f>IF(G24="","",IF(OR(G24&gt;J24,G24&lt;K24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="30">
         <f>IF(H24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O24" s="29">
+      <c r="O24" s="30">
         <f>IF(H24="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="30">
         <f>IF(H24="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD24" s="18">
+        <f>IF($G24="",NA(),IF(OR($G24&gt;$J24,$G24&lt;$K24),$G24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="18">
+        <f>IF(COUNT($G17:$G24)&lt;8,NA(),IF(OR(MIN($G17:$G24)&gt;$B$6,MAX($G17:$G24)&lt;$B$6),$G24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="18">
+        <f>IF($H24="",NA(),IF($H24&gt;$O24,$H24,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7797,19 +9290,19 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>386</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>410</v>
       </c>
-      <c r="D25" s="26" t="n">
+      <c r="D25" s="27" t="n">
         <v>372</v>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="27" t="n">
         <v>386</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="27" t="n">
         <v>409</v>
       </c>
       <c r="G25" s="15">
@@ -7836,16 +9329,28 @@
         <f>IF(G25="","",IF(OR(G25&gt;J25,G25&lt;K25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="30">
         <f>IF(H25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O25" s="29">
+      <c r="O25" s="30">
         <f>IF(H25="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="30">
         <f>IF(H25="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="18">
+        <f>IF($G25="",NA(),IF(OR($G25&gt;$J25,$G25&lt;$K25),$G25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="18">
+        <f>IF(COUNT($G18:$G25)&lt;8,NA(),IF(OR(MIN($G18:$G25)&gt;$B$6,MAX($G18:$G25)&lt;$B$6),$G25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="18">
+        <f>IF($H25="",NA(),IF($H25&gt;$O25,$H25,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7855,19 +9360,19 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>415</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <v>382</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="27" t="n">
         <v>381</v>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="27" t="n">
         <v>415</v>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="27" t="n">
         <v>382</v>
       </c>
       <c r="G26" s="15">
@@ -7894,16 +9399,28 @@
         <f>IF(G26="","",IF(OR(G26&gt;J26,G26&lt;K26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N26" s="29">
+      <c r="N26" s="30">
         <f>IF(H26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O26" s="29">
+      <c r="O26" s="30">
         <f>IF(H26="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P26" s="29">
+      <c r="P26" s="30">
         <f>IF(H26="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD26" s="18">
+        <f>IF($G26="",NA(),IF(OR($G26&gt;$J26,$G26&lt;$K26),$G26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="18">
+        <f>IF(COUNT($G19:$G26)&lt;8,NA(),IF(OR(MIN($G19:$G26)&gt;$B$6,MAX($G19:$G26)&lt;$B$6),$G26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="18">
+        <f>IF($H26="",NA(),IF($H26&gt;$O26,$H26,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7913,19 +9430,19 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>396</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>381</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="27" t="n">
         <v>419</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="27" t="n">
         <v>396</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="27" t="n">
         <v>381</v>
       </c>
       <c r="G27" s="15">
@@ -7952,16 +9469,28 @@
         <f>IF(G27="","",IF(OR(G27&gt;J27,G27&lt;K27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N27" s="29">
+      <c r="N27" s="30">
         <f>IF(H27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O27" s="29">
+      <c r="O27" s="30">
         <f>IF(H27="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P27" s="29">
+      <c r="P27" s="30">
         <f>IF(H27="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD27" s="18">
+        <f>IF($G27="",NA(),IF(OR($G27&gt;$J27,$G27&lt;$K27),$G27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="18">
+        <f>IF(COUNT($G20:$G27)&lt;8,NA(),IF(OR(MIN($G20:$G27)&gt;$B$6,MAX($G20:$G27)&lt;$B$6),$G27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="18">
+        <f>IF($H27="",NA(),IF($H27&gt;$O27,$H27,NA()))</f>
         <v/>
       </c>
     </row>
@@ -7971,19 +9500,19 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>385</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>421</v>
       </c>
-      <c r="D28" s="26" t="n">
+      <c r="D28" s="27" t="n">
         <v>412</v>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="27" t="n">
         <v>385</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="27" t="n">
         <v>421</v>
       </c>
       <c r="G28" s="15">
@@ -8010,16 +9539,28 @@
         <f>IF(G28="","",IF(OR(G28&gt;J28,G28&lt;K28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N28" s="29">
+      <c r="N28" s="30">
         <f>IF(H28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O28" s="29">
+      <c r="O28" s="30">
         <f>IF(H28="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P28" s="29">
+      <c r="P28" s="30">
         <f>IF(H28="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD28" s="18">
+        <f>IF($G28="",NA(),IF(OR($G28&gt;$J28,$G28&lt;$K28),$G28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="18">
+        <f>IF(COUNT($G21:$G28)&lt;8,NA(),IF(OR(MIN($G21:$G28)&gt;$B$6,MAX($G21:$G28)&lt;$B$6),$G28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="18">
+        <f>IF($H28="",NA(),IF($H28&gt;$O28,$H28,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8029,19 +9570,19 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>407</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>413</v>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D29" s="27" t="n">
         <v>378</v>
       </c>
-      <c r="E29" s="26" t="n">
+      <c r="E29" s="27" t="n">
         <v>408</v>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="27" t="n">
         <v>413</v>
       </c>
       <c r="G29" s="15">
@@ -8068,16 +9609,28 @@
         <f>IF(G29="","",IF(OR(G29&gt;J29,G29&lt;K29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N29" s="29">
+      <c r="N29" s="30">
         <f>IF(H29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="29">
+      <c r="O29" s="30">
         <f>IF(H29="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P29" s="29">
+      <c r="P29" s="30">
         <f>IF(H29="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="18">
+        <f>IF($G29="",NA(),IF(OR($G29&gt;$J29,$G29&lt;$K29),$G29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="18">
+        <f>IF(COUNT($G22:$G29)&lt;8,NA(),IF(OR(MIN($G22:$G29)&gt;$B$6,MAX($G22:$G29)&lt;$B$6),$G29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF29" s="18">
+        <f>IF($H29="",NA(),IF($H29&gt;$O29,$H29,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8087,19 +9640,19 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>428</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>389</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="27" t="n">
         <v>408</v>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="27" t="n">
         <v>427</v>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="27" t="n">
         <v>389</v>
       </c>
       <c r="G30" s="15">
@@ -8126,16 +9679,28 @@
         <f>IF(G30="","",IF(OR(G30&gt;J30,G30&lt;K30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N30" s="29">
+      <c r="N30" s="30">
         <f>IF(H30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O30" s="29">
+      <c r="O30" s="30">
         <f>IF(H30="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="30">
         <f>IF(H30="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD30" s="18">
+        <f>IF($G30="",NA(),IF(OR($G30&gt;$J30,$G30&lt;$K30),$G30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="18">
+        <f>IF(COUNT($G23:$G30)&lt;8,NA(),IF(OR(MIN($G23:$G30)&gt;$B$6,MAX($G23:$G30)&lt;$B$6),$G30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF30" s="18">
+        <f>IF($H30="",NA(),IF($H30&gt;$O30,$H30,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8145,19 +9710,19 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <v>403</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <v>407</v>
       </c>
-      <c r="D31" s="26" t="n">
+      <c r="D31" s="27" t="n">
         <v>438</v>
       </c>
-      <c r="E31" s="26" t="n">
+      <c r="E31" s="27" t="n">
         <v>403</v>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="27" t="n">
         <v>407</v>
       </c>
       <c r="G31" s="15">
@@ -8184,16 +9749,28 @@
         <f>IF(G31="","",IF(OR(G31&gt;J31,G31&lt;K31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N31" s="29">
+      <c r="N31" s="30">
         <f>IF(H31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O31" s="29">
+      <c r="O31" s="30">
         <f>IF(H31="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P31" s="29">
+      <c r="P31" s="30">
         <f>IF(H31="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="18">
+        <f>IF($G31="",NA(),IF(OR($G31&gt;$J31,$G31&lt;$K31),$G31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="18">
+        <f>IF(COUNT($G24:$G31)&lt;8,NA(),IF(OR(MIN($G24:$G31)&gt;$B$6,MAX($G24:$G31)&lt;$B$6),$G31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF31" s="18">
+        <f>IF($H31="",NA(),IF($H31&gt;$O31,$H31,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8203,19 +9780,19 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>406</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="27" t="n">
         <v>443</v>
       </c>
-      <c r="D32" s="26" t="n">
+      <c r="D32" s="27" t="n">
         <v>417</v>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="27" t="n">
         <v>406</v>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="27" t="n">
         <v>443</v>
       </c>
       <c r="G32" s="15">
@@ -8242,16 +9819,28 @@
         <f>IF(G32="","",IF(OR(G32&gt;J32,G32&lt;K32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N32" s="29">
+      <c r="N32" s="30">
         <f>IF(H32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O32" s="29">
+      <c r="O32" s="30">
         <f>IF(H32="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P32" s="29">
+      <c r="P32" s="30">
         <f>IF(H32="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD32" s="18">
+        <f>IF($G32="",NA(),IF(OR($G32&gt;$J32,$G32&lt;$K32),$G32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="18">
+        <f>IF(COUNT($G25:$G32)&lt;8,NA(),IF(OR(MIN($G25:$G32)&gt;$B$6,MAX($G25:$G32)&lt;$B$6),$G32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF32" s="18">
+        <f>IF($H32="",NA(),IF($H32&gt;$O32,$H32,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8261,19 +9850,19 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>443</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
         <v>429</v>
       </c>
-      <c r="D33" s="26" t="n">
+      <c r="D33" s="27" t="n">
         <v>405</v>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="E33" s="27" t="n">
         <v>443</v>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="27" t="n">
         <v>429</v>
       </c>
       <c r="G33" s="15">
@@ -8300,16 +9889,28 @@
         <f>IF(G33="","",IF(OR(G33&gt;J33,G33&lt;K33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N33" s="29">
+      <c r="N33" s="30">
         <f>IF(H33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O33" s="29">
+      <c r="O33" s="30">
         <f>IF(H33="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P33" s="29">
+      <c r="P33" s="30">
         <f>IF(H33="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD33" s="18">
+        <f>IF($G33="",NA(),IF(OR($G33&gt;$J33,$G33&lt;$K33),$G33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="18">
+        <f>IF(COUNT($G26:$G33)&lt;8,NA(),IF(OR(MIN($G26:$G33)&gt;$B$6,MAX($G26:$G33)&lt;$B$6),$G33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF33" s="18">
+        <f>IF($H33="",NA(),IF($H33&gt;$O33,$H33,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8319,19 +9920,19 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <v>424</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <v>390</v>
       </c>
-      <c r="D34" s="26" t="n">
+      <c r="D34" s="27" t="n">
         <v>423</v>
       </c>
-      <c r="E34" s="26" t="n">
+      <c r="E34" s="27" t="n">
         <v>424</v>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="27" t="n">
         <v>390</v>
       </c>
       <c r="G34" s="15">
@@ -8358,16 +9959,28 @@
         <f>IF(G34="","",IF(OR(G34&gt;J34,G34&lt;K34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N34" s="29">
+      <c r="N34" s="30">
         <f>IF(H34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O34" s="29">
+      <c r="O34" s="30">
         <f>IF(H34="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P34" s="29">
+      <c r="P34" s="30">
         <f>IF(H34="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD34" s="18">
+        <f>IF($G34="",NA(),IF(OR($G34&gt;$J34,$G34&lt;$K34),$G34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="18">
+        <f>IF(COUNT($G27:$G34)&lt;8,NA(),IF(OR(MIN($G27:$G34)&gt;$B$6,MAX($G27:$G34)&lt;$B$6),$G34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF34" s="18">
+        <f>IF($H34="",NA(),IF($H34&gt;$O34,$H34,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8377,19 +9990,19 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>392</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="27" t="n">
         <v>414</v>
       </c>
-      <c r="D35" s="26" t="n">
+      <c r="D35" s="27" t="n">
         <v>430</v>
       </c>
-      <c r="E35" s="26" t="n">
+      <c r="E35" s="27" t="n">
         <v>392</v>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="27" t="n">
         <v>414</v>
       </c>
       <c r="G35" s="15">
@@ -8416,16 +10029,28 @@
         <f>IF(G35="","",IF(OR(G35&gt;J35,G35&lt;K35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N35" s="29">
+      <c r="N35" s="30">
         <f>IF(H35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O35" s="29">
+      <c r="O35" s="30">
         <f>IF(H35="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P35" s="29">
+      <c r="P35" s="30">
         <f>IF(H35="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD35" s="18">
+        <f>IF($G35="",NA(),IF(OR($G35&gt;$J35,$G35&lt;$K35),$G35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="18">
+        <f>IF(COUNT($G28:$G35)&lt;8,NA(),IF(OR(MIN($G28:$G35)&gt;$B$6,MAX($G28:$G35)&lt;$B$6),$G35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF35" s="18">
+        <f>IF($H35="",NA(),IF($H35&gt;$O35,$H35,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8435,19 +10060,19 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>403</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="27" t="n">
         <v>431</v>
       </c>
-      <c r="D36" s="26" t="n">
+      <c r="D36" s="27" t="n">
         <v>394</v>
       </c>
-      <c r="E36" s="26" t="n">
+      <c r="E36" s="27" t="n">
         <v>403</v>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="27" t="n">
         <v>431</v>
       </c>
       <c r="G36" s="15">
@@ -8474,16 +10099,28 @@
         <f>IF(G36="","",IF(OR(G36&gt;J36,G36&lt;K36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N36" s="29">
+      <c r="N36" s="30">
         <f>IF(H36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O36" s="29">
+      <c r="O36" s="30">
         <f>IF(H36="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P36" s="29">
+      <c r="P36" s="30">
         <f>IF(H36="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD36" s="18">
+        <f>IF($G36="",NA(),IF(OR($G36&gt;$J36,$G36&lt;$K36),$G36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="18">
+        <f>IF(COUNT($G29:$G36)&lt;8,NA(),IF(OR(MIN($G29:$G36)&gt;$B$6,MAX($G29:$G36)&lt;$B$6),$G36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF36" s="18">
+        <f>IF($H36="",NA(),IF($H36&gt;$O36,$H36,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8493,19 +10130,19 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <v>428</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="27" t="n">
         <v>399</v>
       </c>
-      <c r="D37" s="26" t="n">
+      <c r="D37" s="27" t="n">
         <v>393</v>
       </c>
-      <c r="E37" s="26" t="n">
+      <c r="E37" s="27" t="n">
         <v>429</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="27" t="n">
         <v>399</v>
       </c>
       <c r="G37" s="15">
@@ -8532,16 +10169,28 @@
         <f>IF(G37="","",IF(OR(G37&gt;J37,G37&lt;K37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N37" s="29">
+      <c r="N37" s="30">
         <f>IF(H37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O37" s="29">
+      <c r="O37" s="30">
         <f>IF(H37="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P37" s="29">
+      <c r="P37" s="30">
         <f>IF(H37="","",$B$10*$B$7)</f>
+        <v/>
+      </c>
+      <c r="AD37" s="18">
+        <f>IF($G37="",NA(),IF(OR($G37&gt;$J37,$G37&lt;$K37),$G37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="18">
+        <f>IF(COUNT($G30:$G37)&lt;8,NA(),IF(OR(MIN($G30:$G37)&gt;$B$6,MAX($G30:$G37)&lt;$B$6),$G37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF37" s="18">
+        <f>IF($H37="",NA(),IF($H37&gt;$O37,$H37,NA()))</f>
         <v/>
       </c>
     </row>
@@ -8571,7 +10220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:AD39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8583,6 +10232,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -8629,7 +10279,7 @@
           <t>Lambda (weight on the newest point)</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="31" t="n">
         <v>0.2</v>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -8644,7 +10294,7 @@
           <t>L (limit width in sigmas)</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>2.7</v>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -8762,6 +10412,11 @@
           <t>Signal</t>
         </is>
       </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>out of control</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8792,6 +10447,10 @@
         <f>IF(D16="","",IF(OR(D16&gt;F16,D16&lt;G16),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD16" s="18">
+        <f>IF($D16="",NA(),IF(OR($D16&gt;$F16,$D16&lt;$G16),$D16,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8799,7 +10458,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="15">
@@ -8826,6 +10485,10 @@
         <f>IF(D17="","",IF(OR(D17&gt;F17,D17&lt;G17),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD17" s="18">
+        <f>IF($D17="",NA(),IF(OR($D17&gt;$F17,$D17&lt;$G17),$D17,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8833,7 +10496,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="15">
@@ -8860,6 +10523,10 @@
         <f>IF(D18="","",IF(OR(D18&gt;F18,D18&lt;G18),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD18" s="18">
+        <f>IF($D18="",NA(),IF(OR($D18&gt;$F18,$D18&lt;$G18),$D18,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8867,7 +10534,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="15">
@@ -8894,6 +10561,10 @@
         <f>IF(D19="","",IF(OR(D19&gt;F19,D19&lt;G19),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD19" s="18">
+        <f>IF($D19="",NA(),IF(OR($D19&gt;$F19,$D19&lt;$G19),$D19,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8901,7 +10572,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="15">
@@ -8928,6 +10599,10 @@
         <f>IF(D20="","",IF(OR(D20&gt;F20,D20&lt;G20),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD20" s="18">
+        <f>IF($D20="",NA(),IF(OR($D20&gt;$F20,$D20&lt;$G20),$D20,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8935,7 +10610,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="15">
@@ -8962,6 +10637,10 @@
         <f>IF(D21="","",IF(OR(D21&gt;F21,D21&lt;G21),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD21" s="18">
+        <f>IF($D21="",NA(),IF(OR($D21&gt;$F21,$D21&lt;$G21),$D21,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8969,7 +10648,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="15">
@@ -8996,6 +10675,10 @@
         <f>IF(D22="","",IF(OR(D22&gt;F22,D22&lt;G22),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD22" s="18">
+        <f>IF($D22="",NA(),IF(OR($D22&gt;$F22,$D22&lt;$G22),$D22,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9003,7 +10686,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="15">
@@ -9030,6 +10713,10 @@
         <f>IF(D23="","",IF(OR(D23&gt;F23,D23&lt;G23),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD23" s="18">
+        <f>IF($D23="",NA(),IF(OR($D23&gt;$F23,$D23&lt;$G23),$D23,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9037,7 +10724,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="15">
@@ -9064,6 +10751,10 @@
         <f>IF(D24="","",IF(OR(D24&gt;F24,D24&lt;G24),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD24" s="18">
+        <f>IF($D24="",NA(),IF(OR($D24&gt;$F24,$D24&lt;$G24),$D24,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9071,7 +10762,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="15">
@@ -9098,6 +10789,10 @@
         <f>IF(D25="","",IF(OR(D25&gt;F25,D25&lt;G25),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD25" s="18">
+        <f>IF($D25="",NA(),IF(OR($D25&gt;$F25,$D25&lt;$G25),$D25,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9105,7 +10800,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="15">
@@ -9132,6 +10827,10 @@
         <f>IF(D26="","",IF(OR(D26&gt;F26,D26&lt;G26),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD26" s="18">
+        <f>IF($D26="",NA(),IF(OR($D26&gt;$F26,$D26&lt;$G26),$D26,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9139,7 +10838,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="15">
@@ -9166,6 +10865,10 @@
         <f>IF(D27="","",IF(OR(D27&gt;F27,D27&lt;G27),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD27" s="18">
+        <f>IF($D27="",NA(),IF(OR($D27&gt;$F27,$D27&lt;$G27),$D27,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9173,7 +10876,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="19" t="n">
         <v>418</v>
       </c>
       <c r="C28" s="15">
@@ -9200,6 +10903,10 @@
         <f>IF(D28="","",IF(OR(D28&gt;F28,D28&lt;G28),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD28" s="18">
+        <f>IF($D28="",NA(),IF(OR($D28&gt;$F28,$D28&lt;$G28),$D28,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9207,7 +10914,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="19" t="n">
         <v>426</v>
       </c>
       <c r="C29" s="15">
@@ -9234,6 +10941,10 @@
         <f>IF(D29="","",IF(OR(D29&gt;F29,D29&lt;G29),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD29" s="18">
+        <f>IF($D29="",NA(),IF(OR($D29&gt;$F29,$D29&lt;$G29),$D29,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9241,7 +10952,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C30" s="15">
@@ -9268,6 +10979,10 @@
         <f>IF(D30="","",IF(OR(D30&gt;F30,D30&lt;G30),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD30" s="18">
+        <f>IF($D30="",NA(),IF(OR($D30&gt;$F30,$D30&lt;$G30),$D30,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9275,7 +10990,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="19" t="n">
         <v>428</v>
       </c>
       <c r="C31" s="15">
@@ -9302,6 +11017,10 @@
         <f>IF(D31="","",IF(OR(D31&gt;F31,D31&lt;G31),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD31" s="18">
+        <f>IF($D31="",NA(),IF(OR($D31&gt;$F31,$D31&lt;$G31),$D31,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9309,7 +11028,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="19" t="n">
         <v>437</v>
       </c>
       <c r="C32" s="15">
@@ -9336,6 +11055,10 @@
         <f>IF(D32="","",IF(OR(D32&gt;F32,D32&lt;G32),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD32" s="18">
+        <f>IF($D32="",NA(),IF(OR($D32&gt;$F32,$D32&lt;$G32),$D32,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9343,7 +11066,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="19" t="n">
         <v>433</v>
       </c>
       <c r="C33" s="15">
@@ -9370,6 +11093,10 @@
         <f>IF(D33="","",IF(OR(D33&gt;F33,D33&lt;G33),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD33" s="18">
+        <f>IF($D33="",NA(),IF(OR($D33&gt;$F33,$D33&lt;$G33),$D33,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9377,7 +11104,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="19" t="n">
         <v>441</v>
       </c>
       <c r="C34" s="15">
@@ -9404,6 +11131,10 @@
         <f>IF(D34="","",IF(OR(D34&gt;F34,D34&lt;G34),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD34" s="18">
+        <f>IF($D34="",NA(),IF(OR($D34&gt;$F34,$D34&lt;$G34),$D34,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9411,7 +11142,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="19" t="n">
         <v>439</v>
       </c>
       <c r="C35" s="15">
@@ -9438,6 +11169,10 @@
         <f>IF(D35="","",IF(OR(D35&gt;F35,D35&lt;G35),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD35" s="18">
+        <f>IF($D35="",NA(),IF(OR($D35&gt;$F35,$D35&lt;$G35),$D35,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9445,7 +11180,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="19" t="n">
         <v>448</v>
       </c>
       <c r="C36" s="15">
@@ -9472,6 +11207,10 @@
         <f>IF(D36="","",IF(OR(D36&gt;F36,D36&lt;G36),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD36" s="18">
+        <f>IF($D36="",NA(),IF(OR($D36&gt;$F36,$D36&lt;$G36),$D36,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9479,7 +11218,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="19" t="n">
         <v>444</v>
       </c>
       <c r="C37" s="15">
@@ -9506,6 +11245,10 @@
         <f>IF(D37="","",IF(OR(D37&gt;F37,D37&lt;G37),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD37" s="18">
+        <f>IF($D37="",NA(),IF(OR($D37&gt;$F37,$D37&lt;$G37),$D37,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9513,7 +11256,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="19" t="n">
         <v>452</v>
       </c>
       <c r="C38" s="15">
@@ -9540,6 +11283,10 @@
         <f>IF(D38="","",IF(OR(D38&gt;F38,D38&lt;G38),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="AD38" s="18">
+        <f>IF($D38="",NA(),IF(OR($D38&gt;$F38,$D38&lt;$G38),$D38,NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9547,7 +11294,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="18" t="n">
+      <c r="B39" s="19" t="n">
         <v>449</v>
       </c>
       <c r="C39" s="15">
@@ -9572,6 +11319,10 @@
       </c>
       <c r="I39" s="17">
         <f>IF(D39="","",IF(OR(D39&gt;F39,D39&lt;G39),"SIGNAL — the process has drifted",""))</f>
+        <v/>
+      </c>
+      <c r="AD39" s="18">
+        <f>IF($D39="",NA(),IF(OR($D39&gt;$F39,$D39&lt;$G39),$D39,NA()))</f>
         <v/>
       </c>
     </row>
@@ -9600,7 +11351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:AD39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9612,6 +11363,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -9658,7 +11410,7 @@
           <t>k (slack, in sigmas)</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="31" t="n">
         <v>0.5</v>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -9673,7 +11425,7 @@
           <t>h (decision interval)</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -9790,6 +11542,11 @@
           <t>Signal</t>
         </is>
       </c>
+      <c r="AD15" s="5" t="inlineStr">
+        <is>
+          <t>crossed h</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9824,6 +11581,10 @@
         <f>IF(E16="","",IF(E16&gt;$B$6,"SHIFT UP confirmed",IF(F16&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD16" s="18">
+        <f>IF($E16="",NA(),IF(OR($E16&gt;$B$6,$F16&gt;$B$6),MAX($E16,$F16),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9831,7 +11592,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="15">
@@ -9862,6 +11623,10 @@
         <f>IF(E17="","",IF(E17&gt;$B$6,"SHIFT UP confirmed",IF(F17&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD17" s="18">
+        <f>IF($E17="",NA(),IF(OR($E17&gt;$B$6,$F17&gt;$B$6),MAX($E17,$F17),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9869,7 +11634,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="15">
@@ -9900,6 +11665,10 @@
         <f>IF(E18="","",IF(E18&gt;$B$6,"SHIFT UP confirmed",IF(F18&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD18" s="18">
+        <f>IF($E18="",NA(),IF(OR($E18&gt;$B$6,$F18&gt;$B$6),MAX($E18,$F18),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9907,7 +11676,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="15">
@@ -9938,6 +11707,10 @@
         <f>IF(E19="","",IF(E19&gt;$B$6,"SHIFT UP confirmed",IF(F19&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD19" s="18">
+        <f>IF($E19="",NA(),IF(OR($E19&gt;$B$6,$F19&gt;$B$6),MAX($E19,$F19),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9945,7 +11718,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="15">
@@ -9976,6 +11749,10 @@
         <f>IF(E20="","",IF(E20&gt;$B$6,"SHIFT UP confirmed",IF(F20&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD20" s="18">
+        <f>IF($E20="",NA(),IF(OR($E20&gt;$B$6,$F20&gt;$B$6),MAX($E20,$F20),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9983,7 +11760,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="15">
@@ -10014,6 +11791,10 @@
         <f>IF(E21="","",IF(E21&gt;$B$6,"SHIFT UP confirmed",IF(F21&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD21" s="18">
+        <f>IF($E21="",NA(),IF(OR($E21&gt;$B$6,$F21&gt;$B$6),MAX($E21,$F21),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10021,7 +11802,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="15">
@@ -10052,6 +11833,10 @@
         <f>IF(E22="","",IF(E22&gt;$B$6,"SHIFT UP confirmed",IF(F22&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD22" s="18">
+        <f>IF($E22="",NA(),IF(OR($E22&gt;$B$6,$F22&gt;$B$6),MAX($E22,$F22),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10059,7 +11844,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="15">
@@ -10090,6 +11875,10 @@
         <f>IF(E23="","",IF(E23&gt;$B$6,"SHIFT UP confirmed",IF(F23&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD23" s="18">
+        <f>IF($E23="",NA(),IF(OR($E23&gt;$B$6,$F23&gt;$B$6),MAX($E23,$F23),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10097,7 +11886,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="15">
@@ -10128,6 +11917,10 @@
         <f>IF(E24="","",IF(E24&gt;$B$6,"SHIFT UP confirmed",IF(F24&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD24" s="18">
+        <f>IF($E24="",NA(),IF(OR($E24&gt;$B$6,$F24&gt;$B$6),MAX($E24,$F24),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10135,7 +11928,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="15">
@@ -10166,6 +11959,10 @@
         <f>IF(E25="","",IF(E25&gt;$B$6,"SHIFT UP confirmed",IF(F25&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD25" s="18">
+        <f>IF($E25="",NA(),IF(OR($E25&gt;$B$6,$F25&gt;$B$6),MAX($E25,$F25),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10173,7 +11970,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="15">
@@ -10204,6 +12001,10 @@
         <f>IF(E26="","",IF(E26&gt;$B$6,"SHIFT UP confirmed",IF(F26&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD26" s="18">
+        <f>IF($E26="",NA(),IF(OR($E26&gt;$B$6,$F26&gt;$B$6),MAX($E26,$F26),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10211,7 +12012,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="15">
@@ -10242,6 +12043,10 @@
         <f>IF(E27="","",IF(E27&gt;$B$6,"SHIFT UP confirmed",IF(F27&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD27" s="18">
+        <f>IF($E27="",NA(),IF(OR($E27&gt;$B$6,$F27&gt;$B$6),MAX($E27,$F27),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10249,7 +12054,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="19" t="n">
         <v>452</v>
       </c>
       <c r="C28" s="15">
@@ -10280,6 +12085,10 @@
         <f>IF(E28="","",IF(E28&gt;$B$6,"SHIFT UP confirmed",IF(F28&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD28" s="18">
+        <f>IF($E28="",NA(),IF(OR($E28&gt;$B$6,$F28&gt;$B$6),MAX($E28,$F28),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10287,7 +12096,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="19" t="n">
         <v>461</v>
       </c>
       <c r="C29" s="15">
@@ -10318,6 +12127,10 @@
         <f>IF(E29="","",IF(E29&gt;$B$6,"SHIFT UP confirmed",IF(F29&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD29" s="18">
+        <f>IF($E29="",NA(),IF(OR($E29&gt;$B$6,$F29&gt;$B$6),MAX($E29,$F29),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10325,7 +12138,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="19" t="n">
         <v>448</v>
       </c>
       <c r="C30" s="15">
@@ -10356,6 +12169,10 @@
         <f>IF(E30="","",IF(E30&gt;$B$6,"SHIFT UP confirmed",IF(F30&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD30" s="18">
+        <f>IF($E30="",NA(),IF(OR($E30&gt;$B$6,$F30&gt;$B$6),MAX($E30,$F30),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10363,7 +12180,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="19" t="n">
         <v>470</v>
       </c>
       <c r="C31" s="15">
@@ -10394,6 +12211,10 @@
         <f>IF(E31="","",IF(E31&gt;$B$6,"SHIFT UP confirmed",IF(F31&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD31" s="18">
+        <f>IF($E31="",NA(),IF(OR($E31&gt;$B$6,$F31&gt;$B$6),MAX($E31,$F31),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10401,7 +12222,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="19" t="n">
         <v>457</v>
       </c>
       <c r="C32" s="15">
@@ -10432,6 +12253,10 @@
         <f>IF(E32="","",IF(E32&gt;$B$6,"SHIFT UP confirmed",IF(F32&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD32" s="18">
+        <f>IF($E32="",NA(),IF(OR($E32&gt;$B$6,$F32&gt;$B$6),MAX($E32,$F32),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10439,7 +12264,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="19" t="n">
         <v>466</v>
       </c>
       <c r="C33" s="15">
@@ -10470,6 +12295,10 @@
         <f>IF(E33="","",IF(E33&gt;$B$6,"SHIFT UP confirmed",IF(F33&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD33" s="18">
+        <f>IF($E33="",NA(),IF(OR($E33&gt;$B$6,$F33&gt;$B$6),MAX($E33,$F33),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10477,7 +12306,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n">
+      <c r="B34" s="19" t="n">
         <v>449</v>
       </c>
       <c r="C34" s="15">
@@ -10508,6 +12337,10 @@
         <f>IF(E34="","",IF(E34&gt;$B$6,"SHIFT UP confirmed",IF(F34&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD34" s="18">
+        <f>IF($E34="",NA(),IF(OR($E34&gt;$B$6,$F34&gt;$B$6),MAX($E34,$F34),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10515,7 +12348,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="19" t="n">
         <v>463</v>
       </c>
       <c r="C35" s="15">
@@ -10546,6 +12379,10 @@
         <f>IF(E35="","",IF(E35&gt;$B$6,"SHIFT UP confirmed",IF(F35&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD35" s="18">
+        <f>IF($E35="",NA(),IF(OR($E35&gt;$B$6,$F35&gt;$B$6),MAX($E35,$F35),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10553,7 +12390,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="19" t="n">
         <v>471</v>
       </c>
       <c r="C36" s="15">
@@ -10584,6 +12421,10 @@
         <f>IF(E36="","",IF(E36&gt;$B$6,"SHIFT UP confirmed",IF(F36&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD36" s="18">
+        <f>IF($E36="",NA(),IF(OR($E36&gt;$B$6,$F36&gt;$B$6),MAX($E36,$F36),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10591,7 +12432,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="19" t="n">
         <v>455</v>
       </c>
       <c r="C37" s="15">
@@ -10622,6 +12463,10 @@
         <f>IF(E37="","",IF(E37&gt;$B$6,"SHIFT UP confirmed",IF(F37&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD37" s="18">
+        <f>IF($E37="",NA(),IF(OR($E37&gt;$B$6,$F37&gt;$B$6),MAX($E37,$F37),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10629,7 +12474,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n">
+      <c r="B38" s="19" t="n">
         <v>468</v>
       </c>
       <c r="C38" s="15">
@@ -10660,6 +12505,10 @@
         <f>IF(E38="","",IF(E38&gt;$B$6,"SHIFT UP confirmed",IF(F38&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="AD38" s="18">
+        <f>IF($E38="",NA(),IF(OR($E38&gt;$B$6,$F38&gt;$B$6),MAX($E38,$F38),NA()))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10667,7 +12516,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="18" t="n">
+      <c r="B39" s="19" t="n">
         <v>460</v>
       </c>
       <c r="C39" s="15">
@@ -10696,6 +12545,10 @@
       </c>
       <c r="I39" s="17">
         <f>IF(E39="","",IF(E39&gt;$B$6,"SHIFT UP confirmed",IF(F39&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
+        <v/>
+      </c>
+      <c r="AD39" s="18">
+        <f>IF($E39="",NA(),IF(OR($E39&gt;$B$6,$F39&gt;$B$6),MAX($E39,$F39),NA()))</f>
         <v/>
       </c>
     </row>
@@ -10723,7 +12576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:AG37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10734,6 +12587,10 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -10810,7 +12667,7 @@
           <t>Transformed mean</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>AVERAGE(C14:C37)</f>
         <v/>
       </c>
@@ -10826,7 +12683,7 @@
           <t>Transformed MR-bar</t>
         </is>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>AVERAGE(D15:D37)</f>
         <v/>
       </c>
@@ -10837,7 +12694,7 @@
           <t>t-chart UCL / LCL (days)</t>
         </is>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="22">
         <f>TEXT((B7+2.66*B8)^3.6,"#,##0.0")&amp;"  /  "&amp;TEXT(MAX(0,(B7-2.66*B8))^3.6,"#,##0.0")</f>
         <v/>
       </c>
@@ -10944,6 +12801,26 @@
           <t>g median</t>
         </is>
       </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>out of control</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>8 in a row one side (transformed)</t>
+        </is>
+      </c>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>above the g UCL</t>
+        </is>
+      </c>
+      <c r="AG13" s="5" t="inlineStr">
+        <is>
+          <t>8 in a row above the median</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10951,21 +12828,21 @@
           <t>Incident 1</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <f>IF(B14="","",B14^(1/3.6))</f>
         <v/>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <f>IF(B14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="24" t="n">
         <v>12800</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <f>IF(F14="","",$B$10)</f>
         <v/>
       </c>
@@ -10973,24 +12850,40 @@
         <f>IF(B14="","",IF(C14&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C14&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J14" s="33">
+      <c r="J14" s="34">
         <f>IF(B14="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K14" s="33">
+      <c r="K14" s="34">
         <f>IF(B14="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L14" s="33">
+      <c r="L14" s="34">
         <f>IF(B14="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M14" s="34">
+      <c r="M14" s="35">
         <f>IF(F14="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="35">
         <f>IF(F14="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD14" s="18">
+        <f>IF($B14="",NA(),IF(OR($C14&gt;$B$7+2.66*$B$8,$C14&lt;$B$7-2.66*$B$8),$B14,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE14" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF14" s="18">
+        <f>IF($F14="",NA(),IF($F14&gt;$M14,$F14,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG14" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -11000,25 +12893,25 @@
           <t>Incident 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <f>IF(B15="","",B15^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <f>IF(COUNT(C14:C15)=2,ABS(C15-C14),"")</f>
         <v/>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <f>IF(B15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="27" t="n">
         <v>8400</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="33">
         <f>IF(F15="","",$B$10)</f>
         <v/>
       </c>
@@ -11026,24 +12919,40 @@
         <f>IF(B15="","",IF(C15&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C15&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J15" s="33">
+      <c r="J15" s="34">
         <f>IF(B15="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K15" s="33">
+      <c r="K15" s="34">
         <f>IF(B15="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L15" s="33">
+      <c r="L15" s="34">
         <f>IF(B15="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M15" s="34">
+      <c r="M15" s="35">
         <f>IF(F15="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N15" s="34">
+      <c r="N15" s="35">
         <f>IF(F15="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD15" s="18">
+        <f>IF($B15="",NA(),IF(OR($C15&gt;$B$7+2.66*$B$8,$C15&lt;$B$7-2.66*$B$8),$B15,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE15" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF15" s="18">
+        <f>IF($F15="",NA(),IF($F15&gt;$M15,$F15,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG15" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -11053,25 +12962,25 @@
           <t>Incident 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <f>IF(B16="","",B16^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <f>IF(COUNT(C15:C16)=2,ABS(C16-C15),"")</f>
         <v/>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>IF(B16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="27" t="n">
         <v>21600</v>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="33">
         <f>IF(F16="","",$B$10)</f>
         <v/>
       </c>
@@ -11079,24 +12988,40 @@
         <f>IF(B16="","",IF(C16&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C16&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J16" s="33">
+      <c r="J16" s="34">
         <f>IF(B16="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K16" s="33">
+      <c r="K16" s="34">
         <f>IF(B16="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L16" s="33">
+      <c r="L16" s="34">
         <f>IF(B16="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="35">
         <f>IF(F16="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N16" s="34">
+      <c r="N16" s="35">
         <f>IF(F16="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD16" s="18">
+        <f>IF($B16="",NA(),IF(OR($C16&gt;$B$7+2.66*$B$8,$C16&lt;$B$7-2.66*$B$8),$B16,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE16" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF16" s="18">
+        <f>IF($F16="",NA(),IF($F16&gt;$M16,$F16,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG16" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -11106,25 +13031,25 @@
           <t>Incident 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <f>IF(B17="","",B17^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="25">
         <f>IF(COUNT(C16:C17)=2,ABS(C17-C16),"")</f>
         <v/>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="25">
         <f>IF(B17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="27" t="n">
         <v>29800</v>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="33">
         <f>IF(F17="","",$B$10)</f>
         <v/>
       </c>
@@ -11132,24 +13057,40 @@
         <f>IF(B17="","",IF(C17&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C17&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J17" s="33">
+      <c r="J17" s="34">
         <f>IF(B17="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K17" s="33">
+      <c r="K17" s="34">
         <f>IF(B17="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L17" s="33">
+      <c r="L17" s="34">
         <f>IF(B17="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M17" s="34">
+      <c r="M17" s="35">
         <f>IF(F17="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N17" s="34">
+      <c r="N17" s="35">
         <f>IF(F17="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD17" s="18">
+        <f>IF($B17="",NA(),IF(OR($C17&gt;$B$7+2.66*$B$8,$C17&lt;$B$7-2.66*$B$8),$B17,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE17" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF17" s="18">
+        <f>IF($F17="",NA(),IF($F17&gt;$M17,$F17,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG17" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -11159,25 +13100,25 @@
           <t>Incident 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="25">
         <f>IF(B18="","",B18^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="25">
         <f>IF(COUNT(C17:C18)=2,ABS(C18-C17),"")</f>
         <v/>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="25">
         <f>IF(B18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="27" t="n">
         <v>17400</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="33">
         <f>IF(F18="","",$B$10)</f>
         <v/>
       </c>
@@ -11185,24 +13126,40 @@
         <f>IF(B18="","",IF(C18&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C18&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J18" s="33">
+      <c r="J18" s="34">
         <f>IF(B18="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K18" s="33">
+      <c r="K18" s="34">
         <f>IF(B18="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L18" s="33">
+      <c r="L18" s="34">
         <f>IF(B18="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M18" s="34">
+      <c r="M18" s="35">
         <f>IF(F18="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N18" s="34">
+      <c r="N18" s="35">
         <f>IF(F18="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD18" s="18">
+        <f>IF($B18="",NA(),IF(OR($C18&gt;$B$7+2.66*$B$8,$C18&lt;$B$7-2.66*$B$8),$B18,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE18" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF18" s="18">
+        <f>IF($F18="",NA(),IF($F18&gt;$M18,$F18,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG18" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -11212,25 +13169,25 @@
           <t>Incident 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>27</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <f>IF(B19="","",B19^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="25">
         <f>IF(COUNT(C18:C19)=2,ABS(C19-C18),"")</f>
         <v/>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="25">
         <f>IF(B19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="27" t="n">
         <v>26100</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="33">
         <f>IF(F19="","",$B$10)</f>
         <v/>
       </c>
@@ -11238,24 +13195,40 @@
         <f>IF(B19="","",IF(C19&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C19&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J19" s="33">
+      <c r="J19" s="34">
         <f>IF(B19="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K19" s="33">
+      <c r="K19" s="34">
         <f>IF(B19="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L19" s="33">
+      <c r="L19" s="34">
         <f>IF(B19="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="35">
         <f>IF(F19="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N19" s="34">
+      <c r="N19" s="35">
         <f>IF(F19="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD19" s="18">
+        <f>IF($B19="",NA(),IF(OR($C19&gt;$B$7+2.66*$B$8,$C19&lt;$B$7-2.66*$B$8),$B19,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE19" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF19" s="18">
+        <f>IF($F19="",NA(),IF($F19&gt;$M19,$F19,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG19" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -11265,25 +13238,25 @@
           <t>Incident 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>41</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="25">
         <f>IF(B20="","",B20^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="25">
         <f>IF(COUNT(C19:C20)=2,ABS(C20-C19),"")</f>
         <v/>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="25">
         <f>IF(B20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="27" t="n">
         <v>39900</v>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="33">
         <f>IF(F20="","",$B$10)</f>
         <v/>
       </c>
@@ -11291,24 +13264,40 @@
         <f>IF(B20="","",IF(C20&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C20&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J20" s="33">
+      <c r="J20" s="34">
         <f>IF(B20="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K20" s="33">
+      <c r="K20" s="34">
         <f>IF(B20="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L20" s="33">
+      <c r="L20" s="34">
         <f>IF(B20="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="35">
         <f>IF(F20="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="35">
         <f>IF(F20="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD20" s="18">
+        <f>IF($B20="",NA(),IF(OR($C20&gt;$B$7+2.66*$B$8,$C20&lt;$B$7-2.66*$B$8),$B20,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE20" s="18">
+        <f>NA()</f>
+        <v/>
+      </c>
+      <c r="AF20" s="18">
+        <f>IF($F20="",NA(),IF($F20&gt;$M20,$F20,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG20" s="18">
+        <f>NA()</f>
         <v/>
       </c>
     </row>
@@ -11318,25 +13307,25 @@
           <t>Incident 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <f>IF(B21="","",B21^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="25">
         <f>IF(COUNT(C20:C21)=2,ABS(C21-C20),"")</f>
         <v/>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <f>IF(B21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="27" t="n">
         <v>11200</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <f>IF(F21="","",$B$10)</f>
         <v/>
       </c>
@@ -11344,24 +13333,40 @@
         <f>IF(B21="","",IF(C21&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C21&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="34">
         <f>IF(B21="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K21" s="33">
+      <c r="K21" s="34">
         <f>IF(B21="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="34">
         <f>IF(B21="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="35">
         <f>IF(F21="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="35">
         <f>IF(F21="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD21" s="18">
+        <f>IF($B21="",NA(),IF(OR($C21&gt;$B$7+2.66*$B$8,$C21&lt;$B$7-2.66*$B$8),$B21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE21" s="18">
+        <f>IF(COUNT($C14:$C21)&lt;8,NA(),IF(OR(MIN($C14:$C21)&gt;$B$7,MAX($C14:$C21)&lt;$B$7),$B21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF21" s="18">
+        <f>IF($F21="",NA(),IF($F21&gt;$M21,$F21,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG21" s="18">
+        <f>IF(COUNT($F14:$F21)&lt;8,NA(),IF(MIN($F14:$F21)&gt;$N21,$F21,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11371,25 +13376,25 @@
           <t>Incident 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="25">
         <f>IF(B22="","",B22^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="25">
         <f>IF(COUNT(C21:C22)=2,ABS(C22-C21),"")</f>
         <v/>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="25">
         <f>IF(B22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="27" t="n">
         <v>33500</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <f>IF(F22="","",$B$10)</f>
         <v/>
       </c>
@@ -11397,24 +13402,40 @@
         <f>IF(B22="","",IF(C22&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C22&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="34">
         <f>IF(B22="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K22" s="33">
+      <c r="K22" s="34">
         <f>IF(B22="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="34">
         <f>IF(B22="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M22" s="34">
+      <c r="M22" s="35">
         <f>IF(F22="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N22" s="34">
+      <c r="N22" s="35">
         <f>IF(F22="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD22" s="18">
+        <f>IF($B22="",NA(),IF(OR($C22&gt;$B$7+2.66*$B$8,$C22&lt;$B$7-2.66*$B$8),$B22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE22" s="18">
+        <f>IF(COUNT($C15:$C22)&lt;8,NA(),IF(OR(MIN($C15:$C22)&gt;$B$7,MAX($C15:$C22)&lt;$B$7),$B22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF22" s="18">
+        <f>IF($F22="",NA(),IF($F22&gt;$M22,$F22,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG22" s="18">
+        <f>IF(COUNT($F15:$F22)&lt;8,NA(),IF(MIN($F15:$F22)&gt;$N22,$F22,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11424,25 +13445,25 @@
           <t>Incident 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="25">
         <f>IF(B23="","",B23^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="25">
         <f>IF(COUNT(C22:C23)=2,ABS(C23-C22),"")</f>
         <v/>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <f>IF(B23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="27" t="n">
         <v>23100</v>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="33">
         <f>IF(F23="","",$B$10)</f>
         <v/>
       </c>
@@ -11450,24 +13471,40 @@
         <f>IF(B23="","",IF(C23&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C23&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J23" s="33">
+      <c r="J23" s="34">
         <f>IF(B23="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K23" s="33">
+      <c r="K23" s="34">
         <f>IF(B23="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L23" s="33">
+      <c r="L23" s="34">
         <f>IF(B23="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="35">
         <f>IF(F23="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N23" s="34">
+      <c r="N23" s="35">
         <f>IF(F23="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD23" s="18">
+        <f>IF($B23="",NA(),IF(OR($C23&gt;$B$7+2.66*$B$8,$C23&lt;$B$7-2.66*$B$8),$B23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE23" s="18">
+        <f>IF(COUNT($C16:$C23)&lt;8,NA(),IF(OR(MIN($C16:$C23)&gt;$B$7,MAX($C16:$C23)&lt;$B$7),$B23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF23" s="18">
+        <f>IF($F23="",NA(),IF($F23&gt;$M23,$F23,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG23" s="18">
+        <f>IF(COUNT($F16:$F23)&lt;8,NA(),IF(MIN($F16:$F23)&gt;$N23,$F23,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11477,25 +13514,25 @@
           <t>Incident 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>48</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="25">
         <f>IF(B24="","",B24^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="25">
         <f>IF(COUNT(C23:C24)=2,ABS(C24-C23),"")</f>
         <v/>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="25">
         <f>IF(B24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="27" t="n">
         <v>46800</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <f>IF(F24="","",$B$10)</f>
         <v/>
       </c>
@@ -11503,24 +13540,40 @@
         <f>IF(B24="","",IF(C24&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C24&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J24" s="33">
+      <c r="J24" s="34">
         <f>IF(B24="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K24" s="33">
+      <c r="K24" s="34">
         <f>IF(B24="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="34">
         <f>IF(B24="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="35">
         <f>IF(F24="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N24" s="34">
+      <c r="N24" s="35">
         <f>IF(F24="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD24" s="18">
+        <f>IF($B24="",NA(),IF(OR($C24&gt;$B$7+2.66*$B$8,$C24&lt;$B$7-2.66*$B$8),$B24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE24" s="18">
+        <f>IF(COUNT($C17:$C24)&lt;8,NA(),IF(OR(MIN($C17:$C24)&gt;$B$7,MAX($C17:$C24)&lt;$B$7),$B24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF24" s="18">
+        <f>IF($F24="",NA(),IF($F24&gt;$M24,$F24,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG24" s="18">
+        <f>IF(COUNT($F17:$F24)&lt;8,NA(),IF(MIN($F17:$F24)&gt;$N24,$F24,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11530,25 +13583,25 @@
           <t>Incident 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="25">
         <f>IF(B25="","",B25^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="25">
         <f>IF(COUNT(C24:C25)=2,ABS(C25-C24),"")</f>
         <v/>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="25">
         <f>IF(B25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="27" t="n">
         <v>18300</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <f>IF(F25="","",$B$10)</f>
         <v/>
       </c>
@@ -11556,24 +13609,40 @@
         <f>IF(B25="","",IF(C25&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C25&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="34">
         <f>IF(B25="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K25" s="33">
+      <c r="K25" s="34">
         <f>IF(B25="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="34">
         <f>IF(B25="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M25" s="34">
+      <c r="M25" s="35">
         <f>IF(F25="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N25" s="34">
+      <c r="N25" s="35">
         <f>IF(F25="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD25" s="18">
+        <f>IF($B25="",NA(),IF(OR($C25&gt;$B$7+2.66*$B$8,$C25&lt;$B$7-2.66*$B$8),$B25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE25" s="18">
+        <f>IF(COUNT($C18:$C25)&lt;8,NA(),IF(OR(MIN($C18:$C25)&gt;$B$7,MAX($C18:$C25)&lt;$B$7),$B25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF25" s="18">
+        <f>IF($F25="",NA(),IF($F25&gt;$M25,$F25,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG25" s="18">
+        <f>IF(COUNT($F18:$F25)&lt;8,NA(),IF(MIN($F18:$F25)&gt;$N25,$F25,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11583,25 +13652,25 @@
           <t>Incident 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>33</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="25">
         <f>IF(B26="","",B26^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="25">
         <f>IF(COUNT(C25:C26)=2,ABS(C26-C25),"")</f>
         <v/>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="25">
         <f>IF(B26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="27" t="n">
         <v>31700</v>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="33">
         <f>IF(F26="","",$B$10)</f>
         <v/>
       </c>
@@ -11609,24 +13678,40 @@
         <f>IF(B26="","",IF(C26&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C26&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J26" s="33">
+      <c r="J26" s="34">
         <f>IF(B26="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K26" s="33">
+      <c r="K26" s="34">
         <f>IF(B26="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L26" s="33">
+      <c r="L26" s="34">
         <f>IF(B26="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="35">
         <f>IF(F26="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="35">
         <f>IF(F26="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD26" s="18">
+        <f>IF($B26="",NA(),IF(OR($C26&gt;$B$7+2.66*$B$8,$C26&lt;$B$7-2.66*$B$8),$B26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE26" s="18">
+        <f>IF(COUNT($C19:$C26)&lt;8,NA(),IF(OR(MIN($C19:$C26)&gt;$B$7,MAX($C19:$C26)&lt;$B$7),$B26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF26" s="18">
+        <f>IF($F26="",NA(),IF($F26&gt;$M26,$F26,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG26" s="18">
+        <f>IF(COUNT($F19:$F26)&lt;8,NA(),IF(MIN($F19:$F26)&gt;$N26,$F26,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11636,25 +13721,25 @@
           <t>Incident 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <f>IF(B27="","",B27^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="25">
         <f>IF(COUNT(C26:C27)=2,ABS(C27-C26),"")</f>
         <v/>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="25">
         <f>IF(B27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="27" t="n">
         <v>25400</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <f>IF(F27="","",$B$10)</f>
         <v/>
       </c>
@@ -11662,24 +13747,40 @@
         <f>IF(B27="","",IF(C27&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C27&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <f>IF(B27="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <f>IF(B27="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <f>IF(B27="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="35">
         <f>IF(F27="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <f>IF(F27="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD27" s="18">
+        <f>IF($B27="",NA(),IF(OR($C27&gt;$B$7+2.66*$B$8,$C27&lt;$B$7-2.66*$B$8),$B27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE27" s="18">
+        <f>IF(COUNT($C20:$C27)&lt;8,NA(),IF(OR(MIN($C20:$C27)&gt;$B$7,MAX($C20:$C27)&lt;$B$7),$B27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF27" s="18">
+        <f>IF($F27="",NA(),IF($F27&gt;$M27,$F27,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG27" s="18">
+        <f>IF(COUNT($F20:$F27)&lt;8,NA(),IF(MIN($F20:$F27)&gt;$N27,$F27,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11689,25 +13790,25 @@
           <t>Incident 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>52</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="25">
         <f>IF(B28="","",B28^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="25">
         <f>IF(COUNT(C27:C28)=2,ABS(C28-C27),"")</f>
         <v/>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="25">
         <f>IF(B28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="27" t="n">
         <v>50600</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <f>IF(F28="","",$B$10)</f>
         <v/>
       </c>
@@ -11715,24 +13816,40 @@
         <f>IF(B28="","",IF(C28&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C28&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <f>IF(B28="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <f>IF(B28="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <f>IF(B28="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="35">
         <f>IF(F28="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="35">
         <f>IF(F28="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD28" s="18">
+        <f>IF($B28="",NA(),IF(OR($C28&gt;$B$7+2.66*$B$8,$C28&lt;$B$7-2.66*$B$8),$B28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE28" s="18">
+        <f>IF(COUNT($C21:$C28)&lt;8,NA(),IF(OR(MIN($C21:$C28)&gt;$B$7,MAX($C21:$C28)&lt;$B$7),$B28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF28" s="18">
+        <f>IF($F28="",NA(),IF($F28&gt;$M28,$F28,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG28" s="18">
+        <f>IF(COUNT($F21:$F28)&lt;8,NA(),IF(MIN($F21:$F28)&gt;$N28,$F28,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11742,25 +13859,25 @@
           <t>Incident 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="25">
         <f>IF(B29="","",B29^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="25">
         <f>IF(COUNT(C28:C29)=2,ABS(C29-C28),"")</f>
         <v/>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="25">
         <f>IF(B29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="27" t="n">
         <v>20200</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="33">
         <f>IF(F29="","",$B$10)</f>
         <v/>
       </c>
@@ -11768,24 +13885,40 @@
         <f>IF(B29="","",IF(C29&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C29&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J29" s="33">
+      <c r="J29" s="34">
         <f>IF(B29="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K29" s="33">
+      <c r="K29" s="34">
         <f>IF(B29="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L29" s="33">
+      <c r="L29" s="34">
         <f>IF(B29="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M29" s="34">
+      <c r="M29" s="35">
         <f>IF(F29="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N29" s="34">
+      <c r="N29" s="35">
         <f>IF(F29="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD29" s="18">
+        <f>IF($B29="",NA(),IF(OR($C29&gt;$B$7+2.66*$B$8,$C29&lt;$B$7-2.66*$B$8),$B29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE29" s="18">
+        <f>IF(COUNT($C22:$C29)&lt;8,NA(),IF(OR(MIN($C22:$C29)&gt;$B$7,MAX($C22:$C29)&lt;$B$7),$B29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF29" s="18">
+        <f>IF($F29="",NA(),IF($F29&gt;$M29,$F29,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG29" s="18">
+        <f>IF(COUNT($F22:$F29)&lt;8,NA(),IF(MIN($F22:$F29)&gt;$N29,$F29,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11795,25 +13928,25 @@
           <t>Incident 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="25">
         <f>IF(B30="","",B30^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="25">
         <f>IF(COUNT(C29:C30)=2,ABS(C30-C29),"")</f>
         <v/>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="25">
         <f>IF(B30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="27" t="n">
         <v>36900</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="33">
         <f>IF(F30="","",$B$10)</f>
         <v/>
       </c>
@@ -11821,24 +13954,40 @@
         <f>IF(B30="","",IF(C30&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C30&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <f>IF(B30="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <f>IF(B30="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <f>IF(B30="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <f>IF(F30="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N30" s="34">
+      <c r="N30" s="35">
         <f>IF(F30="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD30" s="18">
+        <f>IF($B30="",NA(),IF(OR($C30&gt;$B$7+2.66*$B$8,$C30&lt;$B$7-2.66*$B$8),$B30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE30" s="18">
+        <f>IF(COUNT($C23:$C30)&lt;8,NA(),IF(OR(MIN($C23:$C30)&gt;$B$7,MAX($C23:$C30)&lt;$B$7),$B30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF30" s="18">
+        <f>IF($F30="",NA(),IF($F30&gt;$M30,$F30,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG30" s="18">
+        <f>IF(COUNT($F23:$F30)&lt;8,NA(),IF(MIN($F23:$F30)&gt;$N30,$F30,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11848,25 +13997,25 @@
           <t>Incident 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <f>IF(B31="","",B31^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="25">
         <f>IF(COUNT(C30:C31)=2,ABS(C31-C30),"")</f>
         <v/>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="25">
         <f>IF(B31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="27" t="n">
         <v>27800</v>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="33">
         <f>IF(F31="","",$B$10)</f>
         <v/>
       </c>
@@ -11874,24 +14023,40 @@
         <f>IF(B31="","",IF(C31&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C31&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="34">
         <f>IF(B31="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="34">
         <f>IF(B31="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="34">
         <f>IF(B31="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="35">
         <f>IF(F31="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="35">
         <f>IF(F31="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD31" s="18">
+        <f>IF($B31="",NA(),IF(OR($C31&gt;$B$7+2.66*$B$8,$C31&lt;$B$7-2.66*$B$8),$B31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE31" s="18">
+        <f>IF(COUNT($C24:$C31)&lt;8,NA(),IF(OR(MIN($C24:$C31)&gt;$B$7,MAX($C24:$C31)&lt;$B$7),$B31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF31" s="18">
+        <f>IF($F31="",NA(),IF($F31&gt;$M31,$F31,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG31" s="18">
+        <f>IF(COUNT($F24:$F31)&lt;8,NA(),IF(MIN($F24:$F31)&gt;$N31,$F31,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11901,25 +14066,25 @@
           <t>Incident 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>44</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="25">
         <f>IF(B32="","",B32^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="25">
         <f>IF(COUNT(C31:C32)=2,ABS(C32-C31),"")</f>
         <v/>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="25">
         <f>IF(B32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="27" t="n">
         <v>43100</v>
       </c>
-      <c r="G32" s="32">
+      <c r="G32" s="33">
         <f>IF(F32="","",$B$10)</f>
         <v/>
       </c>
@@ -11927,24 +14092,40 @@
         <f>IF(B32="","",IF(C32&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C32&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J32" s="33">
+      <c r="J32" s="34">
         <f>IF(B32="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K32" s="33">
+      <c r="K32" s="34">
         <f>IF(B32="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L32" s="33">
+      <c r="L32" s="34">
         <f>IF(B32="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M32" s="34">
+      <c r="M32" s="35">
         <f>IF(F32="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N32" s="34">
+      <c r="N32" s="35">
         <f>IF(F32="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD32" s="18">
+        <f>IF($B32="",NA(),IF(OR($C32&gt;$B$7+2.66*$B$8,$C32&lt;$B$7-2.66*$B$8),$B32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE32" s="18">
+        <f>IF(COUNT($C25:$C32)&lt;8,NA(),IF(OR(MIN($C25:$C32)&gt;$B$7,MAX($C25:$C32)&lt;$B$7),$B32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF32" s="18">
+        <f>IF($F32="",NA(),IF($F32&gt;$M32,$F32,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG32" s="18">
+        <f>IF(COUNT($F25:$F32)&lt;8,NA(),IF(MIN($F25:$F32)&gt;$N32,$F32,NA()))</f>
         <v/>
       </c>
     </row>
@@ -11954,25 +14135,25 @@
           <t>Incident 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="25">
         <f>IF(B33="","",B33^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="25">
         <f>IF(COUNT(C32:C33)=2,ABS(C33-C32),"")</f>
         <v/>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="25">
         <f>IF(B33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="27" t="n">
         <v>34600</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <f>IF(F33="","",$B$10)</f>
         <v/>
       </c>
@@ -11980,24 +14161,40 @@
         <f>IF(B33="","",IF(C33&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C33&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="34">
         <f>IF(B33="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="34">
         <f>IF(B33="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L33" s="33">
+      <c r="L33" s="34">
         <f>IF(B33="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="35">
         <f>IF(F33="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="35">
         <f>IF(F33="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD33" s="18">
+        <f>IF($B33="",NA(),IF(OR($C33&gt;$B$7+2.66*$B$8,$C33&lt;$B$7-2.66*$B$8),$B33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE33" s="18">
+        <f>IF(COUNT($C26:$C33)&lt;8,NA(),IF(OR(MIN($C26:$C33)&gt;$B$7,MAX($C26:$C33)&lt;$B$7),$B33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF33" s="18">
+        <f>IF($F33="",NA(),IF($F33&gt;$M33,$F33,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG33" s="18">
+        <f>IF(COUNT($F26:$F33)&lt;8,NA(),IF(MIN($F26:$F33)&gt;$N33,$F33,NA()))</f>
         <v/>
       </c>
     </row>
@@ -12007,25 +14204,25 @@
           <t>Incident 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="25">
         <f>IF(B34="","",B34^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="25">
         <f>IF(COUNT(C33:C34)=2,ABS(C34-C33),"")</f>
         <v/>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="25">
         <f>IF(B34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="27" t="n">
         <v>56900</v>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="33">
         <f>IF(F34="","",$B$10)</f>
         <v/>
       </c>
@@ -12033,24 +14230,40 @@
         <f>IF(B34="","",IF(C34&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C34&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J34" s="33">
+      <c r="J34" s="34">
         <f>IF(B34="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K34" s="33">
+      <c r="K34" s="34">
         <f>IF(B34="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <f>IF(B34="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="35">
         <f>IF(F34="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N34" s="34">
+      <c r="N34" s="35">
         <f>IF(F34="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD34" s="18">
+        <f>IF($B34="",NA(),IF(OR($C34&gt;$B$7+2.66*$B$8,$C34&lt;$B$7-2.66*$B$8),$B34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE34" s="18">
+        <f>IF(COUNT($C27:$C34)&lt;8,NA(),IF(OR(MIN($C27:$C34)&gt;$B$7,MAX($C27:$C34)&lt;$B$7),$B34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF34" s="18">
+        <f>IF($F34="",NA(),IF($F34&gt;$M34,$F34,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG34" s="18">
+        <f>IF(COUNT($F27:$F34)&lt;8,NA(),IF(MIN($F27:$F34)&gt;$N34,$F34,NA()))</f>
         <v/>
       </c>
     </row>
@@ -12060,25 +14273,25 @@
           <t>Incident 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="25">
         <f>IF(B35="","",B35^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="25">
         <f>IF(COUNT(C34:C35)=2,ABS(C35-C34),"")</f>
         <v/>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="25">
         <f>IF(B35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="27" t="n">
         <v>29900</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="33">
         <f>IF(F35="","",$B$10)</f>
         <v/>
       </c>
@@ -12086,24 +14299,40 @@
         <f>IF(B35="","",IF(C35&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C35&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="34">
         <f>IF(B35="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K35" s="33">
+      <c r="K35" s="34">
         <f>IF(B35="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L35" s="33">
+      <c r="L35" s="34">
         <f>IF(B35="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <f>IF(F35="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="35">
         <f>IF(F35="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD35" s="18">
+        <f>IF($B35="",NA(),IF(OR($C35&gt;$B$7+2.66*$B$8,$C35&lt;$B$7-2.66*$B$8),$B35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE35" s="18">
+        <f>IF(COUNT($C28:$C35)&lt;8,NA(),IF(OR(MIN($C28:$C35)&gt;$B$7,MAX($C28:$C35)&lt;$B$7),$B35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF35" s="18">
+        <f>IF($F35="",NA(),IF($F35&gt;$M35,$F35,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG35" s="18">
+        <f>IF(COUNT($F28:$F35)&lt;8,NA(),IF(MIN($F28:$F35)&gt;$N35,$F35,NA()))</f>
         <v/>
       </c>
     </row>
@@ -12113,25 +14342,25 @@
           <t>Incident 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>47</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="25">
         <f>IF(B36="","",B36^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="25">
         <f>IF(COUNT(C35:C36)=2,ABS(C36-C35),"")</f>
         <v/>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="25">
         <f>IF(B36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="27" t="n">
         <v>45200</v>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="33">
         <f>IF(F36="","",$B$10)</f>
         <v/>
       </c>
@@ -12139,24 +14368,40 @@
         <f>IF(B36="","",IF(C36&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C36&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="34">
         <f>IF(B36="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K36" s="33">
+      <c r="K36" s="34">
         <f>IF(B36="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L36" s="33">
+      <c r="L36" s="34">
         <f>IF(B36="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="35">
         <f>IF(F36="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="35">
         <f>IF(F36="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD36" s="18">
+        <f>IF($B36="",NA(),IF(OR($C36&gt;$B$7+2.66*$B$8,$C36&lt;$B$7-2.66*$B$8),$B36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE36" s="18">
+        <f>IF(COUNT($C29:$C36)&lt;8,NA(),IF(OR(MIN($C29:$C36)&gt;$B$7,MAX($C29:$C36)&lt;$B$7),$B36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF36" s="18">
+        <f>IF($F36="",NA(),IF($F36&gt;$M36,$F36,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG36" s="18">
+        <f>IF(COUNT($F29:$F36)&lt;8,NA(),IF(MIN($F29:$F36)&gt;$N36,$F36,NA()))</f>
         <v/>
       </c>
     </row>
@@ -12166,25 +14411,25 @@
           <t>Incident 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="25">
         <f>IF(B37="","",B37^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="25">
         <f>IF(COUNT(C36:C37)=2,ABS(C37-C36),"")</f>
         <v/>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="25">
         <f>IF(B37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="27" t="n">
         <v>38400</v>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="33">
         <f>IF(F37="","",$B$10)</f>
         <v/>
       </c>
@@ -12192,24 +14437,40 @@
         <f>IF(B37="","",IF(C37&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C37&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J37" s="33">
+      <c r="J37" s="34">
         <f>IF(B37="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K37" s="33">
+      <c r="K37" s="34">
         <f>IF(B37="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L37" s="33">
+      <c r="L37" s="34">
         <f>IF(B37="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M37" s="34">
+      <c r="M37" s="35">
         <f>IF(F37="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N37" s="34">
+      <c r="N37" s="35">
         <f>IF(F37="","",MEDIAN($F$14:$F$37))</f>
+        <v/>
+      </c>
+      <c r="AD37" s="18">
+        <f>IF($B37="",NA(),IF(OR($C37&gt;$B$7+2.66*$B$8,$C37&lt;$B$7-2.66*$B$8),$B37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AE37" s="18">
+        <f>IF(COUNT($C30:$C37)&lt;8,NA(),IF(OR(MIN($C30:$C37)&gt;$B$7,MAX($C30:$C37)&lt;$B$7),$B37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AF37" s="18">
+        <f>IF($F37="",NA(),IF($F37&gt;$M37,$F37,NA()))</f>
+        <v/>
+      </c>
+      <c r="AG37" s="18">
+        <f>IF(COUNT($F30:$F37)&lt;8,NA(),IF(MIN($F30:$F37)&gt;$N37,$F37,NA()))</f>
         <v/>
       </c>
     </row>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -526,8 +526,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="480.6867971014493"/>
-          <min val="351.8965362318841"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -810,8 +808,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="133760"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1021,8 +1017,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="72.49899130434784"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1305,8 +1299,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7986299651466527"/>
-          <min val="0.6419525892095937"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1590,8 +1582,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.1001696681397611"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1874,8 +1864,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="434.94"/>
-          <min val="380.46"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2119,8 +2107,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="84.8771"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2364,8 +2350,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="457.6"/>
-          <min val="390.4"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2579,8 +2563,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="27.70511090047391"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -2863,8 +2845,6 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="110.8596101464608"/>
-          <min val="0"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -721,40 +721,6 @@
         <ser>
           <idx val="4"/>
           <order val="4"/>
-          <tx>
-            <v>Median</v>
-          </tx>
-          <spPr>
-            <a:ln w="28000">
-              <a:solidFill>
-                <a:srgbClr val="B45309"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'t and g (rare events)'!$A$14:$A$37</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'t and g (rare events)'!$N$14:$N$37</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
           <tx>
             <v>UCL</v>
           </tx>
@@ -2868,9 +2834,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>33</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="2880000"/>
@@ -2890,7 +2856,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>33</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>
@@ -2917,9 +2883,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>14</col>
+      <col>32</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="2880000"/>
@@ -2944,9 +2910,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>14</col>
+      <col>32</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="2880000"/>
@@ -2971,9 +2937,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>33</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="2880000"/>
@@ -2993,7 +2959,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>33</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>
@@ -3020,9 +2986,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>31</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="2880000"/>
@@ -3047,9 +3013,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>31</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="2880000"/>
@@ -3074,9 +3040,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>13</col>
+      <col>34</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6840000" cy="2880000"/>
@@ -3096,7 +3062,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>34</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -519,8 +519,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -767,8 +767,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="4"/>
+        <tickMarkSkip val="4"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -976,8 +976,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1258,8 +1258,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -1823,8 +1823,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2066,8 +2066,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2309,8 +2309,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2522,8 +2522,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="2"/>
+        <tickMarkSkip val="2"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -2804,8 +2804,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="4"/>
+        <tickMarkSkip val="4"/>
       </catAx>
       <valAx>
         <axId val="100"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -167,6 +167,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3682,6 +3685,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
@@ -3928,10 +3932,10 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Your data — one row per period, oldest first</t>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Your data — one row per period, oldest first  ·  Key: CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · MR = moving range, the gap between one point and the one before it</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -4016,7 +4020,7 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>408</v>
       </c>
       <c r="D14" s="17">
@@ -4039,22 +4043,22 @@
         <f>IF(B14="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <f>IF(B14="","",IF(OR(B14&gt;$B$9,B14&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="T14" s="20" t="n">
+      <c r="T14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="AD14" s="20">
+      <c r="AD14" s="21">
         <f>IF($B14="",NA(),IF(OR($B14&gt;$B$9,$B14&lt;$B$10),$B14,NA()))</f>
         <v/>
       </c>
-      <c r="AE14" s="20">
+      <c r="AE14" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF14" s="20">
+      <c r="AF14" s="21">
         <f>IF($C14="",NA(),IF($C14&gt;$B$11,$C14,NA()))</f>
         <v/>
       </c>
@@ -4065,7 +4069,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n">
+      <c r="B15" s="22" t="n">
         <v>415</v>
       </c>
       <c r="C15" s="17">
@@ -4092,22 +4096,22 @@
         <f>IF(B15="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <f>IF(B15="","",IF(OR(B15&gt;$B$9,B15&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="T15" s="20" t="n">
+      <c r="T15" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="AD15" s="20">
+      <c r="AD15" s="21">
         <f>IF($B15="",NA(),IF(OR($B15&gt;$B$9,$B15&lt;$B$10),$B15,NA()))</f>
         <v/>
       </c>
-      <c r="AE15" s="20">
+      <c r="AE15" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF15" s="20">
+      <c r="AF15" s="21">
         <f>IF($C15="",NA(),IF($C15&gt;$B$11,$C15,NA()))</f>
         <v/>
       </c>
@@ -4118,7 +4122,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n">
+      <c r="B16" s="22" t="n">
         <v>402</v>
       </c>
       <c r="C16" s="17">
@@ -4145,22 +4149,22 @@
         <f>IF(B16="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>IF(B16="","",IF(OR(B16&gt;$B$9,B16&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="T16" s="20" t="n">
+      <c r="T16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="AD16" s="20">
+      <c r="AD16" s="21">
         <f>IF($B16="",NA(),IF(OR($B16&gt;$B$9,$B16&lt;$B$10),$B16,NA()))</f>
         <v/>
       </c>
-      <c r="AE16" s="20">
+      <c r="AE16" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF16" s="20">
+      <c r="AF16" s="21">
         <f>IF($C16="",NA(),IF($C16&gt;$B$11,$C16,NA()))</f>
         <v/>
       </c>
@@ -4171,7 +4175,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n">
+      <c r="B17" s="22" t="n">
         <v>431</v>
       </c>
       <c r="C17" s="17">
@@ -4198,22 +4202,22 @@
         <f>IF(B17="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="20">
         <f>IF(B17="","",IF(OR(B17&gt;$B$9,B17&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="T17" s="20" t="n">
+      <c r="T17" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="AD17" s="20">
+      <c r="AD17" s="21">
         <f>IF($B17="",NA(),IF(OR($B17&gt;$B$9,$B17&lt;$B$10),$B17,NA()))</f>
         <v/>
       </c>
-      <c r="AE17" s="20">
+      <c r="AE17" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF17" s="20">
+      <c r="AF17" s="21">
         <f>IF($C17="",NA(),IF($C17&gt;$B$11,$C17,NA()))</f>
         <v/>
       </c>
@@ -4224,7 +4228,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n">
+      <c r="B18" s="22" t="n">
         <v>419</v>
       </c>
       <c r="C18" s="17">
@@ -4251,22 +4255,22 @@
         <f>IF(B18="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <f>IF(B18="","",IF(OR(B18&gt;$B$9,B18&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="T18" s="20" t="n">
+      <c r="T18" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="AD18" s="20">
+      <c r="AD18" s="21">
         <f>IF($B18="",NA(),IF(OR($B18&gt;$B$9,$B18&lt;$B$10),$B18,NA()))</f>
         <v/>
       </c>
-      <c r="AE18" s="20">
+      <c r="AE18" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF18" s="20">
+      <c r="AF18" s="21">
         <f>IF($C18="",NA(),IF($C18&gt;$B$11,$C18,NA()))</f>
         <v/>
       </c>
@@ -4277,7 +4281,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n">
+      <c r="B19" s="22" t="n">
         <v>396</v>
       </c>
       <c r="C19" s="17">
@@ -4304,22 +4308,22 @@
         <f>IF(B19="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <f>IF(B19="","",IF(OR(B19&gt;$B$9,B19&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="T19" s="20" t="n">
+      <c r="T19" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="AD19" s="20">
+      <c r="AD19" s="21">
         <f>IF($B19="",NA(),IF(OR($B19&gt;$B$9,$B19&lt;$B$10),$B19,NA()))</f>
         <v/>
       </c>
-      <c r="AE19" s="20">
+      <c r="AE19" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF19" s="20">
+      <c r="AF19" s="21">
         <f>IF($C19="",NA(),IF($C19&gt;$B$11,$C19,NA()))</f>
         <v/>
       </c>
@@ -4330,7 +4334,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="22" t="n">
         <v>424</v>
       </c>
       <c r="C20" s="17">
@@ -4357,22 +4361,22 @@
         <f>IF(B20="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="20">
         <f>IF(B20="","",IF(OR(B20&gt;$B$9,B20&lt;$B$10),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="T20" s="20" t="n">
+      <c r="T20" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="AD20" s="20">
+      <c r="AD20" s="21">
         <f>IF($B20="",NA(),IF(OR($B20&gt;$B$9,$B20&lt;$B$10),$B20,NA()))</f>
         <v/>
       </c>
-      <c r="AE20" s="20">
+      <c r="AE20" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF20" s="20">
+      <c r="AF20" s="21">
         <f>IF($C20="",NA(),IF($C20&gt;$B$11,$C20,NA()))</f>
         <v/>
       </c>
@@ -4383,7 +4387,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="22" t="n">
         <v>410</v>
       </c>
       <c r="C21" s="17">
@@ -4410,22 +4414,22 @@
         <f>IF(B21="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="20">
         <f>IF(B21="","",IF(OR(B21&gt;$B$9,B21&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B14:B21)=8,OR(MIN(B14:B21)&gt;$B$6,MAX(B14:B21)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T21" s="20" t="n">
+      <c r="T21" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="AD21" s="20">
+      <c r="AD21" s="21">
         <f>IF($B21="",NA(),IF(OR($B21&gt;$B$9,$B21&lt;$B$10),$B21,NA()))</f>
         <v/>
       </c>
-      <c r="AE21" s="20">
+      <c r="AE21" s="21">
         <f>IF(COUNT($B14:$B21)&lt;8,NA(),IF(OR(MIN($B14:$B21)&gt;$B$6,MAX($B14:$B21)&lt;$B$6),$B21,NA()))</f>
         <v/>
       </c>
-      <c r="AF21" s="20">
+      <c r="AF21" s="21">
         <f>IF($C21="",NA(),IF($C21&gt;$B$11,$C21,NA()))</f>
         <v/>
       </c>
@@ -4436,7 +4440,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="22" t="n">
         <v>438</v>
       </c>
       <c r="C22" s="17">
@@ -4463,22 +4467,22 @@
         <f>IF(B22="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="20">
         <f>IF(B22="","",IF(OR(B22&gt;$B$9,B22&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B15:B22)=8,OR(MIN(B15:B22)&gt;$B$6,MAX(B15:B22)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T22" s="20" t="n">
+      <c r="T22" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="21">
         <f>IF($B22="",NA(),IF(OR($B22&gt;$B$9,$B22&lt;$B$10),$B22,NA()))</f>
         <v/>
       </c>
-      <c r="AE22" s="20">
+      <c r="AE22" s="21">
         <f>IF(COUNT($B15:$B22)&lt;8,NA(),IF(OR(MIN($B15:$B22)&gt;$B$6,MAX($B15:$B22)&lt;$B$6),$B22,NA()))</f>
         <v/>
       </c>
-      <c r="AF22" s="20">
+      <c r="AF22" s="21">
         <f>IF($C22="",NA(),IF($C22&gt;$B$11,$C22,NA()))</f>
         <v/>
       </c>
@@ -4489,7 +4493,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="22" t="n">
         <v>405</v>
       </c>
       <c r="C23" s="17">
@@ -4516,22 +4520,22 @@
         <f>IF(B23="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="20">
         <f>IF(B23="","",IF(OR(B23&gt;$B$9,B23&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B16:B23)=8,OR(MIN(B16:B23)&gt;$B$6,MAX(B16:B23)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T23" s="20" t="n">
+      <c r="T23" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="AD23" s="20">
+      <c r="AD23" s="21">
         <f>IF($B23="",NA(),IF(OR($B23&gt;$B$9,$B23&lt;$B$10),$B23,NA()))</f>
         <v/>
       </c>
-      <c r="AE23" s="20">
+      <c r="AE23" s="21">
         <f>IF(COUNT($B16:$B23)&lt;8,NA(),IF(OR(MIN($B16:$B23)&gt;$B$6,MAX($B16:$B23)&lt;$B$6),$B23,NA()))</f>
         <v/>
       </c>
-      <c r="AF23" s="20">
+      <c r="AF23" s="21">
         <f>IF($C23="",NA(),IF($C23&gt;$B$11,$C23,NA()))</f>
         <v/>
       </c>
@@ -4542,7 +4546,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="22" t="n">
         <v>417</v>
       </c>
       <c r="C24" s="17">
@@ -4569,22 +4573,22 @@
         <f>IF(B24="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>IF(B24="","",IF(OR(B24&gt;$B$9,B24&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B17:B24)=8,OR(MIN(B17:B24)&gt;$B$6,MAX(B17:B24)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T24" s="20" t="n">
+      <c r="T24" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="AD24" s="20">
+      <c r="AD24" s="21">
         <f>IF($B24="",NA(),IF(OR($B24&gt;$B$9,$B24&lt;$B$10),$B24,NA()))</f>
         <v/>
       </c>
-      <c r="AE24" s="20">
+      <c r="AE24" s="21">
         <f>IF(COUNT($B17:$B24)&lt;8,NA(),IF(OR(MIN($B17:$B24)&gt;$B$6,MAX($B17:$B24)&lt;$B$6),$B24,NA()))</f>
         <v/>
       </c>
-      <c r="AF24" s="20">
+      <c r="AF24" s="21">
         <f>IF($C24="",NA(),IF($C24&gt;$B$11,$C24,NA()))</f>
         <v/>
       </c>
@@ -4595,7 +4599,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="22" t="n">
         <v>429</v>
       </c>
       <c r="C25" s="17">
@@ -4622,22 +4626,22 @@
         <f>IF(B25="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <f>IF(B25="","",IF(OR(B25&gt;$B$9,B25&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B18:B25)=8,OR(MIN(B18:B25)&gt;$B$6,MAX(B18:B25)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T25" s="20" t="n">
+      <c r="T25" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="AD25" s="20">
+      <c r="AD25" s="21">
         <f>IF($B25="",NA(),IF(OR($B25&gt;$B$9,$B25&lt;$B$10),$B25,NA()))</f>
         <v/>
       </c>
-      <c r="AE25" s="20">
+      <c r="AE25" s="21">
         <f>IF(COUNT($B18:$B25)&lt;8,NA(),IF(OR(MIN($B18:$B25)&gt;$B$6,MAX($B18:$B25)&lt;$B$6),$B25,NA()))</f>
         <v/>
       </c>
-      <c r="AF25" s="20">
+      <c r="AF25" s="21">
         <f>IF($C25="",NA(),IF($C25&gt;$B$11,$C25,NA()))</f>
         <v/>
       </c>
@@ -4648,7 +4652,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="22" t="n">
         <v>401</v>
       </c>
       <c r="C26" s="17">
@@ -4675,22 +4679,22 @@
         <f>IF(B26="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <f>IF(B26="","",IF(OR(B26&gt;$B$9,B26&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B19:B26)=8,OR(MIN(B19:B26)&gt;$B$6,MAX(B19:B26)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T26" s="20" t="n">
+      <c r="T26" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="AD26" s="20">
+      <c r="AD26" s="21">
         <f>IF($B26="",NA(),IF(OR($B26&gt;$B$9,$B26&lt;$B$10),$B26,NA()))</f>
         <v/>
       </c>
-      <c r="AE26" s="20">
+      <c r="AE26" s="21">
         <f>IF(COUNT($B19:$B26)&lt;8,NA(),IF(OR(MIN($B19:$B26)&gt;$B$6,MAX($B19:$B26)&lt;$B$6),$B26,NA()))</f>
         <v/>
       </c>
-      <c r="AF26" s="20">
+      <c r="AF26" s="21">
         <f>IF($C26="",NA(),IF($C26&gt;$B$11,$C26,NA()))</f>
         <v/>
       </c>
@@ -4701,7 +4705,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="22" t="n">
         <v>422</v>
       </c>
       <c r="C27" s="17">
@@ -4728,22 +4732,22 @@
         <f>IF(B27="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="20">
         <f>IF(B27="","",IF(OR(B27&gt;$B$9,B27&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B20:B27)=8,OR(MIN(B20:B27)&gt;$B$6,MAX(B20:B27)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T27" s="20" t="n">
+      <c r="T27" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="AD27" s="20">
+      <c r="AD27" s="21">
         <f>IF($B27="",NA(),IF(OR($B27&gt;$B$9,$B27&lt;$B$10),$B27,NA()))</f>
         <v/>
       </c>
-      <c r="AE27" s="20">
+      <c r="AE27" s="21">
         <f>IF(COUNT($B20:$B27)&lt;8,NA(),IF(OR(MIN($B20:$B27)&gt;$B$6,MAX($B20:$B27)&lt;$B$6),$B27,NA()))</f>
         <v/>
       </c>
-      <c r="AF27" s="20">
+      <c r="AF27" s="21">
         <f>IF($C27="",NA(),IF($C27&gt;$B$11,$C27,NA()))</f>
         <v/>
       </c>
@@ -4754,7 +4758,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
+      <c r="B28" s="22" t="n">
         <v>413</v>
       </c>
       <c r="C28" s="17">
@@ -4781,22 +4785,22 @@
         <f>IF(B28="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="20">
         <f>IF(B28="","",IF(OR(B28&gt;$B$9,B28&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B21:B28)=8,OR(MIN(B21:B28)&gt;$B$6,MAX(B21:B28)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T28" s="20" t="n">
+      <c r="T28" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="AD28" s="20">
+      <c r="AD28" s="21">
         <f>IF($B28="",NA(),IF(OR($B28&gt;$B$9,$B28&lt;$B$10),$B28,NA()))</f>
         <v/>
       </c>
-      <c r="AE28" s="20">
+      <c r="AE28" s="21">
         <f>IF(COUNT($B21:$B28)&lt;8,NA(),IF(OR(MIN($B21:$B28)&gt;$B$6,MAX($B21:$B28)&lt;$B$6),$B28,NA()))</f>
         <v/>
       </c>
-      <c r="AF28" s="20">
+      <c r="AF28" s="21">
         <f>IF($C28="",NA(),IF($C28&gt;$B$11,$C28,NA()))</f>
         <v/>
       </c>
@@ -4807,7 +4811,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n">
+      <c r="B29" s="22" t="n">
         <v>407</v>
       </c>
       <c r="C29" s="17">
@@ -4834,22 +4838,22 @@
         <f>IF(B29="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="20">
         <f>IF(B29="","",IF(OR(B29&gt;$B$9,B29&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B22:B29)=8,OR(MIN(B22:B29)&gt;$B$6,MAX(B22:B29)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T29" s="20" t="n">
+      <c r="T29" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="AD29" s="20">
+      <c r="AD29" s="21">
         <f>IF($B29="",NA(),IF(OR($B29&gt;$B$9,$B29&lt;$B$10),$B29,NA()))</f>
         <v/>
       </c>
-      <c r="AE29" s="20">
+      <c r="AE29" s="21">
         <f>IF(COUNT($B22:$B29)&lt;8,NA(),IF(OR(MIN($B22:$B29)&gt;$B$6,MAX($B22:$B29)&lt;$B$6),$B29,NA()))</f>
         <v/>
       </c>
-      <c r="AF29" s="20">
+      <c r="AF29" s="21">
         <f>IF($C29="",NA(),IF($C29&gt;$B$11,$C29,NA()))</f>
         <v/>
       </c>
@@ -4860,7 +4864,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
+      <c r="B30" s="22" t="n">
         <v>435</v>
       </c>
       <c r="C30" s="17">
@@ -4887,22 +4891,22 @@
         <f>IF(B30="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <f>IF(B30="","",IF(OR(B30&gt;$B$9,B30&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B23:B30)=8,OR(MIN(B23:B30)&gt;$B$6,MAX(B23:B30)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T30" s="20" t="n">
+      <c r="T30" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="AD30" s="20">
+      <c r="AD30" s="21">
         <f>IF($B30="",NA(),IF(OR($B30&gt;$B$9,$B30&lt;$B$10),$B30,NA()))</f>
         <v/>
       </c>
-      <c r="AE30" s="20">
+      <c r="AE30" s="21">
         <f>IF(COUNT($B23:$B30)&lt;8,NA(),IF(OR(MIN($B23:$B30)&gt;$B$6,MAX($B23:$B30)&lt;$B$6),$B30,NA()))</f>
         <v/>
       </c>
-      <c r="AF30" s="20">
+      <c r="AF30" s="21">
         <f>IF($C30="",NA(),IF($C30&gt;$B$11,$C30,NA()))</f>
         <v/>
       </c>
@@ -4913,7 +4917,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
+      <c r="B31" s="22" t="n">
         <v>398</v>
       </c>
       <c r="C31" s="17">
@@ -4940,22 +4944,22 @@
         <f>IF(B31="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="20">
         <f>IF(B31="","",IF(OR(B31&gt;$B$9,B31&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B24:B31)=8,OR(MIN(B24:B31)&gt;$B$6,MAX(B24:B31)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T31" s="20" t="n">
+      <c r="T31" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="AD31" s="20">
+      <c r="AD31" s="21">
         <f>IF($B31="",NA(),IF(OR($B31&gt;$B$9,$B31&lt;$B$10),$B31,NA()))</f>
         <v/>
       </c>
-      <c r="AE31" s="20">
+      <c r="AE31" s="21">
         <f>IF(COUNT($B24:$B31)&lt;8,NA(),IF(OR(MIN($B24:$B31)&gt;$B$6,MAX($B24:$B31)&lt;$B$6),$B31,NA()))</f>
         <v/>
       </c>
-      <c r="AF31" s="20">
+      <c r="AF31" s="21">
         <f>IF($C31="",NA(),IF($C31&gt;$B$11,$C31,NA()))</f>
         <v/>
       </c>
@@ -4966,7 +4970,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
+      <c r="B32" s="22" t="n">
         <v>420</v>
       </c>
       <c r="C32" s="17">
@@ -4993,22 +4997,22 @@
         <f>IF(B32="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="20">
         <f>IF(B32="","",IF(OR(B32&gt;$B$9,B32&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B25:B32)=8,OR(MIN(B25:B32)&gt;$B$6,MAX(B25:B32)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T32" s="20" t="n">
+      <c r="T32" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="AD32" s="20">
+      <c r="AD32" s="21">
         <f>IF($B32="",NA(),IF(OR($B32&gt;$B$9,$B32&lt;$B$10),$B32,NA()))</f>
         <v/>
       </c>
-      <c r="AE32" s="20">
+      <c r="AE32" s="21">
         <f>IF(COUNT($B25:$B32)&lt;8,NA(),IF(OR(MIN($B25:$B32)&gt;$B$6,MAX($B25:$B32)&lt;$B$6),$B32,NA()))</f>
         <v/>
       </c>
-      <c r="AF32" s="20">
+      <c r="AF32" s="21">
         <f>IF($C32="",NA(),IF($C32&gt;$B$11,$C32,NA()))</f>
         <v/>
       </c>
@@ -5019,7 +5023,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
+      <c r="B33" s="22" t="n">
         <v>411</v>
       </c>
       <c r="C33" s="17">
@@ -5046,22 +5050,22 @@
         <f>IF(B33="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="20">
         <f>IF(B33="","",IF(OR(B33&gt;$B$9,B33&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B26:B33)=8,OR(MIN(B26:B33)&gt;$B$6,MAX(B26:B33)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T33" s="20" t="n">
+      <c r="T33" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="AD33" s="20">
+      <c r="AD33" s="21">
         <f>IF($B33="",NA(),IF(OR($B33&gt;$B$9,$B33&lt;$B$10),$B33,NA()))</f>
         <v/>
       </c>
-      <c r="AE33" s="20">
+      <c r="AE33" s="21">
         <f>IF(COUNT($B26:$B33)&lt;8,NA(),IF(OR(MIN($B26:$B33)&gt;$B$6,MAX($B26:$B33)&lt;$B$6),$B33,NA()))</f>
         <v/>
       </c>
-      <c r="AF33" s="20">
+      <c r="AF33" s="21">
         <f>IF($C33="",NA(),IF($C33&gt;$B$11,$C33,NA()))</f>
         <v/>
       </c>
@@ -5072,7 +5076,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
+      <c r="B34" s="22" t="n">
         <v>442</v>
       </c>
       <c r="C34" s="17">
@@ -5099,22 +5103,22 @@
         <f>IF(B34="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="20">
         <f>IF(B34="","",IF(OR(B34&gt;$B$9,B34&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B27:B34)=8,OR(MIN(B27:B34)&gt;$B$6,MAX(B27:B34)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T34" s="20" t="n">
+      <c r="T34" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="21">
         <f>IF($B34="",NA(),IF(OR($B34&gt;$B$9,$B34&lt;$B$10),$B34,NA()))</f>
         <v/>
       </c>
-      <c r="AE34" s="20">
+      <c r="AE34" s="21">
         <f>IF(COUNT($B27:$B34)&lt;8,NA(),IF(OR(MIN($B27:$B34)&gt;$B$6,MAX($B27:$B34)&lt;$B$6),$B34,NA()))</f>
         <v/>
       </c>
-      <c r="AF34" s="20">
+      <c r="AF34" s="21">
         <f>IF($C34="",NA(),IF($C34&gt;$B$11,$C34,NA()))</f>
         <v/>
       </c>
@@ -5125,7 +5129,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
+      <c r="B35" s="22" t="n">
         <v>404</v>
       </c>
       <c r="C35" s="17">
@@ -5152,22 +5156,22 @@
         <f>IF(B35="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <f>IF(B35="","",IF(OR(B35&gt;$B$9,B35&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B28:B35)=8,OR(MIN(B28:B35)&gt;$B$6,MAX(B28:B35)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T35" s="20" t="n">
+      <c r="T35" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="AD35" s="20">
+      <c r="AD35" s="21">
         <f>IF($B35="",NA(),IF(OR($B35&gt;$B$9,$B35&lt;$B$10),$B35,NA()))</f>
         <v/>
       </c>
-      <c r="AE35" s="20">
+      <c r="AE35" s="21">
         <f>IF(COUNT($B28:$B35)&lt;8,NA(),IF(OR(MIN($B28:$B35)&gt;$B$6,MAX($B28:$B35)&lt;$B$6),$B35,NA()))</f>
         <v/>
       </c>
-      <c r="AF35" s="20">
+      <c r="AF35" s="21">
         <f>IF($C35="",NA(),IF($C35&gt;$B$11,$C35,NA()))</f>
         <v/>
       </c>
@@ -5178,7 +5182,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
+      <c r="B36" s="22" t="n">
         <v>416</v>
       </c>
       <c r="C36" s="17">
@@ -5205,22 +5209,22 @@
         <f>IF(B36="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <f>IF(B36="","",IF(OR(B36&gt;$B$9,B36&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B29:B36)=8,OR(MIN(B29:B36)&gt;$B$6,MAX(B29:B36)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T36" s="20" t="n">
+      <c r="T36" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="21">
         <f>IF($B36="",NA(),IF(OR($B36&gt;$B$9,$B36&lt;$B$10),$B36,NA()))</f>
         <v/>
       </c>
-      <c r="AE36" s="20">
+      <c r="AE36" s="21">
         <f>IF(COUNT($B29:$B36)&lt;8,NA(),IF(OR(MIN($B29:$B36)&gt;$B$6,MAX($B29:$B36)&lt;$B$6),$B36,NA()))</f>
         <v/>
       </c>
-      <c r="AF36" s="20">
+      <c r="AF36" s="21">
         <f>IF($C36="",NA(),IF($C36&gt;$B$11,$C36,NA()))</f>
         <v/>
       </c>
@@ -5231,7 +5235,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
+      <c r="B37" s="22" t="n">
         <v>428</v>
       </c>
       <c r="C37" s="17">
@@ -5258,22 +5262,22 @@
         <f>IF(B37="","",$B$11)</f>
         <v/>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="20">
         <f>IF(B37="","",IF(OR(B37&gt;$B$9,B37&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B30:B37)=8,OR(MIN(B30:B37)&gt;$B$6,MAX(B30:B37)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
-      <c r="T37" s="20" t="n">
+      <c r="T37" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="AD37" s="20">
+      <c r="AD37" s="21">
         <f>IF($B37="",NA(),IF(OR($B37&gt;$B$9,$B37&lt;$B$10),$B37,NA()))</f>
         <v/>
       </c>
-      <c r="AE37" s="20">
+      <c r="AE37" s="21">
         <f>IF(COUNT($B30:$B37)&lt;8,NA(),IF(OR(MIN($B30:$B37)&gt;$B$6,MAX($B30:$B37)&lt;$B$6),$B37,NA()))</f>
         <v/>
       </c>
-      <c r="AF37" s="20">
+      <c r="AF37" s="21">
         <f>IF($C37="",NA(),IF($C37&gt;$B$11,$C37,NA()))</f>
         <v/>
       </c>
@@ -5385,7 +5389,7 @@
           <t>Overall proportion (p-bar)</t>
         </is>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="23">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -5401,7 +5405,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="24">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -5417,7 +5421,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -5433,7 +5437,7 @@
           <t>Ordinary p-chart limits would be</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>"±"&amp;TEXT(3*SQRT(B5*(1-B5)/AVERAGE(B14:B37)),"0.00%")</f>
         <v/>
       </c>
@@ -5446,10 +5450,10 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Your data — one row per day</t>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Your data — one row per day  ·  Key: z = your rate restated in standard deviations, so periods of different size compare · MR = moving range, the gap between one point and the one before it · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -5503,17 +5507,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -5540,17 +5544,17 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>7820</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>5610</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="23">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",SQRT($B$5*(1-$B$5)/B14))</f>
         <v/>
       </c>
@@ -5558,30 +5562,30 @@
         <f>IF(B14="","",(D14-$B$5)/E14)</f>
         <v/>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="29">
         <f>IF(B14="","",MIN(1,$B$5+3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="29">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="29">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T14" s="20" t="n">
+      <c r="T14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="AD14" s="20">
+      <c r="AD14" s="21">
         <f>IF($D14="",NA(),IF(OR($D14&gt;$K14,$D14&lt;$L14),$D14,NA()))</f>
         <v/>
       </c>
-      <c r="AE14" s="20">
+      <c r="AE14" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -5592,17 +5596,17 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <v>8140</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="30" t="n">
         <v>5990</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="23">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",SQRT($B$5*(1-$B$5)/B15))</f>
         <v/>
       </c>
@@ -5614,30 +5618,30 @@
         <f>IF(COUNT(F14:F15)=2,ABS(F15-F14),"")</f>
         <v/>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="29">
         <f>IF(B15="","",MIN(1,$B$5+3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="29">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="29">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T15" s="20" t="n">
+      <c r="T15" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="AD15" s="20">
+      <c r="AD15" s="21">
         <f>IF($D15="",NA(),IF(OR($D15&gt;$K15,$D15&lt;$L15),$D15,NA()))</f>
         <v/>
       </c>
-      <c r="AE15" s="20">
+      <c r="AE15" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -5648,17 +5652,17 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="30" t="n">
         <v>7960</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="30" t="n">
         <v>5570</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="23">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",SQRT($B$5*(1-$B$5)/B16))</f>
         <v/>
       </c>
@@ -5670,30 +5674,30 @@
         <f>IF(COUNT(F15:F16)=2,ABS(F16-F15),"")</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>IF(B16="","",MIN(1,$B$5+3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T16" s="20" t="n">
+      <c r="T16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="AD16" s="20">
+      <c r="AD16" s="21">
         <f>IF($D16="",NA(),IF(OR($D16&gt;$K16,$D16&lt;$L16),$D16,NA()))</f>
         <v/>
       </c>
-      <c r="AE16" s="20">
+      <c r="AE16" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -5704,17 +5708,17 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="30" t="n">
         <v>8310</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="30" t="n">
         <v>6120</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",SQRT($B$5*(1-$B$5)/B17))</f>
         <v/>
       </c>
@@ -5726,30 +5730,30 @@
         <f>IF(COUNT(F16:F17)=2,ABS(F17-F16),"")</f>
         <v/>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="20">
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="29">
         <f>IF(B17="","",MIN(1,$B$5+3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="29">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="29">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T17" s="20" t="n">
+      <c r="T17" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="AD17" s="20">
+      <c r="AD17" s="21">
         <f>IF($D17="",NA(),IF(OR($D17&gt;$K17,$D17&lt;$L17),$D17,NA()))</f>
         <v/>
       </c>
-      <c r="AE17" s="20">
+      <c r="AE17" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -5760,17 +5764,17 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="30" t="n">
         <v>7690</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="30" t="n">
         <v>5410</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="23">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",SQRT($B$5*(1-$B$5)/B18))</f>
         <v/>
       </c>
@@ -5782,30 +5786,30 @@
         <f>IF(COUNT(F17:F18)=2,ABS(F18-F17),"")</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="29">
         <f>IF(B18="","",MIN(1,$B$5+3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="29">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="28">
+      <c r="M18" s="29">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T18" s="20" t="n">
+      <c r="T18" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="AD18" s="20">
+      <c r="AD18" s="21">
         <f>IF($D18="",NA(),IF(OR($D18&gt;$K18,$D18&lt;$L18),$D18,NA()))</f>
         <v/>
       </c>
-      <c r="AE18" s="20">
+      <c r="AE18" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -5816,17 +5820,17 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="30" t="n">
         <v>8020</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="30" t="n">
         <v>5880</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",SQRT($B$5*(1-$B$5)/B19))</f>
         <v/>
       </c>
@@ -5838,30 +5842,30 @@
         <f>IF(COUNT(F18:F19)=2,ABS(F19-F18),"")</f>
         <v/>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="29">
         <f>IF(B19="","",MIN(1,$B$5+3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="29">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="28">
+      <c r="M19" s="29">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T19" s="20" t="n">
+      <c r="T19" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="AD19" s="20">
+      <c r="AD19" s="21">
         <f>IF($D19="",NA(),IF(OR($D19&gt;$K19,$D19&lt;$L19),$D19,NA()))</f>
         <v/>
       </c>
-      <c r="AE19" s="20">
+      <c r="AE19" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -5872,17 +5876,17 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="30" t="n">
         <v>8450</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="30" t="n">
         <v>6210</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",SQRT($B$5*(1-$B$5)/B20))</f>
         <v/>
       </c>
@@ -5894,30 +5898,30 @@
         <f>IF(COUNT(F19:F20)=2,ABS(F20-F19),"")</f>
         <v/>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="20">
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="29">
         <f>IF(B20="","",MIN(1,$B$5+3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="29">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="28">
+      <c r="M20" s="29">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T20" s="20" t="n">
+      <c r="T20" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="AD20" s="20">
+      <c r="AD20" s="21">
         <f>IF($D20="",NA(),IF(OR($D20&gt;$K20,$D20&lt;$L20),$D20,NA()))</f>
         <v/>
       </c>
-      <c r="AE20" s="20">
+      <c r="AE20" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -5928,17 +5932,17 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="30" t="n">
         <v>7880</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="30" t="n">
         <v>5490</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",SQRT($B$5*(1-$B$5)/B21))</f>
         <v/>
       </c>
@@ -5950,30 +5954,30 @@
         <f>IF(COUNT(F20:F21)=2,ABS(F21-F20),"")</f>
         <v/>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="20">
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>IF(B21="","",MIN(1,$B$5+3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T21" s="20" t="n">
+      <c r="T21" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="AD21" s="20">
+      <c r="AD21" s="21">
         <f>IF($D21="",NA(),IF(OR($D21&gt;$K21,$D21&lt;$L21),$D21,NA()))</f>
         <v/>
       </c>
-      <c r="AE21" s="20">
+      <c r="AE21" s="21">
         <f>IF(COUNT($D14:$D21)&lt;8,NA(),IF(OR(MIN($D14:$D21)&gt;$B$5,MAX($D14:$D21)&lt;$B$5),$D21,NA()))</f>
         <v/>
       </c>
@@ -5984,17 +5988,17 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="30" t="n">
         <v>8210</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="30" t="n">
         <v>6050</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",SQRT($B$5*(1-$B$5)/B22))</f>
         <v/>
       </c>
@@ -6006,30 +6010,30 @@
         <f>IF(COUNT(F21:F22)=2,ABS(F22-F21),"")</f>
         <v/>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="20">
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="29">
         <f>IF(B22="","",MIN(1,$B$5+3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="29">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="28">
+      <c r="M22" s="29">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T22" s="20" t="n">
+      <c r="T22" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="21">
         <f>IF($D22="",NA(),IF(OR($D22&gt;$K22,$D22&lt;$L22),$D22,NA()))</f>
         <v/>
       </c>
-      <c r="AE22" s="20">
+      <c r="AE22" s="21">
         <f>IF(COUNT($D15:$D22)&lt;8,NA(),IF(OR(MIN($D15:$D22)&gt;$B$5,MAX($D15:$D22)&lt;$B$5),$D22,NA()))</f>
         <v/>
       </c>
@@ -6040,17 +6044,17 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="30" t="n">
         <v>7740</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="30" t="n">
         <v>5380</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",SQRT($B$5*(1-$B$5)/B23))</f>
         <v/>
       </c>
@@ -6062,30 +6066,30 @@
         <f>IF(COUNT(F22:F23)=2,ABS(F23-F22),"")</f>
         <v/>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="20">
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>IF(B23="","",MIN(1,$B$5+3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T23" s="20" t="n">
+      <c r="T23" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="AD23" s="20">
+      <c r="AD23" s="21">
         <f>IF($D23="",NA(),IF(OR($D23&gt;$K23,$D23&lt;$L23),$D23,NA()))</f>
         <v/>
       </c>
-      <c r="AE23" s="20">
+      <c r="AE23" s="21">
         <f>IF(COUNT($D16:$D23)&lt;8,NA(),IF(OR(MIN($D16:$D23)&gt;$B$5,MAX($D16:$D23)&lt;$B$5),$D23,NA()))</f>
         <v/>
       </c>
@@ -6096,17 +6100,17 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="30" t="n">
         <v>8090</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="30" t="n">
         <v>5940</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",SQRT($B$5*(1-$B$5)/B24))</f>
         <v/>
       </c>
@@ -6118,30 +6122,30 @@
         <f>IF(COUNT(F23:F24)=2,ABS(F24-F23),"")</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="29">
         <f>IF(B24="","",MIN(1,$B$5+3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="29">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="28">
+      <c r="M24" s="29">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T24" s="20" t="n">
+      <c r="T24" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="AD24" s="20">
+      <c r="AD24" s="21">
         <f>IF($D24="",NA(),IF(OR($D24&gt;$K24,$D24&lt;$L24),$D24,NA()))</f>
         <v/>
       </c>
-      <c r="AE24" s="20">
+      <c r="AE24" s="21">
         <f>IF(COUNT($D17:$D24)&lt;8,NA(),IF(OR(MIN($D17:$D24)&gt;$B$5,MAX($D17:$D24)&lt;$B$5),$D24,NA()))</f>
         <v/>
       </c>
@@ -6152,17 +6156,17 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="30" t="n">
         <v>8380</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="30" t="n">
         <v>6180</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",SQRT($B$5*(1-$B$5)/B25))</f>
         <v/>
       </c>
@@ -6174,30 +6178,30 @@
         <f>IF(COUNT(F24:F25)=2,ABS(F25-F24),"")</f>
         <v/>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="29">
         <f>IF(B25="","",MIN(1,$B$5+3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="29">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="28">
+      <c r="M25" s="29">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T25" s="20" t="n">
+      <c r="T25" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="AD25" s="20">
+      <c r="AD25" s="21">
         <f>IF($D25="",NA(),IF(OR($D25&gt;$K25,$D25&lt;$L25),$D25,NA()))</f>
         <v/>
       </c>
-      <c r="AE25" s="20">
+      <c r="AE25" s="21">
         <f>IF(COUNT($D18:$D25)&lt;8,NA(),IF(OR(MIN($D18:$D25)&gt;$B$5,MAX($D18:$D25)&lt;$B$5),$D25,NA()))</f>
         <v/>
       </c>
@@ -6208,17 +6212,17 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="30" t="n">
         <v>7930</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="30" t="n">
         <v>5520</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="23">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",SQRT($B$5*(1-$B$5)/B26))</f>
         <v/>
       </c>
@@ -6230,30 +6234,30 @@
         <f>IF(COUNT(F25:F26)=2,ABS(F26-F25),"")</f>
         <v/>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="28">
+      <c r="K26" s="29">
         <f>IF(B26="","",MIN(1,$B$5+3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="29">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="28">
+      <c r="M26" s="29">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T26" s="20" t="n">
+      <c r="T26" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="AD26" s="20">
+      <c r="AD26" s="21">
         <f>IF($D26="",NA(),IF(OR($D26&gt;$K26,$D26&lt;$L26),$D26,NA()))</f>
         <v/>
       </c>
-      <c r="AE26" s="20">
+      <c r="AE26" s="21">
         <f>IF(COUNT($D19:$D26)&lt;8,NA(),IF(OR(MIN($D19:$D26)&gt;$B$5,MAX($D19:$D26)&lt;$B$5),$D26,NA()))</f>
         <v/>
       </c>
@@ -6264,17 +6268,17 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="30" t="n">
         <v>8260</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="30" t="n">
         <v>6010</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="23">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",SQRT($B$5*(1-$B$5)/B27))</f>
         <v/>
       </c>
@@ -6286,30 +6290,30 @@
         <f>IF(COUNT(F26:F27)=2,ABS(F27-F26),"")</f>
         <v/>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="20">
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="28">
+      <c r="K27" s="29">
         <f>IF(B27="","",MIN(1,$B$5+3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="29">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="28">
+      <c r="M27" s="29">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T27" s="20" t="n">
+      <c r="T27" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="AD27" s="20">
+      <c r="AD27" s="21">
         <f>IF($D27="",NA(),IF(OR($D27&gt;$K27,$D27&lt;$L27),$D27,NA()))</f>
         <v/>
       </c>
-      <c r="AE27" s="20">
+      <c r="AE27" s="21">
         <f>IF(COUNT($D20:$D27)&lt;8,NA(),IF(OR(MIN($D20:$D27)&gt;$B$5,MAX($D20:$D27)&lt;$B$5),$D27,NA()))</f>
         <v/>
       </c>
@@ -6320,17 +6324,17 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="30" t="n">
         <v>7810</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="30" t="n">
         <v>5480</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="23">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",SQRT($B$5*(1-$B$5)/B28))</f>
         <v/>
       </c>
@@ -6342,30 +6346,30 @@
         <f>IF(COUNT(F27:F28)=2,ABS(F28-F27),"")</f>
         <v/>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="20">
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="29">
         <f>IF(B28="","",MIN(1,$B$5+3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="29">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="28">
+      <c r="M28" s="29">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T28" s="20" t="n">
+      <c r="T28" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="AD28" s="20">
+      <c r="AD28" s="21">
         <f>IF($D28="",NA(),IF(OR($D28&gt;$K28,$D28&lt;$L28),$D28,NA()))</f>
         <v/>
       </c>
-      <c r="AE28" s="20">
+      <c r="AE28" s="21">
         <f>IF(COUNT($D21:$D28)&lt;8,NA(),IF(OR(MIN($D21:$D28)&gt;$B$5,MAX($D21:$D28)&lt;$B$5),$D28,NA()))</f>
         <v/>
       </c>
@@ -6376,17 +6380,17 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="30" t="n">
         <v>8150</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="30" t="n">
         <v>5860</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="23">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",SQRT($B$5*(1-$B$5)/B29))</f>
         <v/>
       </c>
@@ -6398,30 +6402,30 @@
         <f>IF(COUNT(F28:F29)=2,ABS(F29-F28),"")</f>
         <v/>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="20">
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="28">
+      <c r="K29" s="29">
         <f>IF(B29="","",MIN(1,$B$5+3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="29">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="28">
+      <c r="M29" s="29">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T29" s="20" t="n">
+      <c r="T29" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="AD29" s="20">
+      <c r="AD29" s="21">
         <f>IF($D29="",NA(),IF(OR($D29&gt;$K29,$D29&lt;$L29),$D29,NA()))</f>
         <v/>
       </c>
-      <c r="AE29" s="20">
+      <c r="AE29" s="21">
         <f>IF(COUNT($D22:$D29)&lt;8,NA(),IF(OR(MIN($D22:$D29)&gt;$B$5,MAX($D22:$D29)&lt;$B$5),$D29,NA()))</f>
         <v/>
       </c>
@@ -6432,17 +6436,17 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="30" t="n">
         <v>8470</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="30" t="n">
         <v>6240</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="23">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",SQRT($B$5*(1-$B$5)/B30))</f>
         <v/>
       </c>
@@ -6454,30 +6458,30 @@
         <f>IF(COUNT(F29:F30)=2,ABS(F30-F29),"")</f>
         <v/>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="28">
+      <c r="K30" s="29">
         <f>IF(B30="","",MIN(1,$B$5+3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="L30" s="28">
+      <c r="L30" s="29">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="28">
+      <c r="M30" s="29">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T30" s="20" t="n">
+      <c r="T30" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="AD30" s="20">
+      <c r="AD30" s="21">
         <f>IF($D30="",NA(),IF(OR($D30&gt;$K30,$D30&lt;$L30),$D30,NA()))</f>
         <v/>
       </c>
-      <c r="AE30" s="20">
+      <c r="AE30" s="21">
         <f>IF(COUNT($D23:$D30)&lt;8,NA(),IF(OR(MIN($D23:$D30)&gt;$B$5,MAX($D23:$D30)&lt;$B$5),$D30,NA()))</f>
         <v/>
       </c>
@@ -6488,17 +6492,17 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="30" t="n">
         <v>7860</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="30" t="n">
         <v>5600</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",SQRT($B$5*(1-$B$5)/B31))</f>
         <v/>
       </c>
@@ -6510,30 +6514,30 @@
         <f>IF(COUNT(F30:F31)=2,ABS(F31-F30),"")</f>
         <v/>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="20">
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="28">
+      <c r="K31" s="29">
         <f>IF(B31="","",MIN(1,$B$5+3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="29">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="28">
+      <c r="M31" s="29">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T31" s="20" t="n">
+      <c r="T31" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="AD31" s="20">
+      <c r="AD31" s="21">
         <f>IF($D31="",NA(),IF(OR($D31&gt;$K31,$D31&lt;$L31),$D31,NA()))</f>
         <v/>
       </c>
-      <c r="AE31" s="20">
+      <c r="AE31" s="21">
         <f>IF(COUNT($D24:$D31)&lt;8,NA(),IF(OR(MIN($D24:$D31)&gt;$B$5,MAX($D24:$D31)&lt;$B$5),$D31,NA()))</f>
         <v/>
       </c>
@@ -6544,17 +6548,17 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="30" t="n">
         <v>8030</v>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="30" t="n">
         <v>5760</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="23">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",SQRT($B$5*(1-$B$5)/B32))</f>
         <v/>
       </c>
@@ -6566,30 +6570,30 @@
         <f>IF(COUNT(F31:F32)=2,ABS(F32-F31),"")</f>
         <v/>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="20">
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="28">
+      <c r="K32" s="29">
         <f>IF(B32="","",MIN(1,$B$5+3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="L32" s="28">
+      <c r="L32" s="29">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="28">
+      <c r="M32" s="29">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T32" s="20" t="n">
+      <c r="T32" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="AD32" s="20">
+      <c r="AD32" s="21">
         <f>IF($D32="",NA(),IF(OR($D32&gt;$K32,$D32&lt;$L32),$D32,NA()))</f>
         <v/>
       </c>
-      <c r="AE32" s="20">
+      <c r="AE32" s="21">
         <f>IF(COUNT($D25:$D32)&lt;8,NA(),IF(OR(MIN($D25:$D32)&gt;$B$5,MAX($D25:$D32)&lt;$B$5),$D32,NA()))</f>
         <v/>
       </c>
@@ -6600,17 +6604,17 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="30" t="n">
         <v>8340</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="30" t="n">
         <v>6090</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="23">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",SQRT($B$5*(1-$B$5)/B33))</f>
         <v/>
       </c>
@@ -6622,30 +6626,30 @@
         <f>IF(COUNT(F32:F33)=2,ABS(F33-F32),"")</f>
         <v/>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="20">
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="28">
+      <c r="K33" s="29">
         <f>IF(B33="","",MIN(1,$B$5+3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="29">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="28">
+      <c r="M33" s="29">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T33" s="20" t="n">
+      <c r="T33" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="AD33" s="20">
+      <c r="AD33" s="21">
         <f>IF($D33="",NA(),IF(OR($D33&gt;$K33,$D33&lt;$L33),$D33,NA()))</f>
         <v/>
       </c>
-      <c r="AE33" s="20">
+      <c r="AE33" s="21">
         <f>IF(COUNT($D26:$D33)&lt;8,NA(),IF(OR(MIN($D26:$D33)&gt;$B$5,MAX($D26:$D33)&lt;$B$5),$D33,NA()))</f>
         <v/>
       </c>
@@ -6656,17 +6660,17 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="30" t="n">
         <v>7900</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="30" t="n">
         <v>5710</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="23">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",SQRT($B$5*(1-$B$5)/B34))</f>
         <v/>
       </c>
@@ -6678,30 +6682,30 @@
         <f>IF(COUNT(F33:F34)=2,ABS(F34-F33),"")</f>
         <v/>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="20">
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="28">
+      <c r="K34" s="29">
         <f>IF(B34="","",MIN(1,$B$5+3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="L34" s="28">
+      <c r="L34" s="29">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="28">
+      <c r="M34" s="29">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T34" s="20" t="n">
+      <c r="T34" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="21">
         <f>IF($D34="",NA(),IF(OR($D34&gt;$K34,$D34&lt;$L34),$D34,NA()))</f>
         <v/>
       </c>
-      <c r="AE34" s="20">
+      <c r="AE34" s="21">
         <f>IF(COUNT($D27:$D34)&lt;8,NA(),IF(OR(MIN($D27:$D34)&gt;$B$5,MAX($D27:$D34)&lt;$B$5),$D34,NA()))</f>
         <v/>
       </c>
@@ -6712,17 +6716,17 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="30" t="n">
         <v>8180</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="30" t="n">
         <v>5900</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="23">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",SQRT($B$5*(1-$B$5)/B35))</f>
         <v/>
       </c>
@@ -6734,30 +6738,30 @@
         <f>IF(COUNT(F34:F35)=2,ABS(F35-F34),"")</f>
         <v/>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="28">
+      <c r="K35" s="29">
         <f>IF(B35="","",MIN(1,$B$5+3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="L35" s="28">
+      <c r="L35" s="29">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="28">
+      <c r="M35" s="29">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T35" s="20" t="n">
+      <c r="T35" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="AD35" s="20">
+      <c r="AD35" s="21">
         <f>IF($D35="",NA(),IF(OR($D35&gt;$K35,$D35&lt;$L35),$D35,NA()))</f>
         <v/>
       </c>
-      <c r="AE35" s="20">
+      <c r="AE35" s="21">
         <f>IF(COUNT($D28:$D35)&lt;8,NA(),IF(OR(MIN($D28:$D35)&gt;$B$5,MAX($D28:$D35)&lt;$B$5),$D35,NA()))</f>
         <v/>
       </c>
@@ -6768,17 +6772,17 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="30" t="n">
         <v>7770</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="30" t="n">
         <v>5450</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="23">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",SQRT($B$5*(1-$B$5)/B36))</f>
         <v/>
       </c>
@@ -6790,30 +6794,30 @@
         <f>IF(COUNT(F35:F36)=2,ABS(F36-F35),"")</f>
         <v/>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="28">
+      <c r="K36" s="29">
         <f>IF(B36="","",MIN(1,$B$5+3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="L36" s="28">
+      <c r="L36" s="29">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="28">
+      <c r="M36" s="29">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T36" s="20" t="n">
+      <c r="T36" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="21">
         <f>IF($D36="",NA(),IF(OR($D36&gt;$K36,$D36&lt;$L36),$D36,NA()))</f>
         <v/>
       </c>
-      <c r="AE36" s="20">
+      <c r="AE36" s="21">
         <f>IF(COUNT($D29:$D36)&lt;8,NA(),IF(OR(MIN($D29:$D36)&gt;$B$5,MAX($D29:$D36)&lt;$B$5),$D36,NA()))</f>
         <v/>
       </c>
@@ -6824,17 +6828,17 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="30" t="n">
         <v>8240</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="30" t="n">
         <v>6020</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="23">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",SQRT($B$5*(1-$B$5)/B37))</f>
         <v/>
       </c>
@@ -6846,30 +6850,30 @@
         <f>IF(COUNT(F36:F37)=2,ABS(F37-F36),"")</f>
         <v/>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="20">
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="28">
+      <c r="K37" s="29">
         <f>IF(B37="","",MIN(1,$B$5+3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="L37" s="28">
+      <c r="L37" s="29">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="28">
+      <c r="M37" s="29">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T37" s="20" t="n">
+      <c r="T37" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="AD37" s="20">
+      <c r="AD37" s="21">
         <f>IF($D37="",NA(),IF(OR($D37&gt;$K37,$D37&lt;$L37),$D37,NA()))</f>
         <v/>
       </c>
-      <c r="AE37" s="20">
+      <c r="AE37" s="21">
         <f>IF(COUNT($D30:$D37)&lt;8,NA(),IF(OR(MIN($D30:$D37)&gt;$B$5,MAX($D30:$D37)&lt;$B$5),$D37,NA()))</f>
         <v/>
       </c>
@@ -6978,7 +6982,7 @@
           <t>Overall rate (u-bar)</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -6994,7 +6998,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="24">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -7010,7 +7014,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -7039,10 +7043,10 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Your data — one row per week</t>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Your data — one row per week  ·  Key: z = your rate restated in standard deviations, so periods of different size compare · MR = moving range, the gap between one point and the one before it · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -7096,17 +7100,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -7133,17 +7137,17 @@
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>1240</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",SQRT($B$5/B14))</f>
         <v/>
       </c>
@@ -7151,30 +7155,30 @@
         <f>IF(B14="","",(D14-$B$5)/E14)</f>
         <v/>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20">
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="32">
         <f>IF(B14="","",$B$5+3*E14*$B$7)</f>
         <v/>
       </c>
-      <c r="L14" s="31">
+      <c r="L14" s="32">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="31">
+      <c r="M14" s="32">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T14" s="20" t="n">
+      <c r="T14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="AD14" s="20">
+      <c r="AD14" s="21">
         <f>IF($D14="",NA(),IF(OR($D14&gt;$K14,$D14&lt;$L14),$D14,NA()))</f>
         <v/>
       </c>
-      <c r="AE14" s="20">
+      <c r="AE14" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -7185,17 +7189,17 @@
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <v>1310</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="30" t="n">
         <v>68</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",SQRT($B$5/B15))</f>
         <v/>
       </c>
@@ -7207,30 +7211,30 @@
         <f>IF(COUNT(F14:F15)=2,ABS(F15-F14),"")</f>
         <v/>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="31">
+      <c r="K15" s="32">
         <f>IF(B15="","",$B$5+3*E15*$B$7)</f>
         <v/>
       </c>
-      <c r="L15" s="31">
+      <c r="L15" s="32">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="31">
+      <c r="M15" s="32">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T15" s="20" t="n">
+      <c r="T15" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="AD15" s="20">
+      <c r="AD15" s="21">
         <f>IF($D15="",NA(),IF(OR($D15&gt;$K15,$D15&lt;$L15),$D15,NA()))</f>
         <v/>
       </c>
-      <c r="AE15" s="20">
+      <c r="AE15" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -7241,17 +7245,17 @@
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="30" t="n">
         <v>1180</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",SQRT($B$5/B16))</f>
         <v/>
       </c>
@@ -7263,30 +7267,30 @@
         <f>IF(COUNT(F15:F16)=2,ABS(F16-F15),"")</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="31">
+      <c r="K16" s="32">
         <f>IF(B16="","",$B$5+3*E16*$B$7)</f>
         <v/>
       </c>
-      <c r="L16" s="31">
+      <c r="L16" s="32">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="31">
+      <c r="M16" s="32">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T16" s="20" t="n">
+      <c r="T16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="AD16" s="20">
+      <c r="AD16" s="21">
         <f>IF($D16="",NA(),IF(OR($D16&gt;$K16,$D16&lt;$L16),$D16,NA()))</f>
         <v/>
       </c>
-      <c r="AE16" s="20">
+      <c r="AE16" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -7297,17 +7301,17 @@
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="30" t="n">
         <v>1420</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="30" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",SQRT($B$5/B17))</f>
         <v/>
       </c>
@@ -7319,30 +7323,30 @@
         <f>IF(COUNT(F16:F17)=2,ABS(F17-F16),"")</f>
         <v/>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="20">
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="31">
+      <c r="K17" s="32">
         <f>IF(B17="","",$B$5+3*E17*$B$7)</f>
         <v/>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="32">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="31">
+      <c r="M17" s="32">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T17" s="20" t="n">
+      <c r="T17" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="AD17" s="20">
+      <c r="AD17" s="21">
         <f>IF($D17="",NA(),IF(OR($D17&gt;$K17,$D17&lt;$L17),$D17,NA()))</f>
         <v/>
       </c>
-      <c r="AE17" s="20">
+      <c r="AE17" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -7353,17 +7357,17 @@
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="30" t="n">
         <v>1275</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",SQRT($B$5/B18))</f>
         <v/>
       </c>
@@ -7375,30 +7379,30 @@
         <f>IF(COUNT(F17:F18)=2,ABS(F18-F17),"")</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="31">
+      <c r="K18" s="32">
         <f>IF(B18="","",$B$5+3*E18*$B$7)</f>
         <v/>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="32">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="31">
+      <c r="M18" s="32">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T18" s="20" t="n">
+      <c r="T18" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="AD18" s="20">
+      <c r="AD18" s="21">
         <f>IF($D18="",NA(),IF(OR($D18&gt;$K18,$D18&lt;$L18),$D18,NA()))</f>
         <v/>
       </c>
-      <c r="AE18" s="20">
+      <c r="AE18" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -7409,17 +7413,17 @@
           <t>Week 6</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="30" t="n">
         <v>1195</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="30" t="n">
         <v>59</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",SQRT($B$5/B19))</f>
         <v/>
       </c>
@@ -7431,30 +7435,30 @@
         <f>IF(COUNT(F18:F19)=2,ABS(F19-F18),"")</f>
         <v/>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="31">
+      <c r="K19" s="32">
         <f>IF(B19="","",$B$5+3*E19*$B$7)</f>
         <v/>
       </c>
-      <c r="L19" s="31">
+      <c r="L19" s="32">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="31">
+      <c r="M19" s="32">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T19" s="20" t="n">
+      <c r="T19" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="AD19" s="20">
+      <c r="AD19" s="21">
         <f>IF($D19="",NA(),IF(OR($D19&gt;$K19,$D19&lt;$L19),$D19,NA()))</f>
         <v/>
       </c>
-      <c r="AE19" s="20">
+      <c r="AE19" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -7465,17 +7469,17 @@
           <t>Week 7</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="30" t="n">
         <v>1360</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="30" t="n">
         <v>56</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",SQRT($B$5/B20))</f>
         <v/>
       </c>
@@ -7487,30 +7491,30 @@
         <f>IF(COUNT(F19:F20)=2,ABS(F20-F19),"")</f>
         <v/>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="20">
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="31">
+      <c r="K20" s="32">
         <f>IF(B20="","",$B$5+3*E20*$B$7)</f>
         <v/>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="32">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="31">
+      <c r="M20" s="32">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T20" s="20" t="n">
+      <c r="T20" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="AD20" s="20">
+      <c r="AD20" s="21">
         <f>IF($D20="",NA(),IF(OR($D20&gt;$K20,$D20&lt;$L20),$D20,NA()))</f>
         <v/>
       </c>
-      <c r="AE20" s="20">
+      <c r="AE20" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -7521,17 +7525,17 @@
           <t>Week 8</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="30" t="n">
         <v>1230</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="30" t="n">
         <v>69</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",SQRT($B$5/B21))</f>
         <v/>
       </c>
@@ -7543,30 +7547,30 @@
         <f>IF(COUNT(F20:F21)=2,ABS(F21-F20),"")</f>
         <v/>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="20">
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <f>IF(B21="","",$B$5+3*E21*$B$7)</f>
         <v/>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="32">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T21" s="20" t="n">
+      <c r="T21" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="AD21" s="20">
+      <c r="AD21" s="21">
         <f>IF($D21="",NA(),IF(OR($D21&gt;$K21,$D21&lt;$L21),$D21,NA()))</f>
         <v/>
       </c>
-      <c r="AE21" s="20">
+      <c r="AE21" s="21">
         <f>IF(COUNT($D14:$D21)&lt;8,NA(),IF(OR(MIN($D14:$D21)&gt;$B$5,MAX($D14:$D21)&lt;$B$5),$D21,NA()))</f>
         <v/>
       </c>
@@ -7577,17 +7581,17 @@
           <t>Week 9</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="30" t="n">
         <v>1405</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",SQRT($B$5/B22))</f>
         <v/>
       </c>
@@ -7599,30 +7603,30 @@
         <f>IF(COUNT(F21:F22)=2,ABS(F22-F21),"")</f>
         <v/>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="20">
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <f>IF(B22="","",$B$5+3*E22*$B$7)</f>
         <v/>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="32">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T22" s="20" t="n">
+      <c r="T22" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="21">
         <f>IF($D22="",NA(),IF(OR($D22&gt;$K22,$D22&lt;$L22),$D22,NA()))</f>
         <v/>
       </c>
-      <c r="AE22" s="20">
+      <c r="AE22" s="21">
         <f>IF(COUNT($D15:$D22)&lt;8,NA(),IF(OR(MIN($D15:$D22)&gt;$B$5,MAX($D15:$D22)&lt;$B$5),$D22,NA()))</f>
         <v/>
       </c>
@@ -7633,17 +7637,17 @@
           <t>Week 10</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="30" t="n">
         <v>1150</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="30" t="n">
         <v>54</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",SQRT($B$5/B23))</f>
         <v/>
       </c>
@@ -7655,30 +7659,30 @@
         <f>IF(COUNT(F22:F23)=2,ABS(F23-F22),"")</f>
         <v/>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="20">
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="31">
+      <c r="K23" s="32">
         <f>IF(B23="","",$B$5+3*E23*$B$7)</f>
         <v/>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="32">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="31">
+      <c r="M23" s="32">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T23" s="20" t="n">
+      <c r="T23" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="AD23" s="20">
+      <c r="AD23" s="21">
         <f>IF($D23="",NA(),IF(OR($D23&gt;$K23,$D23&lt;$L23),$D23,NA()))</f>
         <v/>
       </c>
-      <c r="AE23" s="20">
+      <c r="AE23" s="21">
         <f>IF(COUNT($D16:$D23)&lt;8,NA(),IF(OR(MIN($D16:$D23)&gt;$B$5,MAX($D16:$D23)&lt;$B$5),$D23,NA()))</f>
         <v/>
       </c>
@@ -7689,17 +7693,17 @@
           <t>Week 11</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="30" t="n">
         <v>1290</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="30" t="n">
         <v>49</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",SQRT($B$5/B24))</f>
         <v/>
       </c>
@@ -7711,30 +7715,30 @@
         <f>IF(COUNT(F23:F24)=2,ABS(F24-F23),"")</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <f>IF(B24="","",$B$5+3*E24*$B$7)</f>
         <v/>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="32">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T24" s="20" t="n">
+      <c r="T24" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="AD24" s="20">
+      <c r="AD24" s="21">
         <f>IF($D24="",NA(),IF(OR($D24&gt;$K24,$D24&lt;$L24),$D24,NA()))</f>
         <v/>
       </c>
-      <c r="AE24" s="20">
+      <c r="AE24" s="21">
         <f>IF(COUNT($D17:$D24)&lt;8,NA(),IF(OR(MIN($D17:$D24)&gt;$B$5,MAX($D17:$D24)&lt;$B$5),$D24,NA()))</f>
         <v/>
       </c>
@@ -7745,17 +7749,17 @@
           <t>Week 12</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="30" t="n">
         <v>1375</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="30" t="n">
         <v>74</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="28">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",SQRT($B$5/B25))</f>
         <v/>
       </c>
@@ -7767,30 +7771,30 @@
         <f>IF(COUNT(F24:F25)=2,ABS(F25-F24),"")</f>
         <v/>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <f>IF(B25="","",$B$5+3*E25*$B$7)</f>
         <v/>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="32">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T25" s="20" t="n">
+      <c r="T25" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="AD25" s="20">
+      <c r="AD25" s="21">
         <f>IF($D25="",NA(),IF(OR($D25&gt;$K25,$D25&lt;$L25),$D25,NA()))</f>
         <v/>
       </c>
-      <c r="AE25" s="20">
+      <c r="AE25" s="21">
         <f>IF(COUNT($D18:$D25)&lt;8,NA(),IF(OR(MIN($D18:$D25)&gt;$B$5,MAX($D18:$D25)&lt;$B$5),$D25,NA()))</f>
         <v/>
       </c>
@@ -7801,17 +7805,17 @@
           <t>Week 13</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="30" t="n">
         <v>1215</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="30" t="n">
         <v>39</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",SQRT($B$5/B26))</f>
         <v/>
       </c>
@@ -7823,30 +7827,30 @@
         <f>IF(COUNT(F25:F26)=2,ABS(F26-F25),"")</f>
         <v/>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="32">
         <f>IF(B26="","",$B$5+3*E26*$B$7)</f>
         <v/>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="32">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="31">
+      <c r="M26" s="32">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T26" s="20" t="n">
+      <c r="T26" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="AD26" s="20">
+      <c r="AD26" s="21">
         <f>IF($D26="",NA(),IF(OR($D26&gt;$K26,$D26&lt;$L26),$D26,NA()))</f>
         <v/>
       </c>
-      <c r="AE26" s="20">
+      <c r="AE26" s="21">
         <f>IF(COUNT($D19:$D26)&lt;8,NA(),IF(OR(MIN($D19:$D26)&gt;$B$5,MAX($D19:$D26)&lt;$B$5),$D26,NA()))</f>
         <v/>
       </c>
@@ -7857,17 +7861,17 @@
           <t>Week 14</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="30" t="n">
         <v>1330</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="30" t="n">
         <v>66</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",SQRT($B$5/B27))</f>
         <v/>
       </c>
@@ -7879,30 +7883,30 @@
         <f>IF(COUNT(F26:F27)=2,ABS(F27-F26),"")</f>
         <v/>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="20">
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <f>IF(B27="","",$B$5+3*E27*$B$7)</f>
         <v/>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T27" s="20" t="n">
+      <c r="T27" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="AD27" s="20">
+      <c r="AD27" s="21">
         <f>IF($D27="",NA(),IF(OR($D27&gt;$K27,$D27&lt;$L27),$D27,NA()))</f>
         <v/>
       </c>
-      <c r="AE27" s="20">
+      <c r="AE27" s="21">
         <f>IF(COUNT($D20:$D27)&lt;8,NA(),IF(OR(MIN($D20:$D27)&gt;$B$5,MAX($D20:$D27)&lt;$B$5),$D27,NA()))</f>
         <v/>
       </c>
@@ -7913,17 +7917,17 @@
           <t>Week 15</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="30" t="n">
         <v>1185</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",SQRT($B$5/B28))</f>
         <v/>
       </c>
@@ -7935,30 +7939,30 @@
         <f>IF(COUNT(F27:F28)=2,ABS(F28-F27),"")</f>
         <v/>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="20">
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <f>IF(B28="","",$B$5+3*E28*$B$7)</f>
         <v/>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="32">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="32">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T28" s="20" t="n">
+      <c r="T28" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="AD28" s="20">
+      <c r="AD28" s="21">
         <f>IF($D28="",NA(),IF(OR($D28&gt;$K28,$D28&lt;$L28),$D28,NA()))</f>
         <v/>
       </c>
-      <c r="AE28" s="20">
+      <c r="AE28" s="21">
         <f>IF(COUNT($D21:$D28)&lt;8,NA(),IF(OR(MIN($D21:$D28)&gt;$B$5,MAX($D21:$D28)&lt;$B$5),$D28,NA()))</f>
         <v/>
       </c>
@@ -7969,17 +7973,17 @@
           <t>Week 16</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="30" t="n">
         <v>1265</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",SQRT($B$5/B29))</f>
         <v/>
       </c>
@@ -7991,30 +7995,30 @@
         <f>IF(COUNT(F28:F29)=2,ABS(F29-F28),"")</f>
         <v/>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="20">
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="31">
+      <c r="K29" s="32">
         <f>IF(B29="","",$B$5+3*E29*$B$7)</f>
         <v/>
       </c>
-      <c r="L29" s="31">
+      <c r="L29" s="32">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="31">
+      <c r="M29" s="32">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T29" s="20" t="n">
+      <c r="T29" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="AD29" s="20">
+      <c r="AD29" s="21">
         <f>IF($D29="",NA(),IF(OR($D29&gt;$K29,$D29&lt;$L29),$D29,NA()))</f>
         <v/>
       </c>
-      <c r="AE29" s="20">
+      <c r="AE29" s="21">
         <f>IF(COUNT($D22:$D29)&lt;8,NA(),IF(OR(MIN($D22:$D29)&gt;$B$5,MAX($D22:$D29)&lt;$B$5),$D29,NA()))</f>
         <v/>
       </c>
@@ -8025,17 +8029,17 @@
           <t>Week 17</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="30" t="n">
         <v>1440</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",SQRT($B$5/B30))</f>
         <v/>
       </c>
@@ -8047,30 +8051,30 @@
         <f>IF(COUNT(F29:F30)=2,ABS(F30-F29),"")</f>
         <v/>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="31">
+      <c r="K30" s="32">
         <f>IF(B30="","",$B$5+3*E30*$B$7)</f>
         <v/>
       </c>
-      <c r="L30" s="31">
+      <c r="L30" s="32">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="31">
+      <c r="M30" s="32">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T30" s="20" t="n">
+      <c r="T30" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="AD30" s="20">
+      <c r="AD30" s="21">
         <f>IF($D30="",NA(),IF(OR($D30&gt;$K30,$D30&lt;$L30),$D30,NA()))</f>
         <v/>
       </c>
-      <c r="AE30" s="20">
+      <c r="AE30" s="21">
         <f>IF(COUNT($D23:$D30)&lt;8,NA(),IF(OR(MIN($D23:$D30)&gt;$B$5,MAX($D23:$D30)&lt;$B$5),$D30,NA()))</f>
         <v/>
       </c>
@@ -8081,17 +8085,17 @@
           <t>Week 18</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="30" t="n">
         <v>1205</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="30" t="n">
         <v>54</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",SQRT($B$5/B31))</f>
         <v/>
       </c>
@@ -8103,30 +8107,30 @@
         <f>IF(COUNT(F30:F31)=2,ABS(F31-F30),"")</f>
         <v/>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="20">
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="31">
+      <c r="K31" s="32">
         <f>IF(B31="","",$B$5+3*E31*$B$7)</f>
         <v/>
       </c>
-      <c r="L31" s="31">
+      <c r="L31" s="32">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="31">
+      <c r="M31" s="32">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T31" s="20" t="n">
+      <c r="T31" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="AD31" s="20">
+      <c r="AD31" s="21">
         <f>IF($D31="",NA(),IF(OR($D31&gt;$K31,$D31&lt;$L31),$D31,NA()))</f>
         <v/>
       </c>
-      <c r="AE31" s="20">
+      <c r="AE31" s="21">
         <f>IF(COUNT($D24:$D31)&lt;8,NA(),IF(OR(MIN($D24:$D31)&gt;$B$5,MAX($D24:$D31)&lt;$B$5),$D31,NA()))</f>
         <v/>
       </c>
@@ -8137,17 +8141,17 @@
           <t>Week 19</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="30" t="n">
         <v>1300</v>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",SQRT($B$5/B32))</f>
         <v/>
       </c>
@@ -8159,30 +8163,30 @@
         <f>IF(COUNT(F31:F32)=2,ABS(F32-F31),"")</f>
         <v/>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="20">
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="31">
+      <c r="K32" s="32">
         <f>IF(B32="","",$B$5+3*E32*$B$7)</f>
         <v/>
       </c>
-      <c r="L32" s="31">
+      <c r="L32" s="32">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="31">
+      <c r="M32" s="32">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T32" s="20" t="n">
+      <c r="T32" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="AD32" s="20">
+      <c r="AD32" s="21">
         <f>IF($D32="",NA(),IF(OR($D32&gt;$K32,$D32&lt;$L32),$D32,NA()))</f>
         <v/>
       </c>
-      <c r="AE32" s="20">
+      <c r="AE32" s="21">
         <f>IF(COUNT($D25:$D32)&lt;8,NA(),IF(OR(MIN($D25:$D32)&gt;$B$5,MAX($D25:$D32)&lt;$B$5),$D32,NA()))</f>
         <v/>
       </c>
@@ -8193,17 +8197,17 @@
           <t>Week 20</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="30" t="n">
         <v>1355</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",SQRT($B$5/B33))</f>
         <v/>
       </c>
@@ -8215,30 +8219,30 @@
         <f>IF(COUNT(F32:F33)=2,ABS(F33-F32),"")</f>
         <v/>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="20">
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="31">
+      <c r="K33" s="32">
         <f>IF(B33="","",$B$5+3*E33*$B$7)</f>
         <v/>
       </c>
-      <c r="L33" s="31">
+      <c r="L33" s="32">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="31">
+      <c r="M33" s="32">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T33" s="20" t="n">
+      <c r="T33" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="AD33" s="20">
+      <c r="AD33" s="21">
         <f>IF($D33="",NA(),IF(OR($D33&gt;$K33,$D33&lt;$L33),$D33,NA()))</f>
         <v/>
       </c>
-      <c r="AE33" s="20">
+      <c r="AE33" s="21">
         <f>IF(COUNT($D26:$D33)&lt;8,NA(),IF(OR(MIN($D26:$D33)&gt;$B$5,MAX($D26:$D33)&lt;$B$5),$D33,NA()))</f>
         <v/>
       </c>
@@ -8249,17 +8253,17 @@
           <t>Week 21</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="30" t="n">
         <v>1170</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="30" t="n">
         <v>43</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",SQRT($B$5/B34))</f>
         <v/>
       </c>
@@ -8271,30 +8275,30 @@
         <f>IF(COUNT(F33:F34)=2,ABS(F34-F33),"")</f>
         <v/>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="20">
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="31">
+      <c r="K34" s="32">
         <f>IF(B34="","",$B$5+3*E34*$B$7)</f>
         <v/>
       </c>
-      <c r="L34" s="31">
+      <c r="L34" s="32">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="31">
+      <c r="M34" s="32">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T34" s="20" t="n">
+      <c r="T34" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="21">
         <f>IF($D34="",NA(),IF(OR($D34&gt;$K34,$D34&lt;$L34),$D34,NA()))</f>
         <v/>
       </c>
-      <c r="AE34" s="20">
+      <c r="AE34" s="21">
         <f>IF(COUNT($D27:$D34)&lt;8,NA(),IF(OR(MIN($D27:$D34)&gt;$B$5,MAX($D27:$D34)&lt;$B$5),$D34,NA()))</f>
         <v/>
       </c>
@@ -8305,17 +8309,17 @@
           <t>Week 22</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="30" t="n">
         <v>1285</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="30" t="n">
         <v>62</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",SQRT($B$5/B35))</f>
         <v/>
       </c>
@@ -8327,30 +8331,30 @@
         <f>IF(COUNT(F34:F35)=2,ABS(F35-F34),"")</f>
         <v/>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="31">
+      <c r="K35" s="32">
         <f>IF(B35="","",$B$5+3*E35*$B$7)</f>
         <v/>
       </c>
-      <c r="L35" s="31">
+      <c r="L35" s="32">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="31">
+      <c r="M35" s="32">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T35" s="20" t="n">
+      <c r="T35" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="AD35" s="20">
+      <c r="AD35" s="21">
         <f>IF($D35="",NA(),IF(OR($D35&gt;$K35,$D35&lt;$L35),$D35,NA()))</f>
         <v/>
       </c>
-      <c r="AE35" s="20">
+      <c r="AE35" s="21">
         <f>IF(COUNT($D28:$D35)&lt;8,NA(),IF(OR(MIN($D28:$D35)&gt;$B$5,MAX($D28:$D35)&lt;$B$5),$D35,NA()))</f>
         <v/>
       </c>
@@ -8361,17 +8365,17 @@
           <t>Week 23</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="30" t="n">
         <v>1225</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="28">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",SQRT($B$5/B36))</f>
         <v/>
       </c>
@@ -8383,30 +8387,30 @@
         <f>IF(COUNT(F35:F36)=2,ABS(F36-F35),"")</f>
         <v/>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="31">
+      <c r="K36" s="32">
         <f>IF(B36="","",$B$5+3*E36*$B$7)</f>
         <v/>
       </c>
-      <c r="L36" s="31">
+      <c r="L36" s="32">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="31">
+      <c r="M36" s="32">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T36" s="20" t="n">
+      <c r="T36" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="21">
         <f>IF($D36="",NA(),IF(OR($D36&gt;$K36,$D36&lt;$L36),$D36,NA()))</f>
         <v/>
       </c>
-      <c r="AE36" s="20">
+      <c r="AE36" s="21">
         <f>IF(COUNT($D29:$D36)&lt;8,NA(),IF(OR(MIN($D29:$D36)&gt;$B$5,MAX($D29:$D36)&lt;$B$5),$D36,NA()))</f>
         <v/>
       </c>
@@ -8417,17 +8421,17 @@
           <t>Week 24</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="30" t="n">
         <v>1390</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="30" t="n">
         <v>76</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="28">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",SQRT($B$5/B37))</f>
         <v/>
       </c>
@@ -8439,30 +8443,30 @@
         <f>IF(COUNT(F36:F37)=2,ABS(F37-F36),"")</f>
         <v/>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="20">
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="31">
+      <c r="K37" s="32">
         <f>IF(B37="","",$B$5+3*E37*$B$7)</f>
         <v/>
       </c>
-      <c r="L37" s="31">
+      <c r="L37" s="32">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="31">
+      <c r="M37" s="32">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T37" s="20" t="n">
+      <c r="T37" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="AD37" s="20">
+      <c r="AD37" s="21">
         <f>IF($D37="",NA(),IF(OR($D37&gt;$K37,$D37&lt;$L37),$D37,NA()))</f>
         <v/>
       </c>
-      <c r="AE37" s="20">
+      <c r="AE37" s="21">
         <f>IF(COUNT($D30:$D37)&lt;8,NA(),IF(OR(MIN($D30:$D37)&gt;$B$5,MAX($D30:$D37)&lt;$B$5),$D37,NA()))</f>
         <v/>
       </c>
@@ -8629,7 +8633,7 @@
           <t>A2 for this n</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{1.880;1.023;0.729;0.577;0.483;0.419;0.373;0.337;0.308}),"n out of range")</f>
         <v/>
       </c>
@@ -8645,7 +8649,7 @@
           <t>D4 for this n</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{3.267;2.574;2.282;2.114;2.004;1.924;1.864;1.816;1.777}),"n out of range")</f>
         <v/>
       </c>
@@ -8656,7 +8660,7 @@
           <t>D3 for this n</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{0;0;0;0;0;0.076;0.136;0.184;0.223}),"n out of range")</f>
         <v/>
       </c>
@@ -8672,7 +8676,7 @@
           <t>Xbar UCL / LCL</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <f>TEXT(B6+B8*B7,"#,##0.00")&amp;"  /  "&amp;TEXT(B6-B8*B7,"#,##0.00")</f>
         <v/>
       </c>
@@ -8682,10 +8686,10 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Your data — five observations per subgroup</t>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Your data — five observations per subgroup  ·  Key: OBS 1..n are your individual measurements in one subgroup — one row per period · CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -8788,19 +8792,19 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>419</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="27" t="n">
         <v>381</v>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="27" t="n">
         <v>419</v>
       </c>
       <c r="G14" s="17">
@@ -8823,34 +8827,34 @@
         <f>IF(G14="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>IF(G14="","",IF(OR(G14&gt;J14,G14&lt;K14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="33">
         <f>IF(H14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="32">
+      <c r="O14" s="33">
         <f>IF(H14="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P14" s="32">
+      <c r="P14" s="33">
         <f>IF(H14="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T14" s="20" t="n">
+      <c r="T14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="AD14" s="20">
+      <c r="AD14" s="21">
         <f>IF($G14="",NA(),IF(OR($G14&gt;$J14,$G14&lt;$K14),$G14,NA()))</f>
         <v/>
       </c>
-      <c r="AE14" s="20">
+      <c r="AE14" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF14" s="20">
+      <c r="AF14" s="21">
         <f>IF($H14="",NA(),IF($H14&gt;$O14,$H14,NA()))</f>
         <v/>
       </c>
@@ -8861,19 +8865,19 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="30" t="n">
         <v>395</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="30" t="n">
         <v>400</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="30" t="n">
         <v>395</v>
       </c>
       <c r="G15" s="17">
@@ -8896,34 +8900,34 @@
         <f>IF(G15="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>IF(G15="","",IF(OR(G15&gt;J15,G15&lt;K15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N15" s="32">
+      <c r="N15" s="33">
         <f>IF(H15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="32">
+      <c r="O15" s="33">
         <f>IF(H15="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P15" s="32">
+      <c r="P15" s="33">
         <f>IF(H15="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T15" s="20" t="n">
+      <c r="T15" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="AD15" s="20">
+      <c r="AD15" s="21">
         <f>IF($G15="",NA(),IF(OR($G15&gt;$J15,$G15&lt;$K15),$G15,NA()))</f>
         <v/>
       </c>
-      <c r="AE15" s="20">
+      <c r="AE15" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF15" s="20">
+      <c r="AF15" s="21">
         <f>IF($H15="",NA(),IF($H15&gt;$O15,$H15,NA()))</f>
         <v/>
       </c>
@@ -8934,19 +8938,19 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="30" t="n">
         <v>411</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="30" t="n">
         <v>401</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>438</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="30" t="n">
         <v>410</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="30" t="n">
         <v>401</v>
       </c>
       <c r="G16" s="17">
@@ -8969,34 +8973,34 @@
         <f>IF(G16="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>IF(G16="","",IF(OR(G16&gt;J16,G16&lt;K16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N16" s="32">
+      <c r="N16" s="33">
         <f>IF(H16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O16" s="32">
+      <c r="O16" s="33">
         <f>IF(H16="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P16" s="32">
+      <c r="P16" s="33">
         <f>IF(H16="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T16" s="20" t="n">
+      <c r="T16" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="AD16" s="20">
+      <c r="AD16" s="21">
         <f>IF($G16="",NA(),IF(OR($G16&gt;$J16,$G16&lt;$K16),$G16,NA()))</f>
         <v/>
       </c>
-      <c r="AE16" s="20">
+      <c r="AE16" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF16" s="20">
+      <c r="AF16" s="21">
         <f>IF($H16="",NA(),IF($H16&gt;$O16,$H16,NA()))</f>
         <v/>
       </c>
@@ -9007,19 +9011,19 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="30" t="n">
         <v>402</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="30" t="n">
         <v>440</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="30" t="n">
         <v>425</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="30" t="n">
         <v>402</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="30" t="n">
         <v>440</v>
       </c>
       <c r="G17" s="17">
@@ -9042,34 +9046,34 @@
         <f>IF(G17="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>IF(G17="","",IF(OR(G17&gt;J17,G17&lt;K17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N17" s="32">
+      <c r="N17" s="33">
         <f>IF(H17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O17" s="32">
+      <c r="O17" s="33">
         <f>IF(H17="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P17" s="32">
+      <c r="P17" s="33">
         <f>IF(H17="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T17" s="20" t="n">
+      <c r="T17" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="AD17" s="20">
+      <c r="AD17" s="21">
         <f>IF($G17="",NA(),IF(OR($G17&gt;$J17,$G17&lt;$K17),$G17,NA()))</f>
         <v/>
       </c>
-      <c r="AE17" s="20">
+      <c r="AE17" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF17" s="20">
+      <c r="AF17" s="21">
         <f>IF($H17="",NA(),IF($H17&gt;$O17,$H17,NA()))</f>
         <v/>
       </c>
@@ -9080,19 +9084,19 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="30" t="n">
         <v>437</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="30" t="n">
         <v>437</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="30" t="n">
         <v>404</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="30" t="n">
         <v>437</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="30" t="n">
         <v>437</v>
       </c>
       <c r="G18" s="17">
@@ -9115,34 +9119,34 @@
         <f>IF(G18="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="20">
         <f>IF(G18="","",IF(OR(G18&gt;J18,G18&lt;K18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N18" s="32">
+      <c r="N18" s="33">
         <f>IF(H18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O18" s="32">
+      <c r="O18" s="33">
         <f>IF(H18="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P18" s="32">
+      <c r="P18" s="33">
         <f>IF(H18="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T18" s="20" t="n">
+      <c r="T18" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="AD18" s="20">
+      <c r="AD18" s="21">
         <f>IF($G18="",NA(),IF(OR($G18&gt;$J18,$G18&lt;$K18),$G18,NA()))</f>
         <v/>
       </c>
-      <c r="AE18" s="20">
+      <c r="AE18" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF18" s="20">
+      <c r="AF18" s="21">
         <f>IF($H18="",NA(),IF($H18&gt;$O18,$H18,NA()))</f>
         <v/>
       </c>
@@ -9153,19 +9157,19 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="30" t="n">
         <v>392</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="30" t="n">
         <v>415</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="30" t="n">
         <v>392</v>
       </c>
       <c r="G19" s="17">
@@ -9188,34 +9192,34 @@
         <f>IF(G19="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="20">
         <f>IF(G19="","",IF(OR(G19&gt;J19,G19&lt;K19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N19" s="32">
+      <c r="N19" s="33">
         <f>IF(H19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="32">
+      <c r="O19" s="33">
         <f>IF(H19="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P19" s="32">
+      <c r="P19" s="33">
         <f>IF(H19="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T19" s="20" t="n">
+      <c r="T19" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="AD19" s="20">
+      <c r="AD19" s="21">
         <f>IF($G19="",NA(),IF(OR($G19&gt;$J19,$G19&lt;$K19),$G19,NA()))</f>
         <v/>
       </c>
-      <c r="AE19" s="20">
+      <c r="AE19" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF19" s="20">
+      <c r="AF19" s="21">
         <f>IF($H19="",NA(),IF($H19&gt;$O19,$H19,NA()))</f>
         <v/>
       </c>
@@ -9226,19 +9230,19 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="30" t="n">
         <v>406</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <v>433</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="30" t="n">
         <v>406</v>
       </c>
       <c r="G20" s="17">
@@ -9261,34 +9265,34 @@
         <f>IF(G20="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="20">
         <f>IF(G20="","",IF(OR(G20&gt;J20,G20&lt;K20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N20" s="32">
+      <c r="N20" s="33">
         <f>IF(H20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="32">
+      <c r="O20" s="33">
         <f>IF(H20="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P20" s="32">
+      <c r="P20" s="33">
         <f>IF(H20="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T20" s="20" t="n">
+      <c r="T20" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="AD20" s="20">
+      <c r="AD20" s="21">
         <f>IF($G20="",NA(),IF(OR($G20&gt;$J20,$G20&lt;$K20),$G20,NA()))</f>
         <v/>
       </c>
-      <c r="AE20" s="20">
+      <c r="AE20" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF20" s="20">
+      <c r="AF20" s="21">
         <f>IF($H20="",NA(),IF($H20&gt;$O20,$H20,NA()))</f>
         <v/>
       </c>
@@ -9299,19 +9303,19 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="30" t="n">
         <v>431</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="30" t="n">
         <v>401</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="30" t="n">
         <v>431</v>
       </c>
       <c r="G21" s="17">
@@ -9334,34 +9338,34 @@
         <f>IF(G21="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="20">
         <f>IF(G21="","",IF(OR(G21&gt;J21,G21&lt;K21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <f>IF(H21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <f>IF(H21="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <f>IF(H21="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T21" s="20" t="n">
+      <c r="T21" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="AD21" s="20">
+      <c r="AD21" s="21">
         <f>IF($G21="",NA(),IF(OR($G21&gt;$J21,$G21&lt;$K21),$G21,NA()))</f>
         <v/>
       </c>
-      <c r="AE21" s="20">
+      <c r="AE21" s="21">
         <f>IF(COUNT($G14:$G21)&lt;8,NA(),IF(OR(MIN($G14:$G21)&gt;$B$6,MAX($G14:$G21)&lt;$B$6),$G21,NA()))</f>
         <v/>
       </c>
-      <c r="AF21" s="20">
+      <c r="AF21" s="21">
         <f>IF($H21="",NA(),IF($H21&gt;$O21,$H21,NA()))</f>
         <v/>
       </c>
@@ -9372,19 +9376,19 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="30" t="n">
         <v>425</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="30" t="n">
         <v>407</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="30" t="n">
         <v>387</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="30" t="n">
         <v>425</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="30" t="n">
         <v>406</v>
       </c>
       <c r="G22" s="17">
@@ -9407,34 +9411,34 @@
         <f>IF(G22="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="20">
         <f>IF(G22="","",IF(OR(G22&gt;J22,G22&lt;K22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <f>IF(H22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <f>IF(H22="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <f>IF(H22="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T22" s="20" t="n">
+      <c r="T22" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="21">
         <f>IF($G22="",NA(),IF(OR($G22&gt;$J22,$G22&lt;$K22),$G22,NA()))</f>
         <v/>
       </c>
-      <c r="AE22" s="20">
+      <c r="AE22" s="21">
         <f>IF(COUNT($G15:$G22)&lt;8,NA(),IF(OR(MIN($G15:$G22)&gt;$B$6,MAX($G15:$G22)&lt;$B$6),$G22,NA()))</f>
         <v/>
       </c>
-      <c r="AF22" s="20">
+      <c r="AF22" s="21">
         <f>IF($H22="",NA(),IF($H22&gt;$O22,$H22,NA()))</f>
         <v/>
       </c>
@@ -9445,19 +9449,19 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="30" t="n">
         <v>413</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="30" t="n">
         <v>382</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="30" t="n">
         <v>417</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="30" t="n">
         <v>412</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="30" t="n">
         <v>382</v>
       </c>
       <c r="G23" s="17">
@@ -9480,34 +9484,34 @@
         <f>IF(G23="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="20">
         <f>IF(G23="","",IF(OR(G23&gt;J23,G23&lt;K23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N23" s="32">
+      <c r="N23" s="33">
         <f>IF(H23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="32">
+      <c r="O23" s="33">
         <f>IF(H23="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P23" s="32">
+      <c r="P23" s="33">
         <f>IF(H23="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T23" s="20" t="n">
+      <c r="T23" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="AD23" s="20">
+      <c r="AD23" s="21">
         <f>IF($G23="",NA(),IF(OR($G23&gt;$J23,$G23&lt;$K23),$G23,NA()))</f>
         <v/>
       </c>
-      <c r="AE23" s="20">
+      <c r="AE23" s="21">
         <f>IF(COUNT($G16:$G23)&lt;8,NA(),IF(OR(MIN($G16:$G23)&gt;$B$6,MAX($G16:$G23)&lt;$B$6),$G23,NA()))</f>
         <v/>
       </c>
-      <c r="AF23" s="20">
+      <c r="AF23" s="21">
         <f>IF($H23="",NA(),IF($H23&gt;$O23,$H23,NA()))</f>
         <v/>
       </c>
@@ -9518,19 +9522,19 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="30" t="n">
         <v>367</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="30" t="n">
         <v>393</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="30" t="n">
         <v>404</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="30" t="n">
         <v>367</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="30" t="n">
         <v>394</v>
       </c>
       <c r="G24" s="17">
@@ -9553,34 +9557,34 @@
         <f>IF(G24="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="20">
         <f>IF(G24="","",IF(OR(G24&gt;J24,G24&lt;K24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <f>IF(H24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <f>IF(H24="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <f>IF(H24="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T24" s="20" t="n">
+      <c r="T24" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="AD24" s="20">
+      <c r="AD24" s="21">
         <f>IF($G24="",NA(),IF(OR($G24&gt;$J24,$G24&lt;$K24),$G24,NA()))</f>
         <v/>
       </c>
-      <c r="AE24" s="20">
+      <c r="AE24" s="21">
         <f>IF(COUNT($G17:$G24)&lt;8,NA(),IF(OR(MIN($G17:$G24)&gt;$B$6,MAX($G17:$G24)&lt;$B$6),$G24,NA()))</f>
         <v/>
       </c>
-      <c r="AF24" s="20">
+      <c r="AF24" s="21">
         <f>IF($H24="",NA(),IF($H24&gt;$O24,$H24,NA()))</f>
         <v/>
       </c>
@@ -9591,19 +9595,19 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="30" t="n">
         <v>386</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="30" t="n">
         <v>410</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="30" t="n">
         <v>372</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="30" t="n">
         <v>386</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="30" t="n">
         <v>409</v>
       </c>
       <c r="G25" s="17">
@@ -9626,34 +9630,34 @@
         <f>IF(G25="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="20">
         <f>IF(G25="","",IF(OR(G25&gt;J25,G25&lt;K25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <f>IF(H25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <f>IF(H25="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <f>IF(H25="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T25" s="20" t="n">
+      <c r="T25" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="AD25" s="20">
+      <c r="AD25" s="21">
         <f>IF($G25="",NA(),IF(OR($G25&gt;$J25,$G25&lt;$K25),$G25,NA()))</f>
         <v/>
       </c>
-      <c r="AE25" s="20">
+      <c r="AE25" s="21">
         <f>IF(COUNT($G18:$G25)&lt;8,NA(),IF(OR(MIN($G18:$G25)&gt;$B$6,MAX($G18:$G25)&lt;$B$6),$G25,NA()))</f>
         <v/>
       </c>
-      <c r="AF25" s="20">
+      <c r="AF25" s="21">
         <f>IF($H25="",NA(),IF($H25&gt;$O25,$H25,NA()))</f>
         <v/>
       </c>
@@ -9664,19 +9668,19 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="30" t="n">
         <v>415</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="30" t="n">
         <v>382</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="30" t="n">
         <v>381</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="30" t="n">
         <v>415</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="30" t="n">
         <v>382</v>
       </c>
       <c r="G26" s="17">
@@ -9699,34 +9703,34 @@
         <f>IF(G26="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="20">
         <f>IF(G26="","",IF(OR(G26&gt;J26,G26&lt;K26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N26" s="32">
+      <c r="N26" s="33">
         <f>IF(H26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O26" s="32">
+      <c r="O26" s="33">
         <f>IF(H26="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P26" s="32">
+      <c r="P26" s="33">
         <f>IF(H26="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T26" s="20" t="n">
+      <c r="T26" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="AD26" s="20">
+      <c r="AD26" s="21">
         <f>IF($G26="",NA(),IF(OR($G26&gt;$J26,$G26&lt;$K26),$G26,NA()))</f>
         <v/>
       </c>
-      <c r="AE26" s="20">
+      <c r="AE26" s="21">
         <f>IF(COUNT($G19:$G26)&lt;8,NA(),IF(OR(MIN($G19:$G26)&gt;$B$6,MAX($G19:$G26)&lt;$B$6),$G26,NA()))</f>
         <v/>
       </c>
-      <c r="AF26" s="20">
+      <c r="AF26" s="21">
         <f>IF($H26="",NA(),IF($H26&gt;$O26,$H26,NA()))</f>
         <v/>
       </c>
@@ -9737,19 +9741,19 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="30" t="n">
         <v>381</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="30" t="n">
         <v>419</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="30" t="n">
         <v>381</v>
       </c>
       <c r="G27" s="17">
@@ -9772,34 +9776,34 @@
         <f>IF(G27="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="20">
         <f>IF(G27="","",IF(OR(G27&gt;J27,G27&lt;K27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="33">
         <f>IF(H27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="33">
         <f>IF(H27="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="33">
         <f>IF(H27="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T27" s="20" t="n">
+      <c r="T27" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="AD27" s="20">
+      <c r="AD27" s="21">
         <f>IF($G27="",NA(),IF(OR($G27&gt;$J27,$G27&lt;$K27),$G27,NA()))</f>
         <v/>
       </c>
-      <c r="AE27" s="20">
+      <c r="AE27" s="21">
         <f>IF(COUNT($G20:$G27)&lt;8,NA(),IF(OR(MIN($G20:$G27)&gt;$B$6,MAX($G20:$G27)&lt;$B$6),$G27,NA()))</f>
         <v/>
       </c>
-      <c r="AF27" s="20">
+      <c r="AF27" s="21">
         <f>IF($H27="",NA(),IF($H27&gt;$O27,$H27,NA()))</f>
         <v/>
       </c>
@@ -9810,19 +9814,19 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="30" t="n">
         <v>385</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="30" t="n">
         <v>421</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="30" t="n">
         <v>412</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="30" t="n">
         <v>385</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="30" t="n">
         <v>421</v>
       </c>
       <c r="G28" s="17">
@@ -9845,34 +9849,34 @@
         <f>IF(G28="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="20">
         <f>IF(G28="","",IF(OR(G28&gt;J28,G28&lt;K28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="33">
         <f>IF(H28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="33">
         <f>IF(H28="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="33">
         <f>IF(H28="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T28" s="20" t="n">
+      <c r="T28" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="AD28" s="20">
+      <c r="AD28" s="21">
         <f>IF($G28="",NA(),IF(OR($G28&gt;$J28,$G28&lt;$K28),$G28,NA()))</f>
         <v/>
       </c>
-      <c r="AE28" s="20">
+      <c r="AE28" s="21">
         <f>IF(COUNT($G21:$G28)&lt;8,NA(),IF(OR(MIN($G21:$G28)&gt;$B$6,MAX($G21:$G28)&lt;$B$6),$G28,NA()))</f>
         <v/>
       </c>
-      <c r="AF28" s="20">
+      <c r="AF28" s="21">
         <f>IF($H28="",NA(),IF($H28&gt;$O28,$H28,NA()))</f>
         <v/>
       </c>
@@ -9883,19 +9887,19 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="30" t="n">
         <v>407</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="30" t="n">
         <v>413</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="30" t="n">
         <v>378</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="30" t="n">
         <v>408</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="30" t="n">
         <v>413</v>
       </c>
       <c r="G29" s="17">
@@ -9918,34 +9922,34 @@
         <f>IF(G29="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="20">
         <f>IF(G29="","",IF(OR(G29&gt;J29,G29&lt;K29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="33">
         <f>IF(H29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="33">
         <f>IF(H29="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P29" s="32">
+      <c r="P29" s="33">
         <f>IF(H29="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T29" s="20" t="n">
+      <c r="T29" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="AD29" s="20">
+      <c r="AD29" s="21">
         <f>IF($G29="",NA(),IF(OR($G29&gt;$J29,$G29&lt;$K29),$G29,NA()))</f>
         <v/>
       </c>
-      <c r="AE29" s="20">
+      <c r="AE29" s="21">
         <f>IF(COUNT($G22:$G29)&lt;8,NA(),IF(OR(MIN($G22:$G29)&gt;$B$6,MAX($G22:$G29)&lt;$B$6),$G29,NA()))</f>
         <v/>
       </c>
-      <c r="AF29" s="20">
+      <c r="AF29" s="21">
         <f>IF($H29="",NA(),IF($H29&gt;$O29,$H29,NA()))</f>
         <v/>
       </c>
@@ -9956,19 +9960,19 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="30" t="n">
         <v>428</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="30" t="n">
         <v>389</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="30" t="n">
         <v>408</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="30" t="n">
         <v>427</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="30" t="n">
         <v>389</v>
       </c>
       <c r="G30" s="17">
@@ -9991,34 +9995,34 @@
         <f>IF(G30="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="20">
         <f>IF(G30="","",IF(OR(G30&gt;J30,G30&lt;K30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="33">
         <f>IF(H30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="33">
         <f>IF(H30="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P30" s="32">
+      <c r="P30" s="33">
         <f>IF(H30="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T30" s="20" t="n">
+      <c r="T30" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="AD30" s="20">
+      <c r="AD30" s="21">
         <f>IF($G30="",NA(),IF(OR($G30&gt;$J30,$G30&lt;$K30),$G30,NA()))</f>
         <v/>
       </c>
-      <c r="AE30" s="20">
+      <c r="AE30" s="21">
         <f>IF(COUNT($G23:$G30)&lt;8,NA(),IF(OR(MIN($G23:$G30)&gt;$B$6,MAX($G23:$G30)&lt;$B$6),$G30,NA()))</f>
         <v/>
       </c>
-      <c r="AF30" s="20">
+      <c r="AF30" s="21">
         <f>IF($H30="",NA(),IF($H30&gt;$O30,$H30,NA()))</f>
         <v/>
       </c>
@@ -10029,19 +10033,19 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="30" t="n">
         <v>407</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="30" t="n">
         <v>438</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="30" t="n">
         <v>407</v>
       </c>
       <c r="G31" s="17">
@@ -10064,34 +10068,34 @@
         <f>IF(G31="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="20">
         <f>IF(G31="","",IF(OR(G31&gt;J31,G31&lt;K31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N31" s="32">
+      <c r="N31" s="33">
         <f>IF(H31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O31" s="32">
+      <c r="O31" s="33">
         <f>IF(H31="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P31" s="32">
+      <c r="P31" s="33">
         <f>IF(H31="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T31" s="20" t="n">
+      <c r="T31" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="AD31" s="20">
+      <c r="AD31" s="21">
         <f>IF($G31="",NA(),IF(OR($G31&gt;$J31,$G31&lt;$K31),$G31,NA()))</f>
         <v/>
       </c>
-      <c r="AE31" s="20">
+      <c r="AE31" s="21">
         <f>IF(COUNT($G24:$G31)&lt;8,NA(),IF(OR(MIN($G24:$G31)&gt;$B$6,MAX($G24:$G31)&lt;$B$6),$G31,NA()))</f>
         <v/>
       </c>
-      <c r="AF31" s="20">
+      <c r="AF31" s="21">
         <f>IF($H31="",NA(),IF($H31&gt;$O31,$H31,NA()))</f>
         <v/>
       </c>
@@ -10102,19 +10106,19 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="30" t="n">
         <v>406</v>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="30" t="n">
         <v>443</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="30" t="n">
         <v>417</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="30" t="n">
         <v>406</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="30" t="n">
         <v>443</v>
       </c>
       <c r="G32" s="17">
@@ -10137,34 +10141,34 @@
         <f>IF(G32="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="20">
         <f>IF(G32="","",IF(OR(G32&gt;J32,G32&lt;K32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N32" s="32">
+      <c r="N32" s="33">
         <f>IF(H32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O32" s="32">
+      <c r="O32" s="33">
         <f>IF(H32="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P32" s="32">
+      <c r="P32" s="33">
         <f>IF(H32="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T32" s="20" t="n">
+      <c r="T32" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="AD32" s="20">
+      <c r="AD32" s="21">
         <f>IF($G32="",NA(),IF(OR($G32&gt;$J32,$G32&lt;$K32),$G32,NA()))</f>
         <v/>
       </c>
-      <c r="AE32" s="20">
+      <c r="AE32" s="21">
         <f>IF(COUNT($G25:$G32)&lt;8,NA(),IF(OR(MIN($G25:$G32)&gt;$B$6,MAX($G25:$G32)&lt;$B$6),$G32,NA()))</f>
         <v/>
       </c>
-      <c r="AF32" s="20">
+      <c r="AF32" s="21">
         <f>IF($H32="",NA(),IF($H32&gt;$O32,$H32,NA()))</f>
         <v/>
       </c>
@@ -10175,19 +10179,19 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="30" t="n">
         <v>443</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="30" t="n">
         <v>429</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="30" t="n">
         <v>405</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="30" t="n">
         <v>443</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="30" t="n">
         <v>429</v>
       </c>
       <c r="G33" s="17">
@@ -10210,34 +10214,34 @@
         <f>IF(G33="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="20">
         <f>IF(G33="","",IF(OR(G33&gt;J33,G33&lt;K33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N33" s="32">
+      <c r="N33" s="33">
         <f>IF(H33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O33" s="32">
+      <c r="O33" s="33">
         <f>IF(H33="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P33" s="32">
+      <c r="P33" s="33">
         <f>IF(H33="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T33" s="20" t="n">
+      <c r="T33" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="AD33" s="20">
+      <c r="AD33" s="21">
         <f>IF($G33="",NA(),IF(OR($G33&gt;$J33,$G33&lt;$K33),$G33,NA()))</f>
         <v/>
       </c>
-      <c r="AE33" s="20">
+      <c r="AE33" s="21">
         <f>IF(COUNT($G26:$G33)&lt;8,NA(),IF(OR(MIN($G26:$G33)&gt;$B$6,MAX($G26:$G33)&lt;$B$6),$G33,NA()))</f>
         <v/>
       </c>
-      <c r="AF33" s="20">
+      <c r="AF33" s="21">
         <f>IF($H33="",NA(),IF($H33&gt;$O33,$H33,NA()))</f>
         <v/>
       </c>
@@ -10248,19 +10252,19 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="30" t="n">
         <v>424</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="30" t="n">
         <v>390</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="30" t="n">
         <v>423</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="30" t="n">
         <v>424</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="30" t="n">
         <v>390</v>
       </c>
       <c r="G34" s="17">
@@ -10283,34 +10287,34 @@
         <f>IF(G34="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="20">
         <f>IF(G34="","",IF(OR(G34&gt;J34,G34&lt;K34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N34" s="32">
+      <c r="N34" s="33">
         <f>IF(H34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O34" s="32">
+      <c r="O34" s="33">
         <f>IF(H34="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P34" s="32">
+      <c r="P34" s="33">
         <f>IF(H34="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T34" s="20" t="n">
+      <c r="T34" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="21">
         <f>IF($G34="",NA(),IF(OR($G34&gt;$J34,$G34&lt;$K34),$G34,NA()))</f>
         <v/>
       </c>
-      <c r="AE34" s="20">
+      <c r="AE34" s="21">
         <f>IF(COUNT($G27:$G34)&lt;8,NA(),IF(OR(MIN($G27:$G34)&gt;$B$6,MAX($G27:$G34)&lt;$B$6),$G34,NA()))</f>
         <v/>
       </c>
-      <c r="AF34" s="20">
+      <c r="AF34" s="21">
         <f>IF($H34="",NA(),IF($H34&gt;$O34,$H34,NA()))</f>
         <v/>
       </c>
@@ -10321,19 +10325,19 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="30" t="n">
         <v>392</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="30" t="n">
         <v>414</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="30" t="n">
         <v>392</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="30" t="n">
         <v>414</v>
       </c>
       <c r="G35" s="17">
@@ -10356,34 +10360,34 @@
         <f>IF(G35="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="20">
         <f>IF(G35="","",IF(OR(G35&gt;J35,G35&lt;K35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N35" s="32">
+      <c r="N35" s="33">
         <f>IF(H35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O35" s="32">
+      <c r="O35" s="33">
         <f>IF(H35="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P35" s="32">
+      <c r="P35" s="33">
         <f>IF(H35="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T35" s="20" t="n">
+      <c r="T35" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="AD35" s="20">
+      <c r="AD35" s="21">
         <f>IF($G35="",NA(),IF(OR($G35&gt;$J35,$G35&lt;$K35),$G35,NA()))</f>
         <v/>
       </c>
-      <c r="AE35" s="20">
+      <c r="AE35" s="21">
         <f>IF(COUNT($G28:$G35)&lt;8,NA(),IF(OR(MIN($G28:$G35)&gt;$B$6,MAX($G28:$G35)&lt;$B$6),$G35,NA()))</f>
         <v/>
       </c>
-      <c r="AF35" s="20">
+      <c r="AF35" s="21">
         <f>IF($H35="",NA(),IF($H35&gt;$O35,$H35,NA()))</f>
         <v/>
       </c>
@@ -10394,19 +10398,19 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="30" t="n">
         <v>431</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="30" t="n">
         <v>394</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="30" t="n">
         <v>431</v>
       </c>
       <c r="G36" s="17">
@@ -10429,34 +10433,34 @@
         <f>IF(G36="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="20">
         <f>IF(G36="","",IF(OR(G36&gt;J36,G36&lt;K36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N36" s="32">
+      <c r="N36" s="33">
         <f>IF(H36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O36" s="32">
+      <c r="O36" s="33">
         <f>IF(H36="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P36" s="32">
+      <c r="P36" s="33">
         <f>IF(H36="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T36" s="20" t="n">
+      <c r="T36" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="21">
         <f>IF($G36="",NA(),IF(OR($G36&gt;$J36,$G36&lt;$K36),$G36,NA()))</f>
         <v/>
       </c>
-      <c r="AE36" s="20">
+      <c r="AE36" s="21">
         <f>IF(COUNT($G29:$G36)&lt;8,NA(),IF(OR(MIN($G29:$G36)&gt;$B$6,MAX($G29:$G36)&lt;$B$6),$G36,NA()))</f>
         <v/>
       </c>
-      <c r="AF36" s="20">
+      <c r="AF36" s="21">
         <f>IF($H36="",NA(),IF($H36&gt;$O36,$H36,NA()))</f>
         <v/>
       </c>
@@ -10467,19 +10471,19 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="30" t="n">
         <v>428</v>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="30" t="n">
         <v>399</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="30" t="n">
         <v>393</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="30" t="n">
         <v>429</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="30" t="n">
         <v>399</v>
       </c>
       <c r="G37" s="17">
@@ -10502,34 +10506,34 @@
         <f>IF(G37="","",$B$6-$B$8*$B$7)</f>
         <v/>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="20">
         <f>IF(G37="","",IF(OR(G37&gt;J37,G37&lt;K37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N37" s="32">
+      <c r="N37" s="33">
         <f>IF(H37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O37" s="32">
+      <c r="O37" s="33">
         <f>IF(H37="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P37" s="32">
+      <c r="P37" s="33">
         <f>IF(H37="","",$B$10*$B$7)</f>
         <v/>
       </c>
-      <c r="T37" s="20" t="n">
+      <c r="T37" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="AD37" s="20">
+      <c r="AD37" s="21">
         <f>IF($G37="",NA(),IF(OR($G37&gt;$J37,$G37&lt;$K37),$G37,NA()))</f>
         <v/>
       </c>
-      <c r="AE37" s="20">
+      <c r="AE37" s="21">
         <f>IF(COUNT($G30:$G37)&lt;8,NA(),IF(OR(MIN($G30:$G37)&gt;$B$6,MAX($G30:$G37)&lt;$B$6),$G37,NA()))</f>
         <v/>
       </c>
-      <c r="AF37" s="20">
+      <c r="AF37" s="21">
         <f>IF($H37="",NA(),IF($H37&gt;$O37,$H37,NA()))</f>
         <v/>
       </c>
@@ -10620,7 +10624,7 @@
           <t>Lambda (weight on the newest point)</t>
         </is>
       </c>
-      <c r="B5" s="33" t="n">
+      <c r="B5" s="34" t="n">
         <v>0.2</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -10635,7 +10639,7 @@
           <t>L (limit width in sigmas)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>2.7</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -10696,10 +10700,10 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Your data — one row per period, oldest first</t>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Your data — one row per period, oldest first  ·  Key: CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>
       <c r="B14" s="10" t="n"/>
@@ -10765,7 +10769,7 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>408</v>
       </c>
       <c r="D16" s="17">
@@ -10784,11 +10788,11 @@
         <f>IF(B16="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*1))))</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>IF(D16="","",IF(OR(D16&gt;F16,D16&lt;G16),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD16" s="20">
+      <c r="AD16" s="21">
         <f>IF($D16="",NA(),IF(OR($D16&gt;$F16,$D16&lt;$G16),$D16,NA()))</f>
         <v/>
       </c>
@@ -10799,7 +10803,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n">
+      <c r="B17" s="22" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="17">
@@ -10822,11 +10826,11 @@
         <f>IF(B17="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*2))))</f>
         <v/>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="20">
         <f>IF(D17="","",IF(OR(D17&gt;F17,D17&lt;G17),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD17" s="20">
+      <c r="AD17" s="21">
         <f>IF($D17="",NA(),IF(OR($D17&gt;$F17,$D17&lt;$G17),$D17,NA()))</f>
         <v/>
       </c>
@@ -10837,7 +10841,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n">
+      <c r="B18" s="22" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="17">
@@ -10860,11 +10864,11 @@
         <f>IF(B18="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*3))))</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <f>IF(D18="","",IF(OR(D18&gt;F18,D18&lt;G18),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD18" s="20">
+      <c r="AD18" s="21">
         <f>IF($D18="",NA(),IF(OR($D18&gt;$F18,$D18&lt;$G18),$D18,NA()))</f>
         <v/>
       </c>
@@ -10875,7 +10879,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n">
+      <c r="B19" s="22" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="17">
@@ -10898,11 +10902,11 @@
         <f>IF(B19="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*4))))</f>
         <v/>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <f>IF(D19="","",IF(OR(D19&gt;F19,D19&lt;G19),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD19" s="20">
+      <c r="AD19" s="21">
         <f>IF($D19="",NA(),IF(OR($D19&gt;$F19,$D19&lt;$G19),$D19,NA()))</f>
         <v/>
       </c>
@@ -10913,7 +10917,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="22" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="17">
@@ -10936,11 +10940,11 @@
         <f>IF(B20="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*5))))</f>
         <v/>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="20">
         <f>IF(D20="","",IF(OR(D20&gt;F20,D20&lt;G20),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD20" s="20">
+      <c r="AD20" s="21">
         <f>IF($D20="",NA(),IF(OR($D20&gt;$F20,$D20&lt;$G20),$D20,NA()))</f>
         <v/>
       </c>
@@ -10951,7 +10955,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="22" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="17">
@@ -10974,11 +10978,11 @@
         <f>IF(B21="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*6))))</f>
         <v/>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="20">
         <f>IF(D21="","",IF(OR(D21&gt;F21,D21&lt;G21),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD21" s="20">
+      <c r="AD21" s="21">
         <f>IF($D21="",NA(),IF(OR($D21&gt;$F21,$D21&lt;$G21),$D21,NA()))</f>
         <v/>
       </c>
@@ -10989,7 +10993,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="22" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="17">
@@ -11012,11 +11016,11 @@
         <f>IF(B22="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*7))))</f>
         <v/>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="20">
         <f>IF(D22="","",IF(OR(D22&gt;F22,D22&lt;G22),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="21">
         <f>IF($D22="",NA(),IF(OR($D22&gt;$F22,$D22&lt;$G22),$D22,NA()))</f>
         <v/>
       </c>
@@ -11027,7 +11031,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="22" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="17">
@@ -11050,11 +11054,11 @@
         <f>IF(B23="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*8))))</f>
         <v/>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="20">
         <f>IF(D23="","",IF(OR(D23&gt;F23,D23&lt;G23),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD23" s="20">
+      <c r="AD23" s="21">
         <f>IF($D23="",NA(),IF(OR($D23&gt;$F23,$D23&lt;$G23),$D23,NA()))</f>
         <v/>
       </c>
@@ -11065,7 +11069,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="22" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="17">
@@ -11088,11 +11092,11 @@
         <f>IF(B24="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*9))))</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>IF(D24="","",IF(OR(D24&gt;F24,D24&lt;G24),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD24" s="20">
+      <c r="AD24" s="21">
         <f>IF($D24="",NA(),IF(OR($D24&gt;$F24,$D24&lt;$G24),$D24,NA()))</f>
         <v/>
       </c>
@@ -11103,7 +11107,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="22" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="17">
@@ -11126,11 +11130,11 @@
         <f>IF(B25="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*10))))</f>
         <v/>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <f>IF(D25="","",IF(OR(D25&gt;F25,D25&lt;G25),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD25" s="20">
+      <c r="AD25" s="21">
         <f>IF($D25="",NA(),IF(OR($D25&gt;$F25,$D25&lt;$G25),$D25,NA()))</f>
         <v/>
       </c>
@@ -11141,7 +11145,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="22" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="17">
@@ -11164,11 +11168,11 @@
         <f>IF(B26="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*11))))</f>
         <v/>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <f>IF(D26="","",IF(OR(D26&gt;F26,D26&lt;G26),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD26" s="20">
+      <c r="AD26" s="21">
         <f>IF($D26="",NA(),IF(OR($D26&gt;$F26,$D26&lt;$G26),$D26,NA()))</f>
         <v/>
       </c>
@@ -11179,7 +11183,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="22" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="17">
@@ -11202,11 +11206,11 @@
         <f>IF(B27="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*12))))</f>
         <v/>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="20">
         <f>IF(D27="","",IF(OR(D27&gt;F27,D27&lt;G27),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD27" s="20">
+      <c r="AD27" s="21">
         <f>IF($D27="",NA(),IF(OR($D27&gt;$F27,$D27&lt;$G27),$D27,NA()))</f>
         <v/>
       </c>
@@ -11217,7 +11221,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
+      <c r="B28" s="22" t="n">
         <v>418</v>
       </c>
       <c r="C28" s="17">
@@ -11240,11 +11244,11 @@
         <f>IF(B28="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*13))))</f>
         <v/>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="20">
         <f>IF(D28="","",IF(OR(D28&gt;F28,D28&lt;G28),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD28" s="20">
+      <c r="AD28" s="21">
         <f>IF($D28="",NA(),IF(OR($D28&gt;$F28,$D28&lt;$G28),$D28,NA()))</f>
         <v/>
       </c>
@@ -11255,7 +11259,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n">
+      <c r="B29" s="22" t="n">
         <v>426</v>
       </c>
       <c r="C29" s="17">
@@ -11278,11 +11282,11 @@
         <f>IF(B29="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*14))))</f>
         <v/>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="20">
         <f>IF(D29="","",IF(OR(D29&gt;F29,D29&lt;G29),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD29" s="20">
+      <c r="AD29" s="21">
         <f>IF($D29="",NA(),IF(OR($D29&gt;$F29,$D29&lt;$G29),$D29,NA()))</f>
         <v/>
       </c>
@@ -11293,7 +11297,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
+      <c r="B30" s="22" t="n">
         <v>431</v>
       </c>
       <c r="C30" s="17">
@@ -11316,11 +11320,11 @@
         <f>IF(B30="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*15))))</f>
         <v/>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <f>IF(D30="","",IF(OR(D30&gt;F30,D30&lt;G30),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD30" s="20">
+      <c r="AD30" s="21">
         <f>IF($D30="",NA(),IF(OR($D30&gt;$F30,$D30&lt;$G30),$D30,NA()))</f>
         <v/>
       </c>
@@ -11331,7 +11335,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
+      <c r="B31" s="22" t="n">
         <v>428</v>
       </c>
       <c r="C31" s="17">
@@ -11354,11 +11358,11 @@
         <f>IF(B31="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*16))))</f>
         <v/>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="20">
         <f>IF(D31="","",IF(OR(D31&gt;F31,D31&lt;G31),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD31" s="20">
+      <c r="AD31" s="21">
         <f>IF($D31="",NA(),IF(OR($D31&gt;$F31,$D31&lt;$G31),$D31,NA()))</f>
         <v/>
       </c>
@@ -11369,7 +11373,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
+      <c r="B32" s="22" t="n">
         <v>437</v>
       </c>
       <c r="C32" s="17">
@@ -11392,11 +11396,11 @@
         <f>IF(B32="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*17))))</f>
         <v/>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="20">
         <f>IF(D32="","",IF(OR(D32&gt;F32,D32&lt;G32),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD32" s="20">
+      <c r="AD32" s="21">
         <f>IF($D32="",NA(),IF(OR($D32&gt;$F32,$D32&lt;$G32),$D32,NA()))</f>
         <v/>
       </c>
@@ -11407,7 +11411,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
+      <c r="B33" s="22" t="n">
         <v>433</v>
       </c>
       <c r="C33" s="17">
@@ -11430,11 +11434,11 @@
         <f>IF(B33="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*18))))</f>
         <v/>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="20">
         <f>IF(D33="","",IF(OR(D33&gt;F33,D33&lt;G33),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD33" s="20">
+      <c r="AD33" s="21">
         <f>IF($D33="",NA(),IF(OR($D33&gt;$F33,$D33&lt;$G33),$D33,NA()))</f>
         <v/>
       </c>
@@ -11445,7 +11449,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
+      <c r="B34" s="22" t="n">
         <v>441</v>
       </c>
       <c r="C34" s="17">
@@ -11468,11 +11472,11 @@
         <f>IF(B34="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*19))))</f>
         <v/>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="20">
         <f>IF(D34="","",IF(OR(D34&gt;F34,D34&lt;G34),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="21">
         <f>IF($D34="",NA(),IF(OR($D34&gt;$F34,$D34&lt;$G34),$D34,NA()))</f>
         <v/>
       </c>
@@ -11483,7 +11487,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
+      <c r="B35" s="22" t="n">
         <v>439</v>
       </c>
       <c r="C35" s="17">
@@ -11506,11 +11510,11 @@
         <f>IF(B35="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*20))))</f>
         <v/>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <f>IF(D35="","",IF(OR(D35&gt;F35,D35&lt;G35),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD35" s="20">
+      <c r="AD35" s="21">
         <f>IF($D35="",NA(),IF(OR($D35&gt;$F35,$D35&lt;$G35),$D35,NA()))</f>
         <v/>
       </c>
@@ -11521,7 +11525,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
+      <c r="B36" s="22" t="n">
         <v>448</v>
       </c>
       <c r="C36" s="17">
@@ -11544,11 +11548,11 @@
         <f>IF(B36="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*21))))</f>
         <v/>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <f>IF(D36="","",IF(OR(D36&gt;F36,D36&lt;G36),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="21">
         <f>IF($D36="",NA(),IF(OR($D36&gt;$F36,$D36&lt;$G36),$D36,NA()))</f>
         <v/>
       </c>
@@ -11559,7 +11563,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
+      <c r="B37" s="22" t="n">
         <v>444</v>
       </c>
       <c r="C37" s="17">
@@ -11582,11 +11586,11 @@
         <f>IF(B37="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*22))))</f>
         <v/>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="20">
         <f>IF(D37="","",IF(OR(D37&gt;F37,D37&lt;G37),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD37" s="20">
+      <c r="AD37" s="21">
         <f>IF($D37="",NA(),IF(OR($D37&gt;$F37,$D37&lt;$G37),$D37,NA()))</f>
         <v/>
       </c>
@@ -11597,7 +11601,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
+      <c r="B38" s="22" t="n">
         <v>452</v>
       </c>
       <c r="C38" s="17">
@@ -11620,11 +11624,11 @@
         <f>IF(B38="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*23))))</f>
         <v/>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="20">
         <f>IF(D38="","",IF(OR(D38&gt;F38,D38&lt;G38),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD38" s="20">
+      <c r="AD38" s="21">
         <f>IF($D38="",NA(),IF(OR($D38&gt;$F38,$D38&lt;$G38),$D38,NA()))</f>
         <v/>
       </c>
@@ -11635,7 +11639,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
+      <c r="B39" s="22" t="n">
         <v>449</v>
       </c>
       <c r="C39" s="17">
@@ -11658,11 +11662,11 @@
         <f>IF(B39="","",$B$7-$B$6*$B$9*SQRT($B$5/(2-$B$5)*(1-(1-$B$5)^(2*24))))</f>
         <v/>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="20">
         <f>IF(D39="","",IF(OR(D39&gt;F39,D39&lt;G39),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
-      <c r="AD39" s="20">
+      <c r="AD39" s="21">
         <f>IF($D39="",NA(),IF(OR($D39&gt;$F39,$D39&lt;$G39),$D39,NA()))</f>
         <v/>
       </c>
@@ -11751,7 +11755,7 @@
           <t>k (slack, in sigmas)</t>
         </is>
       </c>
-      <c r="B5" s="33" t="n">
+      <c r="B5" s="34" t="n">
         <v>0.5</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -11766,7 +11770,7 @@
           <t>h (decision interval)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -11822,10 +11826,10 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Your data — one row per period, oldest first</t>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Your data — one row per period, oldest first  ·  Key: SL = service level, the share of contacts answered inside your target time</t>
         </is>
       </c>
       <c r="B14" s="10" t="n"/>
@@ -11895,7 +11899,7 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>408</v>
       </c>
       <c r="D16" s="17">
@@ -11918,11 +11922,11 @@
         <f>IF(B16="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>IF(E16="","",IF(E16&gt;$B$6,"SHIFT UP confirmed",IF(F16&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD16" s="20">
+      <c r="AD16" s="21">
         <f>IF($E16="",NA(),IF(OR($E16&gt;$B$6,$F16&gt;$B$6),MAX($E16,$F16),NA()))</f>
         <v/>
       </c>
@@ -11933,7 +11937,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n">
+      <c r="B17" s="22" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="17">
@@ -11960,11 +11964,11 @@
         <f>IF(B17="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="20">
         <f>IF(E17="","",IF(E17&gt;$B$6,"SHIFT UP confirmed",IF(F17&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD17" s="20">
+      <c r="AD17" s="21">
         <f>IF($E17="",NA(),IF(OR($E17&gt;$B$6,$F17&gt;$B$6),MAX($E17,$F17),NA()))</f>
         <v/>
       </c>
@@ -11975,7 +11979,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n">
+      <c r="B18" s="22" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="17">
@@ -12002,11 +12006,11 @@
         <f>IF(B18="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <f>IF(E18="","",IF(E18&gt;$B$6,"SHIFT UP confirmed",IF(F18&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD18" s="20">
+      <c r="AD18" s="21">
         <f>IF($E18="",NA(),IF(OR($E18&gt;$B$6,$F18&gt;$B$6),MAX($E18,$F18),NA()))</f>
         <v/>
       </c>
@@ -12017,7 +12021,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n">
+      <c r="B19" s="22" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="17">
@@ -12044,11 +12048,11 @@
         <f>IF(B19="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <f>IF(E19="","",IF(E19&gt;$B$6,"SHIFT UP confirmed",IF(F19&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD19" s="20">
+      <c r="AD19" s="21">
         <f>IF($E19="",NA(),IF(OR($E19&gt;$B$6,$F19&gt;$B$6),MAX($E19,$F19),NA()))</f>
         <v/>
       </c>
@@ -12059,7 +12063,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="22" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="17">
@@ -12086,11 +12090,11 @@
         <f>IF(B20="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="20">
         <f>IF(E20="","",IF(E20&gt;$B$6,"SHIFT UP confirmed",IF(F20&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD20" s="20">
+      <c r="AD20" s="21">
         <f>IF($E20="",NA(),IF(OR($E20&gt;$B$6,$F20&gt;$B$6),MAX($E20,$F20),NA()))</f>
         <v/>
       </c>
@@ -12101,7 +12105,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="22" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="17">
@@ -12128,11 +12132,11 @@
         <f>IF(B21="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="20">
         <f>IF(E21="","",IF(E21&gt;$B$6,"SHIFT UP confirmed",IF(F21&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD21" s="20">
+      <c r="AD21" s="21">
         <f>IF($E21="",NA(),IF(OR($E21&gt;$B$6,$F21&gt;$B$6),MAX($E21,$F21),NA()))</f>
         <v/>
       </c>
@@ -12143,7 +12147,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="22" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="17">
@@ -12170,11 +12174,11 @@
         <f>IF(B22="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="20">
         <f>IF(E22="","",IF(E22&gt;$B$6,"SHIFT UP confirmed",IF(F22&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="21">
         <f>IF($E22="",NA(),IF(OR($E22&gt;$B$6,$F22&gt;$B$6),MAX($E22,$F22),NA()))</f>
         <v/>
       </c>
@@ -12185,7 +12189,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="22" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="17">
@@ -12212,11 +12216,11 @@
         <f>IF(B23="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="20">
         <f>IF(E23="","",IF(E23&gt;$B$6,"SHIFT UP confirmed",IF(F23&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD23" s="20">
+      <c r="AD23" s="21">
         <f>IF($E23="",NA(),IF(OR($E23&gt;$B$6,$F23&gt;$B$6),MAX($E23,$F23),NA()))</f>
         <v/>
       </c>
@@ -12227,7 +12231,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="22" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="17">
@@ -12254,11 +12258,11 @@
         <f>IF(B24="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>IF(E24="","",IF(E24&gt;$B$6,"SHIFT UP confirmed",IF(F24&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD24" s="20">
+      <c r="AD24" s="21">
         <f>IF($E24="",NA(),IF(OR($E24&gt;$B$6,$F24&gt;$B$6),MAX($E24,$F24),NA()))</f>
         <v/>
       </c>
@@ -12269,7 +12273,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="22" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="17">
@@ -12296,11 +12300,11 @@
         <f>IF(B25="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <f>IF(E25="","",IF(E25&gt;$B$6,"SHIFT UP confirmed",IF(F25&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD25" s="20">
+      <c r="AD25" s="21">
         <f>IF($E25="",NA(),IF(OR($E25&gt;$B$6,$F25&gt;$B$6),MAX($E25,$F25),NA()))</f>
         <v/>
       </c>
@@ -12311,7 +12315,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="22" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="17">
@@ -12338,11 +12342,11 @@
         <f>IF(B26="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <f>IF(E26="","",IF(E26&gt;$B$6,"SHIFT UP confirmed",IF(F26&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD26" s="20">
+      <c r="AD26" s="21">
         <f>IF($E26="",NA(),IF(OR($E26&gt;$B$6,$F26&gt;$B$6),MAX($E26,$F26),NA()))</f>
         <v/>
       </c>
@@ -12353,7 +12357,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="22" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="17">
@@ -12380,11 +12384,11 @@
         <f>IF(B27="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="20">
         <f>IF(E27="","",IF(E27&gt;$B$6,"SHIFT UP confirmed",IF(F27&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD27" s="20">
+      <c r="AD27" s="21">
         <f>IF($E27="",NA(),IF(OR($E27&gt;$B$6,$F27&gt;$B$6),MAX($E27,$F27),NA()))</f>
         <v/>
       </c>
@@ -12395,7 +12399,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="21" t="n">
+      <c r="B28" s="22" t="n">
         <v>452</v>
       </c>
       <c r="C28" s="17">
@@ -12422,11 +12426,11 @@
         <f>IF(B28="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="20">
         <f>IF(E28="","",IF(E28&gt;$B$6,"SHIFT UP confirmed",IF(F28&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD28" s="20">
+      <c r="AD28" s="21">
         <f>IF($E28="",NA(),IF(OR($E28&gt;$B$6,$F28&gt;$B$6),MAX($E28,$F28),NA()))</f>
         <v/>
       </c>
@@ -12437,7 +12441,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="21" t="n">
+      <c r="B29" s="22" t="n">
         <v>461</v>
       </c>
       <c r="C29" s="17">
@@ -12464,11 +12468,11 @@
         <f>IF(B29="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="20">
         <f>IF(E29="","",IF(E29&gt;$B$6,"SHIFT UP confirmed",IF(F29&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD29" s="20">
+      <c r="AD29" s="21">
         <f>IF($E29="",NA(),IF(OR($E29&gt;$B$6,$F29&gt;$B$6),MAX($E29,$F29),NA()))</f>
         <v/>
       </c>
@@ -12479,7 +12483,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="21" t="n">
+      <c r="B30" s="22" t="n">
         <v>448</v>
       </c>
       <c r="C30" s="17">
@@ -12506,11 +12510,11 @@
         <f>IF(B30="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <f>IF(E30="","",IF(E30&gt;$B$6,"SHIFT UP confirmed",IF(F30&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD30" s="20">
+      <c r="AD30" s="21">
         <f>IF($E30="",NA(),IF(OR($E30&gt;$B$6,$F30&gt;$B$6),MAX($E30,$F30),NA()))</f>
         <v/>
       </c>
@@ -12521,7 +12525,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="21" t="n">
+      <c r="B31" s="22" t="n">
         <v>470</v>
       </c>
       <c r="C31" s="17">
@@ -12548,11 +12552,11 @@
         <f>IF(B31="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="20">
         <f>IF(E31="","",IF(E31&gt;$B$6,"SHIFT UP confirmed",IF(F31&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD31" s="20">
+      <c r="AD31" s="21">
         <f>IF($E31="",NA(),IF(OR($E31&gt;$B$6,$F31&gt;$B$6),MAX($E31,$F31),NA()))</f>
         <v/>
       </c>
@@ -12563,7 +12567,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="21" t="n">
+      <c r="B32" s="22" t="n">
         <v>457</v>
       </c>
       <c r="C32" s="17">
@@ -12590,11 +12594,11 @@
         <f>IF(B32="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="20">
         <f>IF(E32="","",IF(E32&gt;$B$6,"SHIFT UP confirmed",IF(F32&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD32" s="20">
+      <c r="AD32" s="21">
         <f>IF($E32="",NA(),IF(OR($E32&gt;$B$6,$F32&gt;$B$6),MAX($E32,$F32),NA()))</f>
         <v/>
       </c>
@@ -12605,7 +12609,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="21" t="n">
+      <c r="B33" s="22" t="n">
         <v>466</v>
       </c>
       <c r="C33" s="17">
@@ -12632,11 +12636,11 @@
         <f>IF(B33="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="20">
         <f>IF(E33="","",IF(E33&gt;$B$6,"SHIFT UP confirmed",IF(F33&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD33" s="20">
+      <c r="AD33" s="21">
         <f>IF($E33="",NA(),IF(OR($E33&gt;$B$6,$F33&gt;$B$6),MAX($E33,$F33),NA()))</f>
         <v/>
       </c>
@@ -12647,7 +12651,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="21" t="n">
+      <c r="B34" s="22" t="n">
         <v>449</v>
       </c>
       <c r="C34" s="17">
@@ -12674,11 +12678,11 @@
         <f>IF(B34="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="20">
         <f>IF(E34="","",IF(E34&gt;$B$6,"SHIFT UP confirmed",IF(F34&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="21">
         <f>IF($E34="",NA(),IF(OR($E34&gt;$B$6,$F34&gt;$B$6),MAX($E34,$F34),NA()))</f>
         <v/>
       </c>
@@ -12689,7 +12693,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n">
+      <c r="B35" s="22" t="n">
         <v>463</v>
       </c>
       <c r="C35" s="17">
@@ -12716,11 +12720,11 @@
         <f>IF(B35="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <f>IF(E35="","",IF(E35&gt;$B$6,"SHIFT UP confirmed",IF(F35&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD35" s="20">
+      <c r="AD35" s="21">
         <f>IF($E35="",NA(),IF(OR($E35&gt;$B$6,$F35&gt;$B$6),MAX($E35,$F35),NA()))</f>
         <v/>
       </c>
@@ -12731,7 +12735,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
+      <c r="B36" s="22" t="n">
         <v>471</v>
       </c>
       <c r="C36" s="17">
@@ -12758,11 +12762,11 @@
         <f>IF(B36="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <f>IF(E36="","",IF(E36&gt;$B$6,"SHIFT UP confirmed",IF(F36&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="21">
         <f>IF($E36="",NA(),IF(OR($E36&gt;$B$6,$F36&gt;$B$6),MAX($E36,$F36),NA()))</f>
         <v/>
       </c>
@@ -12773,7 +12777,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
+      <c r="B37" s="22" t="n">
         <v>455</v>
       </c>
       <c r="C37" s="17">
@@ -12800,11 +12804,11 @@
         <f>IF(B37="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="20">
         <f>IF(E37="","",IF(E37&gt;$B$6,"SHIFT UP confirmed",IF(F37&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD37" s="20">
+      <c r="AD37" s="21">
         <f>IF($E37="",NA(),IF(OR($E37&gt;$B$6,$F37&gt;$B$6),MAX($E37,$F37),NA()))</f>
         <v/>
       </c>
@@ -12815,7 +12819,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n">
+      <c r="B38" s="22" t="n">
         <v>468</v>
       </c>
       <c r="C38" s="17">
@@ -12842,11 +12846,11 @@
         <f>IF(B38="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="20">
         <f>IF(E38="","",IF(E38&gt;$B$6,"SHIFT UP confirmed",IF(F38&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD38" s="20">
+      <c r="AD38" s="21">
         <f>IF($E38="",NA(),IF(OR($E38&gt;$B$6,$F38&gt;$B$6),MAX($E38,$F38),NA()))</f>
         <v/>
       </c>
@@ -12857,7 +12861,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
+      <c r="B39" s="22" t="n">
         <v>460</v>
       </c>
       <c r="C39" s="17">
@@ -12884,11 +12888,11 @@
         <f>IF(B39="","",-$B$6)</f>
         <v/>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="20">
         <f>IF(E39="","",IF(E39&gt;$B$6,"SHIFT UP confirmed",IF(F39&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
-      <c r="AD39" s="20">
+      <c r="AD39" s="21">
         <f>IF($E39="",NA(),IF(OR($E39&gt;$B$6,$F39&gt;$B$6),MAX($E39,$F39),NA()))</f>
         <v/>
       </c>
@@ -13008,7 +13012,7 @@
           <t>Transformed mean</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>AVERAGE(C14:C37)</f>
         <v/>
       </c>
@@ -13024,7 +13028,7 @@
           <t>Transformed MR-bar</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>AVERAGE(D15:D37)</f>
         <v/>
       </c>
@@ -13035,7 +13039,7 @@
           <t>t-chart UCL / LCL (days)</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <f>TEXT((B7+2.66*B8)^3.6,"#,##0.0")&amp;"  /  "&amp;TEXT(MAX(0,(B7-2.66*B8))^3.6,"#,##0.0")</f>
         <v/>
       </c>
@@ -13077,10 +13081,10 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>One row per event, oldest first</t>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>One row per event, oldest first  ·  Key: CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -13169,61 +13173,61 @@
           <t>Incident 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>IF(B14="","",B14^(1/3.6))</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="27" t="n">
         <v>12800</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="36">
         <f>IF(F14="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="20">
         <f>IF(B14="","",IF(C14&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C14&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J14" s="36">
+      <c r="J14" s="37">
         <f>IF(B14="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K14" s="36">
+      <c r="K14" s="37">
         <f>IF(B14="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L14" s="36">
+      <c r="L14" s="37">
         <f>IF(B14="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="38">
         <f>IF(F14="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N14" s="37">
+      <c r="N14" s="38">
         <f>IF(F14="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD14" s="20">
+      <c r="AD14" s="21">
         <f>IF($B14="",NA(),IF(OR($C14&gt;$B$7+2.66*$B$8,$C14&lt;$B$7-2.66*$B$8),$B14,NA()))</f>
         <v/>
       </c>
-      <c r="AE14" s="20">
+      <c r="AE14" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF14" s="20">
+      <c r="AF14" s="21">
         <f>IF($F14="",NA(),IF($F14&gt;$M14,$F14,NA()))</f>
         <v/>
       </c>
-      <c r="AG14" s="20">
+      <c r="AG14" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -13234,65 +13238,65 @@
           <t>Incident 2</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="28">
         <f>IF(B15="","",B15^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>IF(COUNT(C14:C15)=2,ABS(C15-C14),"")</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="30" t="n">
         <v>8400</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="36">
         <f>IF(F15="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <f>IF(B15="","",IF(C15&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C15&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J15" s="36">
+      <c r="J15" s="37">
         <f>IF(B15="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K15" s="36">
+      <c r="K15" s="37">
         <f>IF(B15="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L15" s="36">
+      <c r="L15" s="37">
         <f>IF(B15="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M15" s="37">
+      <c r="M15" s="38">
         <f>IF(F15="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N15" s="37">
+      <c r="N15" s="38">
         <f>IF(F15="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD15" s="20">
+      <c r="AD15" s="21">
         <f>IF($B15="",NA(),IF(OR($C15&gt;$B$7+2.66*$B$8,$C15&lt;$B$7-2.66*$B$8),$B15,NA()))</f>
         <v/>
       </c>
-      <c r="AE15" s="20">
+      <c r="AE15" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF15" s="20">
+      <c r="AF15" s="21">
         <f>IF($F15="",NA(),IF($F15&gt;$M15,$F15,NA()))</f>
         <v/>
       </c>
-      <c r="AG15" s="20">
+      <c r="AG15" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -13303,65 +13307,65 @@
           <t>Incident 3</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>IF(B16="","",B16^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>IF(COUNT(C15:C16)=2,ABS(C16-C15),"")</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="30" t="n">
         <v>21600</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="36">
         <f>IF(F16="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <f>IF(B16="","",IF(C16&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C16&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J16" s="36">
+      <c r="J16" s="37">
         <f>IF(B16="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K16" s="36">
+      <c r="K16" s="37">
         <f>IF(B16="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="37">
         <f>IF(B16="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M16" s="37">
+      <c r="M16" s="38">
         <f>IF(F16="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N16" s="37">
+      <c r="N16" s="38">
         <f>IF(F16="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD16" s="20">
+      <c r="AD16" s="21">
         <f>IF($B16="",NA(),IF(OR($C16&gt;$B$7+2.66*$B$8,$C16&lt;$B$7-2.66*$B$8),$B16,NA()))</f>
         <v/>
       </c>
-      <c r="AE16" s="20">
+      <c r="AE16" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF16" s="20">
+      <c r="AF16" s="21">
         <f>IF($F16="",NA(),IF($F16&gt;$M16,$F16,NA()))</f>
         <v/>
       </c>
-      <c r="AG16" s="20">
+      <c r="AG16" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -13372,65 +13376,65 @@
           <t>Incident 4</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>IF(B17="","",B17^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>IF(COUNT(C16:C17)=2,ABS(C17-C16),"")</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="30" t="n">
         <v>29800</v>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="36">
         <f>IF(F17="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H17" s="19">
+      <c r="H17" s="20">
         <f>IF(B17="","",IF(C17&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C17&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J17" s="36">
+      <c r="J17" s="37">
         <f>IF(B17="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K17" s="36">
+      <c r="K17" s="37">
         <f>IF(B17="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L17" s="36">
+      <c r="L17" s="37">
         <f>IF(B17="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M17" s="37">
+      <c r="M17" s="38">
         <f>IF(F17="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N17" s="37">
+      <c r="N17" s="38">
         <f>IF(F17="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD17" s="20">
+      <c r="AD17" s="21">
         <f>IF($B17="",NA(),IF(OR($C17&gt;$B$7+2.66*$B$8,$C17&lt;$B$7-2.66*$B$8),$B17,NA()))</f>
         <v/>
       </c>
-      <c r="AE17" s="20">
+      <c r="AE17" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF17" s="20">
+      <c r="AF17" s="21">
         <f>IF($F17="",NA(),IF($F17&gt;$M17,$F17,NA()))</f>
         <v/>
       </c>
-      <c r="AG17" s="20">
+      <c r="AG17" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -13441,65 +13445,65 @@
           <t>Incident 5</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>IF(B18="","",B18^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>IF(COUNT(C17:C18)=2,ABS(C18-C17),"")</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="30" t="n">
         <v>17400</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="36">
         <f>IF(F18="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="20">
         <f>IF(B18="","",IF(C18&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C18&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J18" s="36">
+      <c r="J18" s="37">
         <f>IF(B18="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K18" s="36">
+      <c r="K18" s="37">
         <f>IF(B18="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L18" s="36">
+      <c r="L18" s="37">
         <f>IF(B18="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M18" s="37">
+      <c r="M18" s="38">
         <f>IF(F18="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N18" s="37">
+      <c r="N18" s="38">
         <f>IF(F18="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD18" s="20">
+      <c r="AD18" s="21">
         <f>IF($B18="",NA(),IF(OR($C18&gt;$B$7+2.66*$B$8,$C18&lt;$B$7-2.66*$B$8),$B18,NA()))</f>
         <v/>
       </c>
-      <c r="AE18" s="20">
+      <c r="AE18" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF18" s="20">
+      <c r="AF18" s="21">
         <f>IF($F18="",NA(),IF($F18&gt;$M18,$F18,NA()))</f>
         <v/>
       </c>
-      <c r="AG18" s="20">
+      <c r="AG18" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -13510,65 +13514,65 @@
           <t>Incident 6</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>IF(B19="","",B19^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>IF(COUNT(C18:C19)=2,ABS(C19-C18),"")</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="30" t="n">
         <v>26100</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="36">
         <f>IF(F19="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="20">
         <f>IF(B19="","",IF(C19&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C19&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J19" s="36">
+      <c r="J19" s="37">
         <f>IF(B19="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K19" s="36">
+      <c r="K19" s="37">
         <f>IF(B19="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L19" s="36">
+      <c r="L19" s="37">
         <f>IF(B19="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M19" s="37">
+      <c r="M19" s="38">
         <f>IF(F19="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N19" s="37">
+      <c r="N19" s="38">
         <f>IF(F19="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD19" s="20">
+      <c r="AD19" s="21">
         <f>IF($B19="",NA(),IF(OR($C19&gt;$B$7+2.66*$B$8,$C19&lt;$B$7-2.66*$B$8),$B19,NA()))</f>
         <v/>
       </c>
-      <c r="AE19" s="20">
+      <c r="AE19" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF19" s="20">
+      <c r="AF19" s="21">
         <f>IF($F19="",NA(),IF($F19&gt;$M19,$F19,NA()))</f>
         <v/>
       </c>
-      <c r="AG19" s="20">
+      <c r="AG19" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -13579,65 +13583,65 @@
           <t>Incident 7</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="28">
         <f>IF(B20="","",B20^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>IF(COUNT(C19:C20)=2,ABS(C20-C19),"")</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="30" t="n">
         <v>39900</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="36">
         <f>IF(F20="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="20">
         <f>IF(B20="","",IF(C20&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C20&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="37">
         <f>IF(B20="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="37">
         <f>IF(B20="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L20" s="36">
+      <c r="L20" s="37">
         <f>IF(B20="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M20" s="37">
+      <c r="M20" s="38">
         <f>IF(F20="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N20" s="37">
+      <c r="N20" s="38">
         <f>IF(F20="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD20" s="20">
+      <c r="AD20" s="21">
         <f>IF($B20="",NA(),IF(OR($C20&gt;$B$7+2.66*$B$8,$C20&lt;$B$7-2.66*$B$8),$B20,NA()))</f>
         <v/>
       </c>
-      <c r="AE20" s="20">
+      <c r="AE20" s="21">
         <f>NA()</f>
         <v/>
       </c>
-      <c r="AF20" s="20">
+      <c r="AF20" s="21">
         <f>IF($F20="",NA(),IF($F20&gt;$M20,$F20,NA()))</f>
         <v/>
       </c>
-      <c r="AG20" s="20">
+      <c r="AG20" s="21">
         <f>NA()</f>
         <v/>
       </c>
@@ -13648,65 +13652,65 @@
           <t>Incident 8</t>
         </is>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <f>IF(B21="","",B21^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>IF(COUNT(C20:C21)=2,ABS(C21-C20),"")</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="30" t="n">
         <v>11200</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="36">
         <f>IF(F21="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="20">
         <f>IF(B21="","",IF(C21&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C21&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J21" s="36">
+      <c r="J21" s="37">
         <f>IF(B21="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K21" s="36">
+      <c r="K21" s="37">
         <f>IF(B21="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L21" s="36">
+      <c r="L21" s="37">
         <f>IF(B21="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="38">
         <f>IF(F21="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N21" s="37">
+      <c r="N21" s="38">
         <f>IF(F21="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD21" s="20">
+      <c r="AD21" s="21">
         <f>IF($B21="",NA(),IF(OR($C21&gt;$B$7+2.66*$B$8,$C21&lt;$B$7-2.66*$B$8),$B21,NA()))</f>
         <v/>
       </c>
-      <c r="AE21" s="20">
+      <c r="AE21" s="21">
         <f>IF(COUNT($C14:$C21)&lt;8,NA(),IF(OR(MIN($C14:$C21)&gt;$B$7,MAX($C14:$C21)&lt;$B$7),$B21,NA()))</f>
         <v/>
       </c>
-      <c r="AF21" s="20">
+      <c r="AF21" s="21">
         <f>IF($F21="",NA(),IF($F21&gt;$M21,$F21,NA()))</f>
         <v/>
       </c>
-      <c r="AG21" s="20">
+      <c r="AG21" s="21">
         <f>IF(COUNT($F14:$F21)&lt;8,NA(),IF(MIN($F14:$F21)&gt;$N21,$F21,NA()))</f>
         <v/>
       </c>
@@ -13717,65 +13721,65 @@
           <t>Incident 9</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="28">
         <f>IF(B22="","",B22^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>IF(COUNT(C21:C22)=2,ABS(C22-C21),"")</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="30" t="n">
         <v>33500</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="36">
         <f>IF(F22="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="20">
         <f>IF(B22="","",IF(C22&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C22&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J22" s="36">
+      <c r="J22" s="37">
         <f>IF(B22="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="37">
         <f>IF(B22="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="37">
         <f>IF(B22="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M22" s="37">
+      <c r="M22" s="38">
         <f>IF(F22="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N22" s="37">
+      <c r="N22" s="38">
         <f>IF(F22="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD22" s="20">
+      <c r="AD22" s="21">
         <f>IF($B22="",NA(),IF(OR($C22&gt;$B$7+2.66*$B$8,$C22&lt;$B$7-2.66*$B$8),$B22,NA()))</f>
         <v/>
       </c>
-      <c r="AE22" s="20">
+      <c r="AE22" s="21">
         <f>IF(COUNT($C15:$C22)&lt;8,NA(),IF(OR(MIN($C15:$C22)&gt;$B$7,MAX($C15:$C22)&lt;$B$7),$B22,NA()))</f>
         <v/>
       </c>
-      <c r="AF22" s="20">
+      <c r="AF22" s="21">
         <f>IF($F22="",NA(),IF($F22&gt;$M22,$F22,NA()))</f>
         <v/>
       </c>
-      <c r="AG22" s="20">
+      <c r="AG22" s="21">
         <f>IF(COUNT($F15:$F22)&lt;8,NA(),IF(MIN($F15:$F22)&gt;$N22,$F22,NA()))</f>
         <v/>
       </c>
@@ -13786,65 +13790,65 @@
           <t>Incident 10</t>
         </is>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="28">
         <f>IF(B23="","",B23^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>IF(COUNT(C22:C23)=2,ABS(C23-C22),"")</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="30" t="n">
         <v>23100</v>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="36">
         <f>IF(F23="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="20">
         <f>IF(B23="","",IF(C23&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C23&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J23" s="36">
+      <c r="J23" s="37">
         <f>IF(B23="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="37">
         <f>IF(B23="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L23" s="36">
+      <c r="L23" s="37">
         <f>IF(B23="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M23" s="37">
+      <c r="M23" s="38">
         <f>IF(F23="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N23" s="37">
+      <c r="N23" s="38">
         <f>IF(F23="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD23" s="20">
+      <c r="AD23" s="21">
         <f>IF($B23="",NA(),IF(OR($C23&gt;$B$7+2.66*$B$8,$C23&lt;$B$7-2.66*$B$8),$B23,NA()))</f>
         <v/>
       </c>
-      <c r="AE23" s="20">
+      <c r="AE23" s="21">
         <f>IF(COUNT($C16:$C23)&lt;8,NA(),IF(OR(MIN($C16:$C23)&gt;$B$7,MAX($C16:$C23)&lt;$B$7),$B23,NA()))</f>
         <v/>
       </c>
-      <c r="AF23" s="20">
+      <c r="AF23" s="21">
         <f>IF($F23="",NA(),IF($F23&gt;$M23,$F23,NA()))</f>
         <v/>
       </c>
-      <c r="AG23" s="20">
+      <c r="AG23" s="21">
         <f>IF(COUNT($F16:$F23)&lt;8,NA(),IF(MIN($F16:$F23)&gt;$N23,$F23,NA()))</f>
         <v/>
       </c>
@@ -13855,65 +13859,65 @@
           <t>Incident 11</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="28">
         <f>IF(B24="","",B24^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <f>IF(COUNT(C23:C24)=2,ABS(C24-C23),"")</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="30" t="n">
         <v>46800</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="36">
         <f>IF(F24="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>IF(B24="","",IF(C24&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C24&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J24" s="36">
+      <c r="J24" s="37">
         <f>IF(B24="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="37">
         <f>IF(B24="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L24" s="36">
+      <c r="L24" s="37">
         <f>IF(B24="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M24" s="37">
+      <c r="M24" s="38">
         <f>IF(F24="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N24" s="37">
+      <c r="N24" s="38">
         <f>IF(F24="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD24" s="20">
+      <c r="AD24" s="21">
         <f>IF($B24="",NA(),IF(OR($C24&gt;$B$7+2.66*$B$8,$C24&lt;$B$7-2.66*$B$8),$B24,NA()))</f>
         <v/>
       </c>
-      <c r="AE24" s="20">
+      <c r="AE24" s="21">
         <f>IF(COUNT($C17:$C24)&lt;8,NA(),IF(OR(MIN($C17:$C24)&gt;$B$7,MAX($C17:$C24)&lt;$B$7),$B24,NA()))</f>
         <v/>
       </c>
-      <c r="AF24" s="20">
+      <c r="AF24" s="21">
         <f>IF($F24="",NA(),IF($F24&gt;$M24,$F24,NA()))</f>
         <v/>
       </c>
-      <c r="AG24" s="20">
+      <c r="AG24" s="21">
         <f>IF(COUNT($F17:$F24)&lt;8,NA(),IF(MIN($F17:$F24)&gt;$N24,$F24,NA()))</f>
         <v/>
       </c>
@@ -13924,65 +13928,65 @@
           <t>Incident 12</t>
         </is>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="28">
         <f>IF(B25="","",B25^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="28">
         <f>IF(COUNT(C24:C25)=2,ABS(C25-C24),"")</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="30" t="n">
         <v>18300</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="36">
         <f>IF(F25="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <f>IF(B25="","",IF(C25&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C25&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J25" s="36">
+      <c r="J25" s="37">
         <f>IF(B25="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K25" s="36">
+      <c r="K25" s="37">
         <f>IF(B25="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L25" s="36">
+      <c r="L25" s="37">
         <f>IF(B25="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="38">
         <f>IF(F25="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N25" s="37">
+      <c r="N25" s="38">
         <f>IF(F25="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD25" s="20">
+      <c r="AD25" s="21">
         <f>IF($B25="",NA(),IF(OR($C25&gt;$B$7+2.66*$B$8,$C25&lt;$B$7-2.66*$B$8),$B25,NA()))</f>
         <v/>
       </c>
-      <c r="AE25" s="20">
+      <c r="AE25" s="21">
         <f>IF(COUNT($C18:$C25)&lt;8,NA(),IF(OR(MIN($C18:$C25)&gt;$B$7,MAX($C18:$C25)&lt;$B$7),$B25,NA()))</f>
         <v/>
       </c>
-      <c r="AF25" s="20">
+      <c r="AF25" s="21">
         <f>IF($F25="",NA(),IF($F25&gt;$M25,$F25,NA()))</f>
         <v/>
       </c>
-      <c r="AG25" s="20">
+      <c r="AG25" s="21">
         <f>IF(COUNT($F18:$F25)&lt;8,NA(),IF(MIN($F18:$F25)&gt;$N25,$F25,NA()))</f>
         <v/>
       </c>
@@ -13993,65 +13997,65 @@
           <t>Incident 13</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>IF(B26="","",B26^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>IF(COUNT(C25:C26)=2,ABS(C26-C25),"")</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="30" t="n">
         <v>31700</v>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="36">
         <f>IF(F26="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <f>IF(B26="","",IF(C26&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C26&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J26" s="36">
+      <c r="J26" s="37">
         <f>IF(B26="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K26" s="36">
+      <c r="K26" s="37">
         <f>IF(B26="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L26" s="36">
+      <c r="L26" s="37">
         <f>IF(B26="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M26" s="37">
+      <c r="M26" s="38">
         <f>IF(F26="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N26" s="37">
+      <c r="N26" s="38">
         <f>IF(F26="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD26" s="20">
+      <c r="AD26" s="21">
         <f>IF($B26="",NA(),IF(OR($C26&gt;$B$7+2.66*$B$8,$C26&lt;$B$7-2.66*$B$8),$B26,NA()))</f>
         <v/>
       </c>
-      <c r="AE26" s="20">
+      <c r="AE26" s="21">
         <f>IF(COUNT($C19:$C26)&lt;8,NA(),IF(OR(MIN($C19:$C26)&gt;$B$7,MAX($C19:$C26)&lt;$B$7),$B26,NA()))</f>
         <v/>
       </c>
-      <c r="AF26" s="20">
+      <c r="AF26" s="21">
         <f>IF($F26="",NA(),IF($F26&gt;$M26,$F26,NA()))</f>
         <v/>
       </c>
-      <c r="AG26" s="20">
+      <c r="AG26" s="21">
         <f>IF(COUNT($F19:$F26)&lt;8,NA(),IF(MIN($F19:$F26)&gt;$N26,$F26,NA()))</f>
         <v/>
       </c>
@@ -14062,65 +14066,65 @@
           <t>Incident 14</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>IF(B27="","",B27^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IF(COUNT(C26:C27)=2,ABS(C27-C26),"")</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="30" t="n">
         <v>25400</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="36">
         <f>IF(F27="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="20">
         <f>IF(B27="","",IF(C27&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C27&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J27" s="36">
+      <c r="J27" s="37">
         <f>IF(B27="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K27" s="36">
+      <c r="K27" s="37">
         <f>IF(B27="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L27" s="36">
+      <c r="L27" s="37">
         <f>IF(B27="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M27" s="37">
+      <c r="M27" s="38">
         <f>IF(F27="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N27" s="37">
+      <c r="N27" s="38">
         <f>IF(F27="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD27" s="20">
+      <c r="AD27" s="21">
         <f>IF($B27="",NA(),IF(OR($C27&gt;$B$7+2.66*$B$8,$C27&lt;$B$7-2.66*$B$8),$B27,NA()))</f>
         <v/>
       </c>
-      <c r="AE27" s="20">
+      <c r="AE27" s="21">
         <f>IF(COUNT($C20:$C27)&lt;8,NA(),IF(OR(MIN($C20:$C27)&gt;$B$7,MAX($C20:$C27)&lt;$B$7),$B27,NA()))</f>
         <v/>
       </c>
-      <c r="AF27" s="20">
+      <c r="AF27" s="21">
         <f>IF($F27="",NA(),IF($F27&gt;$M27,$F27,NA()))</f>
         <v/>
       </c>
-      <c r="AG27" s="20">
+      <c r="AG27" s="21">
         <f>IF(COUNT($F20:$F27)&lt;8,NA(),IF(MIN($F20:$F27)&gt;$N27,$F27,NA()))</f>
         <v/>
       </c>
@@ -14131,65 +14135,65 @@
           <t>Incident 15</t>
         </is>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="30" t="n">
         <v>52</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="28">
         <f>IF(B28="","",B28^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>IF(COUNT(C27:C28)=2,ABS(C28-C27),"")</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="30" t="n">
         <v>50600</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="36">
         <f>IF(F28="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="20">
         <f>IF(B28="","",IF(C28&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C28&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J28" s="36">
+      <c r="J28" s="37">
         <f>IF(B28="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="37">
         <f>IF(B28="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L28" s="36">
+      <c r="L28" s="37">
         <f>IF(B28="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M28" s="37">
+      <c r="M28" s="38">
         <f>IF(F28="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N28" s="37">
+      <c r="N28" s="38">
         <f>IF(F28="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD28" s="20">
+      <c r="AD28" s="21">
         <f>IF($B28="",NA(),IF(OR($C28&gt;$B$7+2.66*$B$8,$C28&lt;$B$7-2.66*$B$8),$B28,NA()))</f>
         <v/>
       </c>
-      <c r="AE28" s="20">
+      <c r="AE28" s="21">
         <f>IF(COUNT($C21:$C28)&lt;8,NA(),IF(OR(MIN($C21:$C28)&gt;$B$7,MAX($C21:$C28)&lt;$B$7),$B28,NA()))</f>
         <v/>
       </c>
-      <c r="AF28" s="20">
+      <c r="AF28" s="21">
         <f>IF($F28="",NA(),IF($F28&gt;$M28,$F28,NA()))</f>
         <v/>
       </c>
-      <c r="AG28" s="20">
+      <c r="AG28" s="21">
         <f>IF(COUNT($F21:$F28)&lt;8,NA(),IF(MIN($F21:$F28)&gt;$N28,$F28,NA()))</f>
         <v/>
       </c>
@@ -14200,65 +14204,65 @@
           <t>Incident 16</t>
         </is>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="28">
         <f>IF(B29="","",B29^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>IF(COUNT(C28:C29)=2,ABS(C29-C28),"")</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="30" t="n">
         <v>20200</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="36">
         <f>IF(F29="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="20">
         <f>IF(B29="","",IF(C29&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C29&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J29" s="36">
+      <c r="J29" s="37">
         <f>IF(B29="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K29" s="36">
+      <c r="K29" s="37">
         <f>IF(B29="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L29" s="36">
+      <c r="L29" s="37">
         <f>IF(B29="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M29" s="37">
+      <c r="M29" s="38">
         <f>IF(F29="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N29" s="37">
+      <c r="N29" s="38">
         <f>IF(F29="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD29" s="20">
+      <c r="AD29" s="21">
         <f>IF($B29="",NA(),IF(OR($C29&gt;$B$7+2.66*$B$8,$C29&lt;$B$7-2.66*$B$8),$B29,NA()))</f>
         <v/>
       </c>
-      <c r="AE29" s="20">
+      <c r="AE29" s="21">
         <f>IF(COUNT($C22:$C29)&lt;8,NA(),IF(OR(MIN($C22:$C29)&gt;$B$7,MAX($C22:$C29)&lt;$B$7),$B29,NA()))</f>
         <v/>
       </c>
-      <c r="AF29" s="20">
+      <c r="AF29" s="21">
         <f>IF($F29="",NA(),IF($F29&gt;$M29,$F29,NA()))</f>
         <v/>
       </c>
-      <c r="AG29" s="20">
+      <c r="AG29" s="21">
         <f>IF(COUNT($F22:$F29)&lt;8,NA(),IF(MIN($F22:$F29)&gt;$N29,$F29,NA()))</f>
         <v/>
       </c>
@@ -14269,65 +14273,65 @@
           <t>Incident 17</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="28">
         <f>IF(B30="","",B30^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(COUNT(C29:C30)=2,ABS(C30-C29),"")</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="30" t="n">
         <v>36900</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <f>IF(F30="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="20">
         <f>IF(B30="","",IF(C30&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C30&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="37">
         <f>IF(B30="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <f>IF(B30="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <f>IF(B30="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M30" s="37">
+      <c r="M30" s="38">
         <f>IF(F30="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N30" s="37">
+      <c r="N30" s="38">
         <f>IF(F30="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD30" s="20">
+      <c r="AD30" s="21">
         <f>IF($B30="",NA(),IF(OR($C30&gt;$B$7+2.66*$B$8,$C30&lt;$B$7-2.66*$B$8),$B30,NA()))</f>
         <v/>
       </c>
-      <c r="AE30" s="20">
+      <c r="AE30" s="21">
         <f>IF(COUNT($C23:$C30)&lt;8,NA(),IF(OR(MIN($C23:$C30)&gt;$B$7,MAX($C23:$C30)&lt;$B$7),$B30,NA()))</f>
         <v/>
       </c>
-      <c r="AF30" s="20">
+      <c r="AF30" s="21">
         <f>IF($F30="",NA(),IF($F30&gt;$M30,$F30,NA()))</f>
         <v/>
       </c>
-      <c r="AG30" s="20">
+      <c r="AG30" s="21">
         <f>IF(COUNT($F23:$F30)&lt;8,NA(),IF(MIN($F23:$F30)&gt;$N30,$F30,NA()))</f>
         <v/>
       </c>
@@ -14338,65 +14342,65 @@
           <t>Incident 18</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>IF(B31="","",B31^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IF(COUNT(C30:C31)=2,ABS(C31-C30),"")</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="30" t="n">
         <v>27800</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="36">
         <f>IF(F31="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="20">
         <f>IF(B31="","",IF(C31&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C31&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <f>IF(B31="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <f>IF(B31="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="37">
         <f>IF(B31="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="38">
         <f>IF(F31="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="38">
         <f>IF(F31="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD31" s="20">
+      <c r="AD31" s="21">
         <f>IF($B31="",NA(),IF(OR($C31&gt;$B$7+2.66*$B$8,$C31&lt;$B$7-2.66*$B$8),$B31,NA()))</f>
         <v/>
       </c>
-      <c r="AE31" s="20">
+      <c r="AE31" s="21">
         <f>IF(COUNT($C24:$C31)&lt;8,NA(),IF(OR(MIN($C24:$C31)&gt;$B$7,MAX($C24:$C31)&lt;$B$7),$B31,NA()))</f>
         <v/>
       </c>
-      <c r="AF31" s="20">
+      <c r="AF31" s="21">
         <f>IF($F31="",NA(),IF($F31&gt;$M31,$F31,NA()))</f>
         <v/>
       </c>
-      <c r="AG31" s="20">
+      <c r="AG31" s="21">
         <f>IF(COUNT($F24:$F31)&lt;8,NA(),IF(MIN($F24:$F31)&gt;$N31,$F31,NA()))</f>
         <v/>
       </c>
@@ -14407,65 +14411,65 @@
           <t>Incident 19</t>
         </is>
       </c>
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="28">
         <f>IF(B32="","",B32^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IF(COUNT(C31:C32)=2,ABS(C32-C31),"")</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="30" t="n">
         <v>43100</v>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="36">
         <f>IF(F32="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="20">
         <f>IF(B32="","",IF(C32&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C32&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J32" s="36">
+      <c r="J32" s="37">
         <f>IF(B32="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K32" s="36">
+      <c r="K32" s="37">
         <f>IF(B32="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L32" s="36">
+      <c r="L32" s="37">
         <f>IF(B32="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M32" s="37">
+      <c r="M32" s="38">
         <f>IF(F32="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N32" s="37">
+      <c r="N32" s="38">
         <f>IF(F32="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD32" s="20">
+      <c r="AD32" s="21">
         <f>IF($B32="",NA(),IF(OR($C32&gt;$B$7+2.66*$B$8,$C32&lt;$B$7-2.66*$B$8),$B32,NA()))</f>
         <v/>
       </c>
-      <c r="AE32" s="20">
+      <c r="AE32" s="21">
         <f>IF(COUNT($C25:$C32)&lt;8,NA(),IF(OR(MIN($C25:$C32)&gt;$B$7,MAX($C25:$C32)&lt;$B$7),$B32,NA()))</f>
         <v/>
       </c>
-      <c r="AF32" s="20">
+      <c r="AF32" s="21">
         <f>IF($F32="",NA(),IF($F32&gt;$M32,$F32,NA()))</f>
         <v/>
       </c>
-      <c r="AG32" s="20">
+      <c r="AG32" s="21">
         <f>IF(COUNT($F25:$F32)&lt;8,NA(),IF(MIN($F25:$F32)&gt;$N32,$F32,NA()))</f>
         <v/>
       </c>
@@ -14476,65 +14480,65 @@
           <t>Incident 20</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="28">
         <f>IF(B33="","",B33^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IF(COUNT(C32:C33)=2,ABS(C33-C32),"")</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="30" t="n">
         <v>34600</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <f>IF(F33="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="20">
         <f>IF(B33="","",IF(C33&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C33&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="37">
         <f>IF(B33="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="37">
         <f>IF(B33="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="37">
         <f>IF(B33="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M33" s="37">
+      <c r="M33" s="38">
         <f>IF(F33="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N33" s="37">
+      <c r="N33" s="38">
         <f>IF(F33="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD33" s="20">
+      <c r="AD33" s="21">
         <f>IF($B33="",NA(),IF(OR($C33&gt;$B$7+2.66*$B$8,$C33&lt;$B$7-2.66*$B$8),$B33,NA()))</f>
         <v/>
       </c>
-      <c r="AE33" s="20">
+      <c r="AE33" s="21">
         <f>IF(COUNT($C26:$C33)&lt;8,NA(),IF(OR(MIN($C26:$C33)&gt;$B$7,MAX($C26:$C33)&lt;$B$7),$B33,NA()))</f>
         <v/>
       </c>
-      <c r="AF33" s="20">
+      <c r="AF33" s="21">
         <f>IF($F33="",NA(),IF($F33&gt;$M33,$F33,NA()))</f>
         <v/>
       </c>
-      <c r="AG33" s="20">
+      <c r="AG33" s="21">
         <f>IF(COUNT($F26:$F33)&lt;8,NA(),IF(MIN($F26:$F33)&gt;$N33,$F33,NA()))</f>
         <v/>
       </c>
@@ -14545,65 +14549,65 @@
           <t>Incident 21</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="28">
         <f>IF(B34="","",B34^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IF(COUNT(C33:C34)=2,ABS(C34-C33),"")</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="30" t="n">
         <v>56900</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <f>IF(F34="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="20">
         <f>IF(B34="","",IF(C34&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C34&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J34" s="36">
+      <c r="J34" s="37">
         <f>IF(B34="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K34" s="36">
+      <c r="K34" s="37">
         <f>IF(B34="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L34" s="36">
+      <c r="L34" s="37">
         <f>IF(B34="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M34" s="37">
+      <c r="M34" s="38">
         <f>IF(F34="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N34" s="37">
+      <c r="N34" s="38">
         <f>IF(F34="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD34" s="20">
+      <c r="AD34" s="21">
         <f>IF($B34="",NA(),IF(OR($C34&gt;$B$7+2.66*$B$8,$C34&lt;$B$7-2.66*$B$8),$B34,NA()))</f>
         <v/>
       </c>
-      <c r="AE34" s="20">
+      <c r="AE34" s="21">
         <f>IF(COUNT($C27:$C34)&lt;8,NA(),IF(OR(MIN($C27:$C34)&gt;$B$7,MAX($C27:$C34)&lt;$B$7),$B34,NA()))</f>
         <v/>
       </c>
-      <c r="AF34" s="20">
+      <c r="AF34" s="21">
         <f>IF($F34="",NA(),IF($F34&gt;$M34,$F34,NA()))</f>
         <v/>
       </c>
-      <c r="AG34" s="20">
+      <c r="AG34" s="21">
         <f>IF(COUNT($F27:$F34)&lt;8,NA(),IF(MIN($F27:$F34)&gt;$N34,$F34,NA()))</f>
         <v/>
       </c>
@@ -14614,65 +14618,65 @@
           <t>Incident 22</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="28">
         <f>IF(B35="","",B35^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(COUNT(C34:C35)=2,ABS(C35-C34),"")</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="30" t="n">
         <v>29900</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <f>IF(F35="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="20">
         <f>IF(B35="","",IF(C35&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C35&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="37">
         <f>IF(B35="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="37">
         <f>IF(B35="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>IF(B35="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M35" s="37">
+      <c r="M35" s="38">
         <f>IF(F35="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N35" s="37">
+      <c r="N35" s="38">
         <f>IF(F35="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD35" s="20">
+      <c r="AD35" s="21">
         <f>IF($B35="",NA(),IF(OR($C35&gt;$B$7+2.66*$B$8,$C35&lt;$B$7-2.66*$B$8),$B35,NA()))</f>
         <v/>
       </c>
-      <c r="AE35" s="20">
+      <c r="AE35" s="21">
         <f>IF(COUNT($C28:$C35)&lt;8,NA(),IF(OR(MIN($C28:$C35)&gt;$B$7,MAX($C28:$C35)&lt;$B$7),$B35,NA()))</f>
         <v/>
       </c>
-      <c r="AF35" s="20">
+      <c r="AF35" s="21">
         <f>IF($F35="",NA(),IF($F35&gt;$M35,$F35,NA()))</f>
         <v/>
       </c>
-      <c r="AG35" s="20">
+      <c r="AG35" s="21">
         <f>IF(COUNT($F28:$F35)&lt;8,NA(),IF(MIN($F28:$F35)&gt;$N35,$F35,NA()))</f>
         <v/>
       </c>
@@ -14683,65 +14687,65 @@
           <t>Incident 23</t>
         </is>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="30" t="n">
         <v>47</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="28">
         <f>IF(B36="","",B36^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="28">
         <f>IF(COUNT(C35:C36)=2,ABS(C36-C35),"")</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="30" t="n">
         <v>45200</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <f>IF(F36="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="20">
         <f>IF(B36="","",IF(C36&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C36&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="37">
         <f>IF(B36="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="37">
         <f>IF(B36="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="37">
         <f>IF(B36="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M36" s="37">
+      <c r="M36" s="38">
         <f>IF(F36="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N36" s="37">
+      <c r="N36" s="38">
         <f>IF(F36="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD36" s="20">
+      <c r="AD36" s="21">
         <f>IF($B36="",NA(),IF(OR($C36&gt;$B$7+2.66*$B$8,$C36&lt;$B$7-2.66*$B$8),$B36,NA()))</f>
         <v/>
       </c>
-      <c r="AE36" s="20">
+      <c r="AE36" s="21">
         <f>IF(COUNT($C29:$C36)&lt;8,NA(),IF(OR(MIN($C29:$C36)&gt;$B$7,MAX($C29:$C36)&lt;$B$7),$B36,NA()))</f>
         <v/>
       </c>
-      <c r="AF36" s="20">
+      <c r="AF36" s="21">
         <f>IF($F36="",NA(),IF($F36&gt;$M36,$F36,NA()))</f>
         <v/>
       </c>
-      <c r="AG36" s="20">
+      <c r="AG36" s="21">
         <f>IF(COUNT($F29:$F36)&lt;8,NA(),IF(MIN($F29:$F36)&gt;$N36,$F36,NA()))</f>
         <v/>
       </c>
@@ -14752,65 +14756,65 @@
           <t>Incident 24</t>
         </is>
       </c>
-      <c r="B37" s="29" t="n">
+      <c r="B37" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="28">
         <f>IF(B37="","",B37^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="28">
         <f>IF(COUNT(C36:C37)=2,ABS(C37-C36),"")</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="30" t="n">
         <v>38400</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="36">
         <f>IF(F37="","",$B$10)</f>
         <v/>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="20">
         <f>IF(B37="","",IF(C37&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C37&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J37" s="36">
+      <c r="J37" s="37">
         <f>IF(B37="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K37" s="36">
+      <c r="K37" s="37">
         <f>IF(B37="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>IF(B37="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M37" s="37">
+      <c r="M37" s="38">
         <f>IF(F37="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N37" s="37">
+      <c r="N37" s="38">
         <f>IF(F37="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
-      <c r="AD37" s="20">
+      <c r="AD37" s="21">
         <f>IF($B37="",NA(),IF(OR($C37&gt;$B$7+2.66*$B$8,$C37&lt;$B$7-2.66*$B$8),$B37,NA()))</f>
         <v/>
       </c>
-      <c r="AE37" s="20">
+      <c r="AE37" s="21">
         <f>IF(COUNT($C30:$C37)&lt;8,NA(),IF(OR(MIN($C30:$C37)&gt;$B$7,MAX($C30:$C37)&lt;$B$7),$B37,NA()))</f>
         <v/>
       </c>
-      <c r="AF37" s="20">
+      <c r="AF37" s="21">
         <f>IF($F37="",NA(),IF($F37&gt;$M37,$F37,NA()))</f>
         <v/>
       </c>
-      <c r="AG37" s="20">
+      <c r="AG37" s="21">
         <f>IF(COUNT($F30:$F37)&lt;8,NA(),IF(MIN($F30:$F37)&gt;$N37,$F37,NA()))</f>
         <v/>
       </c>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -173,7 +173,6 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,7 +180,6 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4069,7 +4067,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C15" s="17">
@@ -4122,7 +4120,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C16" s="17">
@@ -4175,7 +4173,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C17" s="17">
@@ -4228,7 +4226,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C18" s="17">
@@ -4281,7 +4279,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C19" s="17">
@@ -4334,7 +4332,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C20" s="17">
@@ -4387,7 +4385,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C21" s="17">
@@ -4440,7 +4438,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C22" s="17">
@@ -4493,7 +4491,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C23" s="17">
@@ -4546,7 +4544,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C24" s="17">
@@ -4599,7 +4597,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C25" s="17">
@@ -4652,7 +4650,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="19" t="n">
         <v>401</v>
       </c>
       <c r="C26" s="17">
@@ -4705,7 +4703,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="19" t="n">
         <v>422</v>
       </c>
       <c r="C27" s="17">
@@ -4758,7 +4756,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="19" t="n">
         <v>413</v>
       </c>
       <c r="C28" s="17">
@@ -4811,7 +4809,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="19" t="n">
         <v>407</v>
       </c>
       <c r="C29" s="17">
@@ -4864,7 +4862,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="19" t="n">
         <v>435</v>
       </c>
       <c r="C30" s="17">
@@ -4917,7 +4915,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="19" t="n">
         <v>398</v>
       </c>
       <c r="C31" s="17">
@@ -4970,7 +4968,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="19" t="n">
         <v>420</v>
       </c>
       <c r="C32" s="17">
@@ -5023,7 +5021,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="19" t="n">
         <v>411</v>
       </c>
       <c r="C33" s="17">
@@ -5076,7 +5074,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="19" t="n">
         <v>442</v>
       </c>
       <c r="C34" s="17">
@@ -5129,7 +5127,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="19" t="n">
         <v>404</v>
       </c>
       <c r="C35" s="17">
@@ -5182,7 +5180,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="19" t="n">
         <v>416</v>
       </c>
       <c r="C36" s="17">
@@ -5235,7 +5233,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="19" t="n">
         <v>428</v>
       </c>
       <c r="C37" s="17">
@@ -5389,7 +5387,7 @@
           <t>Overall proportion (p-bar)</t>
         </is>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -5405,7 +5403,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -5421,7 +5419,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -5437,7 +5435,7 @@
           <t>Ordinary p-chart limits would be</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="24">
         <f>"±"&amp;TEXT(3*SQRT(B5*(1-B5)/AVERAGE(B14:B37)),"0.00%")</f>
         <v/>
       </c>
@@ -5507,17 +5505,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="25" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -5544,17 +5542,17 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>7820</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="26" t="n">
         <v>5610</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="22">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="27">
         <f>IF(B14="","",SQRT($B$5*(1-$B$5)/B14))</f>
         <v/>
       </c>
@@ -5566,15 +5564,15 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="29">
+      <c r="K14" s="28">
         <f>IF(B14="","",MIN(1,$B$5+3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="L14" s="29">
+      <c r="L14" s="28">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="29">
+      <c r="M14" s="28">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
@@ -5596,17 +5594,17 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="26" t="n">
         <v>8140</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="26" t="n">
         <v>5990</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="22">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="27">
         <f>IF(B15="","",SQRT($B$5*(1-$B$5)/B15))</f>
         <v/>
       </c>
@@ -5622,15 +5620,15 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="29">
+      <c r="K15" s="28">
         <f>IF(B15="","",MIN(1,$B$5+3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="L15" s="29">
+      <c r="L15" s="28">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="29">
+      <c r="M15" s="28">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
@@ -5652,17 +5650,17 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="26" t="n">
         <v>7960</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="26" t="n">
         <v>5570</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="22">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <f>IF(B16="","",SQRT($B$5*(1-$B$5)/B16))</f>
         <v/>
       </c>
@@ -5678,15 +5676,15 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="29">
+      <c r="K16" s="28">
         <f>IF(B16="","",MIN(1,$B$5+3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="L16" s="29">
+      <c r="L16" s="28">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="29">
+      <c r="M16" s="28">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
@@ -5708,17 +5706,17 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="26" t="n">
         <v>8310</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="26" t="n">
         <v>6120</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="22">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <f>IF(B17="","",SQRT($B$5*(1-$B$5)/B17))</f>
         <v/>
       </c>
@@ -5734,15 +5732,15 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="28">
         <f>IF(B17="","",MIN(1,$B$5+3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="L17" s="29">
+      <c r="L17" s="28">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="29">
+      <c r="M17" s="28">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
@@ -5764,17 +5762,17 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="26" t="n">
         <v>7690</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="26" t="n">
         <v>5410</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="22">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="27">
         <f>IF(B18="","",SQRT($B$5*(1-$B$5)/B18))</f>
         <v/>
       </c>
@@ -5790,15 +5788,15 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="28">
         <f>IF(B18="","",MIN(1,$B$5+3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="L18" s="29">
+      <c r="L18" s="28">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="29">
+      <c r="M18" s="28">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
@@ -5820,17 +5818,17 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="26" t="n">
         <v>8020</v>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="26" t="n">
         <v>5880</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="22">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="27">
         <f>IF(B19="","",SQRT($B$5*(1-$B$5)/B19))</f>
         <v/>
       </c>
@@ -5846,15 +5844,15 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="28">
         <f>IF(B19="","",MIN(1,$B$5+3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="L19" s="29">
+      <c r="L19" s="28">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="29">
+      <c r="M19" s="28">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
@@ -5876,17 +5874,17 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="26" t="n">
         <v>8450</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="26" t="n">
         <v>6210</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="22">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="27">
         <f>IF(B20="","",SQRT($B$5*(1-$B$5)/B20))</f>
         <v/>
       </c>
@@ -5902,15 +5900,15 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="28">
         <f>IF(B20="","",MIN(1,$B$5+3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="L20" s="29">
+      <c r="L20" s="28">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="28">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
@@ -5932,17 +5930,17 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="26" t="n">
         <v>7880</v>
       </c>
-      <c r="C21" s="30" t="n">
+      <c r="C21" s="26" t="n">
         <v>5490</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="22">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="27">
         <f>IF(B21="","",SQRT($B$5*(1-$B$5)/B21))</f>
         <v/>
       </c>
@@ -5958,15 +5956,15 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="28">
         <f>IF(B21="","",MIN(1,$B$5+3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="28">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="28">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
@@ -5988,17 +5986,17 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="26" t="n">
         <v>8210</v>
       </c>
-      <c r="C22" s="30" t="n">
+      <c r="C22" s="26" t="n">
         <v>6050</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="22">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="27">
         <f>IF(B22="","",SQRT($B$5*(1-$B$5)/B22))</f>
         <v/>
       </c>
@@ -6014,15 +6012,15 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="28">
         <f>IF(B22="","",MIN(1,$B$5+3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="L22" s="29">
+      <c r="L22" s="28">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="28">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
@@ -6044,17 +6042,17 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="26" t="n">
         <v>7740</v>
       </c>
-      <c r="C23" s="30" t="n">
+      <c r="C23" s="26" t="n">
         <v>5380</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="27">
         <f>IF(B23="","",SQRT($B$5*(1-$B$5)/B23))</f>
         <v/>
       </c>
@@ -6070,15 +6068,15 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="28">
         <f>IF(B23="","",MIN(1,$B$5+3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="28">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="28">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
@@ -6100,17 +6098,17 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="26" t="n">
         <v>8090</v>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="26" t="n">
         <v>5940</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="27">
         <f>IF(B24="","",SQRT($B$5*(1-$B$5)/B24))</f>
         <v/>
       </c>
@@ -6126,15 +6124,15 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="28">
         <f>IF(B24="","",MIN(1,$B$5+3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="28">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="28">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
@@ -6156,17 +6154,17 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="26" t="n">
         <v>8380</v>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="26" t="n">
         <v>6180</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="22">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="27">
         <f>IF(B25="","",SQRT($B$5*(1-$B$5)/B25))</f>
         <v/>
       </c>
@@ -6182,15 +6180,15 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="28">
         <f>IF(B25="","",MIN(1,$B$5+3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="28">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="28">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
@@ -6212,17 +6210,17 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="26" t="n">
         <v>7930</v>
       </c>
-      <c r="C26" s="30" t="n">
+      <c r="C26" s="26" t="n">
         <v>5520</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="22">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="27">
         <f>IF(B26="","",SQRT($B$5*(1-$B$5)/B26))</f>
         <v/>
       </c>
@@ -6238,15 +6236,15 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="28">
         <f>IF(B26="","",MIN(1,$B$5+3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="L26" s="29">
+      <c r="L26" s="28">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="29">
+      <c r="M26" s="28">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
@@ -6268,17 +6266,17 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="26" t="n">
         <v>8260</v>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="26" t="n">
         <v>6010</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="22">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="27">
         <f>IF(B27="","",SQRT($B$5*(1-$B$5)/B27))</f>
         <v/>
       </c>
@@ -6294,15 +6292,15 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="28">
         <f>IF(B27="","",MIN(1,$B$5+3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="28">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="29">
+      <c r="M27" s="28">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
@@ -6324,17 +6322,17 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="26" t="n">
         <v>7810</v>
       </c>
-      <c r="C28" s="30" t="n">
+      <c r="C28" s="26" t="n">
         <v>5480</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="22">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="27">
         <f>IF(B28="","",SQRT($B$5*(1-$B$5)/B28))</f>
         <v/>
       </c>
@@ -6350,15 +6348,15 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="28">
         <f>IF(B28="","",MIN(1,$B$5+3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="L28" s="29">
+      <c r="L28" s="28">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="29">
+      <c r="M28" s="28">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
@@ -6380,17 +6378,17 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="26" t="n">
         <v>8150</v>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="26" t="n">
         <v>5860</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="22">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f>IF(B29="","",SQRT($B$5*(1-$B$5)/B29))</f>
         <v/>
       </c>
@@ -6406,15 +6404,15 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="28">
         <f>IF(B29="","",MIN(1,$B$5+3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="L29" s="29">
+      <c r="L29" s="28">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="29">
+      <c r="M29" s="28">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
@@ -6436,17 +6434,17 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>8470</v>
       </c>
-      <c r="C30" s="30" t="n">
+      <c r="C30" s="26" t="n">
         <v>6240</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="22">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="27">
         <f>IF(B30="","",SQRT($B$5*(1-$B$5)/B30))</f>
         <v/>
       </c>
@@ -6462,15 +6460,15 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="28">
         <f>IF(B30="","",MIN(1,$B$5+3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="28">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="29">
+      <c r="M30" s="28">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
@@ -6492,17 +6490,17 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="26" t="n">
         <v>7860</v>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="26" t="n">
         <v>5600</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="22">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="27">
         <f>IF(B31="","",SQRT($B$5*(1-$B$5)/B31))</f>
         <v/>
       </c>
@@ -6518,15 +6516,15 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="28">
         <f>IF(B31="","",MIN(1,$B$5+3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="L31" s="29">
+      <c r="L31" s="28">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="29">
+      <c r="M31" s="28">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
@@ -6548,17 +6546,17 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="26" t="n">
         <v>8030</v>
       </c>
-      <c r="C32" s="30" t="n">
+      <c r="C32" s="26" t="n">
         <v>5760</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="22">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="27">
         <f>IF(B32="","",SQRT($B$5*(1-$B$5)/B32))</f>
         <v/>
       </c>
@@ -6574,15 +6572,15 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="29">
+      <c r="K32" s="28">
         <f>IF(B32="","",MIN(1,$B$5+3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="L32" s="29">
+      <c r="L32" s="28">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="29">
+      <c r="M32" s="28">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
@@ -6604,17 +6602,17 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="26" t="n">
         <v>8340</v>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="26" t="n">
         <v>6090</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="22">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="27">
         <f>IF(B33="","",SQRT($B$5*(1-$B$5)/B33))</f>
         <v/>
       </c>
@@ -6630,15 +6628,15 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="28">
         <f>IF(B33="","",MIN(1,$B$5+3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="L33" s="29">
+      <c r="L33" s="28">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="29">
+      <c r="M33" s="28">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
@@ -6660,17 +6658,17 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="26" t="n">
         <v>7900</v>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="26" t="n">
         <v>5710</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="22">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="27">
         <f>IF(B34="","",SQRT($B$5*(1-$B$5)/B34))</f>
         <v/>
       </c>
@@ -6686,15 +6684,15 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="29">
+      <c r="K34" s="28">
         <f>IF(B34="","",MIN(1,$B$5+3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="L34" s="29">
+      <c r="L34" s="28">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="29">
+      <c r="M34" s="28">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
@@ -6716,17 +6714,17 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="26" t="n">
         <v>8180</v>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="26" t="n">
         <v>5900</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="22">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="27">
         <f>IF(B35="","",SQRT($B$5*(1-$B$5)/B35))</f>
         <v/>
       </c>
@@ -6742,15 +6740,15 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="28">
         <f>IF(B35="","",MIN(1,$B$5+3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="28">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="29">
+      <c r="M35" s="28">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
@@ -6772,17 +6770,17 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="26" t="n">
         <v>7770</v>
       </c>
-      <c r="C36" s="30" t="n">
+      <c r="C36" s="26" t="n">
         <v>5450</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="22">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="27">
         <f>IF(B36="","",SQRT($B$5*(1-$B$5)/B36))</f>
         <v/>
       </c>
@@ -6798,15 +6796,15 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="29">
+      <c r="K36" s="28">
         <f>IF(B36="","",MIN(1,$B$5+3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="L36" s="29">
+      <c r="L36" s="28">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="29">
+      <c r="M36" s="28">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
@@ -6828,17 +6826,17 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="26" t="n">
         <v>8240</v>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="26" t="n">
         <v>6020</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="22">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="27">
         <f>IF(B37="","",SQRT($B$5*(1-$B$5)/B37))</f>
         <v/>
       </c>
@@ -6854,15 +6852,15 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="28">
         <f>IF(B37="","",MIN(1,$B$5+3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="28">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="29">
+      <c r="M37" s="28">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
@@ -6982,7 +6980,7 @@
           <t>Overall rate (u-bar)</t>
         </is>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="29">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -6998,7 +6996,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -7014,7 +7012,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -7100,17 +7098,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="25" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -7137,17 +7135,17 @@
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>1240</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="26" t="n">
         <v>38</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="27">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="27">
         <f>IF(B14="","",SQRT($B$5/B14))</f>
         <v/>
       </c>
@@ -7159,15 +7157,15 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="30">
         <f>IF(B14="","",$B$5+3*E14*$B$7)</f>
         <v/>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="30">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="30">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
@@ -7189,17 +7187,17 @@
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="26" t="n">
         <v>1310</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="26" t="n">
         <v>68</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="27">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="27">
         <f>IF(B15="","",SQRT($B$5/B15))</f>
         <v/>
       </c>
@@ -7215,15 +7213,15 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="32">
+      <c r="K15" s="30">
         <f>IF(B15="","",$B$5+3*E15*$B$7)</f>
         <v/>
       </c>
-      <c r="L15" s="32">
+      <c r="L15" s="30">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="32">
+      <c r="M15" s="30">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
@@ -7245,17 +7243,17 @@
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="26" t="n">
         <v>1180</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <f>IF(B16="","",SQRT($B$5/B16))</f>
         <v/>
       </c>
@@ -7271,15 +7269,15 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="32">
+      <c r="K16" s="30">
         <f>IF(B16="","",$B$5+3*E16*$B$7)</f>
         <v/>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="30">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="32">
+      <c r="M16" s="30">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
@@ -7301,17 +7299,17 @@
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="26" t="n">
         <v>1420</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="26" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <f>IF(B17="","",SQRT($B$5/B17))</f>
         <v/>
       </c>
@@ -7327,15 +7325,15 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="32">
+      <c r="K17" s="30">
         <f>IF(B17="","",$B$5+3*E17*$B$7)</f>
         <v/>
       </c>
-      <c r="L17" s="32">
+      <c r="L17" s="30">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="32">
+      <c r="M17" s="30">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
@@ -7357,17 +7355,17 @@
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="26" t="n">
         <v>1275</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="27">
         <f>IF(B18="","",SQRT($B$5/B18))</f>
         <v/>
       </c>
@@ -7383,15 +7381,15 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="32">
+      <c r="K18" s="30">
         <f>IF(B18="","",$B$5+3*E18*$B$7)</f>
         <v/>
       </c>
-      <c r="L18" s="32">
+      <c r="L18" s="30">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="32">
+      <c r="M18" s="30">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
@@ -7413,17 +7411,17 @@
           <t>Week 6</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="26" t="n">
         <v>1195</v>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="26" t="n">
         <v>59</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="27">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="27">
         <f>IF(B19="","",SQRT($B$5/B19))</f>
         <v/>
       </c>
@@ -7439,15 +7437,15 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="32">
+      <c r="K19" s="30">
         <f>IF(B19="","",$B$5+3*E19*$B$7)</f>
         <v/>
       </c>
-      <c r="L19" s="32">
+      <c r="L19" s="30">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="32">
+      <c r="M19" s="30">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
@@ -7469,17 +7467,17 @@
           <t>Week 7</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="26" t="n">
         <v>1360</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="26" t="n">
         <v>56</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="27">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="27">
         <f>IF(B20="","",SQRT($B$5/B20))</f>
         <v/>
       </c>
@@ -7495,15 +7493,15 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="32">
+      <c r="K20" s="30">
         <f>IF(B20="","",$B$5+3*E20*$B$7)</f>
         <v/>
       </c>
-      <c r="L20" s="32">
+      <c r="L20" s="30">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="32">
+      <c r="M20" s="30">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
@@ -7525,17 +7523,17 @@
           <t>Week 8</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="26" t="n">
         <v>1230</v>
       </c>
-      <c r="C21" s="30" t="n">
+      <c r="C21" s="26" t="n">
         <v>69</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="27">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="27">
         <f>IF(B21="","",SQRT($B$5/B21))</f>
         <v/>
       </c>
@@ -7551,15 +7549,15 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="30">
         <f>IF(B21="","",$B$5+3*E21*$B$7)</f>
         <v/>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="30">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="30">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
@@ -7581,17 +7579,17 @@
           <t>Week 9</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="26" t="n">
         <v>1405</v>
       </c>
-      <c r="C22" s="30" t="n">
+      <c r="C22" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="27">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="27">
         <f>IF(B22="","",SQRT($B$5/B22))</f>
         <v/>
       </c>
@@ -7607,15 +7605,15 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="30">
         <f>IF(B22="","",$B$5+3*E22*$B$7)</f>
         <v/>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="30">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="30">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
@@ -7637,17 +7635,17 @@
           <t>Week 10</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="26" t="n">
         <v>1150</v>
       </c>
-      <c r="C23" s="30" t="n">
+      <c r="C23" s="26" t="n">
         <v>54</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="27">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="27">
         <f>IF(B23="","",SQRT($B$5/B23))</f>
         <v/>
       </c>
@@ -7663,15 +7661,15 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="32">
+      <c r="K23" s="30">
         <f>IF(B23="","",$B$5+3*E23*$B$7)</f>
         <v/>
       </c>
-      <c r="L23" s="32">
+      <c r="L23" s="30">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="32">
+      <c r="M23" s="30">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
@@ -7693,17 +7691,17 @@
           <t>Week 11</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="26" t="n">
         <v>1290</v>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="26" t="n">
         <v>49</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="27">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="27">
         <f>IF(B24="","",SQRT($B$5/B24))</f>
         <v/>
       </c>
@@ -7719,15 +7717,15 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="30">
         <f>IF(B24="","",$B$5+3*E24*$B$7)</f>
         <v/>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="30">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="30">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
@@ -7749,17 +7747,17 @@
           <t>Week 12</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="26" t="n">
         <v>1375</v>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="27">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="27">
         <f>IF(B25="","",SQRT($B$5/B25))</f>
         <v/>
       </c>
@@ -7775,15 +7773,15 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="30">
         <f>IF(B25="","",$B$5+3*E25*$B$7)</f>
         <v/>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="30">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="30">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
@@ -7805,17 +7803,17 @@
           <t>Week 13</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="26" t="n">
         <v>1215</v>
       </c>
-      <c r="C26" s="30" t="n">
+      <c r="C26" s="26" t="n">
         <v>39</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="27">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="27">
         <f>IF(B26="","",SQRT($B$5/B26))</f>
         <v/>
       </c>
@@ -7831,15 +7829,15 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="32">
+      <c r="K26" s="30">
         <f>IF(B26="","",$B$5+3*E26*$B$7)</f>
         <v/>
       </c>
-      <c r="L26" s="32">
+      <c r="L26" s="30">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="32">
+      <c r="M26" s="30">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
@@ -7861,17 +7859,17 @@
           <t>Week 14</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="26" t="n">
         <v>1330</v>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="26" t="n">
         <v>66</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="27">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="27">
         <f>IF(B27="","",SQRT($B$5/B27))</f>
         <v/>
       </c>
@@ -7887,15 +7885,15 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="30">
         <f>IF(B27="","",$B$5+3*E27*$B$7)</f>
         <v/>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="30">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="30">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
@@ -7917,17 +7915,17 @@
           <t>Week 15</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="26" t="n">
         <v>1185</v>
       </c>
-      <c r="C28" s="30" t="n">
+      <c r="C28" s="26" t="n">
         <v>41</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="27">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="27">
         <f>IF(B28="","",SQRT($B$5/B28))</f>
         <v/>
       </c>
@@ -7943,15 +7941,15 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="30">
         <f>IF(B28="","",$B$5+3*E28*$B$7)</f>
         <v/>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="30">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="30">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
@@ -7973,17 +7971,17 @@
           <t>Week 16</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="26" t="n">
         <v>1265</v>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="27">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f>IF(B29="","",SQRT($B$5/B29))</f>
         <v/>
       </c>
@@ -7999,15 +7997,15 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="30">
         <f>IF(B29="","",$B$5+3*E29*$B$7)</f>
         <v/>
       </c>
-      <c r="L29" s="32">
+      <c r="L29" s="30">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="32">
+      <c r="M29" s="30">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
@@ -8029,17 +8027,17 @@
           <t>Week 17</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>1440</v>
       </c>
-      <c r="C30" s="30" t="n">
+      <c r="C30" s="26" t="n">
         <v>58</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="27">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="27">
         <f>IF(B30="","",SQRT($B$5/B30))</f>
         <v/>
       </c>
@@ -8055,15 +8053,15 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="32">
+      <c r="K30" s="30">
         <f>IF(B30="","",$B$5+3*E30*$B$7)</f>
         <v/>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="30">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="32">
+      <c r="M30" s="30">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
@@ -8085,17 +8083,17 @@
           <t>Week 18</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="26" t="n">
         <v>1205</v>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="26" t="n">
         <v>54</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="27">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="27">
         <f>IF(B31="","",SQRT($B$5/B31))</f>
         <v/>
       </c>
@@ -8111,15 +8109,15 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="30">
         <f>IF(B31="","",$B$5+3*E31*$B$7)</f>
         <v/>
       </c>
-      <c r="L31" s="32">
+      <c r="L31" s="30">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="32">
+      <c r="M31" s="30">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
@@ -8141,17 +8139,17 @@
           <t>Week 19</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="26" t="n">
         <v>1300</v>
       </c>
-      <c r="C32" s="30" t="n">
+      <c r="C32" s="26" t="n">
         <v>40</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="27">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="27">
         <f>IF(B32="","",SQRT($B$5/B32))</f>
         <v/>
       </c>
@@ -8167,15 +8165,15 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="32">
+      <c r="K32" s="30">
         <f>IF(B32="","",$B$5+3*E32*$B$7)</f>
         <v/>
       </c>
-      <c r="L32" s="32">
+      <c r="L32" s="30">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="32">
+      <c r="M32" s="30">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
@@ -8197,17 +8195,17 @@
           <t>Week 20</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="26" t="n">
         <v>1355</v>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="27">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="27">
         <f>IF(B33="","",SQRT($B$5/B33))</f>
         <v/>
       </c>
@@ -8223,15 +8221,15 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="30">
         <f>IF(B33="","",$B$5+3*E33*$B$7)</f>
         <v/>
       </c>
-      <c r="L33" s="32">
+      <c r="L33" s="30">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="32">
+      <c r="M33" s="30">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
@@ -8253,17 +8251,17 @@
           <t>Week 21</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="26" t="n">
         <v>1170</v>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="26" t="n">
         <v>43</v>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="27">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="27">
         <f>IF(B34="","",SQRT($B$5/B34))</f>
         <v/>
       </c>
@@ -8279,15 +8277,15 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="30">
         <f>IF(B34="","",$B$5+3*E34*$B$7)</f>
         <v/>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="30">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="32">
+      <c r="M34" s="30">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
@@ -8309,17 +8307,17 @@
           <t>Week 22</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="26" t="n">
         <v>1285</v>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="26" t="n">
         <v>62</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="27">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="27">
         <f>IF(B35="","",SQRT($B$5/B35))</f>
         <v/>
       </c>
@@ -8335,15 +8333,15 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="30">
         <f>IF(B35="","",$B$5+3*E35*$B$7)</f>
         <v/>
       </c>
-      <c r="L35" s="32">
+      <c r="L35" s="30">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="32">
+      <c r="M35" s="30">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
@@ -8365,17 +8363,17 @@
           <t>Week 23</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="26" t="n">
         <v>1225</v>
       </c>
-      <c r="C36" s="30" t="n">
+      <c r="C36" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="27">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="27">
         <f>IF(B36="","",SQRT($B$5/B36))</f>
         <v/>
       </c>
@@ -8391,15 +8389,15 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="32">
+      <c r="K36" s="30">
         <f>IF(B36="","",$B$5+3*E36*$B$7)</f>
         <v/>
       </c>
-      <c r="L36" s="32">
+      <c r="L36" s="30">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="32">
+      <c r="M36" s="30">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
@@ -8421,17 +8419,17 @@
           <t>Week 24</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="26" t="n">
         <v>1390</v>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="26" t="n">
         <v>76</v>
       </c>
-      <c r="D37" s="28">
+      <c r="D37" s="27">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="27">
         <f>IF(B37="","",SQRT($B$5/B37))</f>
         <v/>
       </c>
@@ -8447,15 +8445,15 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="32">
+      <c r="K37" s="30">
         <f>IF(B37="","",$B$5+3*E37*$B$7)</f>
         <v/>
       </c>
-      <c r="L37" s="32">
+      <c r="L37" s="30">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="32">
+      <c r="M37" s="30">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
@@ -8633,7 +8631,7 @@
           <t>A2 for this n</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{1.880;1.023;0.729;0.577;0.483;0.419;0.373;0.337;0.308}),"n out of range")</f>
         <v/>
       </c>
@@ -8649,7 +8647,7 @@
           <t>D4 for this n</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{3.267;2.574;2.282;2.114;2.004;1.924;1.864;1.816;1.777}),"n out of range")</f>
         <v/>
       </c>
@@ -8660,7 +8658,7 @@
           <t>D3 for this n</t>
         </is>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="23">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{0;0;0;0;0;0.076;0.136;0.184;0.223}),"n out of range")</f>
         <v/>
       </c>
@@ -8676,7 +8674,7 @@
           <t>Xbar UCL / LCL</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="24">
         <f>TEXT(B6+B8*B7,"#,##0.00")&amp;"  /  "&amp;TEXT(B6-B8*B7,"#,##0.00")</f>
         <v/>
       </c>
@@ -8792,19 +8790,19 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>400</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="26" t="n">
         <v>419</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="26" t="n">
         <v>381</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="26" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="26" t="n">
         <v>419</v>
       </c>
       <c r="G14" s="17">
@@ -8831,15 +8829,15 @@
         <f>IF(G14="","",IF(OR(G14&gt;J14,G14&lt;K14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N14" s="33">
+      <c r="N14" s="31">
         <f>IF(H14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="33">
+      <c r="O14" s="31">
         <f>IF(H14="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="31">
         <f>IF(H14="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -8865,19 +8863,19 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="26" t="n">
         <v>395</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="26" t="n">
         <v>400</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="26" t="n">
         <v>395</v>
       </c>
       <c r="G15" s="17">
@@ -8904,15 +8902,15 @@
         <f>IF(G15="","",IF(OR(G15&gt;J15,G15&lt;K15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N15" s="33">
+      <c r="N15" s="31">
         <f>IF(H15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="33">
+      <c r="O15" s="31">
         <f>IF(H15="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P15" s="33">
+      <c r="P15" s="31">
         <f>IF(H15="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -8938,19 +8936,19 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="26" t="n">
         <v>411</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="26" t="n">
         <v>401</v>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="26" t="n">
         <v>438</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="26" t="n">
         <v>410</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="26" t="n">
         <v>401</v>
       </c>
       <c r="G16" s="17">
@@ -8977,15 +8975,15 @@
         <f>IF(G16="","",IF(OR(G16&gt;J16,G16&lt;K16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N16" s="33">
+      <c r="N16" s="31">
         <f>IF(H16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O16" s="33">
+      <c r="O16" s="31">
         <f>IF(H16="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P16" s="33">
+      <c r="P16" s="31">
         <f>IF(H16="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9011,19 +9009,19 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="26" t="n">
         <v>402</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="26" t="n">
         <v>440</v>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="26" t="n">
         <v>425</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="26" t="n">
         <v>402</v>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="26" t="n">
         <v>440</v>
       </c>
       <c r="G17" s="17">
@@ -9050,15 +9048,15 @@
         <f>IF(G17="","",IF(OR(G17&gt;J17,G17&lt;K17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N17" s="33">
+      <c r="N17" s="31">
         <f>IF(H17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O17" s="33">
+      <c r="O17" s="31">
         <f>IF(H17="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P17" s="33">
+      <c r="P17" s="31">
         <f>IF(H17="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9084,19 +9082,19 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="26" t="n">
         <v>437</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="26" t="n">
         <v>437</v>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="26" t="n">
         <v>404</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="26" t="n">
         <v>437</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="26" t="n">
         <v>437</v>
       </c>
       <c r="G18" s="17">
@@ -9123,15 +9121,15 @@
         <f>IF(G18="","",IF(OR(G18&gt;J18,G18&lt;K18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N18" s="33">
+      <c r="N18" s="31">
         <f>IF(H18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O18" s="33">
+      <c r="O18" s="31">
         <f>IF(H18="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P18" s="33">
+      <c r="P18" s="31">
         <f>IF(H18="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9157,19 +9155,19 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="26" t="n">
         <v>392</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="26" t="n">
         <v>415</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="26" t="n">
         <v>392</v>
       </c>
       <c r="G19" s="17">
@@ -9196,15 +9194,15 @@
         <f>IF(G19="","",IF(OR(G19&gt;J19,G19&lt;K19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N19" s="33">
+      <c r="N19" s="31">
         <f>IF(H19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="33">
+      <c r="O19" s="31">
         <f>IF(H19="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P19" s="33">
+      <c r="P19" s="31">
         <f>IF(H19="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9230,19 +9228,19 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="26" t="n">
         <v>406</v>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="26" t="n">
         <v>433</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="26" t="n">
         <v>406</v>
       </c>
       <c r="G20" s="17">
@@ -9269,15 +9267,15 @@
         <f>IF(G20="","",IF(OR(G20&gt;J20,G20&lt;K20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N20" s="33">
+      <c r="N20" s="31">
         <f>IF(H20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="33">
+      <c r="O20" s="31">
         <f>IF(H20="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P20" s="33">
+      <c r="P20" s="31">
         <f>IF(H20="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9303,19 +9301,19 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="C21" s="30" t="n">
+      <c r="C21" s="26" t="n">
         <v>431</v>
       </c>
-      <c r="D21" s="30" t="n">
+      <c r="D21" s="26" t="n">
         <v>401</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="26" t="n">
         <v>431</v>
       </c>
       <c r="G21" s="17">
@@ -9342,15 +9340,15 @@
         <f>IF(G21="","",IF(OR(G21&gt;J21,G21&lt;K21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="31">
         <f>IF(H21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="31">
         <f>IF(H21="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="31">
         <f>IF(H21="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9376,19 +9374,19 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="26" t="n">
         <v>425</v>
       </c>
-      <c r="C22" s="30" t="n">
+      <c r="C22" s="26" t="n">
         <v>407</v>
       </c>
-      <c r="D22" s="30" t="n">
+      <c r="D22" s="26" t="n">
         <v>387</v>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="E22" s="26" t="n">
         <v>425</v>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F22" s="26" t="n">
         <v>406</v>
       </c>
       <c r="G22" s="17">
@@ -9415,15 +9413,15 @@
         <f>IF(G22="","",IF(OR(G22&gt;J22,G22&lt;K22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="31">
         <f>IF(H22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="31">
         <f>IF(H22="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="31">
         <f>IF(H22="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9449,19 +9447,19 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="26" t="n">
         <v>413</v>
       </c>
-      <c r="C23" s="30" t="n">
+      <c r="C23" s="26" t="n">
         <v>382</v>
       </c>
-      <c r="D23" s="30" t="n">
+      <c r="D23" s="26" t="n">
         <v>417</v>
       </c>
-      <c r="E23" s="30" t="n">
+      <c r="E23" s="26" t="n">
         <v>412</v>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="26" t="n">
         <v>382</v>
       </c>
       <c r="G23" s="17">
@@ -9488,15 +9486,15 @@
         <f>IF(G23="","",IF(OR(G23&gt;J23,G23&lt;K23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N23" s="33">
+      <c r="N23" s="31">
         <f>IF(H23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="33">
+      <c r="O23" s="31">
         <f>IF(H23="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P23" s="33">
+      <c r="P23" s="31">
         <f>IF(H23="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9522,19 +9520,19 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="26" t="n">
         <v>367</v>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="26" t="n">
         <v>393</v>
       </c>
-      <c r="D24" s="30" t="n">
+      <c r="D24" s="26" t="n">
         <v>404</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E24" s="26" t="n">
         <v>367</v>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F24" s="26" t="n">
         <v>394</v>
       </c>
       <c r="G24" s="17">
@@ -9561,15 +9559,15 @@
         <f>IF(G24="","",IF(OR(G24&gt;J24,G24&lt;K24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="31">
         <f>IF(H24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="31">
         <f>IF(H24="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="31">
         <f>IF(H24="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9595,19 +9593,19 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="26" t="n">
         <v>386</v>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="26" t="n">
         <v>410</v>
       </c>
-      <c r="D25" s="30" t="n">
+      <c r="D25" s="26" t="n">
         <v>372</v>
       </c>
-      <c r="E25" s="30" t="n">
+      <c r="E25" s="26" t="n">
         <v>386</v>
       </c>
-      <c r="F25" s="30" t="n">
+      <c r="F25" s="26" t="n">
         <v>409</v>
       </c>
       <c r="G25" s="17">
@@ -9634,15 +9632,15 @@
         <f>IF(G25="","",IF(OR(G25&gt;J25,G25&lt;K25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="31">
         <f>IF(H25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="31">
         <f>IF(H25="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="31">
         <f>IF(H25="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9668,19 +9666,19 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="26" t="n">
         <v>415</v>
       </c>
-      <c r="C26" s="30" t="n">
+      <c r="C26" s="26" t="n">
         <v>382</v>
       </c>
-      <c r="D26" s="30" t="n">
+      <c r="D26" s="26" t="n">
         <v>381</v>
       </c>
-      <c r="E26" s="30" t="n">
+      <c r="E26" s="26" t="n">
         <v>415</v>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F26" s="26" t="n">
         <v>382</v>
       </c>
       <c r="G26" s="17">
@@ -9707,15 +9705,15 @@
         <f>IF(G26="","",IF(OR(G26&gt;J26,G26&lt;K26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N26" s="33">
+      <c r="N26" s="31">
         <f>IF(H26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O26" s="33">
+      <c r="O26" s="31">
         <f>IF(H26="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P26" s="33">
+      <c r="P26" s="31">
         <f>IF(H26="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9741,19 +9739,19 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="26" t="n">
         <v>381</v>
       </c>
-      <c r="D27" s="30" t="n">
+      <c r="D27" s="26" t="n">
         <v>419</v>
       </c>
-      <c r="E27" s="30" t="n">
+      <c r="E27" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="26" t="n">
         <v>381</v>
       </c>
       <c r="G27" s="17">
@@ -9780,15 +9778,15 @@
         <f>IF(G27="","",IF(OR(G27&gt;J27,G27&lt;K27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="31">
         <f>IF(H27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="31">
         <f>IF(H27="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="31">
         <f>IF(H27="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9814,19 +9812,19 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="26" t="n">
         <v>385</v>
       </c>
-      <c r="C28" s="30" t="n">
+      <c r="C28" s="26" t="n">
         <v>421</v>
       </c>
-      <c r="D28" s="30" t="n">
+      <c r="D28" s="26" t="n">
         <v>412</v>
       </c>
-      <c r="E28" s="30" t="n">
+      <c r="E28" s="26" t="n">
         <v>385</v>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F28" s="26" t="n">
         <v>421</v>
       </c>
       <c r="G28" s="17">
@@ -9853,15 +9851,15 @@
         <f>IF(G28="","",IF(OR(G28&gt;J28,G28&lt;K28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="31">
         <f>IF(H28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="31">
         <f>IF(H28="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="31">
         <f>IF(H28="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9887,19 +9885,19 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="26" t="n">
         <v>407</v>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="26" t="n">
         <v>413</v>
       </c>
-      <c r="D29" s="30" t="n">
+      <c r="D29" s="26" t="n">
         <v>378</v>
       </c>
-      <c r="E29" s="30" t="n">
+      <c r="E29" s="26" t="n">
         <v>408</v>
       </c>
-      <c r="F29" s="30" t="n">
+      <c r="F29" s="26" t="n">
         <v>413</v>
       </c>
       <c r="G29" s="17">
@@ -9926,15 +9924,15 @@
         <f>IF(G29="","",IF(OR(G29&gt;J29,G29&lt;K29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N29" s="33">
+      <c r="N29" s="31">
         <f>IF(H29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="33">
+      <c r="O29" s="31">
         <f>IF(H29="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P29" s="33">
+      <c r="P29" s="31">
         <f>IF(H29="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9960,19 +9958,19 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>428</v>
       </c>
-      <c r="C30" s="30" t="n">
+      <c r="C30" s="26" t="n">
         <v>389</v>
       </c>
-      <c r="D30" s="30" t="n">
+      <c r="D30" s="26" t="n">
         <v>408</v>
       </c>
-      <c r="E30" s="30" t="n">
+      <c r="E30" s="26" t="n">
         <v>427</v>
       </c>
-      <c r="F30" s="30" t="n">
+      <c r="F30" s="26" t="n">
         <v>389</v>
       </c>
       <c r="G30" s="17">
@@ -9999,15 +9997,15 @@
         <f>IF(G30="","",IF(OR(G30&gt;J30,G30&lt;K30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="31">
         <f>IF(H30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="31">
         <f>IF(H30="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="31">
         <f>IF(H30="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10033,19 +10031,19 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="26" t="n">
         <v>407</v>
       </c>
-      <c r="D31" s="30" t="n">
+      <c r="D31" s="26" t="n">
         <v>438</v>
       </c>
-      <c r="E31" s="30" t="n">
+      <c r="E31" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="F31" s="30" t="n">
+      <c r="F31" s="26" t="n">
         <v>407</v>
       </c>
       <c r="G31" s="17">
@@ -10072,15 +10070,15 @@
         <f>IF(G31="","",IF(OR(G31&gt;J31,G31&lt;K31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="31">
         <f>IF(H31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="31">
         <f>IF(H31="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P31" s="33">
+      <c r="P31" s="31">
         <f>IF(H31="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10106,19 +10104,19 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="26" t="n">
         <v>406</v>
       </c>
-      <c r="C32" s="30" t="n">
+      <c r="C32" s="26" t="n">
         <v>443</v>
       </c>
-      <c r="D32" s="30" t="n">
+      <c r="D32" s="26" t="n">
         <v>417</v>
       </c>
-      <c r="E32" s="30" t="n">
+      <c r="E32" s="26" t="n">
         <v>406</v>
       </c>
-      <c r="F32" s="30" t="n">
+      <c r="F32" s="26" t="n">
         <v>443</v>
       </c>
       <c r="G32" s="17">
@@ -10145,15 +10143,15 @@
         <f>IF(G32="","",IF(OR(G32&gt;J32,G32&lt;K32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N32" s="33">
+      <c r="N32" s="31">
         <f>IF(H32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O32" s="33">
+      <c r="O32" s="31">
         <f>IF(H32="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P32" s="33">
+      <c r="P32" s="31">
         <f>IF(H32="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10179,19 +10177,19 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="26" t="n">
         <v>443</v>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="26" t="n">
         <v>429</v>
       </c>
-      <c r="D33" s="30" t="n">
+      <c r="D33" s="26" t="n">
         <v>405</v>
       </c>
-      <c r="E33" s="30" t="n">
+      <c r="E33" s="26" t="n">
         <v>443</v>
       </c>
-      <c r="F33" s="30" t="n">
+      <c r="F33" s="26" t="n">
         <v>429</v>
       </c>
       <c r="G33" s="17">
@@ -10218,15 +10216,15 @@
         <f>IF(G33="","",IF(OR(G33&gt;J33,G33&lt;K33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N33" s="33">
+      <c r="N33" s="31">
         <f>IF(H33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="31">
         <f>IF(H33="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="31">
         <f>IF(H33="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10252,19 +10250,19 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="26" t="n">
         <v>424</v>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="26" t="n">
         <v>390</v>
       </c>
-      <c r="D34" s="30" t="n">
+      <c r="D34" s="26" t="n">
         <v>423</v>
       </c>
-      <c r="E34" s="30" t="n">
+      <c r="E34" s="26" t="n">
         <v>424</v>
       </c>
-      <c r="F34" s="30" t="n">
+      <c r="F34" s="26" t="n">
         <v>390</v>
       </c>
       <c r="G34" s="17">
@@ -10291,15 +10289,15 @@
         <f>IF(G34="","",IF(OR(G34&gt;J34,G34&lt;K34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N34" s="33">
+      <c r="N34" s="31">
         <f>IF(H34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="31">
         <f>IF(H34="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P34" s="33">
+      <c r="P34" s="31">
         <f>IF(H34="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10325,19 +10323,19 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="26" t="n">
         <v>392</v>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="26" t="n">
         <v>414</v>
       </c>
-      <c r="D35" s="30" t="n">
+      <c r="D35" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="E35" s="30" t="n">
+      <c r="E35" s="26" t="n">
         <v>392</v>
       </c>
-      <c r="F35" s="30" t="n">
+      <c r="F35" s="26" t="n">
         <v>414</v>
       </c>
       <c r="G35" s="17">
@@ -10364,15 +10362,15 @@
         <f>IF(G35="","",IF(OR(G35&gt;J35,G35&lt;K35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N35" s="33">
+      <c r="N35" s="31">
         <f>IF(H35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="31">
         <f>IF(H35="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="31">
         <f>IF(H35="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10398,19 +10396,19 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="C36" s="30" t="n">
+      <c r="C36" s="26" t="n">
         <v>431</v>
       </c>
-      <c r="D36" s="30" t="n">
+      <c r="D36" s="26" t="n">
         <v>394</v>
       </c>
-      <c r="E36" s="30" t="n">
+      <c r="E36" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="F36" s="30" t="n">
+      <c r="F36" s="26" t="n">
         <v>431</v>
       </c>
       <c r="G36" s="17">
@@ -10437,15 +10435,15 @@
         <f>IF(G36="","",IF(OR(G36&gt;J36,G36&lt;K36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N36" s="33">
+      <c r="N36" s="31">
         <f>IF(H36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O36" s="33">
+      <c r="O36" s="31">
         <f>IF(H36="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P36" s="33">
+      <c r="P36" s="31">
         <f>IF(H36="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10471,19 +10469,19 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="26" t="n">
         <v>428</v>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="26" t="n">
         <v>399</v>
       </c>
-      <c r="D37" s="30" t="n">
+      <c r="D37" s="26" t="n">
         <v>393</v>
       </c>
-      <c r="E37" s="30" t="n">
+      <c r="E37" s="26" t="n">
         <v>429</v>
       </c>
-      <c r="F37" s="30" t="n">
+      <c r="F37" s="26" t="n">
         <v>399</v>
       </c>
       <c r="G37" s="17">
@@ -10510,15 +10508,15 @@
         <f>IF(G37="","",IF(OR(G37&gt;J37,G37&lt;K37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N37" s="33">
+      <c r="N37" s="31">
         <f>IF(H37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O37" s="33">
+      <c r="O37" s="31">
         <f>IF(H37="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P37" s="33">
+      <c r="P37" s="31">
         <f>IF(H37="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10624,7 +10622,7 @@
           <t>Lambda (weight on the newest point)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="32" t="n">
         <v>0.2</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -10639,7 +10637,7 @@
           <t>L (limit width in sigmas)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="33" t="n">
         <v>2.7</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -10803,7 +10801,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="17">
@@ -10841,7 +10839,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="17">
@@ -10879,7 +10877,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="17">
@@ -10917,7 +10915,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="17">
@@ -10955,7 +10953,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="17">
@@ -10993,7 +10991,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="17">
@@ -11031,7 +11029,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="17">
@@ -11069,7 +11067,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="17">
@@ -11107,7 +11105,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="17">
@@ -11145,7 +11143,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="17">
@@ -11183,7 +11181,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="17">
@@ -11221,7 +11219,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="19" t="n">
         <v>418</v>
       </c>
       <c r="C28" s="17">
@@ -11259,7 +11257,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="19" t="n">
         <v>426</v>
       </c>
       <c r="C29" s="17">
@@ -11297,7 +11295,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C30" s="17">
@@ -11335,7 +11333,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="19" t="n">
         <v>428</v>
       </c>
       <c r="C31" s="17">
@@ -11373,7 +11371,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="19" t="n">
         <v>437</v>
       </c>
       <c r="C32" s="17">
@@ -11411,7 +11409,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="19" t="n">
         <v>433</v>
       </c>
       <c r="C33" s="17">
@@ -11449,7 +11447,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="19" t="n">
         <v>441</v>
       </c>
       <c r="C34" s="17">
@@ -11487,7 +11485,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="19" t="n">
         <v>439</v>
       </c>
       <c r="C35" s="17">
@@ -11525,7 +11523,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="19" t="n">
         <v>448</v>
       </c>
       <c r="C36" s="17">
@@ -11563,7 +11561,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="19" t="n">
         <v>444</v>
       </c>
       <c r="C37" s="17">
@@ -11601,7 +11599,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="19" t="n">
         <v>452</v>
       </c>
       <c r="C38" s="17">
@@ -11639,7 +11637,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n">
+      <c r="B39" s="19" t="n">
         <v>449</v>
       </c>
       <c r="C39" s="17">
@@ -11755,7 +11753,7 @@
           <t>k (slack, in sigmas)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="32" t="n">
         <v>0.5</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -11770,7 +11768,7 @@
           <t>h (decision interval)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="33" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -11937,7 +11935,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="17">
@@ -11979,7 +11977,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="17">
@@ -12021,7 +12019,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="17">
@@ -12063,7 +12061,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="17">
@@ -12105,7 +12103,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="17">
@@ -12147,7 +12145,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="17">
@@ -12189,7 +12187,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="17">
@@ -12231,7 +12229,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="17">
@@ -12273,7 +12271,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="17">
@@ -12315,7 +12313,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="17">
@@ -12357,7 +12355,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="17">
@@ -12399,7 +12397,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="19" t="n">
         <v>452</v>
       </c>
       <c r="C28" s="17">
@@ -12441,7 +12439,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="19" t="n">
         <v>461</v>
       </c>
       <c r="C29" s="17">
@@ -12483,7 +12481,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="19" t="n">
         <v>448</v>
       </c>
       <c r="C30" s="17">
@@ -12525,7 +12523,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="19" t="n">
         <v>470</v>
       </c>
       <c r="C31" s="17">
@@ -12567,7 +12565,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="19" t="n">
         <v>457</v>
       </c>
       <c r="C32" s="17">
@@ -12609,7 +12607,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="19" t="n">
         <v>466</v>
       </c>
       <c r="C33" s="17">
@@ -12651,7 +12649,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="19" t="n">
         <v>449</v>
       </c>
       <c r="C34" s="17">
@@ -12693,7 +12691,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="19" t="n">
         <v>463</v>
       </c>
       <c r="C35" s="17">
@@ -12735,7 +12733,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="19" t="n">
         <v>471</v>
       </c>
       <c r="C36" s="17">
@@ -12777,7 +12775,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="19" t="n">
         <v>455</v>
       </c>
       <c r="C37" s="17">
@@ -12819,7 +12817,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="19" t="n">
         <v>468</v>
       </c>
       <c r="C38" s="17">
@@ -12861,7 +12859,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n">
+      <c r="B39" s="19" t="n">
         <v>460</v>
       </c>
       <c r="C39" s="17">
@@ -13012,7 +13010,7 @@
           <t>Transformed mean</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="29">
         <f>AVERAGE(C14:C37)</f>
         <v/>
       </c>
@@ -13028,7 +13026,7 @@
           <t>Transformed MR-bar</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="29">
         <f>AVERAGE(D15:D37)</f>
         <v/>
       </c>
@@ -13039,7 +13037,7 @@
           <t>t-chart UCL / LCL (days)</t>
         </is>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="24">
         <f>TEXT((B7+2.66*B8)^3.6,"#,##0.0")&amp;"  /  "&amp;TEXT(MAX(0,(B7-2.66*B8))^3.6,"#,##0.0")</f>
         <v/>
       </c>
@@ -13173,21 +13171,21 @@
           <t>Incident 1</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="27">
         <f>IF(B14="","",B14^(1/3.6))</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="27">
         <f>IF(B14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="26" t="n">
         <v>12800</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="34">
         <f>IF(F14="","",$B$10)</f>
         <v/>
       </c>
@@ -13195,23 +13193,23 @@
         <f>IF(B14="","",IF(C14&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C14&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="35">
         <f>IF(B14="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="35">
         <f>IF(B14="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="35">
         <f>IF(B14="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M14" s="38">
+      <c r="M14" s="36">
         <f>IF(F14="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N14" s="38">
+      <c r="N14" s="36">
         <f>IF(F14="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13238,25 +13236,25 @@
           <t>Incident 2</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="27">
         <f>IF(B15="","",B15^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="27">
         <f>IF(COUNT(C14:C15)=2,ABS(C15-C14),"")</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="27">
         <f>IF(B15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="26" t="n">
         <v>8400</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="34">
         <f>IF(F15="","",$B$10)</f>
         <v/>
       </c>
@@ -13264,23 +13262,23 @@
         <f>IF(B15="","",IF(C15&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C15&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="35">
         <f>IF(B15="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="35">
         <f>IF(B15="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="35">
         <f>IF(B15="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M15" s="38">
+      <c r="M15" s="36">
         <f>IF(F15="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N15" s="38">
+      <c r="N15" s="36">
         <f>IF(F15="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13307,25 +13305,25 @@
           <t>Incident 3</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="26" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <f>IF(B16="","",B16^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <f>IF(COUNT(C15:C16)=2,ABS(C16-C15),"")</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <f>IF(B16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="26" t="n">
         <v>21600</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="34">
         <f>IF(F16="","",$B$10)</f>
         <v/>
       </c>
@@ -13333,23 +13331,23 @@
         <f>IF(B16="","",IF(C16&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C16&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="35">
         <f>IF(B16="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="35">
         <f>IF(B16="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L16" s="37">
+      <c r="L16" s="35">
         <f>IF(B16="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M16" s="38">
+      <c r="M16" s="36">
         <f>IF(F16="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N16" s="38">
+      <c r="N16" s="36">
         <f>IF(F16="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13376,25 +13374,25 @@
           <t>Incident 4</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="26" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>IF(B17="","",B17^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>IF(COUNT(C16:C17)=2,ABS(C17-C16),"")</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <f>IF(B17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="26" t="n">
         <v>29800</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="34">
         <f>IF(F17="","",$B$10)</f>
         <v/>
       </c>
@@ -13402,23 +13400,23 @@
         <f>IF(B17="","",IF(C17&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C17&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="35">
         <f>IF(B17="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K17" s="37">
+      <c r="K17" s="35">
         <f>IF(B17="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L17" s="37">
+      <c r="L17" s="35">
         <f>IF(B17="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M17" s="38">
+      <c r="M17" s="36">
         <f>IF(F17="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N17" s="38">
+      <c r="N17" s="36">
         <f>IF(F17="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13445,25 +13443,25 @@
           <t>Incident 5</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <f>IF(B18="","",B18^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <f>IF(COUNT(C17:C18)=2,ABS(C18-C17),"")</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="27">
         <f>IF(B18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="26" t="n">
         <v>17400</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="34">
         <f>IF(F18="","",$B$10)</f>
         <v/>
       </c>
@@ -13471,23 +13469,23 @@
         <f>IF(B18="","",IF(C18&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C18&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J18" s="37">
+      <c r="J18" s="35">
         <f>IF(B18="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K18" s="37">
+      <c r="K18" s="35">
         <f>IF(B18="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L18" s="37">
+      <c r="L18" s="35">
         <f>IF(B18="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M18" s="38">
+      <c r="M18" s="36">
         <f>IF(F18="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N18" s="38">
+      <c r="N18" s="36">
         <f>IF(F18="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13514,25 +13512,25 @@
           <t>Incident 6</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="26" t="n">
         <v>27</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="27">
         <f>IF(B19="","",B19^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="27">
         <f>IF(COUNT(C18:C19)=2,ABS(C19-C18),"")</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="27">
         <f>IF(B19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="26" t="n">
         <v>26100</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="34">
         <f>IF(F19="","",$B$10)</f>
         <v/>
       </c>
@@ -13540,23 +13538,23 @@
         <f>IF(B19="","",IF(C19&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C19&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J19" s="37">
+      <c r="J19" s="35">
         <f>IF(B19="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="35">
         <f>IF(B19="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L19" s="37">
+      <c r="L19" s="35">
         <f>IF(B19="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M19" s="38">
+      <c r="M19" s="36">
         <f>IF(F19="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N19" s="38">
+      <c r="N19" s="36">
         <f>IF(F19="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13583,25 +13581,25 @@
           <t>Incident 7</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="26" t="n">
         <v>41</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <f>IF(B20="","",B20^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="27">
         <f>IF(COUNT(C19:C20)=2,ABS(C20-C19),"")</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="27">
         <f>IF(B20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="26" t="n">
         <v>39900</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="34">
         <f>IF(F20="","",$B$10)</f>
         <v/>
       </c>
@@ -13609,23 +13607,23 @@
         <f>IF(B20="","",IF(C20&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C20&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J20" s="37">
+      <c r="J20" s="35">
         <f>IF(B20="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K20" s="37">
+      <c r="K20" s="35">
         <f>IF(B20="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L20" s="37">
+      <c r="L20" s="35">
         <f>IF(B20="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M20" s="38">
+      <c r="M20" s="36">
         <f>IF(F20="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N20" s="38">
+      <c r="N20" s="36">
         <f>IF(F20="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13652,25 +13650,25 @@
           <t>Incident 8</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <f>IF(B21="","",B21^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="27">
         <f>IF(COUNT(C20:C21)=2,ABS(C21-C20),"")</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="27">
         <f>IF(B21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="26" t="n">
         <v>11200</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="34">
         <f>IF(F21="","",$B$10)</f>
         <v/>
       </c>
@@ -13678,23 +13676,23 @@
         <f>IF(B21="","",IF(C21&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C21&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="35">
         <f>IF(B21="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K21" s="37">
+      <c r="K21" s="35">
         <f>IF(B21="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="35">
         <f>IF(B21="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M21" s="38">
+      <c r="M21" s="36">
         <f>IF(F21="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N21" s="38">
+      <c r="N21" s="36">
         <f>IF(F21="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13721,25 +13719,25 @@
           <t>Incident 9</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="26" t="n">
         <v>35</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="27">
         <f>IF(B22="","",B22^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="27">
         <f>IF(COUNT(C21:C22)=2,ABS(C22-C21),"")</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="27">
         <f>IF(B22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F22" s="26" t="n">
         <v>33500</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="34">
         <f>IF(F22="","",$B$10)</f>
         <v/>
       </c>
@@ -13747,23 +13745,23 @@
         <f>IF(B22="","",IF(C22&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C22&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J22" s="37">
+      <c r="J22" s="35">
         <f>IF(B22="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K22" s="37">
+      <c r="K22" s="35">
         <f>IF(B22="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L22" s="37">
+      <c r="L22" s="35">
         <f>IF(B22="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M22" s="38">
+      <c r="M22" s="36">
         <f>IF(F22="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N22" s="38">
+      <c r="N22" s="36">
         <f>IF(F22="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13790,25 +13788,25 @@
           <t>Incident 10</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="27">
         <f>IF(B23="","",B23^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="27">
         <f>IF(COUNT(C22:C23)=2,ABS(C23-C22),"")</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="27">
         <f>IF(B23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="26" t="n">
         <v>23100</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="34">
         <f>IF(F23="","",$B$10)</f>
         <v/>
       </c>
@@ -13816,23 +13814,23 @@
         <f>IF(B23="","",IF(C23&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C23&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="35">
         <f>IF(B23="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K23" s="37">
+      <c r="K23" s="35">
         <f>IF(B23="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L23" s="37">
+      <c r="L23" s="35">
         <f>IF(B23="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M23" s="38">
+      <c r="M23" s="36">
         <f>IF(F23="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N23" s="38">
+      <c r="N23" s="36">
         <f>IF(F23="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13859,25 +13857,25 @@
           <t>Incident 11</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="27">
         <f>IF(B24="","",B24^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="27">
         <f>IF(COUNT(C23:C24)=2,ABS(C24-C23),"")</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="27">
         <f>IF(B24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F24" s="26" t="n">
         <v>46800</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="34">
         <f>IF(F24="","",$B$10)</f>
         <v/>
       </c>
@@ -13885,23 +13883,23 @@
         <f>IF(B24="","",IF(C24&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C24&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J24" s="37">
+      <c r="J24" s="35">
         <f>IF(B24="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K24" s="37">
+      <c r="K24" s="35">
         <f>IF(B24="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L24" s="37">
+      <c r="L24" s="35">
         <f>IF(B24="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M24" s="38">
+      <c r="M24" s="36">
         <f>IF(F24="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N24" s="38">
+      <c r="N24" s="36">
         <f>IF(F24="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13928,25 +13926,25 @@
           <t>Incident 12</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="27">
         <f>IF(B25="","",B25^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="27">
         <f>IF(COUNT(C24:C25)=2,ABS(C25-C24),"")</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="27">
         <f>IF(B25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F25" s="30" t="n">
+      <c r="F25" s="26" t="n">
         <v>18300</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="34">
         <f>IF(F25="","",$B$10)</f>
         <v/>
       </c>
@@ -13954,23 +13952,23 @@
         <f>IF(B25="","",IF(C25&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C25&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="35">
         <f>IF(B25="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K25" s="37">
+      <c r="K25" s="35">
         <f>IF(B25="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="35">
         <f>IF(B25="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M25" s="38">
+      <c r="M25" s="36">
         <f>IF(F25="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N25" s="38">
+      <c r="N25" s="36">
         <f>IF(F25="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13997,25 +13995,25 @@
           <t>Incident 13</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="26" t="n">
         <v>33</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="27">
         <f>IF(B26="","",B26^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="27">
         <f>IF(COUNT(C25:C26)=2,ABS(C26-C25),"")</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="27">
         <f>IF(B26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F26" s="26" t="n">
         <v>31700</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="34">
         <f>IF(F26="","",$B$10)</f>
         <v/>
       </c>
@@ -14023,23 +14021,23 @@
         <f>IF(B26="","",IF(C26&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C26&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="35">
         <f>IF(B26="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="35">
         <f>IF(B26="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L26" s="37">
+      <c r="L26" s="35">
         <f>IF(B26="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M26" s="38">
+      <c r="M26" s="36">
         <f>IF(F26="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N26" s="38">
+      <c r="N26" s="36">
         <f>IF(F26="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14066,25 +14064,25 @@
           <t>Incident 14</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="26" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="27">
         <f>IF(B27="","",B27^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="27">
         <f>IF(COUNT(C26:C27)=2,ABS(C27-C26),"")</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="27">
         <f>IF(B27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="26" t="n">
         <v>25400</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="34">
         <f>IF(F27="","",$B$10)</f>
         <v/>
       </c>
@@ -14092,23 +14090,23 @@
         <f>IF(B27="","",IF(C27&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C27&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J27" s="37">
+      <c r="J27" s="35">
         <f>IF(B27="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K27" s="37">
+      <c r="K27" s="35">
         <f>IF(B27="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L27" s="37">
+      <c r="L27" s="35">
         <f>IF(B27="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M27" s="38">
+      <c r="M27" s="36">
         <f>IF(F27="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N27" s="38">
+      <c r="N27" s="36">
         <f>IF(F27="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14135,25 +14133,25 @@
           <t>Incident 15</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="27">
         <f>IF(B28="","",B28^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="27">
         <f>IF(COUNT(C27:C28)=2,ABS(C28-C27),"")</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="27">
         <f>IF(B28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F28" s="26" t="n">
         <v>50600</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="34">
         <f>IF(F28="","",$B$10)</f>
         <v/>
       </c>
@@ -14161,23 +14159,23 @@
         <f>IF(B28="","",IF(C28&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C28&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J28" s="37">
+      <c r="J28" s="35">
         <f>IF(B28="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K28" s="37">
+      <c r="K28" s="35">
         <f>IF(B28="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L28" s="37">
+      <c r="L28" s="35">
         <f>IF(B28="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M28" s="38">
+      <c r="M28" s="36">
         <f>IF(F28="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N28" s="38">
+      <c r="N28" s="36">
         <f>IF(F28="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14204,25 +14202,25 @@
           <t>Incident 16</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="26" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="27">
         <f>IF(B29="","",B29^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="27">
         <f>IF(COUNT(C28:C29)=2,ABS(C29-C28),"")</f>
         <v/>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f>IF(B29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F29" s="30" t="n">
+      <c r="F29" s="26" t="n">
         <v>20200</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="34">
         <f>IF(F29="","",$B$10)</f>
         <v/>
       </c>
@@ -14230,23 +14228,23 @@
         <f>IF(B29="","",IF(C29&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C29&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J29" s="37">
+      <c r="J29" s="35">
         <f>IF(B29="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K29" s="37">
+      <c r="K29" s="35">
         <f>IF(B29="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L29" s="37">
+      <c r="L29" s="35">
         <f>IF(B29="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M29" s="38">
+      <c r="M29" s="36">
         <f>IF(F29="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N29" s="38">
+      <c r="N29" s="36">
         <f>IF(F29="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14273,25 +14271,25 @@
           <t>Incident 17</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>38</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="27">
         <f>IF(B30="","",B30^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="27">
         <f>IF(COUNT(C29:C30)=2,ABS(C30-C29),"")</f>
         <v/>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="27">
         <f>IF(B30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F30" s="30" t="n">
+      <c r="F30" s="26" t="n">
         <v>36900</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="34">
         <f>IF(F30="","",$B$10)</f>
         <v/>
       </c>
@@ -14299,23 +14297,23 @@
         <f>IF(B30="","",IF(C30&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C30&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="35">
         <f>IF(B30="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K30" s="37">
+      <c r="K30" s="35">
         <f>IF(B30="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L30" s="37">
+      <c r="L30" s="35">
         <f>IF(B30="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M30" s="38">
+      <c r="M30" s="36">
         <f>IF(F30="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N30" s="38">
+      <c r="N30" s="36">
         <f>IF(F30="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14342,25 +14340,25 @@
           <t>Incident 18</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="26" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="27">
         <f>IF(B31="","",B31^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="27">
         <f>IF(COUNT(C30:C31)=2,ABS(C31-C30),"")</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="27">
         <f>IF(B31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F31" s="30" t="n">
+      <c r="F31" s="26" t="n">
         <v>27800</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="34">
         <f>IF(F31="","",$B$10)</f>
         <v/>
       </c>
@@ -14368,23 +14366,23 @@
         <f>IF(B31="","",IF(C31&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C31&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="35">
         <f>IF(B31="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K31" s="37">
+      <c r="K31" s="35">
         <f>IF(B31="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="35">
         <f>IF(B31="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M31" s="38">
+      <c r="M31" s="36">
         <f>IF(F31="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N31" s="38">
+      <c r="N31" s="36">
         <f>IF(F31="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14411,25 +14409,25 @@
           <t>Incident 19</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="26" t="n">
         <v>44</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="27">
         <f>IF(B32="","",B32^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="27">
         <f>IF(COUNT(C31:C32)=2,ABS(C32-C31),"")</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="27">
         <f>IF(B32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F32" s="30" t="n">
+      <c r="F32" s="26" t="n">
         <v>43100</v>
       </c>
-      <c r="G32" s="36">
+      <c r="G32" s="34">
         <f>IF(F32="","",$B$10)</f>
         <v/>
       </c>
@@ -14437,23 +14435,23 @@
         <f>IF(B32="","",IF(C32&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C32&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J32" s="37">
+      <c r="J32" s="35">
         <f>IF(B32="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K32" s="37">
+      <c r="K32" s="35">
         <f>IF(B32="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L32" s="37">
+      <c r="L32" s="35">
         <f>IF(B32="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M32" s="38">
+      <c r="M32" s="36">
         <f>IF(F32="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N32" s="38">
+      <c r="N32" s="36">
         <f>IF(F32="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14480,25 +14478,25 @@
           <t>Incident 20</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="26" t="n">
         <v>36</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="27">
         <f>IF(B33="","",B33^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="27">
         <f>IF(COUNT(C32:C33)=2,ABS(C33-C32),"")</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="27">
         <f>IF(B33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F33" s="30" t="n">
+      <c r="F33" s="26" t="n">
         <v>34600</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="34">
         <f>IF(F33="","",$B$10)</f>
         <v/>
       </c>
@@ -14506,23 +14504,23 @@
         <f>IF(B33="","",IF(C33&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C33&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J33" s="37">
+      <c r="J33" s="35">
         <f>IF(B33="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K33" s="37">
+      <c r="K33" s="35">
         <f>IF(B33="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L33" s="37">
+      <c r="L33" s="35">
         <f>IF(B33="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M33" s="38">
+      <c r="M33" s="36">
         <f>IF(F33="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N33" s="38">
+      <c r="N33" s="36">
         <f>IF(F33="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14549,25 +14547,25 @@
           <t>Incident 21</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="26" t="n">
         <v>58</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="27">
         <f>IF(B34="","",B34^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="27">
         <f>IF(COUNT(C33:C34)=2,ABS(C34-C33),"")</f>
         <v/>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="27">
         <f>IF(B34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F34" s="30" t="n">
+      <c r="F34" s="26" t="n">
         <v>56900</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="34">
         <f>IF(F34="","",$B$10)</f>
         <v/>
       </c>
@@ -14575,23 +14573,23 @@
         <f>IF(B34="","",IF(C34&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C34&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J34" s="37">
+      <c r="J34" s="35">
         <f>IF(B34="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K34" s="37">
+      <c r="K34" s="35">
         <f>IF(B34="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L34" s="37">
+      <c r="L34" s="35">
         <f>IF(B34="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M34" s="38">
+      <c r="M34" s="36">
         <f>IF(F34="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N34" s="38">
+      <c r="N34" s="36">
         <f>IF(F34="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14618,25 +14616,25 @@
           <t>Incident 22</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="26" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="27">
         <f>IF(B35="","",B35^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="27">
         <f>IF(COUNT(C34:C35)=2,ABS(C35-C34),"")</f>
         <v/>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="27">
         <f>IF(B35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F35" s="30" t="n">
+      <c r="F35" s="26" t="n">
         <v>29900</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="34">
         <f>IF(F35="","",$B$10)</f>
         <v/>
       </c>
@@ -14644,23 +14642,23 @@
         <f>IF(B35="","",IF(C35&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C35&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J35" s="37">
+      <c r="J35" s="35">
         <f>IF(B35="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K35" s="37">
+      <c r="K35" s="35">
         <f>IF(B35="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="35">
         <f>IF(B35="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M35" s="38">
+      <c r="M35" s="36">
         <f>IF(F35="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N35" s="38">
+      <c r="N35" s="36">
         <f>IF(F35="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14687,25 +14685,25 @@
           <t>Incident 23</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="26" t="n">
         <v>47</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="27">
         <f>IF(B36="","",B36^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="27">
         <f>IF(COUNT(C35:C36)=2,ABS(C36-C35),"")</f>
         <v/>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="27">
         <f>IF(B36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F36" s="30" t="n">
+      <c r="F36" s="26" t="n">
         <v>45200</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="34">
         <f>IF(F36="","",$B$10)</f>
         <v/>
       </c>
@@ -14713,23 +14711,23 @@
         <f>IF(B36="","",IF(C36&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C36&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J36" s="37">
+      <c r="J36" s="35">
         <f>IF(B36="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K36" s="37">
+      <c r="K36" s="35">
         <f>IF(B36="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L36" s="37">
+      <c r="L36" s="35">
         <f>IF(B36="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M36" s="38">
+      <c r="M36" s="36">
         <f>IF(F36="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N36" s="38">
+      <c r="N36" s="36">
         <f>IF(F36="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14756,25 +14754,25 @@
           <t>Incident 24</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="26" t="n">
         <v>40</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="27">
         <f>IF(B37="","",B37^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D37" s="28">
+      <c r="D37" s="27">
         <f>IF(COUNT(C36:C37)=2,ABS(C37-C36),"")</f>
         <v/>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="27">
         <f>IF(B37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F37" s="30" t="n">
+      <c r="F37" s="26" t="n">
         <v>38400</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="34">
         <f>IF(F37="","",$B$10)</f>
         <v/>
       </c>
@@ -14782,23 +14780,23 @@
         <f>IF(B37="","",IF(C37&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C37&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J37" s="37">
+      <c r="J37" s="35">
         <f>IF(B37="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K37" s="37">
+      <c r="K37" s="35">
         <f>IF(B37="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="35">
         <f>IF(B37="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M37" s="38">
+      <c r="M37" s="36">
         <f>IF(F37="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N37" s="38">
+      <c r="N37" s="36">
         <f>IF(F37="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -8641,7 +8641,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
           <t>D4 for this n</t>
@@ -8650,6 +8650,11 @@
       <c r="B9" s="23">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{3.267;2.574;2.282;2.114;2.004;1.924;1.864;1.816;1.777}),"n out of range")</f>
         <v/>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Sets the upper limit on the range chart: R-bar x D4. It is the only one of the three that is never zero.</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -10537,10 +10542,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="C8:L8"/>
+    <mergeCell ref="C9:L9"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C3:L3"/>
     <mergeCell ref="C11:L11"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -11815,7 +11815,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Sigma estimate</t>
@@ -11824,6 +11824,11 @@
       <c r="B9" s="17">
         <f>B8/1.128</f>
         <v/>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>The process's ordinary spread, taken from point-to-point movement rather than from a standard deviation — one bad week inflates a standard deviation and this resists that. Every CUSUM value below is counted in these units, so if this is wrong the whole chart is.</t>
+        </is>
       </c>
     </row>
     <row r="10"/>
@@ -12902,8 +12907,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C9:I9"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A1:I1"/>
@@ -13026,7 +13032,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Transformed MR-bar</t>
@@ -13035,6 +13041,11 @@
       <c r="B8" s="29">
         <f>AVERAGE(D15:D37)</f>
         <v/>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>MR-bar = the average moving range, the typical step from one point to the next. It is the spread the limits below are built from, and it is measured on the transformed scale, not in days — do not try to read it as a number of days.</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -14824,7 +14835,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="C6:H6"/>
@@ -14833,6 +14844,7 @@
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C8:H8"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C7:H7"/>
   </mergeCells>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -173,6 +173,7 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +181,7 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4067,7 +4069,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="22" t="n">
         <v>415</v>
       </c>
       <c r="C15" s="17">
@@ -4120,7 +4122,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
+      <c r="B16" s="22" t="n">
         <v>402</v>
       </c>
       <c r="C16" s="17">
@@ -4173,7 +4175,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="22" t="n">
         <v>431</v>
       </c>
       <c r="C17" s="17">
@@ -4226,7 +4228,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="22" t="n">
         <v>419</v>
       </c>
       <c r="C18" s="17">
@@ -4279,7 +4281,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="22" t="n">
         <v>396</v>
       </c>
       <c r="C19" s="17">
@@ -4332,7 +4334,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="22" t="n">
         <v>424</v>
       </c>
       <c r="C20" s="17">
@@ -4385,7 +4387,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="22" t="n">
         <v>410</v>
       </c>
       <c r="C21" s="17">
@@ -4438,7 +4440,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="22" t="n">
         <v>438</v>
       </c>
       <c r="C22" s="17">
@@ -4491,7 +4493,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="22" t="n">
         <v>405</v>
       </c>
       <c r="C23" s="17">
@@ -4544,7 +4546,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="22" t="n">
         <v>417</v>
       </c>
       <c r="C24" s="17">
@@ -4597,7 +4599,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="22" t="n">
         <v>429</v>
       </c>
       <c r="C25" s="17">
@@ -4650,7 +4652,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="22" t="n">
         <v>401</v>
       </c>
       <c r="C26" s="17">
@@ -4703,7 +4705,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="22" t="n">
         <v>422</v>
       </c>
       <c r="C27" s="17">
@@ -4756,7 +4758,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="22" t="n">
         <v>413</v>
       </c>
       <c r="C28" s="17">
@@ -4809,7 +4811,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n">
+      <c r="B29" s="22" t="n">
         <v>407</v>
       </c>
       <c r="C29" s="17">
@@ -4862,7 +4864,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n">
+      <c r="B30" s="22" t="n">
         <v>435</v>
       </c>
       <c r="C30" s="17">
@@ -4915,7 +4917,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="22" t="n">
         <v>398</v>
       </c>
       <c r="C31" s="17">
@@ -4968,7 +4970,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B32" s="22" t="n">
         <v>420</v>
       </c>
       <c r="C32" s="17">
@@ -5021,7 +5023,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B33" s="22" t="n">
         <v>411</v>
       </c>
       <c r="C33" s="17">
@@ -5074,7 +5076,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="19" t="n">
+      <c r="B34" s="22" t="n">
         <v>442</v>
       </c>
       <c r="C34" s="17">
@@ -5127,7 +5129,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="B35" s="22" t="n">
         <v>404</v>
       </c>
       <c r="C35" s="17">
@@ -5180,7 +5182,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n">
+      <c r="B36" s="22" t="n">
         <v>416</v>
       </c>
       <c r="C36" s="17">
@@ -5233,7 +5235,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n">
+      <c r="B37" s="22" t="n">
         <v>428</v>
       </c>
       <c r="C37" s="17">
@@ -5387,7 +5389,7 @@
           <t>Overall proportion (p-bar)</t>
         </is>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="23">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -5403,7 +5405,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="24">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -5419,7 +5421,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -5435,7 +5437,7 @@
           <t>Ordinary p-chart limits would be</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>"±"&amp;TEXT(3*SQRT(B5*(1-B5)/AVERAGE(B14:B37)),"0.00%")</f>
         <v/>
       </c>
@@ -5505,17 +5507,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -5542,17 +5544,17 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>7820</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>5610</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="23">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",SQRT($B$5*(1-$B$5)/B14))</f>
         <v/>
       </c>
@@ -5564,15 +5566,15 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="29">
         <f>IF(B14="","",MIN(1,$B$5+3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="29">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="29">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
@@ -5594,17 +5596,17 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="30" t="n">
         <v>8140</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="30" t="n">
         <v>5990</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="23">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",SQRT($B$5*(1-$B$5)/B15))</f>
         <v/>
       </c>
@@ -5620,15 +5622,15 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="29">
         <f>IF(B15="","",MIN(1,$B$5+3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="29">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="29">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
@@ -5650,17 +5652,17 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="30" t="n">
         <v>7960</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="30" t="n">
         <v>5570</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="23">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",SQRT($B$5*(1-$B$5)/B16))</f>
         <v/>
       </c>
@@ -5676,15 +5678,15 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>IF(B16="","",MIN(1,$B$5+3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
@@ -5706,17 +5708,17 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="30" t="n">
         <v>8310</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="30" t="n">
         <v>6120</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",SQRT($B$5*(1-$B$5)/B17))</f>
         <v/>
       </c>
@@ -5732,15 +5734,15 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="29">
         <f>IF(B17="","",MIN(1,$B$5+3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="29">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="29">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
@@ -5762,17 +5764,17 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="30" t="n">
         <v>7690</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="30" t="n">
         <v>5410</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="23">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",SQRT($B$5*(1-$B$5)/B18))</f>
         <v/>
       </c>
@@ -5788,15 +5790,15 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="29">
         <f>IF(B18="","",MIN(1,$B$5+3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="29">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="28">
+      <c r="M18" s="29">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
@@ -5818,17 +5820,17 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="30" t="n">
         <v>8020</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="30" t="n">
         <v>5880</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",SQRT($B$5*(1-$B$5)/B19))</f>
         <v/>
       </c>
@@ -5844,15 +5846,15 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="29">
         <f>IF(B19="","",MIN(1,$B$5+3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="29">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="28">
+      <c r="M19" s="29">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
@@ -5874,17 +5876,17 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="30" t="n">
         <v>8450</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="30" t="n">
         <v>6210</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",SQRT($B$5*(1-$B$5)/B20))</f>
         <v/>
       </c>
@@ -5900,15 +5902,15 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="29">
         <f>IF(B20="","",MIN(1,$B$5+3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="29">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="28">
+      <c r="M20" s="29">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
@@ -5930,17 +5932,17 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="30" t="n">
         <v>7880</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="30" t="n">
         <v>5490</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",SQRT($B$5*(1-$B$5)/B21))</f>
         <v/>
       </c>
@@ -5956,15 +5958,15 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>IF(B21="","",MIN(1,$B$5+3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
@@ -5986,17 +5988,17 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="30" t="n">
         <v>8210</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="30" t="n">
         <v>6050</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",SQRT($B$5*(1-$B$5)/B22))</f>
         <v/>
       </c>
@@ -6012,15 +6014,15 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="29">
         <f>IF(B22="","",MIN(1,$B$5+3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="29">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="28">
+      <c r="M22" s="29">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
@@ -6042,17 +6044,17 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="30" t="n">
         <v>7740</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="30" t="n">
         <v>5380</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",SQRT($B$5*(1-$B$5)/B23))</f>
         <v/>
       </c>
@@ -6068,15 +6070,15 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>IF(B23="","",MIN(1,$B$5+3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
@@ -6098,17 +6100,17 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="30" t="n">
         <v>8090</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="30" t="n">
         <v>5940</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",SQRT($B$5*(1-$B$5)/B24))</f>
         <v/>
       </c>
@@ -6124,15 +6126,15 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="29">
         <f>IF(B24="","",MIN(1,$B$5+3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="29">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="28">
+      <c r="M24" s="29">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
@@ -6154,17 +6156,17 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="30" t="n">
         <v>8380</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="30" t="n">
         <v>6180</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",SQRT($B$5*(1-$B$5)/B25))</f>
         <v/>
       </c>
@@ -6180,15 +6182,15 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="29">
         <f>IF(B25="","",MIN(1,$B$5+3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="29">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="28">
+      <c r="M25" s="29">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
@@ -6210,17 +6212,17 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="30" t="n">
         <v>7930</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="30" t="n">
         <v>5520</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="23">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",SQRT($B$5*(1-$B$5)/B26))</f>
         <v/>
       </c>
@@ -6236,15 +6238,15 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="28">
+      <c r="K26" s="29">
         <f>IF(B26="","",MIN(1,$B$5+3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="29">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="28">
+      <c r="M26" s="29">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
@@ -6266,17 +6268,17 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="30" t="n">
         <v>8260</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="30" t="n">
         <v>6010</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="23">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",SQRT($B$5*(1-$B$5)/B27))</f>
         <v/>
       </c>
@@ -6292,15 +6294,15 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="28">
+      <c r="K27" s="29">
         <f>IF(B27="","",MIN(1,$B$5+3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="29">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="28">
+      <c r="M27" s="29">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
@@ -6322,17 +6324,17 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="30" t="n">
         <v>7810</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="30" t="n">
         <v>5480</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="23">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",SQRT($B$5*(1-$B$5)/B28))</f>
         <v/>
       </c>
@@ -6348,15 +6350,15 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="29">
         <f>IF(B28="","",MIN(1,$B$5+3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="29">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="28">
+      <c r="M28" s="29">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
@@ -6378,17 +6380,17 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="30" t="n">
         <v>8150</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="30" t="n">
         <v>5860</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="23">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",SQRT($B$5*(1-$B$5)/B29))</f>
         <v/>
       </c>
@@ -6404,15 +6406,15 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="28">
+      <c r="K29" s="29">
         <f>IF(B29="","",MIN(1,$B$5+3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="29">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="28">
+      <c r="M29" s="29">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
@@ -6434,17 +6436,17 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="30" t="n">
         <v>8470</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="30" t="n">
         <v>6240</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="23">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",SQRT($B$5*(1-$B$5)/B30))</f>
         <v/>
       </c>
@@ -6460,15 +6462,15 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="28">
+      <c r="K30" s="29">
         <f>IF(B30="","",MIN(1,$B$5+3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="L30" s="28">
+      <c r="L30" s="29">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="28">
+      <c r="M30" s="29">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
@@ -6490,17 +6492,17 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="30" t="n">
         <v>7860</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="30" t="n">
         <v>5600</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",SQRT($B$5*(1-$B$5)/B31))</f>
         <v/>
       </c>
@@ -6516,15 +6518,15 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="28">
+      <c r="K31" s="29">
         <f>IF(B31="","",MIN(1,$B$5+3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="29">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="28">
+      <c r="M31" s="29">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
@@ -6546,17 +6548,17 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="30" t="n">
         <v>8030</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="30" t="n">
         <v>5760</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="23">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",SQRT($B$5*(1-$B$5)/B32))</f>
         <v/>
       </c>
@@ -6572,15 +6574,15 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="28">
+      <c r="K32" s="29">
         <f>IF(B32="","",MIN(1,$B$5+3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="L32" s="28">
+      <c r="L32" s="29">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="28">
+      <c r="M32" s="29">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
@@ -6602,17 +6604,17 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="30" t="n">
         <v>8340</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="30" t="n">
         <v>6090</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="23">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",SQRT($B$5*(1-$B$5)/B33))</f>
         <v/>
       </c>
@@ -6628,15 +6630,15 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="28">
+      <c r="K33" s="29">
         <f>IF(B33="","",MIN(1,$B$5+3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="29">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="28">
+      <c r="M33" s="29">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
@@ -6658,17 +6660,17 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="30" t="n">
         <v>7900</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="30" t="n">
         <v>5710</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="23">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",SQRT($B$5*(1-$B$5)/B34))</f>
         <v/>
       </c>
@@ -6684,15 +6686,15 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="28">
+      <c r="K34" s="29">
         <f>IF(B34="","",MIN(1,$B$5+3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="L34" s="28">
+      <c r="L34" s="29">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="28">
+      <c r="M34" s="29">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
@@ -6714,17 +6716,17 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="30" t="n">
         <v>8180</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="30" t="n">
         <v>5900</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="23">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",SQRT($B$5*(1-$B$5)/B35))</f>
         <v/>
       </c>
@@ -6740,15 +6742,15 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="28">
+      <c r="K35" s="29">
         <f>IF(B35="","",MIN(1,$B$5+3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="L35" s="28">
+      <c r="L35" s="29">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="28">
+      <c r="M35" s="29">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
@@ -6770,17 +6772,17 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="30" t="n">
         <v>7770</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="30" t="n">
         <v>5450</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="23">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",SQRT($B$5*(1-$B$5)/B36))</f>
         <v/>
       </c>
@@ -6796,15 +6798,15 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="28">
+      <c r="K36" s="29">
         <f>IF(B36="","",MIN(1,$B$5+3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="L36" s="28">
+      <c r="L36" s="29">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="28">
+      <c r="M36" s="29">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
@@ -6826,17 +6828,17 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="30" t="n">
         <v>8240</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="30" t="n">
         <v>6020</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="23">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",SQRT($B$5*(1-$B$5)/B37))</f>
         <v/>
       </c>
@@ -6852,15 +6854,15 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="28">
+      <c r="K37" s="29">
         <f>IF(B37="","",MIN(1,$B$5+3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="L37" s="28">
+      <c r="L37" s="29">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="28">
+      <c r="M37" s="29">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
@@ -6980,7 +6982,7 @@
           <t>Overall rate (u-bar)</t>
         </is>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="31">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -6996,7 +6998,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="24">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -7012,7 +7014,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -7098,17 +7100,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -7135,17 +7137,17 @@
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>1240</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",SQRT($B$5/B14))</f>
         <v/>
       </c>
@@ -7157,15 +7159,15 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="32">
         <f>IF(B14="","",$B$5+3*E14*$B$7)</f>
         <v/>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="32">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="32">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
@@ -7187,17 +7189,17 @@
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="30" t="n">
         <v>1310</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="30" t="n">
         <v>68</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",SQRT($B$5/B15))</f>
         <v/>
       </c>
@@ -7213,15 +7215,15 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="30">
+      <c r="K15" s="32">
         <f>IF(B15="","",$B$5+3*E15*$B$7)</f>
         <v/>
       </c>
-      <c r="L15" s="30">
+      <c r="L15" s="32">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="30">
+      <c r="M15" s="32">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
@@ -7243,17 +7245,17 @@
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="30" t="n">
         <v>1180</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",SQRT($B$5/B16))</f>
         <v/>
       </c>
@@ -7269,15 +7271,15 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="32">
         <f>IF(B16="","",$B$5+3*E16*$B$7)</f>
         <v/>
       </c>
-      <c r="L16" s="30">
+      <c r="L16" s="32">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="30">
+      <c r="M16" s="32">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
@@ -7299,17 +7301,17 @@
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="30" t="n">
         <v>1420</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="30" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",SQRT($B$5/B17))</f>
         <v/>
       </c>
@@ -7325,15 +7327,15 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="32">
         <f>IF(B17="","",$B$5+3*E17*$B$7)</f>
         <v/>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="32">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="32">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
@@ -7355,17 +7357,17 @@
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="30" t="n">
         <v>1275</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",SQRT($B$5/B18))</f>
         <v/>
       </c>
@@ -7381,15 +7383,15 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="32">
         <f>IF(B18="","",$B$5+3*E18*$B$7)</f>
         <v/>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="32">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="30">
+      <c r="M18" s="32">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
@@ -7411,17 +7413,17 @@
           <t>Week 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="30" t="n">
         <v>1195</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="30" t="n">
         <v>59</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",SQRT($B$5/B19))</f>
         <v/>
       </c>
@@ -7437,15 +7439,15 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="32">
         <f>IF(B19="","",$B$5+3*E19*$B$7)</f>
         <v/>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="32">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="32">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
@@ -7467,17 +7469,17 @@
           <t>Week 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="30" t="n">
         <v>1360</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="30" t="n">
         <v>56</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",SQRT($B$5/B20))</f>
         <v/>
       </c>
@@ -7493,15 +7495,15 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="32">
         <f>IF(B20="","",$B$5+3*E20*$B$7)</f>
         <v/>
       </c>
-      <c r="L20" s="30">
+      <c r="L20" s="32">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="32">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
@@ -7523,17 +7525,17 @@
           <t>Week 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="30" t="n">
         <v>1230</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="30" t="n">
         <v>69</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",SQRT($B$5/B21))</f>
         <v/>
       </c>
@@ -7549,15 +7551,15 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="32">
         <f>IF(B21="","",$B$5+3*E21*$B$7)</f>
         <v/>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="32">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="32">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
@@ -7579,17 +7581,17 @@
           <t>Week 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="30" t="n">
         <v>1405</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",SQRT($B$5/B22))</f>
         <v/>
       </c>
@@ -7605,15 +7607,15 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="32">
         <f>IF(B22="","",$B$5+3*E22*$B$7)</f>
         <v/>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="32">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="32">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
@@ -7635,17 +7637,17 @@
           <t>Week 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="30" t="n">
         <v>1150</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="30" t="n">
         <v>54</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",SQRT($B$5/B23))</f>
         <v/>
       </c>
@@ -7661,15 +7663,15 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="32">
         <f>IF(B23="","",$B$5+3*E23*$B$7)</f>
         <v/>
       </c>
-      <c r="L23" s="30">
+      <c r="L23" s="32">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="32">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
@@ -7691,17 +7693,17 @@
           <t>Week 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="30" t="n">
         <v>1290</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="30" t="n">
         <v>49</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",SQRT($B$5/B24))</f>
         <v/>
       </c>
@@ -7717,15 +7719,15 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="32">
         <f>IF(B24="","",$B$5+3*E24*$B$7)</f>
         <v/>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="32">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="32">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
@@ -7747,17 +7749,17 @@
           <t>Week 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="30" t="n">
         <v>1375</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="30" t="n">
         <v>74</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="28">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",SQRT($B$5/B25))</f>
         <v/>
       </c>
@@ -7773,15 +7775,15 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="32">
         <f>IF(B25="","",$B$5+3*E25*$B$7)</f>
         <v/>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="32">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="32">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
@@ -7803,17 +7805,17 @@
           <t>Week 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="30" t="n">
         <v>1215</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="30" t="n">
         <v>39</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",SQRT($B$5/B26))</f>
         <v/>
       </c>
@@ -7829,15 +7831,15 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="32">
         <f>IF(B26="","",$B$5+3*E26*$B$7)</f>
         <v/>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="32">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="32">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
@@ -7859,17 +7861,17 @@
           <t>Week 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="30" t="n">
         <v>1330</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="30" t="n">
         <v>66</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",SQRT($B$5/B27))</f>
         <v/>
       </c>
@@ -7885,15 +7887,15 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="32">
         <f>IF(B27="","",$B$5+3*E27*$B$7)</f>
         <v/>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="32">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="32">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
@@ -7915,17 +7917,17 @@
           <t>Week 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="30" t="n">
         <v>1185</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",SQRT($B$5/B28))</f>
         <v/>
       </c>
@@ -7941,15 +7943,15 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="32">
         <f>IF(B28="","",$B$5+3*E28*$B$7)</f>
         <v/>
       </c>
-      <c r="L28" s="30">
+      <c r="L28" s="32">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="30">
+      <c r="M28" s="32">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
@@ -7971,17 +7973,17 @@
           <t>Week 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="30" t="n">
         <v>1265</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",SQRT($B$5/B29))</f>
         <v/>
       </c>
@@ -7997,15 +7999,15 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="30">
+      <c r="K29" s="32">
         <f>IF(B29="","",$B$5+3*E29*$B$7)</f>
         <v/>
       </c>
-      <c r="L29" s="30">
+      <c r="L29" s="32">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="30">
+      <c r="M29" s="32">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
@@ -8027,17 +8029,17 @@
           <t>Week 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="30" t="n">
         <v>1440</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",SQRT($B$5/B30))</f>
         <v/>
       </c>
@@ -8053,15 +8055,15 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="30">
+      <c r="K30" s="32">
         <f>IF(B30="","",$B$5+3*E30*$B$7)</f>
         <v/>
       </c>
-      <c r="L30" s="30">
+      <c r="L30" s="32">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="30">
+      <c r="M30" s="32">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
@@ -8083,17 +8085,17 @@
           <t>Week 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="30" t="n">
         <v>1205</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="30" t="n">
         <v>54</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",SQRT($B$5/B31))</f>
         <v/>
       </c>
@@ -8109,15 +8111,15 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="30">
+      <c r="K31" s="32">
         <f>IF(B31="","",$B$5+3*E31*$B$7)</f>
         <v/>
       </c>
-      <c r="L31" s="30">
+      <c r="L31" s="32">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="30">
+      <c r="M31" s="32">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
@@ -8139,17 +8141,17 @@
           <t>Week 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="30" t="n">
         <v>1300</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",SQRT($B$5/B32))</f>
         <v/>
       </c>
@@ -8165,15 +8167,15 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="30">
+      <c r="K32" s="32">
         <f>IF(B32="","",$B$5+3*E32*$B$7)</f>
         <v/>
       </c>
-      <c r="L32" s="30">
+      <c r="L32" s="32">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="30">
+      <c r="M32" s="32">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
@@ -8195,17 +8197,17 @@
           <t>Week 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="30" t="n">
         <v>1355</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="30" t="n">
         <v>72</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",SQRT($B$5/B33))</f>
         <v/>
       </c>
@@ -8221,15 +8223,15 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="30">
+      <c r="K33" s="32">
         <f>IF(B33="","",$B$5+3*E33*$B$7)</f>
         <v/>
       </c>
-      <c r="L33" s="30">
+      <c r="L33" s="32">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="30">
+      <c r="M33" s="32">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
@@ -8251,17 +8253,17 @@
           <t>Week 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="30" t="n">
         <v>1170</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="30" t="n">
         <v>43</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",SQRT($B$5/B34))</f>
         <v/>
       </c>
@@ -8277,15 +8279,15 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="30">
+      <c r="K34" s="32">
         <f>IF(B34="","",$B$5+3*E34*$B$7)</f>
         <v/>
       </c>
-      <c r="L34" s="30">
+      <c r="L34" s="32">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="30">
+      <c r="M34" s="32">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
@@ -8307,17 +8309,17 @@
           <t>Week 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="30" t="n">
         <v>1285</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="30" t="n">
         <v>62</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",SQRT($B$5/B35))</f>
         <v/>
       </c>
@@ -8333,15 +8335,15 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="30">
+      <c r="K35" s="32">
         <f>IF(B35="","",$B$5+3*E35*$B$7)</f>
         <v/>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="32">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="30">
+      <c r="M35" s="32">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
@@ -8363,17 +8365,17 @@
           <t>Week 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="30" t="n">
         <v>1225</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="28">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",SQRT($B$5/B36))</f>
         <v/>
       </c>
@@ -8389,15 +8391,15 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="30">
+      <c r="K36" s="32">
         <f>IF(B36="","",$B$5+3*E36*$B$7)</f>
         <v/>
       </c>
-      <c r="L36" s="30">
+      <c r="L36" s="32">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="30">
+      <c r="M36" s="32">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
@@ -8419,17 +8421,17 @@
           <t>Week 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="30" t="n">
         <v>1390</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="30" t="n">
         <v>76</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="28">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",SQRT($B$5/B37))</f>
         <v/>
       </c>
@@ -8445,15 +8447,15 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="30">
+      <c r="K37" s="32">
         <f>IF(B37="","",$B$5+3*E37*$B$7)</f>
         <v/>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="32">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="30">
+      <c r="M37" s="32">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
@@ -8631,7 +8633,7 @@
           <t>A2 for this n</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{1.880;1.023;0.729;0.577;0.483;0.419;0.373;0.337;0.308}),"n out of range")</f>
         <v/>
       </c>
@@ -8647,7 +8649,7 @@
           <t>D4 for this n</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{3.267;2.574;2.282;2.114;2.004;1.924;1.864;1.816;1.777}),"n out of range")</f>
         <v/>
       </c>
@@ -8663,7 +8665,7 @@
           <t>D3 for this n</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{0;0;0;0;0;0.076;0.136;0.184;0.223}),"n out of range")</f>
         <v/>
       </c>
@@ -8679,7 +8681,7 @@
           <t>Xbar UCL / LCL</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <f>TEXT(B6+B8*B7,"#,##0.00")&amp;"  /  "&amp;TEXT(B6-B8*B7,"#,##0.00")</f>
         <v/>
       </c>
@@ -8795,19 +8797,19 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>419</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="27" t="n">
         <v>381</v>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="27" t="n">
         <v>419</v>
       </c>
       <c r="G14" s="17">
@@ -8834,15 +8836,15 @@
         <f>IF(G14="","",IF(OR(G14&gt;J14,G14&lt;K14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="33">
         <f>IF(H14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="31">
+      <c r="O14" s="33">
         <f>IF(H14="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P14" s="31">
+      <c r="P14" s="33">
         <f>IF(H14="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -8868,19 +8870,19 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="30" t="n">
         <v>395</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="30" t="n">
         <v>400</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="30" t="n">
         <v>395</v>
       </c>
       <c r="G15" s="17">
@@ -8907,15 +8909,15 @@
         <f>IF(G15="","",IF(OR(G15&gt;J15,G15&lt;K15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N15" s="31">
+      <c r="N15" s="33">
         <f>IF(H15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="31">
+      <c r="O15" s="33">
         <f>IF(H15="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P15" s="31">
+      <c r="P15" s="33">
         <f>IF(H15="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -8941,19 +8943,19 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="30" t="n">
         <v>411</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="30" t="n">
         <v>401</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="30" t="n">
         <v>438</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="30" t="n">
         <v>410</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="30" t="n">
         <v>401</v>
       </c>
       <c r="G16" s="17">
@@ -8980,15 +8982,15 @@
         <f>IF(G16="","",IF(OR(G16&gt;J16,G16&lt;K16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N16" s="31">
+      <c r="N16" s="33">
         <f>IF(H16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O16" s="31">
+      <c r="O16" s="33">
         <f>IF(H16="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P16" s="31">
+      <c r="P16" s="33">
         <f>IF(H16="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9014,19 +9016,19 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="30" t="n">
         <v>402</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="30" t="n">
         <v>440</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="30" t="n">
         <v>425</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="30" t="n">
         <v>402</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="30" t="n">
         <v>440</v>
       </c>
       <c r="G17" s="17">
@@ -9053,15 +9055,15 @@
         <f>IF(G17="","",IF(OR(G17&gt;J17,G17&lt;K17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N17" s="31">
+      <c r="N17" s="33">
         <f>IF(H17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O17" s="31">
+      <c r="O17" s="33">
         <f>IF(H17="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P17" s="31">
+      <c r="P17" s="33">
         <f>IF(H17="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9087,19 +9089,19 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="30" t="n">
         <v>437</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="30" t="n">
         <v>437</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="30" t="n">
         <v>404</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="30" t="n">
         <v>437</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="30" t="n">
         <v>437</v>
       </c>
       <c r="G18" s="17">
@@ -9126,15 +9128,15 @@
         <f>IF(G18="","",IF(OR(G18&gt;J18,G18&lt;K18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N18" s="31">
+      <c r="N18" s="33">
         <f>IF(H18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O18" s="31">
+      <c r="O18" s="33">
         <f>IF(H18="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P18" s="31">
+      <c r="P18" s="33">
         <f>IF(H18="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9160,19 +9162,19 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="30" t="n">
         <v>392</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="30" t="n">
         <v>415</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="30" t="n">
         <v>392</v>
       </c>
       <c r="G19" s="17">
@@ -9199,15 +9201,15 @@
         <f>IF(G19="","",IF(OR(G19&gt;J19,G19&lt;K19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N19" s="31">
+      <c r="N19" s="33">
         <f>IF(H19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="31">
+      <c r="O19" s="33">
         <f>IF(H19="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P19" s="31">
+      <c r="P19" s="33">
         <f>IF(H19="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9233,19 +9235,19 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="30" t="n">
         <v>406</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="30" t="n">
         <v>433</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="30" t="n">
         <v>406</v>
       </c>
       <c r="G20" s="17">
@@ -9272,15 +9274,15 @@
         <f>IF(G20="","",IF(OR(G20&gt;J20,G20&lt;K20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N20" s="31">
+      <c r="N20" s="33">
         <f>IF(H20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="31">
+      <c r="O20" s="33">
         <f>IF(H20="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P20" s="31">
+      <c r="P20" s="33">
         <f>IF(H20="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9306,19 +9308,19 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="30" t="n">
         <v>431</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="30" t="n">
         <v>401</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="30" t="n">
         <v>431</v>
       </c>
       <c r="G21" s="17">
@@ -9345,15 +9347,15 @@
         <f>IF(G21="","",IF(OR(G21&gt;J21,G21&lt;K21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="33">
         <f>IF(H21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="33">
         <f>IF(H21="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="33">
         <f>IF(H21="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9379,19 +9381,19 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="30" t="n">
         <v>425</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="30" t="n">
         <v>407</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="30" t="n">
         <v>387</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="30" t="n">
         <v>425</v>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="30" t="n">
         <v>406</v>
       </c>
       <c r="G22" s="17">
@@ -9418,15 +9420,15 @@
         <f>IF(G22="","",IF(OR(G22&gt;J22,G22&lt;K22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="33">
         <f>IF(H22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="33">
         <f>IF(H22="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="33">
         <f>IF(H22="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9452,19 +9454,19 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="30" t="n">
         <v>413</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="30" t="n">
         <v>382</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="30" t="n">
         <v>417</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="30" t="n">
         <v>412</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="30" t="n">
         <v>382</v>
       </c>
       <c r="G23" s="17">
@@ -9491,15 +9493,15 @@
         <f>IF(G23="","",IF(OR(G23&gt;J23,G23&lt;K23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N23" s="31">
+      <c r="N23" s="33">
         <f>IF(H23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="31">
+      <c r="O23" s="33">
         <f>IF(H23="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P23" s="31">
+      <c r="P23" s="33">
         <f>IF(H23="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9525,19 +9527,19 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="30" t="n">
         <v>367</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="30" t="n">
         <v>393</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="30" t="n">
         <v>404</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="30" t="n">
         <v>367</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="30" t="n">
         <v>394</v>
       </c>
       <c r="G24" s="17">
@@ -9564,15 +9566,15 @@
         <f>IF(G24="","",IF(OR(G24&gt;J24,G24&lt;K24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="33">
         <f>IF(H24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="33">
         <f>IF(H24="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="33">
         <f>IF(H24="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9598,19 +9600,19 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="30" t="n">
         <v>386</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="30" t="n">
         <v>410</v>
       </c>
-      <c r="D25" s="26" t="n">
+      <c r="D25" s="30" t="n">
         <v>372</v>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="30" t="n">
         <v>386</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="30" t="n">
         <v>409</v>
       </c>
       <c r="G25" s="17">
@@ -9637,15 +9639,15 @@
         <f>IF(G25="","",IF(OR(G25&gt;J25,G25&lt;K25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="33">
         <f>IF(H25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="33">
         <f>IF(H25="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="33">
         <f>IF(H25="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9671,19 +9673,19 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="30" t="n">
         <v>415</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="30" t="n">
         <v>382</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="30" t="n">
         <v>381</v>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="30" t="n">
         <v>415</v>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="30" t="n">
         <v>382</v>
       </c>
       <c r="G26" s="17">
@@ -9710,15 +9712,15 @@
         <f>IF(G26="","",IF(OR(G26&gt;J26,G26&lt;K26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N26" s="31">
+      <c r="N26" s="33">
         <f>IF(H26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O26" s="31">
+      <c r="O26" s="33">
         <f>IF(H26="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P26" s="31">
+      <c r="P26" s="33">
         <f>IF(H26="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9744,19 +9746,19 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="30" t="n">
         <v>381</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="30" t="n">
         <v>419</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="30" t="n">
         <v>396</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="30" t="n">
         <v>381</v>
       </c>
       <c r="G27" s="17">
@@ -9783,15 +9785,15 @@
         <f>IF(G27="","",IF(OR(G27&gt;J27,G27&lt;K27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="33">
         <f>IF(H27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="33">
         <f>IF(H27="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="33">
         <f>IF(H27="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9817,19 +9819,19 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="30" t="n">
         <v>385</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="30" t="n">
         <v>421</v>
       </c>
-      <c r="D28" s="26" t="n">
+      <c r="D28" s="30" t="n">
         <v>412</v>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="30" t="n">
         <v>385</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="30" t="n">
         <v>421</v>
       </c>
       <c r="G28" s="17">
@@ -9856,15 +9858,15 @@
         <f>IF(G28="","",IF(OR(G28&gt;J28,G28&lt;K28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="33">
         <f>IF(H28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="33">
         <f>IF(H28="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="33">
         <f>IF(H28="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9890,19 +9892,19 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="30" t="n">
         <v>407</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="30" t="n">
         <v>413</v>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D29" s="30" t="n">
         <v>378</v>
       </c>
-      <c r="E29" s="26" t="n">
+      <c r="E29" s="30" t="n">
         <v>408</v>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="30" t="n">
         <v>413</v>
       </c>
       <c r="G29" s="17">
@@ -9929,15 +9931,15 @@
         <f>IF(G29="","",IF(OR(G29&gt;J29,G29&lt;K29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N29" s="31">
+      <c r="N29" s="33">
         <f>IF(H29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="31">
+      <c r="O29" s="33">
         <f>IF(H29="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P29" s="31">
+      <c r="P29" s="33">
         <f>IF(H29="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9963,19 +9965,19 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="30" t="n">
         <v>428</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="30" t="n">
         <v>389</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="30" t="n">
         <v>408</v>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="30" t="n">
         <v>427</v>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="30" t="n">
         <v>389</v>
       </c>
       <c r="G30" s="17">
@@ -10002,15 +10004,15 @@
         <f>IF(G30="","",IF(OR(G30&gt;J30,G30&lt;K30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N30" s="31">
+      <c r="N30" s="33">
         <f>IF(H30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O30" s="31">
+      <c r="O30" s="33">
         <f>IF(H30="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P30" s="31">
+      <c r="P30" s="33">
         <f>IF(H30="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10036,19 +10038,19 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="30" t="n">
         <v>407</v>
       </c>
-      <c r="D31" s="26" t="n">
+      <c r="D31" s="30" t="n">
         <v>438</v>
       </c>
-      <c r="E31" s="26" t="n">
+      <c r="E31" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="30" t="n">
         <v>407</v>
       </c>
       <c r="G31" s="17">
@@ -10075,15 +10077,15 @@
         <f>IF(G31="","",IF(OR(G31&gt;J31,G31&lt;K31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N31" s="31">
+      <c r="N31" s="33">
         <f>IF(H31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O31" s="31">
+      <c r="O31" s="33">
         <f>IF(H31="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P31" s="31">
+      <c r="P31" s="33">
         <f>IF(H31="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10109,19 +10111,19 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="30" t="n">
         <v>406</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="30" t="n">
         <v>443</v>
       </c>
-      <c r="D32" s="26" t="n">
+      <c r="D32" s="30" t="n">
         <v>417</v>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="30" t="n">
         <v>406</v>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="30" t="n">
         <v>443</v>
       </c>
       <c r="G32" s="17">
@@ -10148,15 +10150,15 @@
         <f>IF(G32="","",IF(OR(G32&gt;J32,G32&lt;K32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N32" s="31">
+      <c r="N32" s="33">
         <f>IF(H32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O32" s="31">
+      <c r="O32" s="33">
         <f>IF(H32="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P32" s="31">
+      <c r="P32" s="33">
         <f>IF(H32="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10182,19 +10184,19 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="30" t="n">
         <v>443</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="30" t="n">
         <v>429</v>
       </c>
-      <c r="D33" s="26" t="n">
+      <c r="D33" s="30" t="n">
         <v>405</v>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="E33" s="30" t="n">
         <v>443</v>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="30" t="n">
         <v>429</v>
       </c>
       <c r="G33" s="17">
@@ -10221,15 +10223,15 @@
         <f>IF(G33="","",IF(OR(G33&gt;J33,G33&lt;K33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N33" s="31">
+      <c r="N33" s="33">
         <f>IF(H33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O33" s="31">
+      <c r="O33" s="33">
         <f>IF(H33="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P33" s="31">
+      <c r="P33" s="33">
         <f>IF(H33="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10255,19 +10257,19 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="30" t="n">
         <v>424</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="30" t="n">
         <v>390</v>
       </c>
-      <c r="D34" s="26" t="n">
+      <c r="D34" s="30" t="n">
         <v>423</v>
       </c>
-      <c r="E34" s="26" t="n">
+      <c r="E34" s="30" t="n">
         <v>424</v>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="30" t="n">
         <v>390</v>
       </c>
       <c r="G34" s="17">
@@ -10294,15 +10296,15 @@
         <f>IF(G34="","",IF(OR(G34&gt;J34,G34&lt;K34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N34" s="31">
+      <c r="N34" s="33">
         <f>IF(H34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O34" s="31">
+      <c r="O34" s="33">
         <f>IF(H34="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P34" s="31">
+      <c r="P34" s="33">
         <f>IF(H34="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10328,19 +10330,19 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="30" t="n">
         <v>392</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="30" t="n">
         <v>414</v>
       </c>
-      <c r="D35" s="26" t="n">
+      <c r="D35" s="30" t="n">
         <v>430</v>
       </c>
-      <c r="E35" s="26" t="n">
+      <c r="E35" s="30" t="n">
         <v>392</v>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="30" t="n">
         <v>414</v>
       </c>
       <c r="G35" s="17">
@@ -10367,15 +10369,15 @@
         <f>IF(G35="","",IF(OR(G35&gt;J35,G35&lt;K35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N35" s="31">
+      <c r="N35" s="33">
         <f>IF(H35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O35" s="31">
+      <c r="O35" s="33">
         <f>IF(H35="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P35" s="31">
+      <c r="P35" s="33">
         <f>IF(H35="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10401,19 +10403,19 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="30" t="n">
         <v>431</v>
       </c>
-      <c r="D36" s="26" t="n">
+      <c r="D36" s="30" t="n">
         <v>394</v>
       </c>
-      <c r="E36" s="26" t="n">
+      <c r="E36" s="30" t="n">
         <v>403</v>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="30" t="n">
         <v>431</v>
       </c>
       <c r="G36" s="17">
@@ -10440,15 +10442,15 @@
         <f>IF(G36="","",IF(OR(G36&gt;J36,G36&lt;K36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N36" s="31">
+      <c r="N36" s="33">
         <f>IF(H36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O36" s="31">
+      <c r="O36" s="33">
         <f>IF(H36="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P36" s="31">
+      <c r="P36" s="33">
         <f>IF(H36="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10474,19 +10476,19 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="30" t="n">
         <v>428</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="30" t="n">
         <v>399</v>
       </c>
-      <c r="D37" s="26" t="n">
+      <c r="D37" s="30" t="n">
         <v>393</v>
       </c>
-      <c r="E37" s="26" t="n">
+      <c r="E37" s="30" t="n">
         <v>429</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="30" t="n">
         <v>399</v>
       </c>
       <c r="G37" s="17">
@@ -10513,15 +10515,15 @@
         <f>IF(G37="","",IF(OR(G37&gt;J37,G37&lt;K37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N37" s="31">
+      <c r="N37" s="33">
         <f>IF(H37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O37" s="31">
+      <c r="O37" s="33">
         <f>IF(H37="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P37" s="31">
+      <c r="P37" s="33">
         <f>IF(H37="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10628,7 +10630,7 @@
           <t>Lambda (weight on the newest point)</t>
         </is>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="34" t="n">
         <v>0.2</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -10643,7 +10645,7 @@
           <t>L (limit width in sigmas)</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="35" t="n">
         <v>2.7</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -10807,7 +10809,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="22" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="17">
@@ -10845,7 +10847,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="22" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="17">
@@ -10883,7 +10885,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="22" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="17">
@@ -10921,7 +10923,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="22" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="17">
@@ -10959,7 +10961,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="22" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="17">
@@ -10997,7 +10999,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="22" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="17">
@@ -11035,7 +11037,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="22" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="17">
@@ -11073,7 +11075,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="22" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="17">
@@ -11111,7 +11113,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="22" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="17">
@@ -11149,7 +11151,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="22" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="17">
@@ -11187,7 +11189,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="22" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="17">
@@ -11225,7 +11227,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="22" t="n">
         <v>418</v>
       </c>
       <c r="C28" s="17">
@@ -11263,7 +11265,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n">
+      <c r="B29" s="22" t="n">
         <v>426</v>
       </c>
       <c r="C29" s="17">
@@ -11301,7 +11303,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n">
+      <c r="B30" s="22" t="n">
         <v>431</v>
       </c>
       <c r="C30" s="17">
@@ -11339,7 +11341,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="22" t="n">
         <v>428</v>
       </c>
       <c r="C31" s="17">
@@ -11377,7 +11379,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B32" s="22" t="n">
         <v>437</v>
       </c>
       <c r="C32" s="17">
@@ -11415,7 +11417,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B33" s="22" t="n">
         <v>433</v>
       </c>
       <c r="C33" s="17">
@@ -11453,7 +11455,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="19" t="n">
+      <c r="B34" s="22" t="n">
         <v>441</v>
       </c>
       <c r="C34" s="17">
@@ -11491,7 +11493,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="B35" s="22" t="n">
         <v>439</v>
       </c>
       <c r="C35" s="17">
@@ -11529,7 +11531,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n">
+      <c r="B36" s="22" t="n">
         <v>448</v>
       </c>
       <c r="C36" s="17">
@@ -11567,7 +11569,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n">
+      <c r="B37" s="22" t="n">
         <v>444</v>
       </c>
       <c r="C37" s="17">
@@ -11605,7 +11607,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="19" t="n">
+      <c r="B38" s="22" t="n">
         <v>452</v>
       </c>
       <c r="C38" s="17">
@@ -11643,7 +11645,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n">
+      <c r="B39" s="22" t="n">
         <v>449</v>
       </c>
       <c r="C39" s="17">
@@ -11759,7 +11761,7 @@
           <t>k (slack, in sigmas)</t>
         </is>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="34" t="n">
         <v>0.5</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -11774,7 +11776,7 @@
           <t>h (decision interval)</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="35" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -11946,7 +11948,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="22" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="17">
@@ -11988,7 +11990,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="22" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="17">
@@ -12030,7 +12032,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="22" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="17">
@@ -12072,7 +12074,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="22" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="17">
@@ -12114,7 +12116,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="22" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="17">
@@ -12156,7 +12158,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="22" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="17">
@@ -12198,7 +12200,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="22" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="17">
@@ -12240,7 +12242,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="22" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="17">
@@ -12282,7 +12284,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="22" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="17">
@@ -12324,7 +12326,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B26" s="22" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="17">
@@ -12366,7 +12368,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n">
+      <c r="B27" s="22" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="17">
@@ -12408,7 +12410,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="19" t="n">
+      <c r="B28" s="22" t="n">
         <v>452</v>
       </c>
       <c r="C28" s="17">
@@ -12450,7 +12452,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n">
+      <c r="B29" s="22" t="n">
         <v>461</v>
       </c>
       <c r="C29" s="17">
@@ -12492,7 +12494,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n">
+      <c r="B30" s="22" t="n">
         <v>448</v>
       </c>
       <c r="C30" s="17">
@@ -12534,7 +12536,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="22" t="n">
         <v>470</v>
       </c>
       <c r="C31" s="17">
@@ -12576,7 +12578,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B32" s="22" t="n">
         <v>457</v>
       </c>
       <c r="C32" s="17">
@@ -12618,7 +12620,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B33" s="22" t="n">
         <v>466</v>
       </c>
       <c r="C33" s="17">
@@ -12660,7 +12662,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="19" t="n">
+      <c r="B34" s="22" t="n">
         <v>449</v>
       </c>
       <c r="C34" s="17">
@@ -12702,7 +12704,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="B35" s="22" t="n">
         <v>463</v>
       </c>
       <c r="C35" s="17">
@@ -12744,7 +12746,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n">
+      <c r="B36" s="22" t="n">
         <v>471</v>
       </c>
       <c r="C36" s="17">
@@ -12786,7 +12788,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="19" t="n">
+      <c r="B37" s="22" t="n">
         <v>455</v>
       </c>
       <c r="C37" s="17">
@@ -12828,7 +12830,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="19" t="n">
+      <c r="B38" s="22" t="n">
         <v>468</v>
       </c>
       <c r="C38" s="17">
@@ -12870,7 +12872,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n">
+      <c r="B39" s="22" t="n">
         <v>460</v>
       </c>
       <c r="C39" s="17">
@@ -13022,7 +13024,7 @@
           <t>Transformed mean</t>
         </is>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="31">
         <f>AVERAGE(C14:C37)</f>
         <v/>
       </c>
@@ -13038,7 +13040,7 @@
           <t>Transformed MR-bar</t>
         </is>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="31">
         <f>AVERAGE(D15:D37)</f>
         <v/>
       </c>
@@ -13054,7 +13056,7 @@
           <t>t-chart UCL / LCL (days)</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <f>TEXT((B7+2.66*B8)^3.6,"#,##0.0")&amp;"  /  "&amp;TEXT(MAX(0,(B7-2.66*B8))^3.6,"#,##0.0")</f>
         <v/>
       </c>
@@ -13188,21 +13190,21 @@
           <t>Incident 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>IF(B14="","",B14^(1/3.6))</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="27" t="n">
         <v>12800</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="36">
         <f>IF(F14="","",$B$10)</f>
         <v/>
       </c>
@@ -13210,23 +13212,23 @@
         <f>IF(B14="","",IF(C14&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C14&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="37">
         <f>IF(B14="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K14" s="35">
+      <c r="K14" s="37">
         <f>IF(B14="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L14" s="35">
+      <c r="L14" s="37">
         <f>IF(B14="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M14" s="36">
+      <c r="M14" s="38">
         <f>IF(F14="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="38">
         <f>IF(F14="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13253,25 +13255,25 @@
           <t>Incident 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="28">
         <f>IF(B15="","",B15^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>IF(COUNT(C14:C15)=2,ABS(C15-C14),"")</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="30" t="n">
         <v>8400</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="36">
         <f>IF(F15="","",$B$10)</f>
         <v/>
       </c>
@@ -13279,23 +13281,23 @@
         <f>IF(B15="","",IF(C15&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C15&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="37">
         <f>IF(B15="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K15" s="35">
+      <c r="K15" s="37">
         <f>IF(B15="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L15" s="35">
+      <c r="L15" s="37">
         <f>IF(B15="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M15" s="36">
+      <c r="M15" s="38">
         <f>IF(F15="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N15" s="36">
+      <c r="N15" s="38">
         <f>IF(F15="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13322,25 +13324,25 @@
           <t>Incident 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>IF(B16="","",B16^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>IF(COUNT(C15:C16)=2,ABS(C16-C15),"")</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="30" t="n">
         <v>21600</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="36">
         <f>IF(F16="","",$B$10)</f>
         <v/>
       </c>
@@ -13348,23 +13350,23 @@
         <f>IF(B16="","",IF(C16&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C16&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="37">
         <f>IF(B16="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K16" s="35">
+      <c r="K16" s="37">
         <f>IF(B16="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L16" s="35">
+      <c r="L16" s="37">
         <f>IF(B16="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="38">
         <f>IF(F16="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N16" s="36">
+      <c r="N16" s="38">
         <f>IF(F16="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13391,25 +13393,25 @@
           <t>Incident 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>IF(B17="","",B17^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>IF(COUNT(C16:C17)=2,ABS(C17-C16),"")</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="30" t="n">
         <v>29800</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="36">
         <f>IF(F17="","",$B$10)</f>
         <v/>
       </c>
@@ -13417,23 +13419,23 @@
         <f>IF(B17="","",IF(C17&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C17&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="37">
         <f>IF(B17="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K17" s="35">
+      <c r="K17" s="37">
         <f>IF(B17="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L17" s="35">
+      <c r="L17" s="37">
         <f>IF(B17="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M17" s="36">
+      <c r="M17" s="38">
         <f>IF(F17="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N17" s="36">
+      <c r="N17" s="38">
         <f>IF(F17="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13460,25 +13462,25 @@
           <t>Incident 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>IF(B18="","",B18^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>IF(COUNT(C17:C18)=2,ABS(C18-C17),"")</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="30" t="n">
         <v>17400</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="36">
         <f>IF(F18="","",$B$10)</f>
         <v/>
       </c>
@@ -13486,23 +13488,23 @@
         <f>IF(B18="","",IF(C18&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C18&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="37">
         <f>IF(B18="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="37">
         <f>IF(B18="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L18" s="35">
+      <c r="L18" s="37">
         <f>IF(B18="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M18" s="36">
+      <c r="M18" s="38">
         <f>IF(F18="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N18" s="36">
+      <c r="N18" s="38">
         <f>IF(F18="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13529,25 +13531,25 @@
           <t>Incident 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="30" t="n">
         <v>27</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>IF(B19="","",B19^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>IF(COUNT(C18:C19)=2,ABS(C19-C18),"")</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="30" t="n">
         <v>26100</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="36">
         <f>IF(F19="","",$B$10)</f>
         <v/>
       </c>
@@ -13555,23 +13557,23 @@
         <f>IF(B19="","",IF(C19&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C19&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="37">
         <f>IF(B19="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K19" s="35">
+      <c r="K19" s="37">
         <f>IF(B19="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L19" s="35">
+      <c r="L19" s="37">
         <f>IF(B19="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M19" s="36">
+      <c r="M19" s="38">
         <f>IF(F19="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N19" s="36">
+      <c r="N19" s="38">
         <f>IF(F19="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13598,25 +13600,25 @@
           <t>Incident 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="30" t="n">
         <v>41</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="28">
         <f>IF(B20="","",B20^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>IF(COUNT(C19:C20)=2,ABS(C20-C19),"")</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="30" t="n">
         <v>39900</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="36">
         <f>IF(F20="","",$B$10)</f>
         <v/>
       </c>
@@ -13624,23 +13626,23 @@
         <f>IF(B20="","",IF(C20&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C20&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="37">
         <f>IF(B20="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K20" s="35">
+      <c r="K20" s="37">
         <f>IF(B20="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L20" s="35">
+      <c r="L20" s="37">
         <f>IF(B20="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="38">
         <f>IF(F20="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="38">
         <f>IF(F20="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13667,25 +13669,25 @@
           <t>Incident 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <f>IF(B21="","",B21^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>IF(COUNT(C20:C21)=2,ABS(C21-C20),"")</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="30" t="n">
         <v>11200</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="36">
         <f>IF(F21="","",$B$10)</f>
         <v/>
       </c>
@@ -13693,23 +13695,23 @@
         <f>IF(B21="","",IF(C21&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C21&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="37">
         <f>IF(B21="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="37">
         <f>IF(B21="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L21" s="35">
+      <c r="L21" s="37">
         <f>IF(B21="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M21" s="36">
+      <c r="M21" s="38">
         <f>IF(F21="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N21" s="36">
+      <c r="N21" s="38">
         <f>IF(F21="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13736,25 +13738,25 @@
           <t>Incident 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="28">
         <f>IF(B22="","",B22^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>IF(COUNT(C21:C22)=2,ABS(C22-C21),"")</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="30" t="n">
         <v>33500</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="36">
         <f>IF(F22="","",$B$10)</f>
         <v/>
       </c>
@@ -13762,23 +13764,23 @@
         <f>IF(B22="","",IF(C22&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C22&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="37">
         <f>IF(B22="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K22" s="35">
+      <c r="K22" s="37">
         <f>IF(B22="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L22" s="35">
+      <c r="L22" s="37">
         <f>IF(B22="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="38">
         <f>IF(F22="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N22" s="36">
+      <c r="N22" s="38">
         <f>IF(F22="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13805,25 +13807,25 @@
           <t>Incident 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="28">
         <f>IF(B23="","",B23^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>IF(COUNT(C22:C23)=2,ABS(C23-C22),"")</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="30" t="n">
         <v>23100</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="36">
         <f>IF(F23="","",$B$10)</f>
         <v/>
       </c>
@@ -13831,23 +13833,23 @@
         <f>IF(B23="","",IF(C23&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C23&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="37">
         <f>IF(B23="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K23" s="35">
+      <c r="K23" s="37">
         <f>IF(B23="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L23" s="35">
+      <c r="L23" s="37">
         <f>IF(B23="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M23" s="36">
+      <c r="M23" s="38">
         <f>IF(F23="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N23" s="36">
+      <c r="N23" s="38">
         <f>IF(F23="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13874,25 +13876,25 @@
           <t>Incident 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="28">
         <f>IF(B24="","",B24^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <f>IF(COUNT(C23:C24)=2,ABS(C24-C23),"")</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="30" t="n">
         <v>46800</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="36">
         <f>IF(F24="","",$B$10)</f>
         <v/>
       </c>
@@ -13900,23 +13902,23 @@
         <f>IF(B24="","",IF(C24&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C24&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="37">
         <f>IF(B24="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K24" s="35">
+      <c r="K24" s="37">
         <f>IF(B24="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L24" s="35">
+      <c r="L24" s="37">
         <f>IF(B24="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M24" s="36">
+      <c r="M24" s="38">
         <f>IF(F24="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N24" s="36">
+      <c r="N24" s="38">
         <f>IF(F24="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13943,25 +13945,25 @@
           <t>Incident 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="28">
         <f>IF(B25="","",B25^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="28">
         <f>IF(COUNT(C24:C25)=2,ABS(C25-C24),"")</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="30" t="n">
         <v>18300</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="36">
         <f>IF(F25="","",$B$10)</f>
         <v/>
       </c>
@@ -13969,23 +13971,23 @@
         <f>IF(B25="","",IF(C25&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C25&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="37">
         <f>IF(B25="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K25" s="35">
+      <c r="K25" s="37">
         <f>IF(B25="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L25" s="35">
+      <c r="L25" s="37">
         <f>IF(B25="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M25" s="36">
+      <c r="M25" s="38">
         <f>IF(F25="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N25" s="36">
+      <c r="N25" s="38">
         <f>IF(F25="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14012,25 +14014,25 @@
           <t>Incident 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="30" t="n">
         <v>33</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>IF(B26="","",B26^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>IF(COUNT(C25:C26)=2,ABS(C26-C25),"")</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="30" t="n">
         <v>31700</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="36">
         <f>IF(F26="","",$B$10)</f>
         <v/>
       </c>
@@ -14038,23 +14040,23 @@
         <f>IF(B26="","",IF(C26&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C26&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="37">
         <f>IF(B26="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K26" s="35">
+      <c r="K26" s="37">
         <f>IF(B26="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L26" s="35">
+      <c r="L26" s="37">
         <f>IF(B26="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M26" s="36">
+      <c r="M26" s="38">
         <f>IF(F26="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N26" s="36">
+      <c r="N26" s="38">
         <f>IF(F26="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14081,25 +14083,25 @@
           <t>Incident 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>IF(B27="","",B27^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IF(COUNT(C26:C27)=2,ABS(C27-C26),"")</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="30" t="n">
         <v>25400</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="36">
         <f>IF(F27="","",$B$10)</f>
         <v/>
       </c>
@@ -14107,23 +14109,23 @@
         <f>IF(B27="","",IF(C27&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C27&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="37">
         <f>IF(B27="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="37">
         <f>IF(B27="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="37">
         <f>IF(B27="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M27" s="36">
+      <c r="M27" s="38">
         <f>IF(F27="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N27" s="36">
+      <c r="N27" s="38">
         <f>IF(F27="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14150,25 +14152,25 @@
           <t>Incident 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="30" t="n">
         <v>52</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="28">
         <f>IF(B28="","",B28^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>IF(COUNT(C27:C28)=2,ABS(C28-C27),"")</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="30" t="n">
         <v>50600</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="36">
         <f>IF(F28="","",$B$10)</f>
         <v/>
       </c>
@@ -14176,23 +14178,23 @@
         <f>IF(B28="","",IF(C28&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C28&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="37">
         <f>IF(B28="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K28" s="35">
+      <c r="K28" s="37">
         <f>IF(B28="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L28" s="35">
+      <c r="L28" s="37">
         <f>IF(B28="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M28" s="36">
+      <c r="M28" s="38">
         <f>IF(F28="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N28" s="36">
+      <c r="N28" s="38">
         <f>IF(F28="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14219,25 +14221,25 @@
           <t>Incident 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="28">
         <f>IF(B29="","",B29^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>IF(COUNT(C28:C29)=2,ABS(C29-C28),"")</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="30" t="n">
         <v>20200</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="36">
         <f>IF(F29="","",$B$10)</f>
         <v/>
       </c>
@@ -14245,23 +14247,23 @@
         <f>IF(B29="","",IF(C29&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C29&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="37">
         <f>IF(B29="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="37">
         <f>IF(B29="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="37">
         <f>IF(B29="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M29" s="36">
+      <c r="M29" s="38">
         <f>IF(F29="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N29" s="36">
+      <c r="N29" s="38">
         <f>IF(F29="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14288,25 +14290,25 @@
           <t>Incident 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="28">
         <f>IF(B30="","",B30^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(COUNT(C29:C30)=2,ABS(C30-C29),"")</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="30" t="n">
         <v>36900</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="36">
         <f>IF(F30="","",$B$10)</f>
         <v/>
       </c>
@@ -14314,23 +14316,23 @@
         <f>IF(B30="","",IF(C30&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C30&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="37">
         <f>IF(B30="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="37">
         <f>IF(B30="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="37">
         <f>IF(B30="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="38">
         <f>IF(F30="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="38">
         <f>IF(F30="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14357,25 +14359,25 @@
           <t>Incident 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>IF(B31="","",B31^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IF(COUNT(C30:C31)=2,ABS(C31-C30),"")</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="30" t="n">
         <v>27800</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="36">
         <f>IF(F31="","",$B$10)</f>
         <v/>
       </c>
@@ -14383,23 +14385,23 @@
         <f>IF(B31="","",IF(C31&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C31&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="37">
         <f>IF(B31="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="37">
         <f>IF(B31="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="37">
         <f>IF(B31="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="38">
         <f>IF(F31="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="38">
         <f>IF(F31="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14426,25 +14428,25 @@
           <t>Incident 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="30" t="n">
         <v>44</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="28">
         <f>IF(B32="","",B32^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IF(COUNT(C31:C32)=2,ABS(C32-C31),"")</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="30" t="n">
         <v>43100</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="36">
         <f>IF(F32="","",$B$10)</f>
         <v/>
       </c>
@@ -14452,23 +14454,23 @@
         <f>IF(B32="","",IF(C32&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C32&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="37">
         <f>IF(B32="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K32" s="35">
+      <c r="K32" s="37">
         <f>IF(B32="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L32" s="35">
+      <c r="L32" s="37">
         <f>IF(B32="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M32" s="36">
+      <c r="M32" s="38">
         <f>IF(F32="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N32" s="36">
+      <c r="N32" s="38">
         <f>IF(F32="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14495,25 +14497,25 @@
           <t>Incident 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="28">
         <f>IF(B33="","",B33^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IF(COUNT(C32:C33)=2,ABS(C33-C32),"")</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="30" t="n">
         <v>34600</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="36">
         <f>IF(F33="","",$B$10)</f>
         <v/>
       </c>
@@ -14521,23 +14523,23 @@
         <f>IF(B33="","",IF(C33&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C33&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="37">
         <f>IF(B33="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="37">
         <f>IF(B33="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="37">
         <f>IF(B33="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="38">
         <f>IF(F33="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="38">
         <f>IF(F33="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14564,25 +14566,25 @@
           <t>Incident 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="28">
         <f>IF(B34="","",B34^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IF(COUNT(C33:C34)=2,ABS(C34-C33),"")</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="30" t="n">
         <v>56900</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="36">
         <f>IF(F34="","",$B$10)</f>
         <v/>
       </c>
@@ -14590,23 +14592,23 @@
         <f>IF(B34="","",IF(C34&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C34&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="37">
         <f>IF(B34="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="37">
         <f>IF(B34="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="37">
         <f>IF(B34="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M34" s="36">
+      <c r="M34" s="38">
         <f>IF(F34="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N34" s="36">
+      <c r="N34" s="38">
         <f>IF(F34="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14633,25 +14635,25 @@
           <t>Incident 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="28">
         <f>IF(B35="","",B35^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(COUNT(C34:C35)=2,ABS(C35-C34),"")</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="30" t="n">
         <v>29900</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="36">
         <f>IF(F35="","",$B$10)</f>
         <v/>
       </c>
@@ -14659,23 +14661,23 @@
         <f>IF(B35="","",IF(C35&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C35&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="37">
         <f>IF(B35="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="37">
         <f>IF(B35="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="37">
         <f>IF(B35="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="38">
         <f>IF(F35="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="38">
         <f>IF(F35="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14702,25 +14704,25 @@
           <t>Incident 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="30" t="n">
         <v>47</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="28">
         <f>IF(B36="","",B36^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="28">
         <f>IF(COUNT(C35:C36)=2,ABS(C36-C35),"")</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="30" t="n">
         <v>45200</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="36">
         <f>IF(F36="","",$B$10)</f>
         <v/>
       </c>
@@ -14728,23 +14730,23 @@
         <f>IF(B36="","",IF(C36&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C36&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="37">
         <f>IF(B36="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="37">
         <f>IF(B36="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="37">
         <f>IF(B36="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="38">
         <f>IF(F36="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="38">
         <f>IF(F36="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14771,25 +14773,25 @@
           <t>Incident 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="28">
         <f>IF(B37="","",B37^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="28">
         <f>IF(COUNT(C36:C37)=2,ABS(C37-C36),"")</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="30" t="n">
         <v>38400</v>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="36">
         <f>IF(F37="","",$B$10)</f>
         <v/>
       </c>
@@ -14797,23 +14799,23 @@
         <f>IF(B37="","",IF(C37&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C37&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="37">
         <f>IF(B37="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K37" s="35">
+      <c r="K37" s="37">
         <f>IF(B37="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L37" s="35">
+      <c r="L37" s="37">
         <f>IF(B37="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M37" s="36">
+      <c r="M37" s="38">
         <f>IF(F37="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N37" s="36">
+      <c r="N37" s="38">
         <f>IF(F37="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -134,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -173,7 +173,6 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,7 +180,6 @@
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3413,10 +3411,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="45" customHeight="1">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2. Go to that tab. Overwrite the yellow column with your own numbers, oldest first. The green row is a worked example — replace it too once you have the hang of it.</t>
+          <t>2. Go to that tab. The green cells are a worked example — 24 periods of real-shaped support data, so the chart and its limits say something the moment you open it. Overwrite them with your own numbers, oldest first. The yellow cell above is a setting you choose, not data.</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4067,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C15" s="17">
@@ -4122,7 +4120,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C16" s="17">
@@ -4175,7 +4173,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C17" s="17">
@@ -4228,7 +4226,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C18" s="17">
@@ -4281,7 +4279,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C19" s="17">
@@ -4334,7 +4332,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C20" s="17">
@@ -4387,7 +4385,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C21" s="17">
@@ -4440,7 +4438,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C22" s="17">
@@ -4493,7 +4491,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C23" s="17">
@@ -4546,7 +4544,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C24" s="17">
@@ -4599,7 +4597,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C25" s="17">
@@ -4652,7 +4650,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="19" t="n">
         <v>401</v>
       </c>
       <c r="C26" s="17">
@@ -4705,7 +4703,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="19" t="n">
         <v>422</v>
       </c>
       <c r="C27" s="17">
@@ -4758,7 +4756,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="19" t="n">
         <v>413</v>
       </c>
       <c r="C28" s="17">
@@ -4811,7 +4809,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="19" t="n">
         <v>407</v>
       </c>
       <c r="C29" s="17">
@@ -4864,7 +4862,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="19" t="n">
         <v>435</v>
       </c>
       <c r="C30" s="17">
@@ -4917,7 +4915,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="19" t="n">
         <v>398</v>
       </c>
       <c r="C31" s="17">
@@ -4970,7 +4968,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="19" t="n">
         <v>420</v>
       </c>
       <c r="C32" s="17">
@@ -5023,7 +5021,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="19" t="n">
         <v>411</v>
       </c>
       <c r="C33" s="17">
@@ -5076,7 +5074,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="19" t="n">
         <v>442</v>
       </c>
       <c r="C34" s="17">
@@ -5129,7 +5127,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="19" t="n">
         <v>404</v>
       </c>
       <c r="C35" s="17">
@@ -5182,7 +5180,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="19" t="n">
         <v>416</v>
       </c>
       <c r="C36" s="17">
@@ -5235,7 +5233,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="19" t="n">
         <v>428</v>
       </c>
       <c r="C37" s="17">
@@ -5389,7 +5387,7 @@
           <t>Overall proportion (p-bar)</t>
         </is>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="22">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -5405,7 +5403,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -5421,7 +5419,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -5437,7 +5435,7 @@
           <t>Ordinary p-chart limits would be</t>
         </is>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="24">
         <f>"±"&amp;TEXT(3*SQRT(B5*(1-B5)/AVERAGE(B14:B37)),"0.00%")</f>
         <v/>
       </c>
@@ -5507,17 +5505,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="25" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -5544,17 +5542,17 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>7820</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="26" t="n">
         <v>5610</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="22">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="27">
         <f>IF(B14="","",SQRT($B$5*(1-$B$5)/B14))</f>
         <v/>
       </c>
@@ -5566,15 +5564,15 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="29">
+      <c r="K14" s="28">
         <f>IF(B14="","",MIN(1,$B$5+3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="L14" s="29">
+      <c r="L14" s="28">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="29">
+      <c r="M14" s="28">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
@@ -5596,17 +5594,17 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="26" t="n">
         <v>8140</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="26" t="n">
         <v>5990</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="22">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="27">
         <f>IF(B15="","",SQRT($B$5*(1-$B$5)/B15))</f>
         <v/>
       </c>
@@ -5622,15 +5620,15 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="29">
+      <c r="K15" s="28">
         <f>IF(B15="","",MIN(1,$B$5+3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="L15" s="29">
+      <c r="L15" s="28">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="29">
+      <c r="M15" s="28">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
@@ -5652,17 +5650,17 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="26" t="n">
         <v>7960</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="26" t="n">
         <v>5570</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="22">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <f>IF(B16="","",SQRT($B$5*(1-$B$5)/B16))</f>
         <v/>
       </c>
@@ -5678,15 +5676,15 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="29">
+      <c r="K16" s="28">
         <f>IF(B16="","",MIN(1,$B$5+3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="L16" s="29">
+      <c r="L16" s="28">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="29">
+      <c r="M16" s="28">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
@@ -5708,17 +5706,17 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="26" t="n">
         <v>8310</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="26" t="n">
         <v>6120</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="22">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <f>IF(B17="","",SQRT($B$5*(1-$B$5)/B17))</f>
         <v/>
       </c>
@@ -5734,15 +5732,15 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="29">
+      <c r="K17" s="28">
         <f>IF(B17="","",MIN(1,$B$5+3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="L17" s="29">
+      <c r="L17" s="28">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="29">
+      <c r="M17" s="28">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
@@ -5764,17 +5762,17 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="26" t="n">
         <v>7690</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="26" t="n">
         <v>5410</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="22">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="27">
         <f>IF(B18="","",SQRT($B$5*(1-$B$5)/B18))</f>
         <v/>
       </c>
@@ -5790,15 +5788,15 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="28">
         <f>IF(B18="","",MIN(1,$B$5+3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="L18" s="29">
+      <c r="L18" s="28">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="29">
+      <c r="M18" s="28">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
@@ -5820,17 +5818,17 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="26" t="n">
         <v>8020</v>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="26" t="n">
         <v>5880</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="22">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="27">
         <f>IF(B19="","",SQRT($B$5*(1-$B$5)/B19))</f>
         <v/>
       </c>
@@ -5846,15 +5844,15 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="29">
+      <c r="K19" s="28">
         <f>IF(B19="","",MIN(1,$B$5+3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="L19" s="29">
+      <c r="L19" s="28">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="29">
+      <c r="M19" s="28">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
@@ -5876,17 +5874,17 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="26" t="n">
         <v>8450</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="26" t="n">
         <v>6210</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="22">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="27">
         <f>IF(B20="","",SQRT($B$5*(1-$B$5)/B20))</f>
         <v/>
       </c>
@@ -5902,15 +5900,15 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="29">
+      <c r="K20" s="28">
         <f>IF(B20="","",MIN(1,$B$5+3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="L20" s="29">
+      <c r="L20" s="28">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="29">
+      <c r="M20" s="28">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
@@ -5932,17 +5930,17 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="26" t="n">
         <v>7880</v>
       </c>
-      <c r="C21" s="30" t="n">
+      <c r="C21" s="26" t="n">
         <v>5490</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="22">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="27">
         <f>IF(B21="","",SQRT($B$5*(1-$B$5)/B21))</f>
         <v/>
       </c>
@@ -5958,15 +5956,15 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="28">
         <f>IF(B21="","",MIN(1,$B$5+3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="28">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="28">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
@@ -5988,17 +5986,17 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="26" t="n">
         <v>8210</v>
       </c>
-      <c r="C22" s="30" t="n">
+      <c r="C22" s="26" t="n">
         <v>6050</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="22">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="27">
         <f>IF(B22="","",SQRT($B$5*(1-$B$5)/B22))</f>
         <v/>
       </c>
@@ -6014,15 +6012,15 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="28">
         <f>IF(B22="","",MIN(1,$B$5+3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="L22" s="29">
+      <c r="L22" s="28">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="28">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
@@ -6044,17 +6042,17 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="26" t="n">
         <v>7740</v>
       </c>
-      <c r="C23" s="30" t="n">
+      <c r="C23" s="26" t="n">
         <v>5380</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="27">
         <f>IF(B23="","",SQRT($B$5*(1-$B$5)/B23))</f>
         <v/>
       </c>
@@ -6070,15 +6068,15 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="28">
         <f>IF(B23="","",MIN(1,$B$5+3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="28">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="28">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
@@ -6100,17 +6098,17 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="26" t="n">
         <v>8090</v>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="26" t="n">
         <v>5940</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="27">
         <f>IF(B24="","",SQRT($B$5*(1-$B$5)/B24))</f>
         <v/>
       </c>
@@ -6126,15 +6124,15 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="28">
         <f>IF(B24="","",MIN(1,$B$5+3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="28">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="28">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
@@ -6156,17 +6154,17 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="26" t="n">
         <v>8380</v>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="26" t="n">
         <v>6180</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="22">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="27">
         <f>IF(B25="","",SQRT($B$5*(1-$B$5)/B25))</f>
         <v/>
       </c>
@@ -6182,15 +6180,15 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="28">
         <f>IF(B25="","",MIN(1,$B$5+3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="28">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="28">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
@@ -6212,17 +6210,17 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="26" t="n">
         <v>7930</v>
       </c>
-      <c r="C26" s="30" t="n">
+      <c r="C26" s="26" t="n">
         <v>5520</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="22">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="27">
         <f>IF(B26="","",SQRT($B$5*(1-$B$5)/B26))</f>
         <v/>
       </c>
@@ -6238,15 +6236,15 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="28">
         <f>IF(B26="","",MIN(1,$B$5+3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="L26" s="29">
+      <c r="L26" s="28">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="29">
+      <c r="M26" s="28">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
@@ -6268,17 +6266,17 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="26" t="n">
         <v>8260</v>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="26" t="n">
         <v>6010</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="22">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="27">
         <f>IF(B27="","",SQRT($B$5*(1-$B$5)/B27))</f>
         <v/>
       </c>
@@ -6294,15 +6292,15 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="28">
         <f>IF(B27="","",MIN(1,$B$5+3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="L27" s="29">
+      <c r="L27" s="28">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="29">
+      <c r="M27" s="28">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
@@ -6324,17 +6322,17 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="26" t="n">
         <v>7810</v>
       </c>
-      <c r="C28" s="30" t="n">
+      <c r="C28" s="26" t="n">
         <v>5480</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="22">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="27">
         <f>IF(B28="","",SQRT($B$5*(1-$B$5)/B28))</f>
         <v/>
       </c>
@@ -6350,15 +6348,15 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="28">
         <f>IF(B28="","",MIN(1,$B$5+3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="L28" s="29">
+      <c r="L28" s="28">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="29">
+      <c r="M28" s="28">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
@@ -6380,17 +6378,17 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="26" t="n">
         <v>8150</v>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="26" t="n">
         <v>5860</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="22">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f>IF(B29="","",SQRT($B$5*(1-$B$5)/B29))</f>
         <v/>
       </c>
@@ -6406,15 +6404,15 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="28">
         <f>IF(B29="","",MIN(1,$B$5+3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="L29" s="29">
+      <c r="L29" s="28">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="29">
+      <c r="M29" s="28">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
@@ -6436,17 +6434,17 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>8470</v>
       </c>
-      <c r="C30" s="30" t="n">
+      <c r="C30" s="26" t="n">
         <v>6240</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="22">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="27">
         <f>IF(B30="","",SQRT($B$5*(1-$B$5)/B30))</f>
         <v/>
       </c>
@@ -6462,15 +6460,15 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="29">
+      <c r="K30" s="28">
         <f>IF(B30="","",MIN(1,$B$5+3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="L30" s="29">
+      <c r="L30" s="28">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="29">
+      <c r="M30" s="28">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
@@ -6492,17 +6490,17 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="26" t="n">
         <v>7860</v>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="26" t="n">
         <v>5600</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="22">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="27">
         <f>IF(B31="","",SQRT($B$5*(1-$B$5)/B31))</f>
         <v/>
       </c>
@@ -6518,15 +6516,15 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="29">
+      <c r="K31" s="28">
         <f>IF(B31="","",MIN(1,$B$5+3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="L31" s="29">
+      <c r="L31" s="28">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="29">
+      <c r="M31" s="28">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
@@ -6548,17 +6546,17 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="26" t="n">
         <v>8030</v>
       </c>
-      <c r="C32" s="30" t="n">
+      <c r="C32" s="26" t="n">
         <v>5760</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="22">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="27">
         <f>IF(B32="","",SQRT($B$5*(1-$B$5)/B32))</f>
         <v/>
       </c>
@@ -6574,15 +6572,15 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="29">
+      <c r="K32" s="28">
         <f>IF(B32="","",MIN(1,$B$5+3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="L32" s="29">
+      <c r="L32" s="28">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="29">
+      <c r="M32" s="28">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
@@ -6604,17 +6602,17 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="26" t="n">
         <v>8340</v>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="26" t="n">
         <v>6090</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="22">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="27">
         <f>IF(B33="","",SQRT($B$5*(1-$B$5)/B33))</f>
         <v/>
       </c>
@@ -6630,15 +6628,15 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="28">
         <f>IF(B33="","",MIN(1,$B$5+3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="L33" s="29">
+      <c r="L33" s="28">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="29">
+      <c r="M33" s="28">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
@@ -6660,17 +6658,17 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="26" t="n">
         <v>7900</v>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="26" t="n">
         <v>5710</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="22">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="27">
         <f>IF(B34="","",SQRT($B$5*(1-$B$5)/B34))</f>
         <v/>
       </c>
@@ -6686,15 +6684,15 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="29">
+      <c r="K34" s="28">
         <f>IF(B34="","",MIN(1,$B$5+3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="L34" s="29">
+      <c r="L34" s="28">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="29">
+      <c r="M34" s="28">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
@@ -6716,17 +6714,17 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="26" t="n">
         <v>8180</v>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="26" t="n">
         <v>5900</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="22">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="27">
         <f>IF(B35="","",SQRT($B$5*(1-$B$5)/B35))</f>
         <v/>
       </c>
@@ -6742,15 +6740,15 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="28">
         <f>IF(B35="","",MIN(1,$B$5+3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="28">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="29">
+      <c r="M35" s="28">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
@@ -6772,17 +6770,17 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="26" t="n">
         <v>7770</v>
       </c>
-      <c r="C36" s="30" t="n">
+      <c r="C36" s="26" t="n">
         <v>5450</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="22">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="27">
         <f>IF(B36="","",SQRT($B$5*(1-$B$5)/B36))</f>
         <v/>
       </c>
@@ -6798,15 +6796,15 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="29">
+      <c r="K36" s="28">
         <f>IF(B36="","",MIN(1,$B$5+3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="L36" s="29">
+      <c r="L36" s="28">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="29">
+      <c r="M36" s="28">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
@@ -6828,17 +6826,17 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="26" t="n">
         <v>8240</v>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="26" t="n">
         <v>6020</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="22">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="27">
         <f>IF(B37="","",SQRT($B$5*(1-$B$5)/B37))</f>
         <v/>
       </c>
@@ -6854,15 +6852,15 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="29">
+      <c r="K37" s="28">
         <f>IF(B37="","",MIN(1,$B$5+3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="28">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="29">
+      <c r="M37" s="28">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
@@ -6982,7 +6980,7 @@
           <t>Overall rate (u-bar)</t>
         </is>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="29">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -6998,7 +6996,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -7014,7 +7012,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -7100,17 +7098,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="25" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -7137,17 +7135,17 @@
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>1240</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="26" t="n">
         <v>38</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="27">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="27">
         <f>IF(B14="","",SQRT($B$5/B14))</f>
         <v/>
       </c>
@@ -7159,15 +7157,15 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="30">
         <f>IF(B14="","",$B$5+3*E14*$B$7)</f>
         <v/>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="30">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="30">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
@@ -7189,17 +7187,17 @@
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="26" t="n">
         <v>1310</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="26" t="n">
         <v>68</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="27">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="27">
         <f>IF(B15="","",SQRT($B$5/B15))</f>
         <v/>
       </c>
@@ -7215,15 +7213,15 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="32">
+      <c r="K15" s="30">
         <f>IF(B15="","",$B$5+3*E15*$B$7)</f>
         <v/>
       </c>
-      <c r="L15" s="32">
+      <c r="L15" s="30">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="32">
+      <c r="M15" s="30">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
@@ -7245,17 +7243,17 @@
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="26" t="n">
         <v>1180</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <f>IF(B16="","",SQRT($B$5/B16))</f>
         <v/>
       </c>
@@ -7271,15 +7269,15 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="32">
+      <c r="K16" s="30">
         <f>IF(B16="","",$B$5+3*E16*$B$7)</f>
         <v/>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="30">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="32">
+      <c r="M16" s="30">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
@@ -7301,17 +7299,17 @@
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="26" t="n">
         <v>1420</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="26" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <f>IF(B17="","",SQRT($B$5/B17))</f>
         <v/>
       </c>
@@ -7327,15 +7325,15 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="32">
+      <c r="K17" s="30">
         <f>IF(B17="","",$B$5+3*E17*$B$7)</f>
         <v/>
       </c>
-      <c r="L17" s="32">
+      <c r="L17" s="30">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="32">
+      <c r="M17" s="30">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
@@ -7357,17 +7355,17 @@
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="26" t="n">
         <v>1275</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="27">
         <f>IF(B18="","",SQRT($B$5/B18))</f>
         <v/>
       </c>
@@ -7383,15 +7381,15 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="32">
+      <c r="K18" s="30">
         <f>IF(B18="","",$B$5+3*E18*$B$7)</f>
         <v/>
       </c>
-      <c r="L18" s="32">
+      <c r="L18" s="30">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="32">
+      <c r="M18" s="30">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
@@ -7413,17 +7411,17 @@
           <t>Week 6</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="26" t="n">
         <v>1195</v>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="26" t="n">
         <v>59</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="27">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="27">
         <f>IF(B19="","",SQRT($B$5/B19))</f>
         <v/>
       </c>
@@ -7439,15 +7437,15 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="32">
+      <c r="K19" s="30">
         <f>IF(B19="","",$B$5+3*E19*$B$7)</f>
         <v/>
       </c>
-      <c r="L19" s="32">
+      <c r="L19" s="30">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="32">
+      <c r="M19" s="30">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
@@ -7469,17 +7467,17 @@
           <t>Week 7</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="26" t="n">
         <v>1360</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="26" t="n">
         <v>56</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="27">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="27">
         <f>IF(B20="","",SQRT($B$5/B20))</f>
         <v/>
       </c>
@@ -7495,15 +7493,15 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="32">
+      <c r="K20" s="30">
         <f>IF(B20="","",$B$5+3*E20*$B$7)</f>
         <v/>
       </c>
-      <c r="L20" s="32">
+      <c r="L20" s="30">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="32">
+      <c r="M20" s="30">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
@@ -7525,17 +7523,17 @@
           <t>Week 8</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="26" t="n">
         <v>1230</v>
       </c>
-      <c r="C21" s="30" t="n">
+      <c r="C21" s="26" t="n">
         <v>69</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="27">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="27">
         <f>IF(B21="","",SQRT($B$5/B21))</f>
         <v/>
       </c>
@@ -7551,15 +7549,15 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="30">
         <f>IF(B21="","",$B$5+3*E21*$B$7)</f>
         <v/>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="30">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="30">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
@@ -7581,17 +7579,17 @@
           <t>Week 9</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="26" t="n">
         <v>1405</v>
       </c>
-      <c r="C22" s="30" t="n">
+      <c r="C22" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="27">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="27">
         <f>IF(B22="","",SQRT($B$5/B22))</f>
         <v/>
       </c>
@@ -7607,15 +7605,15 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="30">
         <f>IF(B22="","",$B$5+3*E22*$B$7)</f>
         <v/>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="30">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="30">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
@@ -7637,17 +7635,17 @@
           <t>Week 10</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="26" t="n">
         <v>1150</v>
       </c>
-      <c r="C23" s="30" t="n">
+      <c r="C23" s="26" t="n">
         <v>54</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="27">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="27">
         <f>IF(B23="","",SQRT($B$5/B23))</f>
         <v/>
       </c>
@@ -7663,15 +7661,15 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="32">
+      <c r="K23" s="30">
         <f>IF(B23="","",$B$5+3*E23*$B$7)</f>
         <v/>
       </c>
-      <c r="L23" s="32">
+      <c r="L23" s="30">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="32">
+      <c r="M23" s="30">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
@@ -7693,17 +7691,17 @@
           <t>Week 11</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="26" t="n">
         <v>1290</v>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="26" t="n">
         <v>49</v>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="27">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="27">
         <f>IF(B24="","",SQRT($B$5/B24))</f>
         <v/>
       </c>
@@ -7719,15 +7717,15 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="30">
         <f>IF(B24="","",$B$5+3*E24*$B$7)</f>
         <v/>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="30">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="30">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
@@ -7749,17 +7747,17 @@
           <t>Week 12</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="26" t="n">
         <v>1375</v>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="26" t="n">
         <v>74</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="27">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="27">
         <f>IF(B25="","",SQRT($B$5/B25))</f>
         <v/>
       </c>
@@ -7775,15 +7773,15 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="30">
         <f>IF(B25="","",$B$5+3*E25*$B$7)</f>
         <v/>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="30">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="30">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
@@ -7805,17 +7803,17 @@
           <t>Week 13</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="26" t="n">
         <v>1215</v>
       </c>
-      <c r="C26" s="30" t="n">
+      <c r="C26" s="26" t="n">
         <v>39</v>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="27">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="27">
         <f>IF(B26="","",SQRT($B$5/B26))</f>
         <v/>
       </c>
@@ -7831,15 +7829,15 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="32">
+      <c r="K26" s="30">
         <f>IF(B26="","",$B$5+3*E26*$B$7)</f>
         <v/>
       </c>
-      <c r="L26" s="32">
+      <c r="L26" s="30">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="32">
+      <c r="M26" s="30">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
@@ -7861,17 +7859,17 @@
           <t>Week 14</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="26" t="n">
         <v>1330</v>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="26" t="n">
         <v>66</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="27">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="27">
         <f>IF(B27="","",SQRT($B$5/B27))</f>
         <v/>
       </c>
@@ -7887,15 +7885,15 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="30">
         <f>IF(B27="","",$B$5+3*E27*$B$7)</f>
         <v/>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="30">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="30">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
@@ -7917,17 +7915,17 @@
           <t>Week 15</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="26" t="n">
         <v>1185</v>
       </c>
-      <c r="C28" s="30" t="n">
+      <c r="C28" s="26" t="n">
         <v>41</v>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="27">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="27">
         <f>IF(B28="","",SQRT($B$5/B28))</f>
         <v/>
       </c>
@@ -7943,15 +7941,15 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="30">
         <f>IF(B28="","",$B$5+3*E28*$B$7)</f>
         <v/>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="30">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="30">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
@@ -7973,17 +7971,17 @@
           <t>Week 16</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="26" t="n">
         <v>1265</v>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="27">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f>IF(B29="","",SQRT($B$5/B29))</f>
         <v/>
       </c>
@@ -7999,15 +7997,15 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="32">
+      <c r="K29" s="30">
         <f>IF(B29="","",$B$5+3*E29*$B$7)</f>
         <v/>
       </c>
-      <c r="L29" s="32">
+      <c r="L29" s="30">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="32">
+      <c r="M29" s="30">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
@@ -8029,17 +8027,17 @@
           <t>Week 17</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>1440</v>
       </c>
-      <c r="C30" s="30" t="n">
+      <c r="C30" s="26" t="n">
         <v>58</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="27">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="27">
         <f>IF(B30="","",SQRT($B$5/B30))</f>
         <v/>
       </c>
@@ -8055,15 +8053,15 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="32">
+      <c r="K30" s="30">
         <f>IF(B30="","",$B$5+3*E30*$B$7)</f>
         <v/>
       </c>
-      <c r="L30" s="32">
+      <c r="L30" s="30">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="32">
+      <c r="M30" s="30">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
@@ -8085,17 +8083,17 @@
           <t>Week 18</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="26" t="n">
         <v>1205</v>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="26" t="n">
         <v>54</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="27">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="27">
         <f>IF(B31="","",SQRT($B$5/B31))</f>
         <v/>
       </c>
@@ -8111,15 +8109,15 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="30">
         <f>IF(B31="","",$B$5+3*E31*$B$7)</f>
         <v/>
       </c>
-      <c r="L31" s="32">
+      <c r="L31" s="30">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="32">
+      <c r="M31" s="30">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
@@ -8141,17 +8139,17 @@
           <t>Week 19</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="26" t="n">
         <v>1300</v>
       </c>
-      <c r="C32" s="30" t="n">
+      <c r="C32" s="26" t="n">
         <v>40</v>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="27">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="27">
         <f>IF(B32="","",SQRT($B$5/B32))</f>
         <v/>
       </c>
@@ -8167,15 +8165,15 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="32">
+      <c r="K32" s="30">
         <f>IF(B32="","",$B$5+3*E32*$B$7)</f>
         <v/>
       </c>
-      <c r="L32" s="32">
+      <c r="L32" s="30">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="32">
+      <c r="M32" s="30">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
@@ -8197,17 +8195,17 @@
           <t>Week 20</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="26" t="n">
         <v>1355</v>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="27">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="27">
         <f>IF(B33="","",SQRT($B$5/B33))</f>
         <v/>
       </c>
@@ -8223,15 +8221,15 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="30">
         <f>IF(B33="","",$B$5+3*E33*$B$7)</f>
         <v/>
       </c>
-      <c r="L33" s="32">
+      <c r="L33" s="30">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="32">
+      <c r="M33" s="30">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
@@ -8253,17 +8251,17 @@
           <t>Week 21</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="26" t="n">
         <v>1170</v>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="26" t="n">
         <v>43</v>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="27">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="27">
         <f>IF(B34="","",SQRT($B$5/B34))</f>
         <v/>
       </c>
@@ -8279,15 +8277,15 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="30">
         <f>IF(B34="","",$B$5+3*E34*$B$7)</f>
         <v/>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="30">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="32">
+      <c r="M34" s="30">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
@@ -8309,17 +8307,17 @@
           <t>Week 22</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="26" t="n">
         <v>1285</v>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="26" t="n">
         <v>62</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="27">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="27">
         <f>IF(B35="","",SQRT($B$5/B35))</f>
         <v/>
       </c>
@@ -8335,15 +8333,15 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="30">
         <f>IF(B35="","",$B$5+3*E35*$B$7)</f>
         <v/>
       </c>
-      <c r="L35" s="32">
+      <c r="L35" s="30">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="32">
+      <c r="M35" s="30">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
@@ -8365,17 +8363,17 @@
           <t>Week 23</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="26" t="n">
         <v>1225</v>
       </c>
-      <c r="C36" s="30" t="n">
+      <c r="C36" s="26" t="n">
         <v>42</v>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="27">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="27">
         <f>IF(B36="","",SQRT($B$5/B36))</f>
         <v/>
       </c>
@@ -8391,15 +8389,15 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="32">
+      <c r="K36" s="30">
         <f>IF(B36="","",$B$5+3*E36*$B$7)</f>
         <v/>
       </c>
-      <c r="L36" s="32">
+      <c r="L36" s="30">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="32">
+      <c r="M36" s="30">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
@@ -8421,17 +8419,17 @@
           <t>Week 24</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="26" t="n">
         <v>1390</v>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="26" t="n">
         <v>76</v>
       </c>
-      <c r="D37" s="28">
+      <c r="D37" s="27">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="27">
         <f>IF(B37="","",SQRT($B$5/B37))</f>
         <v/>
       </c>
@@ -8447,15 +8445,15 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="32">
+      <c r="K37" s="30">
         <f>IF(B37="","",$B$5+3*E37*$B$7)</f>
         <v/>
       </c>
-      <c r="L37" s="32">
+      <c r="L37" s="30">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="32">
+      <c r="M37" s="30">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
@@ -8633,7 +8631,7 @@
           <t>A2 for this n</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{1.880;1.023;0.729;0.577;0.483;0.419;0.373;0.337;0.308}),"n out of range")</f>
         <v/>
       </c>
@@ -8649,7 +8647,7 @@
           <t>D4 for this n</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{3.267;2.574;2.282;2.114;2.004;1.924;1.864;1.816;1.777}),"n out of range")</f>
         <v/>
       </c>
@@ -8665,7 +8663,7 @@
           <t>D3 for this n</t>
         </is>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="23">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{0;0;0;0;0;0.076;0.136;0.184;0.223}),"n out of range")</f>
         <v/>
       </c>
@@ -8681,7 +8679,7 @@
           <t>Xbar UCL / LCL</t>
         </is>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="24">
         <f>TEXT(B6+B8*B7,"#,##0.00")&amp;"  /  "&amp;TEXT(B6-B8*B7,"#,##0.00")</f>
         <v/>
       </c>
@@ -8797,19 +8795,19 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>400</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="26" t="n">
         <v>419</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="26" t="n">
         <v>381</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="26" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="26" t="n">
         <v>419</v>
       </c>
       <c r="G14" s="17">
@@ -8836,15 +8834,15 @@
         <f>IF(G14="","",IF(OR(G14&gt;J14,G14&lt;K14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N14" s="33">
+      <c r="N14" s="31">
         <f>IF(H14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="33">
+      <c r="O14" s="31">
         <f>IF(H14="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P14" s="33">
+      <c r="P14" s="31">
         <f>IF(H14="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -8870,19 +8868,19 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="C15" s="30" t="n">
+      <c r="C15" s="26" t="n">
         <v>395</v>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="26" t="n">
         <v>400</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="26" t="n">
         <v>395</v>
       </c>
       <c r="G15" s="17">
@@ -8909,15 +8907,15 @@
         <f>IF(G15="","",IF(OR(G15&gt;J15,G15&lt;K15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N15" s="33">
+      <c r="N15" s="31">
         <f>IF(H15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="33">
+      <c r="O15" s="31">
         <f>IF(H15="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P15" s="33">
+      <c r="P15" s="31">
         <f>IF(H15="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -8943,19 +8941,19 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="26" t="n">
         <v>411</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="26" t="n">
         <v>401</v>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="26" t="n">
         <v>438</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="26" t="n">
         <v>410</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="26" t="n">
         <v>401</v>
       </c>
       <c r="G16" s="17">
@@ -8982,15 +8980,15 @@
         <f>IF(G16="","",IF(OR(G16&gt;J16,G16&lt;K16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N16" s="33">
+      <c r="N16" s="31">
         <f>IF(H16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O16" s="33">
+      <c r="O16" s="31">
         <f>IF(H16="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P16" s="33">
+      <c r="P16" s="31">
         <f>IF(H16="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9016,19 +9014,19 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="26" t="n">
         <v>402</v>
       </c>
-      <c r="C17" s="30" t="n">
+      <c r="C17" s="26" t="n">
         <v>440</v>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="26" t="n">
         <v>425</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="26" t="n">
         <v>402</v>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="26" t="n">
         <v>440</v>
       </c>
       <c r="G17" s="17">
@@ -9055,15 +9053,15 @@
         <f>IF(G17="","",IF(OR(G17&gt;J17,G17&lt;K17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N17" s="33">
+      <c r="N17" s="31">
         <f>IF(H17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O17" s="33">
+      <c r="O17" s="31">
         <f>IF(H17="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P17" s="33">
+      <c r="P17" s="31">
         <f>IF(H17="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9089,19 +9087,19 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="26" t="n">
         <v>437</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="26" t="n">
         <v>437</v>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="26" t="n">
         <v>404</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="26" t="n">
         <v>437</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="26" t="n">
         <v>437</v>
       </c>
       <c r="G18" s="17">
@@ -9128,15 +9126,15 @@
         <f>IF(G18="","",IF(OR(G18&gt;J18,G18&lt;K18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N18" s="33">
+      <c r="N18" s="31">
         <f>IF(H18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O18" s="33">
+      <c r="O18" s="31">
         <f>IF(H18="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P18" s="33">
+      <c r="P18" s="31">
         <f>IF(H18="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9162,19 +9160,19 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="26" t="n">
         <v>392</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="26" t="n">
         <v>415</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="26" t="n">
         <v>392</v>
       </c>
       <c r="G19" s="17">
@@ -9201,15 +9199,15 @@
         <f>IF(G19="","",IF(OR(G19&gt;J19,G19&lt;K19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N19" s="33">
+      <c r="N19" s="31">
         <f>IF(H19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="33">
+      <c r="O19" s="31">
         <f>IF(H19="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P19" s="33">
+      <c r="P19" s="31">
         <f>IF(H19="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9235,19 +9233,19 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="26" t="n">
         <v>406</v>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="26" t="n">
         <v>433</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="26" t="n">
         <v>406</v>
       </c>
       <c r="G20" s="17">
@@ -9274,15 +9272,15 @@
         <f>IF(G20="","",IF(OR(G20&gt;J20,G20&lt;K20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N20" s="33">
+      <c r="N20" s="31">
         <f>IF(H20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="33">
+      <c r="O20" s="31">
         <f>IF(H20="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P20" s="33">
+      <c r="P20" s="31">
         <f>IF(H20="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9308,19 +9306,19 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="C21" s="30" t="n">
+      <c r="C21" s="26" t="n">
         <v>431</v>
       </c>
-      <c r="D21" s="30" t="n">
+      <c r="D21" s="26" t="n">
         <v>401</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="26" t="n">
         <v>431</v>
       </c>
       <c r="G21" s="17">
@@ -9347,15 +9345,15 @@
         <f>IF(G21="","",IF(OR(G21&gt;J21,G21&lt;K21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="31">
         <f>IF(H21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="31">
         <f>IF(H21="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="31">
         <f>IF(H21="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9381,19 +9379,19 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="26" t="n">
         <v>425</v>
       </c>
-      <c r="C22" s="30" t="n">
+      <c r="C22" s="26" t="n">
         <v>407</v>
       </c>
-      <c r="D22" s="30" t="n">
+      <c r="D22" s="26" t="n">
         <v>387</v>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="E22" s="26" t="n">
         <v>425</v>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F22" s="26" t="n">
         <v>406</v>
       </c>
       <c r="G22" s="17">
@@ -9420,15 +9418,15 @@
         <f>IF(G22="","",IF(OR(G22&gt;J22,G22&lt;K22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="31">
         <f>IF(H22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="31">
         <f>IF(H22="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="31">
         <f>IF(H22="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9454,19 +9452,19 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="26" t="n">
         <v>413</v>
       </c>
-      <c r="C23" s="30" t="n">
+      <c r="C23" s="26" t="n">
         <v>382</v>
       </c>
-      <c r="D23" s="30" t="n">
+      <c r="D23" s="26" t="n">
         <v>417</v>
       </c>
-      <c r="E23" s="30" t="n">
+      <c r="E23" s="26" t="n">
         <v>412</v>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="26" t="n">
         <v>382</v>
       </c>
       <c r="G23" s="17">
@@ -9493,15 +9491,15 @@
         <f>IF(G23="","",IF(OR(G23&gt;J23,G23&lt;K23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N23" s="33">
+      <c r="N23" s="31">
         <f>IF(H23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="33">
+      <c r="O23" s="31">
         <f>IF(H23="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P23" s="33">
+      <c r="P23" s="31">
         <f>IF(H23="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9527,19 +9525,19 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="26" t="n">
         <v>367</v>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="26" t="n">
         <v>393</v>
       </c>
-      <c r="D24" s="30" t="n">
+      <c r="D24" s="26" t="n">
         <v>404</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E24" s="26" t="n">
         <v>367</v>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F24" s="26" t="n">
         <v>394</v>
       </c>
       <c r="G24" s="17">
@@ -9566,15 +9564,15 @@
         <f>IF(G24="","",IF(OR(G24&gt;J24,G24&lt;K24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="31">
         <f>IF(H24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="31">
         <f>IF(H24="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="31">
         <f>IF(H24="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9600,19 +9598,19 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="26" t="n">
         <v>386</v>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="26" t="n">
         <v>410</v>
       </c>
-      <c r="D25" s="30" t="n">
+      <c r="D25" s="26" t="n">
         <v>372</v>
       </c>
-      <c r="E25" s="30" t="n">
+      <c r="E25" s="26" t="n">
         <v>386</v>
       </c>
-      <c r="F25" s="30" t="n">
+      <c r="F25" s="26" t="n">
         <v>409</v>
       </c>
       <c r="G25" s="17">
@@ -9639,15 +9637,15 @@
         <f>IF(G25="","",IF(OR(G25&gt;J25,G25&lt;K25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="31">
         <f>IF(H25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="31">
         <f>IF(H25="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="31">
         <f>IF(H25="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9673,19 +9671,19 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="26" t="n">
         <v>415</v>
       </c>
-      <c r="C26" s="30" t="n">
+      <c r="C26" s="26" t="n">
         <v>382</v>
       </c>
-      <c r="D26" s="30" t="n">
+      <c r="D26" s="26" t="n">
         <v>381</v>
       </c>
-      <c r="E26" s="30" t="n">
+      <c r="E26" s="26" t="n">
         <v>415</v>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F26" s="26" t="n">
         <v>382</v>
       </c>
       <c r="G26" s="17">
@@ -9712,15 +9710,15 @@
         <f>IF(G26="","",IF(OR(G26&gt;J26,G26&lt;K26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N26" s="33">
+      <c r="N26" s="31">
         <f>IF(H26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O26" s="33">
+      <c r="O26" s="31">
         <f>IF(H26="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P26" s="33">
+      <c r="P26" s="31">
         <f>IF(H26="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9746,19 +9744,19 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="26" t="n">
         <v>381</v>
       </c>
-      <c r="D27" s="30" t="n">
+      <c r="D27" s="26" t="n">
         <v>419</v>
       </c>
-      <c r="E27" s="30" t="n">
+      <c r="E27" s="26" t="n">
         <v>396</v>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="26" t="n">
         <v>381</v>
       </c>
       <c r="G27" s="17">
@@ -9785,15 +9783,15 @@
         <f>IF(G27="","",IF(OR(G27&gt;J27,G27&lt;K27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="31">
         <f>IF(H27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="31">
         <f>IF(H27="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="31">
         <f>IF(H27="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9819,19 +9817,19 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="26" t="n">
         <v>385</v>
       </c>
-      <c r="C28" s="30" t="n">
+      <c r="C28" s="26" t="n">
         <v>421</v>
       </c>
-      <c r="D28" s="30" t="n">
+      <c r="D28" s="26" t="n">
         <v>412</v>
       </c>
-      <c r="E28" s="30" t="n">
+      <c r="E28" s="26" t="n">
         <v>385</v>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F28" s="26" t="n">
         <v>421</v>
       </c>
       <c r="G28" s="17">
@@ -9858,15 +9856,15 @@
         <f>IF(G28="","",IF(OR(G28&gt;J28,G28&lt;K28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="31">
         <f>IF(H28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="31">
         <f>IF(H28="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="31">
         <f>IF(H28="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9892,19 +9890,19 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="26" t="n">
         <v>407</v>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="26" t="n">
         <v>413</v>
       </c>
-      <c r="D29" s="30" t="n">
+      <c r="D29" s="26" t="n">
         <v>378</v>
       </c>
-      <c r="E29" s="30" t="n">
+      <c r="E29" s="26" t="n">
         <v>408</v>
       </c>
-      <c r="F29" s="30" t="n">
+      <c r="F29" s="26" t="n">
         <v>413</v>
       </c>
       <c r="G29" s="17">
@@ -9931,15 +9929,15 @@
         <f>IF(G29="","",IF(OR(G29&gt;J29,G29&lt;K29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N29" s="33">
+      <c r="N29" s="31">
         <f>IF(H29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="33">
+      <c r="O29" s="31">
         <f>IF(H29="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P29" s="33">
+      <c r="P29" s="31">
         <f>IF(H29="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9965,19 +9963,19 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>428</v>
       </c>
-      <c r="C30" s="30" t="n">
+      <c r="C30" s="26" t="n">
         <v>389</v>
       </c>
-      <c r="D30" s="30" t="n">
+      <c r="D30" s="26" t="n">
         <v>408</v>
       </c>
-      <c r="E30" s="30" t="n">
+      <c r="E30" s="26" t="n">
         <v>427</v>
       </c>
-      <c r="F30" s="30" t="n">
+      <c r="F30" s="26" t="n">
         <v>389</v>
       </c>
       <c r="G30" s="17">
@@ -10004,15 +10002,15 @@
         <f>IF(G30="","",IF(OR(G30&gt;J30,G30&lt;K30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="31">
         <f>IF(H30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="31">
         <f>IF(H30="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="31">
         <f>IF(H30="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10038,19 +10036,19 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="26" t="n">
         <v>407</v>
       </c>
-      <c r="D31" s="30" t="n">
+      <c r="D31" s="26" t="n">
         <v>438</v>
       </c>
-      <c r="E31" s="30" t="n">
+      <c r="E31" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="F31" s="30" t="n">
+      <c r="F31" s="26" t="n">
         <v>407</v>
       </c>
       <c r="G31" s="17">
@@ -10077,15 +10075,15 @@
         <f>IF(G31="","",IF(OR(G31&gt;J31,G31&lt;K31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="31">
         <f>IF(H31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="31">
         <f>IF(H31="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P31" s="33">
+      <c r="P31" s="31">
         <f>IF(H31="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10111,19 +10109,19 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="26" t="n">
         <v>406</v>
       </c>
-      <c r="C32" s="30" t="n">
+      <c r="C32" s="26" t="n">
         <v>443</v>
       </c>
-      <c r="D32" s="30" t="n">
+      <c r="D32" s="26" t="n">
         <v>417</v>
       </c>
-      <c r="E32" s="30" t="n">
+      <c r="E32" s="26" t="n">
         <v>406</v>
       </c>
-      <c r="F32" s="30" t="n">
+      <c r="F32" s="26" t="n">
         <v>443</v>
       </c>
       <c r="G32" s="17">
@@ -10150,15 +10148,15 @@
         <f>IF(G32="","",IF(OR(G32&gt;J32,G32&lt;K32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N32" s="33">
+      <c r="N32" s="31">
         <f>IF(H32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O32" s="33">
+      <c r="O32" s="31">
         <f>IF(H32="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P32" s="33">
+      <c r="P32" s="31">
         <f>IF(H32="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10184,19 +10182,19 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="26" t="n">
         <v>443</v>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="26" t="n">
         <v>429</v>
       </c>
-      <c r="D33" s="30" t="n">
+      <c r="D33" s="26" t="n">
         <v>405</v>
       </c>
-      <c r="E33" s="30" t="n">
+      <c r="E33" s="26" t="n">
         <v>443</v>
       </c>
-      <c r="F33" s="30" t="n">
+      <c r="F33" s="26" t="n">
         <v>429</v>
       </c>
       <c r="G33" s="17">
@@ -10223,15 +10221,15 @@
         <f>IF(G33="","",IF(OR(G33&gt;J33,G33&lt;K33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N33" s="33">
+      <c r="N33" s="31">
         <f>IF(H33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="31">
         <f>IF(H33="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="31">
         <f>IF(H33="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10257,19 +10255,19 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="26" t="n">
         <v>424</v>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="26" t="n">
         <v>390</v>
       </c>
-      <c r="D34" s="30" t="n">
+      <c r="D34" s="26" t="n">
         <v>423</v>
       </c>
-      <c r="E34" s="30" t="n">
+      <c r="E34" s="26" t="n">
         <v>424</v>
       </c>
-      <c r="F34" s="30" t="n">
+      <c r="F34" s="26" t="n">
         <v>390</v>
       </c>
       <c r="G34" s="17">
@@ -10296,15 +10294,15 @@
         <f>IF(G34="","",IF(OR(G34&gt;J34,G34&lt;K34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N34" s="33">
+      <c r="N34" s="31">
         <f>IF(H34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="31">
         <f>IF(H34="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P34" s="33">
+      <c r="P34" s="31">
         <f>IF(H34="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10330,19 +10328,19 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="26" t="n">
         <v>392</v>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="26" t="n">
         <v>414</v>
       </c>
-      <c r="D35" s="30" t="n">
+      <c r="D35" s="26" t="n">
         <v>430</v>
       </c>
-      <c r="E35" s="30" t="n">
+      <c r="E35" s="26" t="n">
         <v>392</v>
       </c>
-      <c r="F35" s="30" t="n">
+      <c r="F35" s="26" t="n">
         <v>414</v>
       </c>
       <c r="G35" s="17">
@@ -10369,15 +10367,15 @@
         <f>IF(G35="","",IF(OR(G35&gt;J35,G35&lt;K35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N35" s="33">
+      <c r="N35" s="31">
         <f>IF(H35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="31">
         <f>IF(H35="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="31">
         <f>IF(H35="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10403,19 +10401,19 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="C36" s="30" t="n">
+      <c r="C36" s="26" t="n">
         <v>431</v>
       </c>
-      <c r="D36" s="30" t="n">
+      <c r="D36" s="26" t="n">
         <v>394</v>
       </c>
-      <c r="E36" s="30" t="n">
+      <c r="E36" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="F36" s="30" t="n">
+      <c r="F36" s="26" t="n">
         <v>431</v>
       </c>
       <c r="G36" s="17">
@@ -10442,15 +10440,15 @@
         <f>IF(G36="","",IF(OR(G36&gt;J36,G36&lt;K36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N36" s="33">
+      <c r="N36" s="31">
         <f>IF(H36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O36" s="33">
+      <c r="O36" s="31">
         <f>IF(H36="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P36" s="33">
+      <c r="P36" s="31">
         <f>IF(H36="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10476,19 +10474,19 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="26" t="n">
         <v>428</v>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="26" t="n">
         <v>399</v>
       </c>
-      <c r="D37" s="30" t="n">
+      <c r="D37" s="26" t="n">
         <v>393</v>
       </c>
-      <c r="E37" s="30" t="n">
+      <c r="E37" s="26" t="n">
         <v>429</v>
       </c>
-      <c r="F37" s="30" t="n">
+      <c r="F37" s="26" t="n">
         <v>399</v>
       </c>
       <c r="G37" s="17">
@@ -10515,15 +10513,15 @@
         <f>IF(G37="","",IF(OR(G37&gt;J37,G37&lt;K37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N37" s="33">
+      <c r="N37" s="31">
         <f>IF(H37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O37" s="33">
+      <c r="O37" s="31">
         <f>IF(H37="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P37" s="33">
+      <c r="P37" s="31">
         <f>IF(H37="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10630,7 +10628,7 @@
           <t>Lambda (weight on the newest point)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="32" t="n">
         <v>0.2</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -10645,7 +10643,7 @@
           <t>L (limit width in sigmas)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="33" t="n">
         <v>2.7</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -10809,7 +10807,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="17">
@@ -10847,7 +10845,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="17">
@@ -10885,7 +10883,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="17">
@@ -10923,7 +10921,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="17">
@@ -10961,7 +10959,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="17">
@@ -10999,7 +10997,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="17">
@@ -11037,7 +11035,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="17">
@@ -11075,7 +11073,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="17">
@@ -11113,7 +11111,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="17">
@@ -11151,7 +11149,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="17">
@@ -11189,7 +11187,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="17">
@@ -11227,7 +11225,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="19" t="n">
         <v>418</v>
       </c>
       <c r="C28" s="17">
@@ -11265,7 +11263,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="19" t="n">
         <v>426</v>
       </c>
       <c r="C29" s="17">
@@ -11303,7 +11301,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C30" s="17">
@@ -11341,7 +11339,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="19" t="n">
         <v>428</v>
       </c>
       <c r="C31" s="17">
@@ -11379,7 +11377,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="19" t="n">
         <v>437</v>
       </c>
       <c r="C32" s="17">
@@ -11417,7 +11415,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="19" t="n">
         <v>433</v>
       </c>
       <c r="C33" s="17">
@@ -11455,7 +11453,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="19" t="n">
         <v>441</v>
       </c>
       <c r="C34" s="17">
@@ -11493,7 +11491,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="19" t="n">
         <v>439</v>
       </c>
       <c r="C35" s="17">
@@ -11531,7 +11529,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="19" t="n">
         <v>448</v>
       </c>
       <c r="C36" s="17">
@@ -11569,7 +11567,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="19" t="n">
         <v>444</v>
       </c>
       <c r="C37" s="17">
@@ -11607,7 +11605,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="19" t="n">
         <v>452</v>
       </c>
       <c r="C38" s="17">
@@ -11645,7 +11643,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n">
+      <c r="B39" s="19" t="n">
         <v>449</v>
       </c>
       <c r="C39" s="17">
@@ -11761,7 +11759,7 @@
           <t>k (slack, in sigmas)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="32" t="n">
         <v>0.5</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -11776,7 +11774,7 @@
           <t>h (decision interval)</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="33" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -11948,7 +11946,7 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="19" t="n">
         <v>415</v>
       </c>
       <c r="C17" s="17">
@@ -11990,7 +11988,7 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="19" t="n">
         <v>402</v>
       </c>
       <c r="C18" s="17">
@@ -12032,7 +12030,7 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="19" t="n">
         <v>431</v>
       </c>
       <c r="C19" s="17">
@@ -12074,7 +12072,7 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="19" t="n">
         <v>419</v>
       </c>
       <c r="C20" s="17">
@@ -12116,7 +12114,7 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="19" t="n">
         <v>396</v>
       </c>
       <c r="C21" s="17">
@@ -12158,7 +12156,7 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="19" t="n">
         <v>424</v>
       </c>
       <c r="C22" s="17">
@@ -12200,7 +12198,7 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="19" t="n">
         <v>410</v>
       </c>
       <c r="C23" s="17">
@@ -12242,7 +12240,7 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="19" t="n">
         <v>438</v>
       </c>
       <c r="C24" s="17">
@@ -12284,7 +12282,7 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="19" t="n">
         <v>405</v>
       </c>
       <c r="C25" s="17">
@@ -12326,7 +12324,7 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="19" t="n">
         <v>417</v>
       </c>
       <c r="C26" s="17">
@@ -12368,7 +12366,7 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="19" t="n">
         <v>429</v>
       </c>
       <c r="C27" s="17">
@@ -12410,7 +12408,7 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="19" t="n">
         <v>452</v>
       </c>
       <c r="C28" s="17">
@@ -12452,7 +12450,7 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="19" t="n">
         <v>461</v>
       </c>
       <c r="C29" s="17">
@@ -12494,7 +12492,7 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="19" t="n">
         <v>448</v>
       </c>
       <c r="C30" s="17">
@@ -12536,7 +12534,7 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="19" t="n">
         <v>470</v>
       </c>
       <c r="C31" s="17">
@@ -12578,7 +12576,7 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="19" t="n">
         <v>457</v>
       </c>
       <c r="C32" s="17">
@@ -12620,7 +12618,7 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="19" t="n">
         <v>466</v>
       </c>
       <c r="C33" s="17">
@@ -12662,7 +12660,7 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="19" t="n">
         <v>449</v>
       </c>
       <c r="C34" s="17">
@@ -12704,7 +12702,7 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="19" t="n">
         <v>463</v>
       </c>
       <c r="C35" s="17">
@@ -12746,7 +12744,7 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="19" t="n">
         <v>471</v>
       </c>
       <c r="C36" s="17">
@@ -12788,7 +12786,7 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="19" t="n">
         <v>455</v>
       </c>
       <c r="C37" s="17">
@@ -12830,7 +12828,7 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n">
+      <c r="B38" s="19" t="n">
         <v>468</v>
       </c>
       <c r="C38" s="17">
@@ -12872,7 +12870,7 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B39" s="22" t="n">
+      <c r="B39" s="19" t="n">
         <v>460</v>
       </c>
       <c r="C39" s="17">
@@ -13024,7 +13022,7 @@
           <t>Transformed mean</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="29">
         <f>AVERAGE(C14:C37)</f>
         <v/>
       </c>
@@ -13040,7 +13038,7 @@
           <t>Transformed MR-bar</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="29">
         <f>AVERAGE(D15:D37)</f>
         <v/>
       </c>
@@ -13056,7 +13054,7 @@
           <t>t-chart UCL / LCL (days)</t>
         </is>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="24">
         <f>TEXT((B7+2.66*B8)^3.6,"#,##0.0")&amp;"  /  "&amp;TEXT(MAX(0,(B7-2.66*B8))^3.6,"#,##0.0")</f>
         <v/>
       </c>
@@ -13190,21 +13188,21 @@
           <t>Incident 1</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="27">
         <f>IF(B14="","",B14^(1/3.6))</f>
         <v/>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="27">
         <f>IF(B14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="26" t="n">
         <v>12800</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="34">
         <f>IF(F14="","",$B$10)</f>
         <v/>
       </c>
@@ -13212,23 +13210,23 @@
         <f>IF(B14="","",IF(C14&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C14&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="35">
         <f>IF(B14="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="35">
         <f>IF(B14="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="35">
         <f>IF(B14="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M14" s="38">
+      <c r="M14" s="36">
         <f>IF(F14="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N14" s="38">
+      <c r="N14" s="36">
         <f>IF(F14="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13255,25 +13253,25 @@
           <t>Incident 2</t>
         </is>
       </c>
-      <c r="B15" s="30" t="n">
+      <c r="B15" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="27">
         <f>IF(B15="","",B15^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="27">
         <f>IF(COUNT(C14:C15)=2,ABS(C15-C14),"")</f>
         <v/>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="27">
         <f>IF(B15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="26" t="n">
         <v>8400</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="34">
         <f>IF(F15="","",$B$10)</f>
         <v/>
       </c>
@@ -13281,23 +13279,23 @@
         <f>IF(B15="","",IF(C15&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C15&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="35">
         <f>IF(B15="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K15" s="37">
+      <c r="K15" s="35">
         <f>IF(B15="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="35">
         <f>IF(B15="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M15" s="38">
+      <c r="M15" s="36">
         <f>IF(F15="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N15" s="38">
+      <c r="N15" s="36">
         <f>IF(F15="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13324,25 +13322,25 @@
           <t>Incident 3</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="26" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <f>IF(B16="","",B16^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <f>IF(COUNT(C15:C16)=2,ABS(C16-C15),"")</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <f>IF(B16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="26" t="n">
         <v>21600</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="34">
         <f>IF(F16="","",$B$10)</f>
         <v/>
       </c>
@@ -13350,23 +13348,23 @@
         <f>IF(B16="","",IF(C16&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C16&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="35">
         <f>IF(B16="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K16" s="37">
+      <c r="K16" s="35">
         <f>IF(B16="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L16" s="37">
+      <c r="L16" s="35">
         <f>IF(B16="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M16" s="38">
+      <c r="M16" s="36">
         <f>IF(F16="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N16" s="38">
+      <c r="N16" s="36">
         <f>IF(F16="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13393,25 +13391,25 @@
           <t>Incident 4</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n">
+      <c r="B17" s="26" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>IF(B17="","",B17^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>IF(COUNT(C16:C17)=2,ABS(C17-C16),"")</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <f>IF(B17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="26" t="n">
         <v>29800</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="34">
         <f>IF(F17="","",$B$10)</f>
         <v/>
       </c>
@@ -13419,23 +13417,23 @@
         <f>IF(B17="","",IF(C17&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C17&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J17" s="37">
+      <c r="J17" s="35">
         <f>IF(B17="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K17" s="37">
+      <c r="K17" s="35">
         <f>IF(B17="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L17" s="37">
+      <c r="L17" s="35">
         <f>IF(B17="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M17" s="38">
+      <c r="M17" s="36">
         <f>IF(F17="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N17" s="38">
+      <c r="N17" s="36">
         <f>IF(F17="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13462,25 +13460,25 @@
           <t>Incident 5</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <f>IF(B18="","",B18^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <f>IF(COUNT(C17:C18)=2,ABS(C18-C17),"")</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="27">
         <f>IF(B18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="26" t="n">
         <v>17400</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="34">
         <f>IF(F18="","",$B$10)</f>
         <v/>
       </c>
@@ -13488,23 +13486,23 @@
         <f>IF(B18="","",IF(C18&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C18&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J18" s="37">
+      <c r="J18" s="35">
         <f>IF(B18="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K18" s="37">
+      <c r="K18" s="35">
         <f>IF(B18="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L18" s="37">
+      <c r="L18" s="35">
         <f>IF(B18="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M18" s="38">
+      <c r="M18" s="36">
         <f>IF(F18="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N18" s="38">
+      <c r="N18" s="36">
         <f>IF(F18="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13531,25 +13529,25 @@
           <t>Incident 6</t>
         </is>
       </c>
-      <c r="B19" s="30" t="n">
+      <c r="B19" s="26" t="n">
         <v>27</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="27">
         <f>IF(B19="","",B19^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="27">
         <f>IF(COUNT(C18:C19)=2,ABS(C19-C18),"")</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="27">
         <f>IF(B19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="26" t="n">
         <v>26100</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="34">
         <f>IF(F19="","",$B$10)</f>
         <v/>
       </c>
@@ -13557,23 +13555,23 @@
         <f>IF(B19="","",IF(C19&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C19&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J19" s="37">
+      <c r="J19" s="35">
         <f>IF(B19="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="35">
         <f>IF(B19="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L19" s="37">
+      <c r="L19" s="35">
         <f>IF(B19="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M19" s="38">
+      <c r="M19" s="36">
         <f>IF(F19="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N19" s="38">
+      <c r="N19" s="36">
         <f>IF(F19="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13600,25 +13598,25 @@
           <t>Incident 7</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="26" t="n">
         <v>41</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <f>IF(B20="","",B20^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="27">
         <f>IF(COUNT(C19:C20)=2,ABS(C20-C19),"")</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="27">
         <f>IF(B20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="26" t="n">
         <v>39900</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="34">
         <f>IF(F20="","",$B$10)</f>
         <v/>
       </c>
@@ -13626,23 +13624,23 @@
         <f>IF(B20="","",IF(C20&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C20&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J20" s="37">
+      <c r="J20" s="35">
         <f>IF(B20="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K20" s="37">
+      <c r="K20" s="35">
         <f>IF(B20="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L20" s="37">
+      <c r="L20" s="35">
         <f>IF(B20="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M20" s="38">
+      <c r="M20" s="36">
         <f>IF(F20="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N20" s="38">
+      <c r="N20" s="36">
         <f>IF(F20="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13669,25 +13667,25 @@
           <t>Incident 8</t>
         </is>
       </c>
-      <c r="B21" s="30" t="n">
+      <c r="B21" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <f>IF(B21="","",B21^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="27">
         <f>IF(COUNT(C20:C21)=2,ABS(C21-C20),"")</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="27">
         <f>IF(B21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="26" t="n">
         <v>11200</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="34">
         <f>IF(F21="","",$B$10)</f>
         <v/>
       </c>
@@ -13695,23 +13693,23 @@
         <f>IF(B21="","",IF(C21&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C21&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J21" s="37">
+      <c r="J21" s="35">
         <f>IF(B21="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K21" s="37">
+      <c r="K21" s="35">
         <f>IF(B21="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="35">
         <f>IF(B21="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M21" s="38">
+      <c r="M21" s="36">
         <f>IF(F21="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N21" s="38">
+      <c r="N21" s="36">
         <f>IF(F21="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13738,25 +13736,25 @@
           <t>Incident 9</t>
         </is>
       </c>
-      <c r="B22" s="30" t="n">
+      <c r="B22" s="26" t="n">
         <v>35</v>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="27">
         <f>IF(B22="","",B22^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="27">
         <f>IF(COUNT(C21:C22)=2,ABS(C22-C21),"")</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="27">
         <f>IF(B22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F22" s="26" t="n">
         <v>33500</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="34">
         <f>IF(F22="","",$B$10)</f>
         <v/>
       </c>
@@ -13764,23 +13762,23 @@
         <f>IF(B22="","",IF(C22&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C22&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J22" s="37">
+      <c r="J22" s="35">
         <f>IF(B22="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K22" s="37">
+      <c r="K22" s="35">
         <f>IF(B22="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L22" s="37">
+      <c r="L22" s="35">
         <f>IF(B22="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M22" s="38">
+      <c r="M22" s="36">
         <f>IF(F22="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N22" s="38">
+      <c r="N22" s="36">
         <f>IF(F22="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13807,25 +13805,25 @@
           <t>Incident 10</t>
         </is>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="27">
         <f>IF(B23="","",B23^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="27">
         <f>IF(COUNT(C22:C23)=2,ABS(C23-C22),"")</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="27">
         <f>IF(B23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="26" t="n">
         <v>23100</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="34">
         <f>IF(F23="","",$B$10)</f>
         <v/>
       </c>
@@ -13833,23 +13831,23 @@
         <f>IF(B23="","",IF(C23&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C23&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J23" s="37">
+      <c r="J23" s="35">
         <f>IF(B23="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K23" s="37">
+      <c r="K23" s="35">
         <f>IF(B23="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L23" s="37">
+      <c r="L23" s="35">
         <f>IF(B23="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M23" s="38">
+      <c r="M23" s="36">
         <f>IF(F23="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N23" s="38">
+      <c r="N23" s="36">
         <f>IF(F23="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13876,25 +13874,25 @@
           <t>Incident 11</t>
         </is>
       </c>
-      <c r="B24" s="30" t="n">
+      <c r="B24" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="27">
         <f>IF(B24="","",B24^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="27">
         <f>IF(COUNT(C23:C24)=2,ABS(C24-C23),"")</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="27">
         <f>IF(B24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F24" s="26" t="n">
         <v>46800</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="34">
         <f>IF(F24="","",$B$10)</f>
         <v/>
       </c>
@@ -13902,23 +13900,23 @@
         <f>IF(B24="","",IF(C24&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C24&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J24" s="37">
+      <c r="J24" s="35">
         <f>IF(B24="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K24" s="37">
+      <c r="K24" s="35">
         <f>IF(B24="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L24" s="37">
+      <c r="L24" s="35">
         <f>IF(B24="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M24" s="38">
+      <c r="M24" s="36">
         <f>IF(F24="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N24" s="38">
+      <c r="N24" s="36">
         <f>IF(F24="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13945,25 +13943,25 @@
           <t>Incident 12</t>
         </is>
       </c>
-      <c r="B25" s="30" t="n">
+      <c r="B25" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="27">
         <f>IF(B25="","",B25^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="27">
         <f>IF(COUNT(C24:C25)=2,ABS(C25-C24),"")</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="27">
         <f>IF(B25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F25" s="30" t="n">
+      <c r="F25" s="26" t="n">
         <v>18300</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="34">
         <f>IF(F25="","",$B$10)</f>
         <v/>
       </c>
@@ -13971,23 +13969,23 @@
         <f>IF(B25="","",IF(C25&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C25&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J25" s="37">
+      <c r="J25" s="35">
         <f>IF(B25="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K25" s="37">
+      <c r="K25" s="35">
         <f>IF(B25="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="35">
         <f>IF(B25="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M25" s="38">
+      <c r="M25" s="36">
         <f>IF(F25="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N25" s="38">
+      <c r="N25" s="36">
         <f>IF(F25="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14014,25 +14012,25 @@
           <t>Incident 13</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n">
+      <c r="B26" s="26" t="n">
         <v>33</v>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="27">
         <f>IF(B26="","",B26^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="27">
         <f>IF(COUNT(C25:C26)=2,ABS(C26-C25),"")</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="27">
         <f>IF(B26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F26" s="26" t="n">
         <v>31700</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="34">
         <f>IF(F26="","",$B$10)</f>
         <v/>
       </c>
@@ -14040,23 +14038,23 @@
         <f>IF(B26="","",IF(C26&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C26&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J26" s="37">
+      <c r="J26" s="35">
         <f>IF(B26="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K26" s="37">
+      <c r="K26" s="35">
         <f>IF(B26="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L26" s="37">
+      <c r="L26" s="35">
         <f>IF(B26="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M26" s="38">
+      <c r="M26" s="36">
         <f>IF(F26="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N26" s="38">
+      <c r="N26" s="36">
         <f>IF(F26="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14083,25 +14081,25 @@
           <t>Incident 14</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n">
+      <c r="B27" s="26" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="27">
         <f>IF(B27="","",B27^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="27">
         <f>IF(COUNT(C26:C27)=2,ABS(C27-C26),"")</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="27">
         <f>IF(B27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F27" s="30" t="n">
+      <c r="F27" s="26" t="n">
         <v>25400</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="34">
         <f>IF(F27="","",$B$10)</f>
         <v/>
       </c>
@@ -14109,23 +14107,23 @@
         <f>IF(B27="","",IF(C27&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C27&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J27" s="37">
+      <c r="J27" s="35">
         <f>IF(B27="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K27" s="37">
+      <c r="K27" s="35">
         <f>IF(B27="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L27" s="37">
+      <c r="L27" s="35">
         <f>IF(B27="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M27" s="38">
+      <c r="M27" s="36">
         <f>IF(F27="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N27" s="38">
+      <c r="N27" s="36">
         <f>IF(F27="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14152,25 +14150,25 @@
           <t>Incident 15</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n">
+      <c r="B28" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="27">
         <f>IF(B28="","",B28^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="27">
         <f>IF(COUNT(C27:C28)=2,ABS(C28-C27),"")</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="27">
         <f>IF(B28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F28" s="26" t="n">
         <v>50600</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="34">
         <f>IF(F28="","",$B$10)</f>
         <v/>
       </c>
@@ -14178,23 +14176,23 @@
         <f>IF(B28="","",IF(C28&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C28&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J28" s="37">
+      <c r="J28" s="35">
         <f>IF(B28="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K28" s="37">
+      <c r="K28" s="35">
         <f>IF(B28="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L28" s="37">
+      <c r="L28" s="35">
         <f>IF(B28="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M28" s="38">
+      <c r="M28" s="36">
         <f>IF(F28="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N28" s="38">
+      <c r="N28" s="36">
         <f>IF(F28="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14221,25 +14219,25 @@
           <t>Incident 16</t>
         </is>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="26" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="27">
         <f>IF(B29="","",B29^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="27">
         <f>IF(COUNT(C28:C29)=2,ABS(C29-C28),"")</f>
         <v/>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="27">
         <f>IF(B29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F29" s="30" t="n">
+      <c r="F29" s="26" t="n">
         <v>20200</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="34">
         <f>IF(F29="","",$B$10)</f>
         <v/>
       </c>
@@ -14247,23 +14245,23 @@
         <f>IF(B29="","",IF(C29&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C29&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J29" s="37">
+      <c r="J29" s="35">
         <f>IF(B29="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K29" s="37">
+      <c r="K29" s="35">
         <f>IF(B29="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L29" s="37">
+      <c r="L29" s="35">
         <f>IF(B29="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M29" s="38">
+      <c r="M29" s="36">
         <f>IF(F29="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N29" s="38">
+      <c r="N29" s="36">
         <f>IF(F29="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14290,25 +14288,25 @@
           <t>Incident 17</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n">
+      <c r="B30" s="26" t="n">
         <v>38</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="27">
         <f>IF(B30="","",B30^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="27">
         <f>IF(COUNT(C29:C30)=2,ABS(C30-C29),"")</f>
         <v/>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="27">
         <f>IF(B30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F30" s="30" t="n">
+      <c r="F30" s="26" t="n">
         <v>36900</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="34">
         <f>IF(F30="","",$B$10)</f>
         <v/>
       </c>
@@ -14316,23 +14314,23 @@
         <f>IF(B30="","",IF(C30&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C30&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="35">
         <f>IF(B30="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K30" s="37">
+      <c r="K30" s="35">
         <f>IF(B30="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L30" s="37">
+      <c r="L30" s="35">
         <f>IF(B30="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M30" s="38">
+      <c r="M30" s="36">
         <f>IF(F30="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N30" s="38">
+      <c r="N30" s="36">
         <f>IF(F30="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14359,25 +14357,25 @@
           <t>Incident 18</t>
         </is>
       </c>
-      <c r="B31" s="30" t="n">
+      <c r="B31" s="26" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="27">
         <f>IF(B31="","",B31^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="27">
         <f>IF(COUNT(C30:C31)=2,ABS(C31-C30),"")</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="27">
         <f>IF(B31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F31" s="30" t="n">
+      <c r="F31" s="26" t="n">
         <v>27800</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="34">
         <f>IF(F31="","",$B$10)</f>
         <v/>
       </c>
@@ -14385,23 +14383,23 @@
         <f>IF(B31="","",IF(C31&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C31&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="35">
         <f>IF(B31="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K31" s="37">
+      <c r="K31" s="35">
         <f>IF(B31="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="35">
         <f>IF(B31="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M31" s="38">
+      <c r="M31" s="36">
         <f>IF(F31="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N31" s="38">
+      <c r="N31" s="36">
         <f>IF(F31="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14428,25 +14426,25 @@
           <t>Incident 19</t>
         </is>
       </c>
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="26" t="n">
         <v>44</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="27">
         <f>IF(B32="","",B32^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="27">
         <f>IF(COUNT(C31:C32)=2,ABS(C32-C31),"")</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="27">
         <f>IF(B32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F32" s="30" t="n">
+      <c r="F32" s="26" t="n">
         <v>43100</v>
       </c>
-      <c r="G32" s="36">
+      <c r="G32" s="34">
         <f>IF(F32="","",$B$10)</f>
         <v/>
       </c>
@@ -14454,23 +14452,23 @@
         <f>IF(B32="","",IF(C32&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C32&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J32" s="37">
+      <c r="J32" s="35">
         <f>IF(B32="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K32" s="37">
+      <c r="K32" s="35">
         <f>IF(B32="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L32" s="37">
+      <c r="L32" s="35">
         <f>IF(B32="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M32" s="38">
+      <c r="M32" s="36">
         <f>IF(F32="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N32" s="38">
+      <c r="N32" s="36">
         <f>IF(F32="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14497,25 +14495,25 @@
           <t>Incident 20</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="26" t="n">
         <v>36</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="27">
         <f>IF(B33="","",B33^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="27">
         <f>IF(COUNT(C32:C33)=2,ABS(C33-C32),"")</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="27">
         <f>IF(B33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F33" s="30" t="n">
+      <c r="F33" s="26" t="n">
         <v>34600</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="34">
         <f>IF(F33="","",$B$10)</f>
         <v/>
       </c>
@@ -14523,23 +14521,23 @@
         <f>IF(B33="","",IF(C33&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C33&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J33" s="37">
+      <c r="J33" s="35">
         <f>IF(B33="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K33" s="37">
+      <c r="K33" s="35">
         <f>IF(B33="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L33" s="37">
+      <c r="L33" s="35">
         <f>IF(B33="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M33" s="38">
+      <c r="M33" s="36">
         <f>IF(F33="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N33" s="38">
+      <c r="N33" s="36">
         <f>IF(F33="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14566,25 +14564,25 @@
           <t>Incident 21</t>
         </is>
       </c>
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="26" t="n">
         <v>58</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="27">
         <f>IF(B34="","",B34^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="27">
         <f>IF(COUNT(C33:C34)=2,ABS(C34-C33),"")</f>
         <v/>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="27">
         <f>IF(B34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F34" s="30" t="n">
+      <c r="F34" s="26" t="n">
         <v>56900</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="34">
         <f>IF(F34="","",$B$10)</f>
         <v/>
       </c>
@@ -14592,23 +14590,23 @@
         <f>IF(B34="","",IF(C34&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C34&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J34" s="37">
+      <c r="J34" s="35">
         <f>IF(B34="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K34" s="37">
+      <c r="K34" s="35">
         <f>IF(B34="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L34" s="37">
+      <c r="L34" s="35">
         <f>IF(B34="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M34" s="38">
+      <c r="M34" s="36">
         <f>IF(F34="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N34" s="38">
+      <c r="N34" s="36">
         <f>IF(F34="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14635,25 +14633,25 @@
           <t>Incident 22</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="26" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="27">
         <f>IF(B35="","",B35^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="27">
         <f>IF(COUNT(C34:C35)=2,ABS(C35-C34),"")</f>
         <v/>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="27">
         <f>IF(B35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F35" s="30" t="n">
+      <c r="F35" s="26" t="n">
         <v>29900</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="34">
         <f>IF(F35="","",$B$10)</f>
         <v/>
       </c>
@@ -14661,23 +14659,23 @@
         <f>IF(B35="","",IF(C35&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C35&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J35" s="37">
+      <c r="J35" s="35">
         <f>IF(B35="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K35" s="37">
+      <c r="K35" s="35">
         <f>IF(B35="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="35">
         <f>IF(B35="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M35" s="38">
+      <c r="M35" s="36">
         <f>IF(F35="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N35" s="38">
+      <c r="N35" s="36">
         <f>IF(F35="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14704,25 +14702,25 @@
           <t>Incident 23</t>
         </is>
       </c>
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="26" t="n">
         <v>47</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="27">
         <f>IF(B36="","",B36^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="27">
         <f>IF(COUNT(C35:C36)=2,ABS(C36-C35),"")</f>
         <v/>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="27">
         <f>IF(B36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F36" s="30" t="n">
+      <c r="F36" s="26" t="n">
         <v>45200</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="34">
         <f>IF(F36="","",$B$10)</f>
         <v/>
       </c>
@@ -14730,23 +14728,23 @@
         <f>IF(B36="","",IF(C36&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C36&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J36" s="37">
+      <c r="J36" s="35">
         <f>IF(B36="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K36" s="37">
+      <c r="K36" s="35">
         <f>IF(B36="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L36" s="37">
+      <c r="L36" s="35">
         <f>IF(B36="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M36" s="38">
+      <c r="M36" s="36">
         <f>IF(F36="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N36" s="38">
+      <c r="N36" s="36">
         <f>IF(F36="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14773,25 +14771,25 @@
           <t>Incident 24</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="26" t="n">
         <v>40</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="27">
         <f>IF(B37="","",B37^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D37" s="28">
+      <c r="D37" s="27">
         <f>IF(COUNT(C36:C37)=2,ABS(C37-C36),"")</f>
         <v/>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="27">
         <f>IF(B37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F37" s="30" t="n">
+      <c r="F37" s="26" t="n">
         <v>38400</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="34">
         <f>IF(F37="","",$B$10)</f>
         <v/>
       </c>
@@ -14799,23 +14797,23 @@
         <f>IF(B37="","",IF(C37&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C37&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J37" s="37">
+      <c r="J37" s="35">
         <f>IF(B37="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K37" s="37">
+      <c r="K37" s="35">
         <f>IF(B37="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="35">
         <f>IF(B37="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M37" s="38">
+      <c r="M37" s="36">
         <f>IF(F37="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N37" s="38">
+      <c r="N37" s="36">
         <f>IF(F37="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -3507,6 +3507,9 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B10"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="B34" s="19" t="n">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C34" s="17">
         <f>IF(COUNT(B33:B34)=2,ABS(B34-B33),"")</f>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>404</v>
+        <v>471</v>
       </c>
       <c r="C35" s="17">
         <f>IF(COUNT(B34:B35)=2,ABS(B35-B34),"")</f>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="B36" s="19" t="n">
-        <v>416</v>
+        <v>478</v>
       </c>
       <c r="C36" s="17">
         <f>IF(COUNT(B35:B36)=2,ABS(B36-B35),"")</f>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="B37" s="19" t="n">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="C37" s="17">
         <f>IF(COUNT(B36:B37)=2,ABS(B37-B36),"")</f>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="B36" s="26" t="n">
-        <v>7770</v>
+        <v>8120</v>
       </c>
       <c r="C36" s="26" t="n">
-        <v>5450</v>
+        <v>5180</v>
       </c>
       <c r="D36" s="22">
         <f>IF(B36="","",C36/B36)</f>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="B37" s="26" t="n">
-        <v>8240</v>
+        <v>7950</v>
       </c>
       <c r="C37" s="26" t="n">
-        <v>6020</v>
+        <v>5060</v>
       </c>
       <c r="D37" s="22">
         <f>IF(B37="","",C37/B37)</f>
@@ -8370,7 +8370,7 @@
         <v>1225</v>
       </c>
       <c r="C36" s="26" t="n">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="D36" s="27">
         <f>IF(B36="","",C36/B36)</f>
@@ -8426,7 +8426,7 @@
         <v>1390</v>
       </c>
       <c r="C37" s="26" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D37" s="27">
         <f>IF(B37="","",C37/B37)</f>
@@ -8799,19 +8799,19 @@
         </is>
       </c>
       <c r="B14" s="26" t="n">
+        <v>446</v>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>410</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>407</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>399</v>
+      </c>
+      <c r="F14" s="26" t="n">
         <v>400</v>
-      </c>
-      <c r="C14" s="26" t="n">
-        <v>419</v>
-      </c>
-      <c r="D14" s="26" t="n">
-        <v>381</v>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>400</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>419</v>
       </c>
       <c r="G14" s="17">
         <f>IF(COUNT(B14:F14)=0,"",AVERAGE(B14:F14))</f>
@@ -8872,19 +8872,19 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C15" s="26" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D15" s="26" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>395</v>
+        <v>432</v>
       </c>
       <c r="G15" s="17">
         <f>IF(COUNT(B15:F15)=0,"",AVERAGE(B15:F15))</f>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="B16" s="26" t="n">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C16" s="26" t="n">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D16" s="26" t="n">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="G16" s="17">
         <f>IF(COUNT(B16:F16)=0,"",AVERAGE(B16:F16))</f>
@@ -9018,19 +9018,19 @@
         </is>
       </c>
       <c r="B17" s="26" t="n">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c r="C17" s="26" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D17" s="26" t="n">
-        <v>425</v>
+        <v>393</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="G17" s="17">
         <f>IF(COUNT(B17:F17)=0,"",AVERAGE(B17:F17))</f>
@@ -9091,19 +9091,19 @@
         </is>
       </c>
       <c r="B18" s="26" t="n">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="C18" s="26" t="n">
-        <v>437</v>
+        <v>409</v>
       </c>
       <c r="D18" s="26" t="n">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>437</v>
+        <v>403</v>
       </c>
       <c r="G18" s="17">
         <f>IF(COUNT(B18:F18)=0,"",AVERAGE(B18:F18))</f>
@@ -9164,19 +9164,19 @@
         </is>
       </c>
       <c r="B19" s="26" t="n">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="C19" s="26" t="n">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="D19" s="26" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>430</v>
+        <v>407</v>
       </c>
       <c r="F19" s="26" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G19" s="17">
         <f>IF(COUNT(B19:F19)=0,"",AVERAGE(B19:F19))</f>
@@ -9237,19 +9237,19 @@
         </is>
       </c>
       <c r="B20" s="26" t="n">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="C20" s="26" t="n">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="D20" s="26" t="n">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="G20" s="17">
         <f>IF(COUNT(B20:F20)=0,"",AVERAGE(B20:F20))</f>
@@ -9310,19 +9310,19 @@
         </is>
       </c>
       <c r="B21" s="26" t="n">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C21" s="26" t="n">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="D21" s="26" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="F21" s="26" t="n">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="G21" s="17">
         <f>IF(COUNT(B21:F21)=0,"",AVERAGE(B21:F21))</f>
@@ -9383,19 +9383,19 @@
         </is>
       </c>
       <c r="B22" s="26" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="C22" s="26" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D22" s="26" t="n">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="F22" s="26" t="n">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="G22" s="17">
         <f>IF(COUNT(B22:F22)=0,"",AVERAGE(B22:F22))</f>
@@ -9456,19 +9456,19 @@
         </is>
       </c>
       <c r="B23" s="26" t="n">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C23" s="26" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="D23" s="26" t="n">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="F23" s="26" t="n">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="G23" s="17">
         <f>IF(COUNT(B23:F23)=0,"",AVERAGE(B23:F23))</f>
@@ -9529,19 +9529,19 @@
         </is>
       </c>
       <c r="B24" s="26" t="n">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="C24" s="26" t="n">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D24" s="26" t="n">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="F24" s="26" t="n">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="G24" s="17">
         <f>IF(COUNT(B24:F24)=0,"",AVERAGE(B24:F24))</f>
@@ -9602,19 +9602,19 @@
         </is>
       </c>
       <c r="B25" s="26" t="n">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C25" s="26" t="n">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D25" s="26" t="n">
-        <v>372</v>
+        <v>424</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="F25" s="26" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="G25" s="17">
         <f>IF(COUNT(B25:F25)=0,"",AVERAGE(B25:F25))</f>
@@ -9675,19 +9675,19 @@
         </is>
       </c>
       <c r="B26" s="26" t="n">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="C26" s="26" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D26" s="26" t="n">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="G26" s="17">
         <f>IF(COUNT(B26:F26)=0,"",AVERAGE(B26:F26))</f>
@@ -9748,19 +9748,19 @@
         </is>
       </c>
       <c r="B27" s="26" t="n">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C27" s="26" t="n">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D27" s="26" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="G27" s="17">
         <f>IF(COUNT(B27:F27)=0,"",AVERAGE(B27:F27))</f>
@@ -9821,19 +9821,19 @@
         </is>
       </c>
       <c r="B28" s="26" t="n">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="C28" s="26" t="n">
-        <v>421</v>
+        <v>383</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="G28" s="17">
         <f>IF(COUNT(B28:F28)=0,"",AVERAGE(B28:F28))</f>
@@ -9894,19 +9894,19 @@
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C29" s="26" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D29" s="26" t="n">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="F29" s="26" t="n">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="G29" s="17">
         <f>IF(COUNT(B29:F29)=0,"",AVERAGE(B29:F29))</f>
@@ -9967,19 +9967,19 @@
         </is>
       </c>
       <c r="B30" s="26" t="n">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C30" s="26" t="n">
-        <v>389</v>
+        <v>419</v>
       </c>
       <c r="D30" s="26" t="n">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="F30" s="26" t="n">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="G30" s="17">
         <f>IF(COUNT(B30:F30)=0,"",AVERAGE(B30:F30))</f>
@@ -10040,19 +10040,19 @@
         </is>
       </c>
       <c r="B31" s="26" t="n">
+        <v>397</v>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>383</v>
+      </c>
+      <c r="D31" s="26" t="n">
         <v>403</v>
       </c>
-      <c r="C31" s="26" t="n">
-        <v>407</v>
-      </c>
-      <c r="D31" s="26" t="n">
-        <v>438</v>
-      </c>
       <c r="E31" s="26" t="n">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="F31" s="26" t="n">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="G31" s="17">
         <f>IF(COUNT(B31:F31)=0,"",AVERAGE(B31:F31))</f>
@@ -10113,19 +10113,19 @@
         </is>
       </c>
       <c r="B32" s="26" t="n">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="C32" s="26" t="n">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="D32" s="26" t="n">
+        <v>391</v>
+      </c>
+      <c r="E32" s="26" t="n">
         <v>417</v>
       </c>
-      <c r="E32" s="26" t="n">
-        <v>406</v>
-      </c>
       <c r="F32" s="26" t="n">
-        <v>443</v>
+        <v>383</v>
       </c>
       <c r="G32" s="17">
         <f>IF(COUNT(B32:F32)=0,"",AVERAGE(B32:F32))</f>
@@ -10186,19 +10186,19 @@
         </is>
       </c>
       <c r="B33" s="26" t="n">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="C33" s="26" t="n">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="D33" s="26" t="n">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>443</v>
+        <v>386</v>
       </c>
       <c r="F33" s="26" t="n">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G33" s="17">
         <f>IF(COUNT(B33:F33)=0,"",AVERAGE(B33:F33))</f>
@@ -10259,19 +10259,19 @@
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="C34" s="26" t="n">
-        <v>390</v>
+        <v>437</v>
       </c>
       <c r="D34" s="26" t="n">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="F34" s="26" t="n">
-        <v>390</v>
+        <v>433</v>
       </c>
       <c r="G34" s="17">
         <f>IF(COUNT(B34:F34)=0,"",AVERAGE(B34:F34))</f>
@@ -10332,19 +10332,19 @@
         </is>
       </c>
       <c r="B35" s="26" t="n">
-        <v>392</v>
+        <v>448</v>
       </c>
       <c r="C35" s="26" t="n">
-        <v>414</v>
+        <v>463</v>
       </c>
       <c r="D35" s="26" t="n">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="F35" s="26" t="n">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G35" s="17">
         <f>IF(COUNT(B35:F35)=0,"",AVERAGE(B35:F35))</f>
@@ -10405,19 +10405,19 @@
         </is>
       </c>
       <c r="B36" s="26" t="n">
-        <v>403</v>
+        <v>459</v>
       </c>
       <c r="C36" s="26" t="n">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="D36" s="26" t="n">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="F36" s="26" t="n">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="G36" s="17">
         <f>IF(COUNT(B36:F36)=0,"",AVERAGE(B36:F36))</f>
@@ -10478,19 +10478,19 @@
         </is>
       </c>
       <c r="B37" s="26" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C37" s="26" t="n">
-        <v>399</v>
+        <v>429</v>
       </c>
       <c r="D37" s="26" t="n">
-        <v>393</v>
+        <v>452</v>
       </c>
       <c r="E37" s="26" t="n">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F37" s="26" t="n">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="G37" s="17">
         <f>IF(COUNT(B37:F37)=0,"",AVERAGE(B37:F37))</f>
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="B37" s="26" t="n">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="C37" s="27">
         <f>IF(B37="","",B37^(1/3.6))</f>
@@ -14790,7 +14790,7 @@
         <v/>
       </c>
       <c r="F37" s="26" t="n">
-        <v>38400</v>
+        <v>161000</v>
       </c>
       <c r="G37" s="34">
         <f>IF(F37="","",$B$10)</f>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -3933,10 +3933,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per period, oldest first  ·  Key: CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · MR = moving range, the gap between one point and the one before it</t>
+          <t>Your data — one row per period, oldest first  ·  Key: Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself · CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · MR = moving range, the gap between one point and the one before it</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -5451,10 +5451,10 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per day  ·  Key: z = your rate restated in standard deviations, so periods of different size compare · MR = moving range, the gap between one point and the one before it · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · CL = centre line, the average the chart is drawn around</t>
+          <t>Your data — one row per day  ·  Key: Sigma p = the standard deviation expected for THAT day's sample size, so a quiet day gets wider limits than a busy one. Day 1 has 7,820 contacts and a sigma p of 0.00507 (E14) from the overall 72.05% (B5). On a p-prime chart this is then multiplied by sigma z, 4.61 here (B7), which is the Laney correction for a rate that moves more between days than binomial sampling alone can explain · z = your rate restated in standard deviations, so periods of different size compare · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -7044,10 +7044,10 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per week  ·  Key: z = your rate restated in standard deviations, so periods of different size compare · MR = moving range, the gap between one point and the one before it · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · CL = centre line, the average the chart is drawn around</t>
+          <t>Your data — one row per week  ·  Key: Sigma u = the standard deviation expected for that week's exposure, so a week with more audited contacts gets tighter limits. Week 1 audited 1,240 and gets 0.00592 (E14) from the overall rate of 0.0434 defects per contact (B5); the Laney sigma z of 2.63 (B7) then widens it for overdispersion. A plain u-chart would have cried wolf on the quiet weeks and had nothing left to say about the loud ones · z = your rate restated in standard deviations, so periods of different size compare · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -10707,10 +10707,10 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14" ht="24" customHeight="1">
+    <row r="14" ht="72" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per period, oldest first  ·  Key: CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+          <t>Your data — one row per period, oldest first  ·  Key: Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself · CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>
       <c r="B14" s="10" t="n"/>
@@ -11838,10 +11838,10 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14" ht="24" customHeight="1">
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per period, oldest first  ·  Key: SL = service level, the share of contacts answered inside your target time</t>
+          <t>Your data — one row per period, oldest first  ·  Key: Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself · SL = service level, the share of contacts answered inside your target time</t>
         </is>
       </c>
       <c r="B14" s="10" t="n"/>
@@ -13099,10 +13099,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="14" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>One row per event, oldest first  ·  Key: CL = centre line, the average the chart is drawn around</t>
+          <t>One row per event, oldest first  ·  Key: Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself · CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -3933,10 +3933,14 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="72" customHeight="1">
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per period, oldest first  ·  Key: Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself · CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · MR = moving range, the gap between one point and the one before it</t>
+          <t>Your data — one row per period, oldest first  ·  Key:
+• Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself
+• CL = centre line, the average the chart is drawn around
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line
+• MR = moving range, the gap between one point and the one before it</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -5451,10 +5455,14 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12" ht="72" customHeight="1">
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per day  ·  Key: Sigma p = the standard deviation expected for THAT day's sample size, so a quiet day gets wider limits than a busy one. Day 1 has 7,820 contacts and a sigma p of 0.00507 (E14) from the overall 72.05% (B5). On a p-prime chart this is then multiplied by sigma z, 4.61 here (B7), which is the Laney correction for a rate that moves more between days than binomial sampling alone can explain · z = your rate restated in standard deviations, so periods of different size compare · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · CL = centre line, the average the chart is drawn around</t>
+          <t>Your data — one row per day  ·  Key:
+• Sigma p = the standard deviation expected for THAT day's sample size, so a quiet day gets wider limits than a busy one. Day 1 has 7,820 contacts and a sigma p of 0.00507 (E14) from the overall 72.05% (B5). On a p-prime chart this is then multiplied by sigma z, 4.61 here (B7), which is the Laney correction for a rate that moves more between days than binomial sampling alone can explain
+• z = your rate restated in standard deviations, so periods of different size compare
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line
+• CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -7044,10 +7052,14 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12" ht="72" customHeight="1">
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per week  ·  Key: Sigma u = the standard deviation expected for that week's exposure, so a week with more audited contacts gets tighter limits. Week 1 audited 1,240 and gets 0.00592 (E14) from the overall rate of 0.0434 defects per contact (B5); the Laney sigma z of 2.63 (B7) then widens it for overdispersion. A plain u-chart would have cried wolf on the quiet weeks and had nothing left to say about the loud ones · z = your rate restated in standard deviations, so periods of different size compare · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line · CL = centre line, the average the chart is drawn around</t>
+          <t>Your data — one row per week  ·  Key:
+• Sigma u = the standard deviation expected for that week's exposure, so a week with more audited contacts gets tighter limits. Week 1 audited 1,240 and gets 0.00592 (E14) from the overall rate of 0.0434 defects per contact (B5); the Laney sigma z of 2.63 (B7) then widens it for overdispersion. A plain u-chart would have cried wolf on the quiet weeks and had nothing left to say about the loud ones
+• z = your rate restated in standard deviations, so periods of different size compare
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line
+• CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -8692,10 +8704,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Your data — five observations per subgroup  ·  Key: OBS 1..n are your individual measurements in one subgroup — one row per period · CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+          <t>Your data — five observations per subgroup  ·  Key:
+• OBS 1..n are your individual measurements in one subgroup — one row per period
+• CL = centre line, the average the chart is drawn around
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -10707,10 +10722,13 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14" ht="72" customHeight="1">
+    <row r="14" ht="84" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per period, oldest first  ·  Key: Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself · CL = centre line, the average the chart is drawn around · UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+          <t>Your data — one row per period, oldest first  ·  Key:
+• Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself
+• CL = centre line, the average the chart is drawn around
+• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
         </is>
       </c>
       <c r="B14" s="10" t="n"/>
@@ -11838,10 +11856,12 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="72" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Your data — one row per period, oldest first  ·  Key: Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself · SL = service level, the share of contacts answered inside your target time</t>
+          <t>Your data — one row per period, oldest first  ·  Key:
+• Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself
+• SL = service level, the share of contacts answered inside your target time</t>
         </is>
       </c>
       <c r="B14" s="10" t="n"/>
@@ -13099,10 +13119,12 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>One row per event, oldest first  ·  Key: Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself · CL = centre line, the average the chart is drawn around</t>
+          <t>One row per event, oldest first  ·  Key:
+• Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself
+• CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -134,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -173,6 +178,9 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3747,7 +3755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3759,6 +3767,15 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
     <col width="4" customWidth="1" min="30" max="30"/>
     <col width="4" customWidth="1" min="31" max="31"/>
@@ -4439,7 +4456,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="77" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Day 9</t>
@@ -4476,6 +4493,12 @@
         <f>IF(B22="","",IF(OR(B22&gt;$B$9,B22&lt;$B$10),"OUT OF CONTROL",IF(AND(COUNT(B15:B22)=8,OR(MIN(B15:B22)&gt;$B$6,MAX(B15:B22)&lt;$B$6)),"8 in a row one side — shift","")))</f>
         <v/>
       </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  One point per period against limits frozen from the baseline window. Limits are held still on purpose — recomputing them as data arrives lets the line follow a drift, and a chart that follows the process it is watching cannot signal that the process moved. The worked example runs flat for twenty points and then steps past the upper limit twice.
+SO:  Two points past the limit is a special cause: find what changed on those days before touching the process. Do not re-baseline to make the signal go away — that is the one action this chart exists to prevent.</t>
+        </is>
+      </c>
       <c r="T22" s="21" t="n">
         <v>9</v>
       </c>
@@ -5287,13 +5310,23 @@
         <v/>
       </c>
     </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="K38" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  The gap between consecutive points. Read it WITH the chart above: level moving while spread holds still is a shift, and both moving together is usually a measurement or definition change rather than a process one. In the worked example the range stays in control while the individuals chart signals — the level moved and the spread did not.
+SO:  Range in control with the individuals chart signalling means the level moved and the spread did not — look for a step change, a release or a rule change, not for a noisy process. If both signal together, check the definition before you check the process.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
+    <mergeCell ref="K38:S38"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C9:I9"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K22:S22"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="C10:I10"/>
@@ -5327,7 +5360,15 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="30" max="30"/>
     <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
@@ -5394,7 +5435,7 @@
           <t>Overall proportion (p-bar)</t>
         </is>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="23">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -5410,7 +5451,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="24">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -5426,7 +5467,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -5442,7 +5483,7 @@
           <t>Ordinary p-chart limits would be</t>
         </is>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>"±"&amp;TEXT(3*SQRT(B5*(1-B5)/AVERAGE(B14:B37)),"0.00%")</f>
         <v/>
       </c>
@@ -5516,17 +5557,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -5553,17 +5594,17 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>7820</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>5610</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="23">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",SQRT($B$5*(1-$B$5)/B14))</f>
         <v/>
       </c>
@@ -5575,15 +5616,15 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="29">
         <f>IF(B14="","",MIN(1,$B$5+3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="29">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="29">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
@@ -5605,17 +5646,17 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>8140</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>5990</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="23">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",SQRT($B$5*(1-$B$5)/B15))</f>
         <v/>
       </c>
@@ -5631,15 +5672,15 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="29">
         <f>IF(B15="","",MIN(1,$B$5+3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="29">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="29">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
@@ -5661,17 +5702,17 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>7960</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>5570</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="23">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",SQRT($B$5*(1-$B$5)/B16))</f>
         <v/>
       </c>
@@ -5687,15 +5728,15 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>IF(B16="","",MIN(1,$B$5+3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
@@ -5717,17 +5758,17 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>8310</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>6120</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="23">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",SQRT($B$5*(1-$B$5)/B17))</f>
         <v/>
       </c>
@@ -5743,15 +5784,15 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="29">
         <f>IF(B17="","",MIN(1,$B$5+3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="29">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="29">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
@@ -5773,17 +5814,17 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>7690</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>5410</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="23">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",SQRT($B$5*(1-$B$5)/B18))</f>
         <v/>
       </c>
@@ -5799,15 +5840,15 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="29">
         <f>IF(B18="","",MIN(1,$B$5+3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="29">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="28">
+      <c r="M18" s="29">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
@@ -5829,17 +5870,17 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>8020</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>5880</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="23">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",SQRT($B$5*(1-$B$5)/B19))</f>
         <v/>
       </c>
@@ -5855,15 +5896,15 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="29">
         <f>IF(B19="","",MIN(1,$B$5+3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="L19" s="28">
+      <c r="L19" s="29">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="28">
+      <c r="M19" s="29">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
@@ -5885,17 +5926,17 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>8450</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>6210</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="23">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",SQRT($B$5*(1-$B$5)/B20))</f>
         <v/>
       </c>
@@ -5911,15 +5952,15 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="29">
         <f>IF(B20="","",MIN(1,$B$5+3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="L20" s="28">
+      <c r="L20" s="29">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="28">
+      <c r="M20" s="29">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
@@ -5941,17 +5982,17 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>7880</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>5490</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",SQRT($B$5*(1-$B$5)/B21))</f>
         <v/>
       </c>
@@ -5967,15 +6008,15 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>IF(B21="","",MIN(1,$B$5+3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
@@ -5991,23 +6032,23 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>8210</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>6050</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",SQRT($B$5*(1-$B$5)/B22))</f>
         <v/>
       </c>
@@ -6023,20 +6064,23 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="29">
         <f>IF(B22="","",MIN(1,$B$5+3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="L22" s="28">
+      <c r="L22" s="29">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="28">
+      <c r="M22" s="29">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T22" s="21" t="n">
-        <v>9</v>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  A proportion per period, with limits that widen on quiet days and tighten on busy ones. The Laney correction is what stops a plain p-chart signalling on every point once the samples get large. Two points fall through the lower limit in the worked example — a service-level collapse while volume held.
+SO:  Two days through the lower limit is a collapse, not noise. Pull those days' contacts and find the cause the same week — a point outside the limits is worth more the day it happens than in any monthly review.</t>
+        </is>
       </c>
       <c r="AD22" s="21">
         <f>IF($D22="",NA(),IF(OR($D22&gt;$K22,$D22&lt;$L22),$D22,NA()))</f>
@@ -6053,17 +6097,17 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>7740</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>5380</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="23">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",SQRT($B$5*(1-$B$5)/B23))</f>
         <v/>
       </c>
@@ -6079,15 +6123,15 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>IF(B23="","",MIN(1,$B$5+3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
@@ -6109,17 +6153,17 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>8090</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>5940</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="23">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",SQRT($B$5*(1-$B$5)/B24))</f>
         <v/>
       </c>
@@ -6135,15 +6179,15 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="29">
         <f>IF(B24="","",MIN(1,$B$5+3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="29">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="28">
+      <c r="M24" s="29">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
@@ -6165,17 +6209,17 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>8380</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>6180</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="23">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",SQRT($B$5*(1-$B$5)/B25))</f>
         <v/>
       </c>
@@ -6191,15 +6235,15 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="29">
         <f>IF(B25="","",MIN(1,$B$5+3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="29">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="28">
+      <c r="M25" s="29">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
@@ -6221,17 +6265,17 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>7930</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <v>5520</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="23">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",SQRT($B$5*(1-$B$5)/B26))</f>
         <v/>
       </c>
@@ -6247,15 +6291,15 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="28">
+      <c r="K26" s="29">
         <f>IF(B26="","",MIN(1,$B$5+3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="29">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="28">
+      <c r="M26" s="29">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
@@ -6277,17 +6321,17 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>8260</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>6010</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="23">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",SQRT($B$5*(1-$B$5)/B27))</f>
         <v/>
       </c>
@@ -6303,15 +6347,15 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="28">
+      <c r="K27" s="29">
         <f>IF(B27="","",MIN(1,$B$5+3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="29">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="28">
+      <c r="M27" s="29">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
@@ -6333,17 +6377,17 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>7810</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>5480</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="23">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",SQRT($B$5*(1-$B$5)/B28))</f>
         <v/>
       </c>
@@ -6359,15 +6403,15 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="29">
         <f>IF(B28="","",MIN(1,$B$5+3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="29">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="28">
+      <c r="M28" s="29">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
@@ -6389,17 +6433,17 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>8150</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>5860</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="23">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",SQRT($B$5*(1-$B$5)/B29))</f>
         <v/>
       </c>
@@ -6415,15 +6459,15 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="28">
+      <c r="K29" s="29">
         <f>IF(B29="","",MIN(1,$B$5+3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="29">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="28">
+      <c r="M29" s="29">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
@@ -6445,17 +6489,17 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>8470</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>6240</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="23">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",SQRT($B$5*(1-$B$5)/B30))</f>
         <v/>
       </c>
@@ -6471,15 +6515,15 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="28">
+      <c r="K30" s="29">
         <f>IF(B30="","",MIN(1,$B$5+3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="L30" s="28">
+      <c r="L30" s="29">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="28">
+      <c r="M30" s="29">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
@@ -6501,17 +6545,17 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <v>7860</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <v>5600</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",SQRT($B$5*(1-$B$5)/B31))</f>
         <v/>
       </c>
@@ -6527,15 +6571,15 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="28">
+      <c r="K31" s="29">
         <f>IF(B31="","",MIN(1,$B$5+3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="29">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="28">
+      <c r="M31" s="29">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
@@ -6557,17 +6601,17 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>8030</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="27" t="n">
         <v>5760</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="23">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",SQRT($B$5*(1-$B$5)/B32))</f>
         <v/>
       </c>
@@ -6583,15 +6627,15 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="28">
+      <c r="K32" s="29">
         <f>IF(B32="","",MIN(1,$B$5+3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="L32" s="28">
+      <c r="L32" s="29">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="28">
+      <c r="M32" s="29">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
@@ -6613,17 +6657,17 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>8340</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
         <v>6090</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="23">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",SQRT($B$5*(1-$B$5)/B33))</f>
         <v/>
       </c>
@@ -6639,15 +6683,15 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="28">
+      <c r="K33" s="29">
         <f>IF(B33="","",MIN(1,$B$5+3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="29">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="28">
+      <c r="M33" s="29">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
@@ -6669,17 +6713,17 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <v>7900</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <v>5710</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="23">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",SQRT($B$5*(1-$B$5)/B34))</f>
         <v/>
       </c>
@@ -6695,15 +6739,15 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="28">
+      <c r="K34" s="29">
         <f>IF(B34="","",MIN(1,$B$5+3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="L34" s="28">
+      <c r="L34" s="29">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="28">
+      <c r="M34" s="29">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
@@ -6725,17 +6769,17 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>8180</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="27" t="n">
         <v>5900</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="23">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",SQRT($B$5*(1-$B$5)/B35))</f>
         <v/>
       </c>
@@ -6751,15 +6795,15 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="28">
+      <c r="K35" s="29">
         <f>IF(B35="","",MIN(1,$B$5+3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="L35" s="28">
+      <c r="L35" s="29">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="28">
+      <c r="M35" s="29">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
@@ -6781,17 +6825,17 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>8120</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="27" t="n">
         <v>5180</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="23">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",SQRT($B$5*(1-$B$5)/B36))</f>
         <v/>
       </c>
@@ -6807,15 +6851,15 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="28">
+      <c r="K36" s="29">
         <f>IF(B36="","",MIN(1,$B$5+3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="L36" s="28">
+      <c r="L36" s="29">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="28">
+      <c r="M36" s="29">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
@@ -6837,17 +6881,17 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <v>7950</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="27" t="n">
         <v>5060</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="23">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",SQRT($B$5*(1-$B$5)/B37))</f>
         <v/>
       </c>
@@ -6863,15 +6907,15 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="28">
+      <c r="K37" s="29">
         <f>IF(B37="","",MIN(1,$B$5+3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="L37" s="28">
+      <c r="L37" s="29">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="28">
+      <c r="M37" s="29">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
@@ -6888,13 +6932,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:I7"/>
+    <mergeCell ref="O22:W22"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="C5:I5"/>
@@ -6924,7 +6969,15 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="30" max="30"/>
     <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
@@ -6991,7 +7044,7 @@
           <t>Overall rate (u-bar)</t>
         </is>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <f>SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$C$14:$C$37)/SUMIF($T$14:$T$37,"&lt;="&amp;$B$3,$B$14:$B$37)</f>
         <v/>
       </c>
@@ -7007,7 +7060,7 @@
           <t>Average moving range of z</t>
         </is>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="24">
         <f>IFERROR(SUMIF($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37)/COUNTIFS($T$15:$T$37,"&lt;="&amp;$B$3,$G$15:$G$37,"&gt;"&amp;-9.9E+307),"")</f>
         <v/>
       </c>
@@ -7023,7 +7076,7 @@
           <t>Sigma z (Laney adjustment)</t>
         </is>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <f>MAX(1,B6/1.128)</f>
         <v/>
       </c>
@@ -7113,17 +7166,17 @@
           <t>Signal</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="26" t="inlineStr">
         <is>
           <t>UCL</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
         <is>
           <t>LCL</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
@@ -7150,17 +7203,17 @@
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>1240</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>IF(B14="","",C14/B14)</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",SQRT($B$5/B14))</f>
         <v/>
       </c>
@@ -7172,15 +7225,15 @@
         <f>IF(D14="","",IF(OR(D14&gt;K14,D14&lt;L14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="31">
         <f>IF(B14="","",$B$5+3*E14*$B$7)</f>
         <v/>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="31">
         <f>IF(B14="","",MAX(0,$B$5-3*E14*$B$7))</f>
         <v/>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="31">
         <f>IF(B14="","",$B$5)</f>
         <v/>
       </c>
@@ -7202,17 +7255,17 @@
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>1310</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>68</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>IF(B15="","",C15/B15)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",SQRT($B$5/B15))</f>
         <v/>
       </c>
@@ -7228,15 +7281,15 @@
         <f>IF(D15="","",IF(OR(D15&gt;K15,D15&lt;L15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K15" s="30">
+      <c r="K15" s="31">
         <f>IF(B15="","",$B$5+3*E15*$B$7)</f>
         <v/>
       </c>
-      <c r="L15" s="30">
+      <c r="L15" s="31">
         <f>IF(B15="","",MAX(0,$B$5-3*E15*$B$7))</f>
         <v/>
       </c>
-      <c r="M15" s="30">
+      <c r="M15" s="31">
         <f>IF(B15="","",$B$5)</f>
         <v/>
       </c>
@@ -7258,17 +7311,17 @@
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>1180</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>IF(B16="","",C16/B16)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",SQRT($B$5/B16))</f>
         <v/>
       </c>
@@ -7284,15 +7337,15 @@
         <f>IF(D16="","",IF(OR(D16&gt;K16,D16&lt;L16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="31">
         <f>IF(B16="","",$B$5+3*E16*$B$7)</f>
         <v/>
       </c>
-      <c r="L16" s="30">
+      <c r="L16" s="31">
         <f>IF(B16="","",MAX(0,$B$5-3*E16*$B$7))</f>
         <v/>
       </c>
-      <c r="M16" s="30">
+      <c r="M16" s="31">
         <f>IF(B16="","",$B$5)</f>
         <v/>
       </c>
@@ -7314,17 +7367,17 @@
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>1420</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>IF(B17="","",C17/B17)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",SQRT($B$5/B17))</f>
         <v/>
       </c>
@@ -7340,15 +7393,15 @@
         <f>IF(D17="","",IF(OR(D17&gt;K17,D17&lt;L17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="31">
         <f>IF(B17="","",$B$5+3*E17*$B$7)</f>
         <v/>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="31">
         <f>IF(B17="","",MAX(0,$B$5-3*E17*$B$7))</f>
         <v/>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="31">
         <f>IF(B17="","",$B$5)</f>
         <v/>
       </c>
@@ -7370,17 +7423,17 @@
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>1275</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>IF(B18="","",C18/B18)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",SQRT($B$5/B18))</f>
         <v/>
       </c>
@@ -7396,15 +7449,15 @@
         <f>IF(D18="","",IF(OR(D18&gt;K18,D18&lt;L18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="31">
         <f>IF(B18="","",$B$5+3*E18*$B$7)</f>
         <v/>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="31">
         <f>IF(B18="","",MAX(0,$B$5-3*E18*$B$7))</f>
         <v/>
       </c>
-      <c r="M18" s="30">
+      <c r="M18" s="31">
         <f>IF(B18="","",$B$5)</f>
         <v/>
       </c>
@@ -7426,17 +7479,17 @@
           <t>Week 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>1195</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>59</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>IF(B19="","",C19/B19)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",SQRT($B$5/B19))</f>
         <v/>
       </c>
@@ -7452,15 +7505,15 @@
         <f>IF(D19="","",IF(OR(D19&gt;K19,D19&lt;L19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="31">
         <f>IF(B19="","",$B$5+3*E19*$B$7)</f>
         <v/>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="31">
         <f>IF(B19="","",MAX(0,$B$5-3*E19*$B$7))</f>
         <v/>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="31">
         <f>IF(B19="","",$B$5)</f>
         <v/>
       </c>
@@ -7482,17 +7535,17 @@
           <t>Week 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>1360</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>IF(B20="","",C20/B20)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",SQRT($B$5/B20))</f>
         <v/>
       </c>
@@ -7508,15 +7561,15 @@
         <f>IF(D20="","",IF(OR(D20&gt;K20,D20&lt;L20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K20" s="30">
+      <c r="K20" s="31">
         <f>IF(B20="","",$B$5+3*E20*$B$7)</f>
         <v/>
       </c>
-      <c r="L20" s="30">
+      <c r="L20" s="31">
         <f>IF(B20="","",MAX(0,$B$5-3*E20*$B$7))</f>
         <v/>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="31">
         <f>IF(B20="","",$B$5)</f>
         <v/>
       </c>
@@ -7538,17 +7591,17 @@
           <t>Week 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>1230</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>69</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>IF(B21="","",C21/B21)</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",SQRT($B$5/B21))</f>
         <v/>
       </c>
@@ -7564,15 +7617,15 @@
         <f>IF(D21="","",IF(OR(D21&gt;K21,D21&lt;L21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <f>IF(B21="","",$B$5+3*E21*$B$7)</f>
         <v/>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="31">
         <f>IF(B21="","",MAX(0,$B$5-3*E21*$B$7))</f>
         <v/>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="31">
         <f>IF(B21="","",$B$5)</f>
         <v/>
       </c>
@@ -7588,23 +7641,23 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="77" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Week 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>1405</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>IF(B22="","",C22/B22)</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",SQRT($B$5/B22))</f>
         <v/>
       </c>
@@ -7620,20 +7673,23 @@
         <f>IF(D22="","",IF(OR(D22&gt;K22,D22&lt;L22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="31">
         <f>IF(B22="","",$B$5+3*E22*$B$7)</f>
         <v/>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="31">
         <f>IF(B22="","",MAX(0,$B$5-3*E22*$B$7))</f>
         <v/>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="31">
         <f>IF(B22="","",$B$5)</f>
         <v/>
       </c>
-      <c r="T22" s="21" t="n">
-        <v>9</v>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Defects per unit audited, not the share of units with a defect — one contact can carry several. Same correction as the p′ chart and for the same reason: audit rates move more between weeks than sampling alone explains, and without it the chart cries wolf on the quiet weeks.
+SO:  A rate that trebles is a special cause: audit those weeks' contacts rather than re-training the team. And if sigma z is well above 1, say so when you report — the limits are wider than a plain chart would have drawn and that is the honest picture.</t>
+        </is>
       </c>
       <c r="AD22" s="21">
         <f>IF($D22="",NA(),IF(OR($D22&gt;$K22,$D22&lt;$L22),$D22,NA()))</f>
@@ -7650,17 +7706,17 @@
           <t>Week 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>1150</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>54</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>IF(B23="","",C23/B23)</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",SQRT($B$5/B23))</f>
         <v/>
       </c>
@@ -7676,15 +7732,15 @@
         <f>IF(D23="","",IF(OR(D23&gt;K23,D23&lt;L23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K23" s="30">
+      <c r="K23" s="31">
         <f>IF(B23="","",$B$5+3*E23*$B$7)</f>
         <v/>
       </c>
-      <c r="L23" s="30">
+      <c r="L23" s="31">
         <f>IF(B23="","",MAX(0,$B$5-3*E23*$B$7))</f>
         <v/>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="31">
         <f>IF(B23="","",$B$5)</f>
         <v/>
       </c>
@@ -7706,17 +7762,17 @@
           <t>Week 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>1290</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <f>IF(B24="","",C24/B24)</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",SQRT($B$5/B24))</f>
         <v/>
       </c>
@@ -7732,15 +7788,15 @@
         <f>IF(D24="","",IF(OR(D24&gt;K24,D24&lt;L24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="31">
         <f>IF(B24="","",$B$5+3*E24*$B$7)</f>
         <v/>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <f>IF(B24="","",MAX(0,$B$5-3*E24*$B$7))</f>
         <v/>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="31">
         <f>IF(B24="","",$B$5)</f>
         <v/>
       </c>
@@ -7762,17 +7818,17 @@
           <t>Week 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>1375</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>74</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="28">
         <f>IF(B25="","",C25/B25)</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",SQRT($B$5/B25))</f>
         <v/>
       </c>
@@ -7788,15 +7844,15 @@
         <f>IF(D25="","",IF(OR(D25&gt;K25,D25&lt;L25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <f>IF(B25="","",$B$5+3*E25*$B$7)</f>
         <v/>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="31">
         <f>IF(B25="","",MAX(0,$B$5-3*E25*$B$7))</f>
         <v/>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="31">
         <f>IF(B25="","",$B$5)</f>
         <v/>
       </c>
@@ -7818,17 +7874,17 @@
           <t>Week 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>1215</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <v>39</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>IF(B26="","",C26/B26)</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",SQRT($B$5/B26))</f>
         <v/>
       </c>
@@ -7844,15 +7900,15 @@
         <f>IF(D26="","",IF(OR(D26&gt;K26,D26&lt;L26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="31">
         <f>IF(B26="","",$B$5+3*E26*$B$7)</f>
         <v/>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="31">
         <f>IF(B26="","",MAX(0,$B$5-3*E26*$B$7))</f>
         <v/>
       </c>
-      <c r="M26" s="30">
+      <c r="M26" s="31">
         <f>IF(B26="","",$B$5)</f>
         <v/>
       </c>
@@ -7874,17 +7930,17 @@
           <t>Week 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>1330</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>66</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IF(B27="","",C27/B27)</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",SQRT($B$5/B27))</f>
         <v/>
       </c>
@@ -7900,15 +7956,15 @@
         <f>IF(D27="","",IF(OR(D27&gt;K27,D27&lt;L27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="31">
         <f>IF(B27="","",$B$5+3*E27*$B$7)</f>
         <v/>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="31">
         <f>IF(B27="","",MAX(0,$B$5-3*E27*$B$7))</f>
         <v/>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="31">
         <f>IF(B27="","",$B$5)</f>
         <v/>
       </c>
@@ -7930,17 +7986,17 @@
           <t>Week 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>1185</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>41</v>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>IF(B28="","",C28/B28)</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",SQRT($B$5/B28))</f>
         <v/>
       </c>
@@ -7956,15 +8012,15 @@
         <f>IF(D28="","",IF(OR(D28&gt;K28,D28&lt;L28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="31">
         <f>IF(B28="","",$B$5+3*E28*$B$7)</f>
         <v/>
       </c>
-      <c r="L28" s="30">
+      <c r="L28" s="31">
         <f>IF(B28="","",MAX(0,$B$5-3*E28*$B$7))</f>
         <v/>
       </c>
-      <c r="M28" s="30">
+      <c r="M28" s="31">
         <f>IF(B28="","",$B$5)</f>
         <v/>
       </c>
@@ -7986,17 +8042,17 @@
           <t>Week 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>1265</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>72</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>IF(B29="","",C29/B29)</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",SQRT($B$5/B29))</f>
         <v/>
       </c>
@@ -8012,15 +8068,15 @@
         <f>IF(D29="","",IF(OR(D29&gt;K29,D29&lt;L29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K29" s="30">
+      <c r="K29" s="31">
         <f>IF(B29="","",$B$5+3*E29*$B$7)</f>
         <v/>
       </c>
-      <c r="L29" s="30">
+      <c r="L29" s="31">
         <f>IF(B29="","",MAX(0,$B$5-3*E29*$B$7))</f>
         <v/>
       </c>
-      <c r="M29" s="30">
+      <c r="M29" s="31">
         <f>IF(B29="","",$B$5)</f>
         <v/>
       </c>
@@ -8042,17 +8098,17 @@
           <t>Week 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>1440</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(B30="","",C30/B30)</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",SQRT($B$5/B30))</f>
         <v/>
       </c>
@@ -8068,15 +8124,15 @@
         <f>IF(D30="","",IF(OR(D30&gt;K30,D30&lt;L30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K30" s="30">
+      <c r="K30" s="31">
         <f>IF(B30="","",$B$5+3*E30*$B$7)</f>
         <v/>
       </c>
-      <c r="L30" s="30">
+      <c r="L30" s="31">
         <f>IF(B30="","",MAX(0,$B$5-3*E30*$B$7))</f>
         <v/>
       </c>
-      <c r="M30" s="30">
+      <c r="M30" s="31">
         <f>IF(B30="","",$B$5)</f>
         <v/>
       </c>
@@ -8098,17 +8154,17 @@
           <t>Week 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <v>1205</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <v>54</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IF(B31="","",C31/B31)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",SQRT($B$5/B31))</f>
         <v/>
       </c>
@@ -8124,15 +8180,15 @@
         <f>IF(D31="","",IF(OR(D31&gt;K31,D31&lt;L31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K31" s="30">
+      <c r="K31" s="31">
         <f>IF(B31="","",$B$5+3*E31*$B$7)</f>
         <v/>
       </c>
-      <c r="L31" s="30">
+      <c r="L31" s="31">
         <f>IF(B31="","",MAX(0,$B$5-3*E31*$B$7))</f>
         <v/>
       </c>
-      <c r="M31" s="30">
+      <c r="M31" s="31">
         <f>IF(B31="","",$B$5)</f>
         <v/>
       </c>
@@ -8154,17 +8210,17 @@
           <t>Week 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>1300</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IF(B32="","",C32/B32)</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",SQRT($B$5/B32))</f>
         <v/>
       </c>
@@ -8180,15 +8236,15 @@
         <f>IF(D32="","",IF(OR(D32&gt;K32,D32&lt;L32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K32" s="30">
+      <c r="K32" s="31">
         <f>IF(B32="","",$B$5+3*E32*$B$7)</f>
         <v/>
       </c>
-      <c r="L32" s="30">
+      <c r="L32" s="31">
         <f>IF(B32="","",MAX(0,$B$5-3*E32*$B$7))</f>
         <v/>
       </c>
-      <c r="M32" s="30">
+      <c r="M32" s="31">
         <f>IF(B32="","",$B$5)</f>
         <v/>
       </c>
@@ -8210,17 +8266,17 @@
           <t>Week 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>1355</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
         <v>72</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IF(B33="","",C33/B33)</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",SQRT($B$5/B33))</f>
         <v/>
       </c>
@@ -8236,15 +8292,15 @@
         <f>IF(D33="","",IF(OR(D33&gt;K33,D33&lt;L33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K33" s="30">
+      <c r="K33" s="31">
         <f>IF(B33="","",$B$5+3*E33*$B$7)</f>
         <v/>
       </c>
-      <c r="L33" s="30">
+      <c r="L33" s="31">
         <f>IF(B33="","",MAX(0,$B$5-3*E33*$B$7))</f>
         <v/>
       </c>
-      <c r="M33" s="30">
+      <c r="M33" s="31">
         <f>IF(B33="","",$B$5)</f>
         <v/>
       </c>
@@ -8266,17 +8322,17 @@
           <t>Week 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <v>1170</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <v>43</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IF(B34="","",C34/B34)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",SQRT($B$5/B34))</f>
         <v/>
       </c>
@@ -8292,15 +8348,15 @@
         <f>IF(D34="","",IF(OR(D34&gt;K34,D34&lt;L34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K34" s="30">
+      <c r="K34" s="31">
         <f>IF(B34="","",$B$5+3*E34*$B$7)</f>
         <v/>
       </c>
-      <c r="L34" s="30">
+      <c r="L34" s="31">
         <f>IF(B34="","",MAX(0,$B$5-3*E34*$B$7))</f>
         <v/>
       </c>
-      <c r="M34" s="30">
+      <c r="M34" s="31">
         <f>IF(B34="","",$B$5)</f>
         <v/>
       </c>
@@ -8322,17 +8378,17 @@
           <t>Week 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>1285</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="27" t="n">
         <v>62</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(B35="","",C35/B35)</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",SQRT($B$5/B35))</f>
         <v/>
       </c>
@@ -8348,15 +8404,15 @@
         <f>IF(D35="","",IF(OR(D35&gt;K35,D35&lt;L35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K35" s="30">
+      <c r="K35" s="31">
         <f>IF(B35="","",$B$5+3*E35*$B$7)</f>
         <v/>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="31">
         <f>IF(B35="","",MAX(0,$B$5-3*E35*$B$7))</f>
         <v/>
       </c>
-      <c r="M35" s="30">
+      <c r="M35" s="31">
         <f>IF(B35="","",$B$5)</f>
         <v/>
       </c>
@@ -8378,17 +8434,17 @@
           <t>Week 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>1225</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="27" t="n">
         <v>119</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="28">
         <f>IF(B36="","",C36/B36)</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",SQRT($B$5/B36))</f>
         <v/>
       </c>
@@ -8404,15 +8460,15 @@
         <f>IF(D36="","",IF(OR(D36&gt;K36,D36&lt;L36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K36" s="30">
+      <c r="K36" s="31">
         <f>IF(B36="","",$B$5+3*E36*$B$7)</f>
         <v/>
       </c>
-      <c r="L36" s="30">
+      <c r="L36" s="31">
         <f>IF(B36="","",MAX(0,$B$5-3*E36*$B$7))</f>
         <v/>
       </c>
-      <c r="M36" s="30">
+      <c r="M36" s="31">
         <f>IF(B36="","",$B$5)</f>
         <v/>
       </c>
@@ -8434,17 +8490,17 @@
           <t>Week 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <v>1390</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="27" t="n">
         <v>132</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="28">
         <f>IF(B37="","",C37/B37)</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",SQRT($B$5/B37))</f>
         <v/>
       </c>
@@ -8460,15 +8516,15 @@
         <f>IF(D37="","",IF(OR(D37&gt;K37,D37&lt;L37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="K37" s="30">
+      <c r="K37" s="31">
         <f>IF(B37="","",$B$5+3*E37*$B$7)</f>
         <v/>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="31">
         <f>IF(B37="","",MAX(0,$B$5-3*E37*$B$7))</f>
         <v/>
       </c>
-      <c r="M37" s="30">
+      <c r="M37" s="31">
         <f>IF(B37="","",$B$5)</f>
         <v/>
       </c>
@@ -8485,13 +8541,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:I7"/>
+    <mergeCell ref="O22:W22"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="C5:I5"/>
@@ -8509,7 +8566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AF39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8524,7 +8581,15 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
     <col width="4" customWidth="1" min="30" max="30"/>
     <col width="4" customWidth="1" min="31" max="31"/>
     <col width="4" customWidth="1" min="32" max="32"/>
@@ -8646,7 +8711,7 @@
           <t>A2 for this n</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{1.880;1.023;0.729;0.577;0.483;0.419;0.373;0.337;0.308}),"n out of range")</f>
         <v/>
       </c>
@@ -8662,7 +8727,7 @@
           <t>D4 for this n</t>
         </is>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{3.267;2.574;2.282;2.114;2.004;1.924;1.864;1.816;1.777}),"n out of range")</f>
         <v/>
       </c>
@@ -8678,7 +8743,7 @@
           <t>D3 for this n</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="24">
         <f>IFERROR(LOOKUP(B5,{2;3;4;5;6;7;8;9;10},{0;0;0;0;0;0.076;0.136;0.184;0.223}),"n out of range")</f>
         <v/>
       </c>
@@ -8694,7 +8759,7 @@
           <t>Xbar UCL / LCL</t>
         </is>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <f>TEXT(B6+B8*B7,"#,##0.00")&amp;"  /  "&amp;TEXT(B6-B8*B7,"#,##0.00")</f>
         <v/>
       </c>
@@ -8813,19 +8878,19 @@
           <t>Day 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>446</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <v>410</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="27" t="n">
         <v>407</v>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="27" t="n">
         <v>399</v>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="27" t="n">
         <v>400</v>
       </c>
       <c r="G14" s="17">
@@ -8852,15 +8917,15 @@
         <f>IF(G14="","",IF(OR(G14&gt;J14,G14&lt;K14),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="32">
         <f>IF(H14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O14" s="31">
+      <c r="O14" s="32">
         <f>IF(H14="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P14" s="31">
+      <c r="P14" s="32">
         <f>IF(H14="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -8886,19 +8951,19 @@
           <t>Day 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>428</v>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="27" t="n">
         <v>399</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="27" t="n">
         <v>370</v>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="27" t="n">
         <v>401</v>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="27" t="n">
         <v>432</v>
       </c>
       <c r="G15" s="17">
@@ -8925,15 +8990,15 @@
         <f>IF(G15="","",IF(OR(G15&gt;J15,G15&lt;K15),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N15" s="31">
+      <c r="N15" s="32">
         <f>IF(H15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O15" s="31">
+      <c r="O15" s="32">
         <f>IF(H15="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P15" s="31">
+      <c r="P15" s="32">
         <f>IF(H15="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -8959,19 +9024,19 @@
           <t>Day 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>414</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>421</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="27" t="n">
         <v>423</v>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="27" t="n">
         <v>416</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="27" t="n">
         <v>391</v>
       </c>
       <c r="G16" s="17">
@@ -8998,15 +9063,15 @@
         <f>IF(G16="","",IF(OR(G16&gt;J16,G16&lt;K16),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N16" s="31">
+      <c r="N16" s="32">
         <f>IF(H16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O16" s="31">
+      <c r="O16" s="32">
         <f>IF(H16="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P16" s="31">
+      <c r="P16" s="32">
         <f>IF(H16="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9032,19 +9097,19 @@
           <t>Day 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>442</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>441</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="27" t="n">
         <v>393</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="27" t="n">
         <v>410</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="27" t="n">
         <v>429</v>
       </c>
       <c r="G17" s="17">
@@ -9071,15 +9136,15 @@
         <f>IF(G17="","",IF(OR(G17&gt;J17,G17&lt;K17),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N17" s="31">
+      <c r="N17" s="32">
         <f>IF(H17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O17" s="31">
+      <c r="O17" s="32">
         <f>IF(H17="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P17" s="31">
+      <c r="P17" s="32">
         <f>IF(H17="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9105,19 +9170,19 @@
           <t>Day 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>407</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="27" t="n">
         <v>409</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="27" t="n">
         <v>391</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="27" t="n">
         <v>419</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="27" t="n">
         <v>403</v>
       </c>
       <c r="G18" s="17">
@@ -9144,15 +9209,15 @@
         <f>IF(G18="","",IF(OR(G18&gt;J18,G18&lt;K18),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N18" s="31">
+      <c r="N18" s="32">
         <f>IF(H18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O18" s="31">
+      <c r="O18" s="32">
         <f>IF(H18="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P18" s="31">
+      <c r="P18" s="32">
         <f>IF(H18="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9178,19 +9243,19 @@
           <t>Day 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>415</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>429</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="27" t="n">
         <v>421</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="27" t="n">
         <v>407</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="27" t="n">
         <v>389</v>
       </c>
       <c r="G19" s="17">
@@ -9217,15 +9282,15 @@
         <f>IF(G19="","",IF(OR(G19&gt;J19,G19&lt;K19),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N19" s="31">
+      <c r="N19" s="32">
         <f>IF(H19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O19" s="31">
+      <c r="O19" s="32">
         <f>IF(H19="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P19" s="31">
+      <c r="P19" s="32">
         <f>IF(H19="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9251,19 +9316,19 @@
           <t>Day 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>415</v>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>418</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="27" t="n">
         <v>421</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="27" t="n">
         <v>428</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="27" t="n">
         <v>426</v>
       </c>
       <c r="G20" s="17">
@@ -9290,15 +9355,15 @@
         <f>IF(G20="","",IF(OR(G20&gt;J20,G20&lt;K20),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N20" s="31">
+      <c r="N20" s="32">
         <f>IF(H20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O20" s="31">
+      <c r="O20" s="32">
         <f>IF(H20="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P20" s="31">
+      <c r="P20" s="32">
         <f>IF(H20="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9324,19 +9389,19 @@
           <t>Day 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>414</v>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>385</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="27" t="n">
         <v>404</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="27" t="n">
         <v>389</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="27" t="n">
         <v>416</v>
       </c>
       <c r="G21" s="17">
@@ -9363,15 +9428,15 @@
         <f>IF(G21="","",IF(OR(G21&gt;J21,G21&lt;K21),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="32">
         <f>IF(H21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="32">
         <f>IF(H21="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="32">
         <f>IF(H21="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9397,19 +9462,19 @@
           <t>Day 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="C22" s="26" t="n">
+      <c r="C22" s="27" t="n">
         <v>404</v>
       </c>
-      <c r="D22" s="26" t="n">
+      <c r="D22" s="27" t="n">
         <v>406</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="27" t="n">
         <v>392</v>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="27" t="n">
         <v>434</v>
       </c>
       <c r="G22" s="17">
@@ -9436,15 +9501,15 @@
         <f>IF(G22="","",IF(OR(G22&gt;J22,G22&lt;K22),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="32">
         <f>IF(H22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="32">
         <f>IF(H22="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <f>IF(H22="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9470,19 +9535,19 @@
           <t>Day 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>419</v>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="27" t="n">
         <v>399</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="27" t="n">
         <v>433</v>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="27" t="n">
         <v>405</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="27" t="n">
         <v>376</v>
       </c>
       <c r="G23" s="17">
@@ -9509,15 +9574,15 @@
         <f>IF(G23="","",IF(OR(G23&gt;J23,G23&lt;K23),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N23" s="31">
+      <c r="N23" s="32">
         <f>IF(H23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O23" s="31">
+      <c r="O23" s="32">
         <f>IF(H23="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P23" s="31">
+      <c r="P23" s="32">
         <f>IF(H23="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9543,19 +9608,19 @@
           <t>Day 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>394</v>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="27" t="n">
         <v>399</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="27" t="n">
         <v>398</v>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="27" t="n">
         <v>380</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="27" t="n">
         <v>414</v>
       </c>
       <c r="G24" s="17">
@@ -9582,15 +9647,15 @@
         <f>IF(G24="","",IF(OR(G24&gt;J24,G24&lt;K24),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="32">
         <f>IF(H24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="32">
         <f>IF(H24="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="32">
         <f>IF(H24="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9616,19 +9681,19 @@
           <t>Day 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>397</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <v>401</v>
       </c>
-      <c r="D25" s="26" t="n">
+      <c r="D25" s="27" t="n">
         <v>424</v>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="27" t="n">
         <v>403</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="27" t="n">
         <v>429</v>
       </c>
       <c r="G25" s="17">
@@ -9655,15 +9720,15 @@
         <f>IF(G25="","",IF(OR(G25&gt;J25,G25&lt;K25),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="32">
         <f>IF(H25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="32">
         <f>IF(H25="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="32">
         <f>IF(H25="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9689,19 +9754,19 @@
           <t>Day 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>392</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="27" t="n">
         <v>379</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="27" t="n">
         <v>406</v>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="27" t="n">
         <v>404</v>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="27" t="n">
         <v>396</v>
       </c>
       <c r="G26" s="17">
@@ -9728,15 +9793,15 @@
         <f>IF(G26="","",IF(OR(G26&gt;J26,G26&lt;K26),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N26" s="31">
+      <c r="N26" s="32">
         <f>IF(H26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O26" s="31">
+      <c r="O26" s="32">
         <f>IF(H26="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P26" s="31">
+      <c r="P26" s="32">
         <f>IF(H26="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9762,19 +9827,19 @@
           <t>Day 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>408</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <v>392</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="27" t="n">
         <v>420</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="27" t="n">
         <v>390</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="27" t="n">
         <v>394</v>
       </c>
       <c r="G27" s="17">
@@ -9801,15 +9866,15 @@
         <f>IF(G27="","",IF(OR(G27&gt;J27,G27&lt;K27),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <f>IF(H27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <f>IF(H27="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <f>IF(H27="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9835,19 +9900,19 @@
           <t>Day 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>415</v>
       </c>
-      <c r="C28" s="26" t="n">
+      <c r="C28" s="27" t="n">
         <v>383</v>
       </c>
-      <c r="D28" s="26" t="n">
+      <c r="D28" s="27" t="n">
         <v>411</v>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="27" t="n">
         <v>403</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="27" t="n">
         <v>407</v>
       </c>
       <c r="G28" s="17">
@@ -9874,15 +9939,15 @@
         <f>IF(G28="","",IF(OR(G28&gt;J28,G28&lt;K28),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="32">
         <f>IF(H28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="32">
         <f>IF(H28="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="32">
         <f>IF(H28="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9908,19 +9973,19 @@
           <t>Day 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>399</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>415</v>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D29" s="27" t="n">
         <v>400</v>
       </c>
-      <c r="E29" s="26" t="n">
+      <c r="E29" s="27" t="n">
         <v>452</v>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="27" t="n">
         <v>406</v>
       </c>
       <c r="G29" s="17">
@@ -9947,15 +10012,15 @@
         <f>IF(G29="","",IF(OR(G29&gt;J29,G29&lt;K29),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N29" s="31">
+      <c r="N29" s="32">
         <f>IF(H29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O29" s="31">
+      <c r="O29" s="32">
         <f>IF(H29="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P29" s="31">
+      <c r="P29" s="32">
         <f>IF(H29="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -9981,19 +10046,19 @@
           <t>Day 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>425</v>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="27" t="n">
         <v>419</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="27" t="n">
         <v>418</v>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="27" t="n">
         <v>407</v>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="27" t="n">
         <v>411</v>
       </c>
       <c r="G30" s="17">
@@ -10020,15 +10085,15 @@
         <f>IF(G30="","",IF(OR(G30&gt;J30,G30&lt;K30),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N30" s="31">
+      <c r="N30" s="32">
         <f>IF(H30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O30" s="31">
+      <c r="O30" s="32">
         <f>IF(H30="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P30" s="31">
+      <c r="P30" s="32">
         <f>IF(H30="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10054,19 +10119,19 @@
           <t>Day 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <v>397</v>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="27" t="n">
         <v>383</v>
       </c>
-      <c r="D31" s="26" t="n">
+      <c r="D31" s="27" t="n">
         <v>403</v>
       </c>
-      <c r="E31" s="26" t="n">
+      <c r="E31" s="27" t="n">
         <v>413</v>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="27" t="n">
         <v>401</v>
       </c>
       <c r="G31" s="17">
@@ -10093,15 +10158,15 @@
         <f>IF(G31="","",IF(OR(G31&gt;J31,G31&lt;K31),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N31" s="31">
+      <c r="N31" s="32">
         <f>IF(H31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O31" s="31">
+      <c r="O31" s="32">
         <f>IF(H31="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P31" s="31">
+      <c r="P31" s="32">
         <f>IF(H31="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10127,19 +10192,19 @@
           <t>Day 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>420</v>
       </c>
-      <c r="C32" s="26" t="n">
+      <c r="C32" s="27" t="n">
         <v>414</v>
       </c>
-      <c r="D32" s="26" t="n">
+      <c r="D32" s="27" t="n">
         <v>391</v>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="27" t="n">
         <v>417</v>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="27" t="n">
         <v>383</v>
       </c>
       <c r="G32" s="17">
@@ -10166,15 +10231,15 @@
         <f>IF(G32="","",IF(OR(G32&gt;J32,G32&lt;K32),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N32" s="31">
+      <c r="N32" s="32">
         <f>IF(H32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O32" s="31">
+      <c r="O32" s="32">
         <f>IF(H32="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P32" s="31">
+      <c r="P32" s="32">
         <f>IF(H32="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10200,19 +10265,19 @@
           <t>Day 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>424</v>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="27" t="n">
         <v>416</v>
       </c>
-      <c r="D33" s="26" t="n">
+      <c r="D33" s="27" t="n">
         <v>402</v>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="E33" s="27" t="n">
         <v>386</v>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="27" t="n">
         <v>436</v>
       </c>
       <c r="G33" s="17">
@@ -10239,15 +10304,15 @@
         <f>IF(G33="","",IF(OR(G33&gt;J33,G33&lt;K33),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N33" s="31">
+      <c r="N33" s="32">
         <f>IF(H33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O33" s="31">
+      <c r="O33" s="32">
         <f>IF(H33="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P33" s="31">
+      <c r="P33" s="32">
         <f>IF(H33="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10273,19 +10338,19 @@
           <t>Day 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <v>459</v>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="27" t="n">
         <v>437</v>
       </c>
-      <c r="D34" s="26" t="n">
+      <c r="D34" s="27" t="n">
         <v>461</v>
       </c>
-      <c r="E34" s="26" t="n">
+      <c r="E34" s="27" t="n">
         <v>443</v>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="27" t="n">
         <v>433</v>
       </c>
       <c r="G34" s="17">
@@ -10312,15 +10377,15 @@
         <f>IF(G34="","",IF(OR(G34&gt;J34,G34&lt;K34),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N34" s="31">
+      <c r="N34" s="32">
         <f>IF(H34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O34" s="31">
+      <c r="O34" s="32">
         <f>IF(H34="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P34" s="31">
+      <c r="P34" s="32">
         <f>IF(H34="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10346,19 +10411,19 @@
           <t>Day 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>448</v>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="27" t="n">
         <v>463</v>
       </c>
-      <c r="D35" s="26" t="n">
+      <c r="D35" s="27" t="n">
         <v>458</v>
       </c>
-      <c r="E35" s="26" t="n">
+      <c r="E35" s="27" t="n">
         <v>417</v>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="27" t="n">
         <v>428</v>
       </c>
       <c r="G35" s="17">
@@ -10385,15 +10450,15 @@
         <f>IF(G35="","",IF(OR(G35&gt;J35,G35&lt;K35),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N35" s="31">
+      <c r="N35" s="32">
         <f>IF(H35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O35" s="31">
+      <c r="O35" s="32">
         <f>IF(H35="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P35" s="31">
+      <c r="P35" s="32">
         <f>IF(H35="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10419,19 +10484,19 @@
           <t>Day 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>459</v>
       </c>
-      <c r="C36" s="26" t="n">
+      <c r="C36" s="27" t="n">
         <v>448</v>
       </c>
-      <c r="D36" s="26" t="n">
+      <c r="D36" s="27" t="n">
         <v>447</v>
       </c>
-      <c r="E36" s="26" t="n">
+      <c r="E36" s="27" t="n">
         <v>429</v>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="27" t="n">
         <v>442</v>
       </c>
       <c r="G36" s="17">
@@ -10458,15 +10523,15 @@
         <f>IF(G36="","",IF(OR(G36&gt;J36,G36&lt;K36),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N36" s="31">
+      <c r="N36" s="32">
         <f>IF(H36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O36" s="31">
+      <c r="O36" s="32">
         <f>IF(H36="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P36" s="31">
+      <c r="P36" s="32">
         <f>IF(H36="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10492,19 +10557,19 @@
           <t>Day 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <v>433</v>
       </c>
-      <c r="C37" s="26" t="n">
+      <c r="C37" s="27" t="n">
         <v>429</v>
       </c>
-      <c r="D37" s="26" t="n">
+      <c r="D37" s="27" t="n">
         <v>452</v>
       </c>
-      <c r="E37" s="26" t="n">
+      <c r="E37" s="27" t="n">
         <v>425</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="27" t="n">
         <v>459</v>
       </c>
       <c r="G37" s="17">
@@ -10531,15 +10596,15 @@
         <f>IF(G37="","",IF(OR(G37&gt;J37,G37&lt;K37),"OUT OF CONTROL",""))</f>
         <v/>
       </c>
-      <c r="N37" s="31">
+      <c r="N37" s="32">
         <f>IF(H37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="O37" s="31">
+      <c r="O37" s="32">
         <f>IF(H37="","",$B$9*$B$7)</f>
         <v/>
       </c>
-      <c r="P37" s="31">
+      <c r="P37" s="32">
         <f>IF(H37="","",$B$10*$B$7)</f>
         <v/>
       </c>
@@ -10559,16 +10624,34 @@
         <v/>
       </c>
     </row>
+    <row r="38" ht="77" customHeight="1">
+      <c r="N38" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Subgroup averages against limits from the baseline window. Read the range chart first: limits here are computed from the within-subgroup spread, so if that is unstable these limits are meaningless. The worked example steps up across the last four subgroups while the range chart stays put.
+SO:  The last four subgroups sit above the limit with the range chart calm, so the average has shifted while the spread has not. Date the shift against your change log and confirm the cause before adjusting anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="77" customHeight="1">
+      <c r="N39" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Within-subgroup range, and the title is the instruction. This chart supplies the sigma the Xbar chart's limits are built from, so an out-of-control range invalidates the chart above it. Settle the spread, then read the average.
+SO:  If this chart signals, stop — fix the spread and recompute the limits before reading the Xbar chart at all. Acting on an Xbar chart built from an unstable range is the most common way a control chart sends a team after the wrong thing.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="N38:V38"/>
     <mergeCell ref="C8:L8"/>
     <mergeCell ref="C9:L9"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C3:L3"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C7:L7"/>
+    <mergeCell ref="N39:V39"/>
     <mergeCell ref="C6:L6"/>
     <mergeCell ref="C10:L10"/>
     <mergeCell ref="A12:L12"/>
@@ -10599,6 +10682,15 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="4" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
@@ -10646,7 +10738,7 @@
           <t>Lambda (weight on the newest point)</t>
         </is>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="33" t="n">
         <v>0.2</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -10661,7 +10753,7 @@
           <t>L (limit width in sigmas)</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="34" t="n">
         <v>2.7</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -11012,7 +11104,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Day 7</t>
@@ -11045,6 +11137,12 @@
         <f>IF(D22="","",IF(OR(D22&gt;F22,D22&lt;G22),"SIGNAL — the process has drifted",""))</f>
         <v/>
       </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Each point is a weighted memory of the ones before, so a small sustained shift shows up here long before it breaks an individuals chart. The trade is responsiveness: a single wild point barely moves the line, so run it alongside an I chart rather than instead of one.
+SO:  Treat a sustained EWMA signal as a real drift and go looking, but confirm on an individuals chart before you act on a single point — this chart is deliberately slow to react to one wild value.</t>
+        </is>
+      </c>
       <c r="AD22" s="21">
         <f>IF($D22="",NA(),IF(OR($D22&gt;$F22,$D22&lt;$G22),$D22,NA()))</f>
         <v/>
@@ -11697,12 +11795,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C9:I9"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K22:S22"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="A4:I4"/>
@@ -11733,6 +11832,15 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="4" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
@@ -11780,7 +11888,7 @@
           <t>k (slack, in sigmas)</t>
         </is>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -11795,7 +11903,7 @@
           <t>h (decision interval)</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="34" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -12173,7 +12281,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Day 7</t>
@@ -12210,6 +12318,12 @@
         <f>IF(E22="","",IF(E22&gt;$B$6,"SHIFT UP confirmed",IF(F22&gt;$B$6,"SHIFT DOWN confirmed","")))</f>
         <v/>
       </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  It accumulates departures from target, so the SLOPE is the signal and the height is only history. The value is diagnostic: where the line starts climbing dates the change, which an individuals chart cannot tell you. In the worked example it starts climbing well before any single point looks unusual.
+SO:  Read the date the slope changes, not the height, and go to the change log for that day. This is the chart that tells you WHEN, which is usually the fastest route to what.</t>
+        </is>
+      </c>
       <c r="AD22" s="21">
         <f>IF($E22="",NA(),IF(OR($E22&gt;$B$6,$F22&gt;$B$6),MAX($E22,$F22),NA()))</f>
         <v/>
@@ -12930,12 +13044,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C9:I9"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K22:S22"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="A4:I4"/>
@@ -12954,7 +13069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG37"/>
+  <dimension ref="A1:AG39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -12965,6 +13080,18 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="30" max="30"/>
     <col width="4" customWidth="1" min="31" max="31"/>
     <col width="4" customWidth="1" min="32" max="32"/>
@@ -13045,7 +13172,7 @@
           <t>Transformed mean</t>
         </is>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <f>AVERAGE(C14:C37)</f>
         <v/>
       </c>
@@ -13061,7 +13188,7 @@
           <t>Transformed MR-bar</t>
         </is>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <f>AVERAGE(D15:D37)</f>
         <v/>
       </c>
@@ -13077,7 +13204,7 @@
           <t>t-chart UCL / LCL (days)</t>
         </is>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <f>TEXT((B7+2.66*B8)^3.6,"#,##0.0")&amp;"  /  "&amp;TEXT(MAX(0,(B7-2.66*B8))^3.6,"#,##0.0")</f>
         <v/>
       </c>
@@ -13213,21 +13340,21 @@
           <t>Incident 1</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>IF(B14="","",B14^(1/3.6))</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF(B14="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="27" t="n">
         <v>12800</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="35">
         <f>IF(F14="","",$B$10)</f>
         <v/>
       </c>
@@ -13235,23 +13362,23 @@
         <f>IF(B14="","",IF(C14&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C14&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="36">
         <f>IF(B14="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K14" s="35">
+      <c r="K14" s="36">
         <f>IF(B14="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L14" s="35">
+      <c r="L14" s="36">
         <f>IF(B14="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M14" s="36">
+      <c r="M14" s="37">
         <f>IF(F14="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="37">
         <f>IF(F14="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13278,25 +13405,25 @@
           <t>Incident 2</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="28">
         <f>IF(B15="","",B15^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="28">
         <f>IF(COUNT(C14:C15)=2,ABS(C15-C14),"")</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="28">
         <f>IF(B15="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F15" s="26" t="n">
+      <c r="F15" s="27" t="n">
         <v>8400</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="35">
         <f>IF(F15="","",$B$10)</f>
         <v/>
       </c>
@@ -13304,23 +13431,23 @@
         <f>IF(B15="","",IF(C15&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C15&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="36">
         <f>IF(B15="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K15" s="35">
+      <c r="K15" s="36">
         <f>IF(B15="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L15" s="35">
+      <c r="L15" s="36">
         <f>IF(B15="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M15" s="36">
+      <c r="M15" s="37">
         <f>IF(F15="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N15" s="36">
+      <c r="N15" s="37">
         <f>IF(F15="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13347,25 +13474,25 @@
           <t>Incident 3</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>IF(B16="","",B16^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>IF(COUNT(C15:C16)=2,ABS(C16-C15),"")</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>IF(B16="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="27" t="n">
         <v>21600</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="35">
         <f>IF(F16="","",$B$10)</f>
         <v/>
       </c>
@@ -13373,23 +13500,23 @@
         <f>IF(B16="","",IF(C16&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C16&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="36">
         <f>IF(B16="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K16" s="35">
+      <c r="K16" s="36">
         <f>IF(B16="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L16" s="35">
+      <c r="L16" s="36">
         <f>IF(B16="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M16" s="36">
+      <c r="M16" s="37">
         <f>IF(F16="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N16" s="36">
+      <c r="N16" s="37">
         <f>IF(F16="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13416,25 +13543,25 @@
           <t>Incident 4</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>IF(B17="","",B17^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>IF(COUNT(C16:C17)=2,ABS(C17-C16),"")</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>IF(B17="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="27" t="n">
         <v>29800</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="35">
         <f>IF(F17="","",$B$10)</f>
         <v/>
       </c>
@@ -13442,23 +13569,23 @@
         <f>IF(B17="","",IF(C17&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C17&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="36">
         <f>IF(B17="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K17" s="35">
+      <c r="K17" s="36">
         <f>IF(B17="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L17" s="35">
+      <c r="L17" s="36">
         <f>IF(B17="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M17" s="36">
+      <c r="M17" s="37">
         <f>IF(F17="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N17" s="36">
+      <c r="N17" s="37">
         <f>IF(F17="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13485,25 +13612,25 @@
           <t>Incident 5</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>IF(B18="","",B18^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>IF(COUNT(C17:C18)=2,ABS(C18-C17),"")</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>IF(B18="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="27" t="n">
         <v>17400</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="35">
         <f>IF(F18="","",$B$10)</f>
         <v/>
       </c>
@@ -13511,23 +13638,23 @@
         <f>IF(B18="","",IF(C18&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C18&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="36">
         <f>IF(B18="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="36">
         <f>IF(B18="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L18" s="35">
+      <c r="L18" s="36">
         <f>IF(B18="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M18" s="36">
+      <c r="M18" s="37">
         <f>IF(F18="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N18" s="36">
+      <c r="N18" s="37">
         <f>IF(F18="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13554,25 +13681,25 @@
           <t>Incident 6</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <v>27</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>IF(B19="","",B19^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>IF(COUNT(C18:C19)=2,ABS(C19-C18),"")</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>IF(B19="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="27" t="n">
         <v>26100</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="35">
         <f>IF(F19="","",$B$10)</f>
         <v/>
       </c>
@@ -13580,23 +13707,23 @@
         <f>IF(B19="","",IF(C19&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C19&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="36">
         <f>IF(B19="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K19" s="35">
+      <c r="K19" s="36">
         <f>IF(B19="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L19" s="35">
+      <c r="L19" s="36">
         <f>IF(B19="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M19" s="36">
+      <c r="M19" s="37">
         <f>IF(F19="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N19" s="36">
+      <c r="N19" s="37">
         <f>IF(F19="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13623,25 +13750,25 @@
           <t>Incident 7</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <v>41</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="28">
         <f>IF(B20="","",B20^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>IF(COUNT(C19:C20)=2,ABS(C20-C19),"")</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>IF(B20="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="27" t="n">
         <v>39900</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="35">
         <f>IF(F20="","",$B$10)</f>
         <v/>
       </c>
@@ -13649,23 +13776,23 @@
         <f>IF(B20="","",IF(C20&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C20&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="36">
         <f>IF(B20="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K20" s="35">
+      <c r="K20" s="36">
         <f>IF(B20="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L20" s="35">
+      <c r="L20" s="36">
         <f>IF(B20="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="37">
         <f>IF(F20="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="37">
         <f>IF(F20="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13692,25 +13819,25 @@
           <t>Incident 8</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <f>IF(B21="","",B21^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>IF(COUNT(C20:C21)=2,ABS(C21-C20),"")</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>IF(B21="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="27" t="n">
         <v>11200</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="35">
         <f>IF(F21="","",$B$10)</f>
         <v/>
       </c>
@@ -13718,23 +13845,23 @@
         <f>IF(B21="","",IF(C21&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C21&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="36">
         <f>IF(B21="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="36">
         <f>IF(B21="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L21" s="35">
+      <c r="L21" s="36">
         <f>IF(B21="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M21" s="36">
+      <c r="M21" s="37">
         <f>IF(F21="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N21" s="36">
+      <c r="N21" s="37">
         <f>IF(F21="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13761,25 +13888,25 @@
           <t>Incident 9</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="28">
         <f>IF(B22="","",B22^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="28">
         <f>IF(COUNT(C21:C22)=2,ABS(C22-C21),"")</f>
         <v/>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="28">
         <f>IF(B22="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="27" t="n">
         <v>33500</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="35">
         <f>IF(F22="","",$B$10)</f>
         <v/>
       </c>
@@ -13787,23 +13914,23 @@
         <f>IF(B22="","",IF(C22&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C22&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="36">
         <f>IF(B22="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K22" s="35">
+      <c r="K22" s="36">
         <f>IF(B22="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L22" s="35">
+      <c r="L22" s="36">
         <f>IF(B22="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="37">
         <f>IF(F22="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N22" s="36">
+      <c r="N22" s="37">
         <f>IF(F22="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13830,25 +13957,25 @@
           <t>Incident 10</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="28">
         <f>IF(B23="","",B23^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f>IF(COUNT(C22:C23)=2,ABS(C23-C22),"")</f>
         <v/>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f>IF(B23="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="27" t="n">
         <v>23100</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="35">
         <f>IF(F23="","",$B$10)</f>
         <v/>
       </c>
@@ -13856,23 +13983,23 @@
         <f>IF(B23="","",IF(C23&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C23&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="36">
         <f>IF(B23="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K23" s="35">
+      <c r="K23" s="36">
         <f>IF(B23="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L23" s="35">
+      <c r="L23" s="36">
         <f>IF(B23="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M23" s="36">
+      <c r="M23" s="37">
         <f>IF(F23="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N23" s="36">
+      <c r="N23" s="37">
         <f>IF(F23="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13899,25 +14026,25 @@
           <t>Incident 11</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <v>48</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="28">
         <f>IF(B24="","",B24^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <f>IF(COUNT(C23:C24)=2,ABS(C24-C23),"")</f>
         <v/>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <f>IF(B24="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="27" t="n">
         <v>46800</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="35">
         <f>IF(F24="","",$B$10)</f>
         <v/>
       </c>
@@ -13925,23 +14052,23 @@
         <f>IF(B24="","",IF(C24&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C24&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="36">
         <f>IF(B24="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K24" s="35">
+      <c r="K24" s="36">
         <f>IF(B24="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L24" s="35">
+      <c r="L24" s="36">
         <f>IF(B24="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M24" s="36">
+      <c r="M24" s="37">
         <f>IF(F24="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N24" s="36">
+      <c r="N24" s="37">
         <f>IF(F24="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -13968,25 +14095,25 @@
           <t>Incident 12</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="28">
         <f>IF(B25="","",B25^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="28">
         <f>IF(COUNT(C24:C25)=2,ABS(C25-C24),"")</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="28">
         <f>IF(B25="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="27" t="n">
         <v>18300</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="35">
         <f>IF(F25="","",$B$10)</f>
         <v/>
       </c>
@@ -13994,23 +14121,23 @@
         <f>IF(B25="","",IF(C25&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C25&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="36">
         <f>IF(B25="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K25" s="35">
+      <c r="K25" s="36">
         <f>IF(B25="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L25" s="35">
+      <c r="L25" s="36">
         <f>IF(B25="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M25" s="36">
+      <c r="M25" s="37">
         <f>IF(F25="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N25" s="36">
+      <c r="N25" s="37">
         <f>IF(F25="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14037,25 +14164,25 @@
           <t>Incident 13</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>33</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>IF(B26="","",B26^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>IF(COUNT(C25:C26)=2,ABS(C26-C25),"")</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>IF(B26="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="27" t="n">
         <v>31700</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="35">
         <f>IF(F26="","",$B$10)</f>
         <v/>
       </c>
@@ -14063,23 +14190,23 @@
         <f>IF(B26="","",IF(C26&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C26&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="36">
         <f>IF(B26="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K26" s="35">
+      <c r="K26" s="36">
         <f>IF(B26="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L26" s="35">
+      <c r="L26" s="36">
         <f>IF(B26="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M26" s="36">
+      <c r="M26" s="37">
         <f>IF(F26="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N26" s="36">
+      <c r="N26" s="37">
         <f>IF(F26="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14106,25 +14233,25 @@
           <t>Incident 14</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>IF(B27="","",B27^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IF(COUNT(C26:C27)=2,ABS(C27-C26),"")</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(B27="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="27" t="n">
         <v>25400</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="35">
         <f>IF(F27="","",$B$10)</f>
         <v/>
       </c>
@@ -14132,23 +14259,23 @@
         <f>IF(B27="","",IF(C27&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C27&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="36">
         <f>IF(B27="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="36">
         <f>IF(B27="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="36">
         <f>IF(B27="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M27" s="36">
+      <c r="M27" s="37">
         <f>IF(F27="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N27" s="36">
+      <c r="N27" s="37">
         <f>IF(F27="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14175,25 +14302,25 @@
           <t>Incident 15</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>52</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="28">
         <f>IF(B28="","",B28^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>IF(COUNT(C27:C28)=2,ABS(C28-C27),"")</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>IF(B28="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="27" t="n">
         <v>50600</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="35">
         <f>IF(F28="","",$B$10)</f>
         <v/>
       </c>
@@ -14201,23 +14328,23 @@
         <f>IF(B28="","",IF(C28&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C28&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="36">
         <f>IF(B28="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K28" s="35">
+      <c r="K28" s="36">
         <f>IF(B28="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L28" s="35">
+      <c r="L28" s="36">
         <f>IF(B28="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M28" s="36">
+      <c r="M28" s="37">
         <f>IF(F28="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N28" s="36">
+      <c r="N28" s="37">
         <f>IF(F28="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14244,25 +14371,25 @@
           <t>Incident 16</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="28">
         <f>IF(B29="","",B29^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>IF(COUNT(C28:C29)=2,ABS(C29-C28),"")</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>IF(B29="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="27" t="n">
         <v>20200</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="35">
         <f>IF(F29="","",$B$10)</f>
         <v/>
       </c>
@@ -14270,23 +14397,23 @@
         <f>IF(B29="","",IF(C29&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C29&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="36">
         <f>IF(B29="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="36">
         <f>IF(B29="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="36">
         <f>IF(B29="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M29" s="36">
+      <c r="M29" s="37">
         <f>IF(F29="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N29" s="36">
+      <c r="N29" s="37">
         <f>IF(F29="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14313,25 +14440,25 @@
           <t>Incident 17</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="28">
         <f>IF(B30="","",B30^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>IF(COUNT(C29:C30)=2,ABS(C30-C29),"")</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>IF(B30="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F30" s="26" t="n">
+      <c r="F30" s="27" t="n">
         <v>36900</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <f>IF(F30="","",$B$10)</f>
         <v/>
       </c>
@@ -14339,23 +14466,23 @@
         <f>IF(B30="","",IF(C30&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C30&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="36">
         <f>IF(B30="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="36">
         <f>IF(B30="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="36">
         <f>IF(B30="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="37">
         <f>IF(F30="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <f>IF(F30="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14382,25 +14509,25 @@
           <t>Incident 18</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>IF(B31="","",B31^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>IF(COUNT(C30:C31)=2,ABS(C31-C30),"")</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>IF(B31="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F31" s="26" t="n">
+      <c r="F31" s="27" t="n">
         <v>27800</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <f>IF(F31="","",$B$10)</f>
         <v/>
       </c>
@@ -14408,23 +14535,23 @@
         <f>IF(B31="","",IF(C31&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C31&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="36">
         <f>IF(B31="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="36">
         <f>IF(B31="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="36">
         <f>IF(B31="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="37">
         <f>IF(F31="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="37">
         <f>IF(F31="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14451,25 +14578,25 @@
           <t>Incident 19</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>44</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="28">
         <f>IF(B32="","",B32^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>IF(COUNT(C31:C32)=2,ABS(C32-C31),"")</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>IF(B32="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="27" t="n">
         <v>43100</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="35">
         <f>IF(F32="","",$B$10)</f>
         <v/>
       </c>
@@ -14477,23 +14604,23 @@
         <f>IF(B32="","",IF(C32&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C32&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="36">
         <f>IF(B32="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K32" s="35">
+      <c r="K32" s="36">
         <f>IF(B32="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L32" s="35">
+      <c r="L32" s="36">
         <f>IF(B32="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M32" s="36">
+      <c r="M32" s="37">
         <f>IF(F32="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N32" s="36">
+      <c r="N32" s="37">
         <f>IF(F32="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14520,25 +14647,25 @@
           <t>Incident 20</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="28">
         <f>IF(B33="","",B33^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>IF(COUNT(C32:C33)=2,ABS(C33-C32),"")</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>IF(B33="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="27" t="n">
         <v>34600</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="35">
         <f>IF(F33="","",$B$10)</f>
         <v/>
       </c>
@@ -14546,23 +14673,23 @@
         <f>IF(B33="","",IF(C33&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C33&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <f>IF(B33="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <f>IF(B33="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <f>IF(B33="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="37">
         <f>IF(F33="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="37">
         <f>IF(F33="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14589,25 +14716,25 @@
           <t>Incident 21</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="28">
         <f>IF(B34="","",B34^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>IF(COUNT(C33:C34)=2,ABS(C34-C33),"")</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>IF(B34="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F34" s="26" t="n">
+      <c r="F34" s="27" t="n">
         <v>56900</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <f>IF(F34="","",$B$10)</f>
         <v/>
       </c>
@@ -14615,23 +14742,23 @@
         <f>IF(B34="","",IF(C34&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C34&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="36">
         <f>IF(B34="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="36">
         <f>IF(B34="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="36">
         <f>IF(B34="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M34" s="36">
+      <c r="M34" s="37">
         <f>IF(F34="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N34" s="36">
+      <c r="N34" s="37">
         <f>IF(F34="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14658,25 +14785,25 @@
           <t>Incident 22</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="28">
         <f>IF(B35="","",B35^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>IF(COUNT(C34:C35)=2,ABS(C35-C34),"")</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>IF(B35="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F35" s="26" t="n">
+      <c r="F35" s="27" t="n">
         <v>29900</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="35">
         <f>IF(F35="","",$B$10)</f>
         <v/>
       </c>
@@ -14684,23 +14811,23 @@
         <f>IF(B35="","",IF(C35&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C35&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <f>IF(B35="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <f>IF(B35="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <f>IF(B35="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="37">
         <f>IF(F35="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="37">
         <f>IF(F35="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14727,25 +14854,25 @@
           <t>Incident 23</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>47</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="28">
         <f>IF(B36="","",B36^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="28">
         <f>IF(COUNT(C35:C36)=2,ABS(C36-C35),"")</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>IF(B36="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F36" s="26" t="n">
+      <c r="F36" s="27" t="n">
         <v>45200</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <f>IF(F36="","",$B$10)</f>
         <v/>
       </c>
@@ -14753,23 +14880,23 @@
         <f>IF(B36="","",IF(C36&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C36&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <f>IF(B36="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <f>IF(B36="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <f>IF(B36="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="37">
         <f>IF(F36="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="37">
         <f>IF(F36="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14796,25 +14923,25 @@
           <t>Incident 24</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <v>168</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="28">
         <f>IF(B37="","",B37^(1/3.6))</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="28">
         <f>IF(COUNT(C36:C37)=2,ABS(C37-C36),"")</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>IF(B37="","",$B$7)</f>
         <v/>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="27" t="n">
         <v>161000</v>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="35">
         <f>IF(F37="","",$B$10)</f>
         <v/>
       </c>
@@ -14822,23 +14949,23 @@
         <f>IF(B37="","",IF(C37&gt;$B$7+2.66*$B$8,"Longer gap than expected — improvement",IF(C37&lt;$B$7-2.66*$B$8,"Shorter gap than expected — investigate","")))</f>
         <v/>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="36">
         <f>IF(B37="","",($B$7+2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="K37" s="35">
+      <c r="K37" s="36">
         <f>IF(B37="","",MAX(0,$B$7-2.66*$B$8)^3.6)</f>
         <v/>
       </c>
-      <c r="L37" s="35">
+      <c r="L37" s="36">
         <f>IF(B37="","",$B$7^3.6)</f>
         <v/>
       </c>
-      <c r="M37" s="36">
+      <c r="M37" s="37">
         <f>IF(F37="","",$B$11)</f>
         <v/>
       </c>
-      <c r="N37" s="36">
+      <c r="N37" s="37">
         <f>IF(F37="","",MEDIAN($F$14:$F$37))</f>
         <v/>
       </c>
@@ -14859,13 +14986,31 @@
         <v/>
       </c>
     </row>
+    <row r="38" ht="66" customHeight="1">
+      <c r="N38" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Time between rare events, so up is improvement and the upper limit is the one worth breaking. There is no frozen baseline here — the limits move with the data, so a gap has to be long enough to clear limits it widens itself. Gaps are exponential, not normal, which is why the chart works on a transformed scale.
+SO:  A gap past the upper limit is improvement — find out what changed and write it into the control plan so it survives. Improvement signals get investigated as rarely as they get held on to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="66" customHeight="1">
+      <c r="Q39" s="22" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  The same question counted in contacts rather than days, which is the one to use when volume swings. A rate that looks flat in days can be improving in contacts if you are simply handling more — and the reverse, which is the trap.
+SO:  Use this one when volume is moving. If days-between is flat while contacts-between rises, the process is improving and the calendar is hiding it — report both or you will argue about the wrong number.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C11:H11"/>
+    <mergeCell ref="N38:V38"/>
+    <mergeCell ref="Q39:Y39"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C9:H9"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -3407,137 +3407,173 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Control charts — seven chart types, one workbook</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>Yellow cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Every chart the program's selection table sends you to is built here, on your own numbers, with the control limits written as live formulas so you can see exactly where each line comes from.</t>
+          <t>You fill these in.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>How to use it</t>
+          <t>Blue cells</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Calculated for you. Do not type over them — they contain formulas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Control charts — seven chart types, one workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Every chart the program's selection table sends you to is built here, on your own numbers, with the control limits written as live formulas so you can see exactly where each line comes from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>How to use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>1. Open the 'Pick your chart' tab and find the row that matches the data you have.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
-      <c r="B6" s="2" t="inlineStr">
+    <row r="12" ht="45" customHeight="1">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2. Go to that tab. The green cells are a worked example — 24 periods of real-shaped support data, so the chart and its limits say something the moment you open it. Overwrite them with your own numbers, oldest first. The yellow cell above is a setting you choose, not data.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="2" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>3. The chart, the limits and the signal column update themselves. Nothing else needs touching.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="2" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>4. Blue cells are calculated. Read the formula bar on any of them to see the arithmetic — the constants (1.128, 2.66, 3.267, A2, D3, D4) are all visible, not buried.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="1" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>The two mistakes that kill SPC in a support organisation</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="75" customHeight="1">
-      <c r="B10" s="2" t="inlineStr">
+    <row r="16" ht="75" customHeight="1">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Using an ordinary p-chart on high-volume percentages. At 8,000 contacts a day the binomial limits around a 72% FCR are about plus or minus 1.5 points, while real daily FCR swings 4 points from contact mix and staffing alone. Almost every point reads as out of control, the team stops trusting the chart, and SPC is discredited within a month. The Laney p-prime tab fixes this — check its 'sigma z' cell: if it is well above 1.0, an ordinary p-chart was never going to work on your data.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="B11" s="2" t="inlineStr">
+    <row r="17" ht="45" customHeight="1">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Recomputing the limits every week. Limits come from a baseline window and then stay put. If you recompute them continuously, a process that is slowly getting worse drags its own limits down with it and never signals.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="1" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Where the numbers come from</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="B13" s="2" t="inlineStr">
+    <row r="19" ht="45" customHeight="1">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Daily volumes and outcome counts: your contact platform's daily summary (Genesys, NICE, Five9, Zendesk Explore, Salesforce reports). Defect counts: your QA tool's audit export. Incident dates: the incident management system, not a spreadsheet somebody keeps by hand.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="1" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>Reading a chart honestly</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="B15" s="2" t="inlineStr">
+    <row r="21" ht="45" customHeight="1">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>A point outside a limit, eight points in a row on one side, or a run of six steadily rising or falling all mean something changed. Anything else is noise and reacting to it makes the process worse — that is tampering, and it is the single most expensive habit in operations management.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Sigma p = the standard deviation expected for THAT day's sample size, so a quiet day gets wider limits than a busy one. Day 1 has 7,820 contacts and a sigma p of 0.00507 (E14) from the overall 72.05% (B5). On a p-prime chart this is then multiplied by sigma z, 4.61 here (B7), which is the Laney correction for a rate that moves more between days than binomial sampling alone can explain</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Sigma u = the standard deviation expected for that week's exposure, so a week with more audited contacts gets tighter limits. Week 1 audited 1,240 and gets 0.00592 (E14) from the overall rate of 0.0434 defects per contact (B5); the Laney sigma z of 2.63 (B7) then widens it for overdispersion. A plain u-chart would have cried wolf on the quiet weeks and had nothing left to say about the loud ones</t>
         </is>
       </c>
     </row>
     <row r="22"/>
     <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Moving range = the gap between this point and the one before it, always positive. It is where an I-MR chart gets its limits: the average of these gaps, 19.53 here, divided by 1.128 gives a sigma of 17.31 (B7, B8), so a point-to-point measure sets the limits rather than the spread of the whole series. That is the point — a slow drift cannot widen the limits and hide itself</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sigma p = the standard deviation expected for THAT day's sample size, so a quiet day gets wider limits than a busy one. Day 1 has 7,820 contacts and a sigma p of 0.00507 (E14) from the overall 72.05% (B5). On a p-prime chart this is then multiplied by sigma z, 4.61 here (B7), which is the Laney correction for a rate that moves more between days than binomial sampling alone can explain</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="33" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Sigma u = the standard deviation expected for that week's exposure, so a week with more audited contacts gets tighter limits. Week 1 audited 1,240 and gets 0.00592 (E14) from the overall rate of 0.0434 defects per contact (B5); the Laney sigma z of 2.63 (B7) then widens it for overdispersion. A plain u-chart would have cried wolf on the quiet weeks and had nothing left to say about the loud ones</t>
+        </is>
+      </c>
+    </row>
     <row r="28"/>
     <row r="29"/>
     <row r="30"/>
@@ -3553,11 +3589,11 @@
     <row r="40"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B10"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="B16"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -5443,9 +5443,6 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="30" max="30"/>
     <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
@@ -6109,7 +6106,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="66" customHeight="1">
+    <row r="22" ht="110" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Day 9</t>
@@ -6158,6 +6155,9 @@
           <t>HOW TO READ IT.  A proportion per period, with limits that widen on quiet days and tighten on busy ones. The Laney correction is what stops a plain p-chart signalling on every point once the samples get large. Two points fall through the lower limit in the worked example — a service-level collapse while volume held.
 SO:  Two days through the lower limit is a collapse, not noise. Pull those days' contacts and find the cause the same week — a point outside the limits is worth more the day it happens than in any monthly review.</t>
         </is>
+      </c>
+      <c r="T22" s="23" t="n">
+        <v>9</v>
       </c>
       <c r="AD22" s="23">
         <f>IF($D22="",NA(),IF(OR($D22&gt;$K22,$D22&lt;$L22),$D22,NA()))</f>
@@ -7016,9 +7016,9 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:I7"/>
-    <mergeCell ref="O22:W22"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="O22:S22"/>
     <mergeCell ref="C5:I5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -7052,9 +7052,6 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="3" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="30" max="30"/>
     <col width="4" customWidth="1" min="31" max="31"/>
   </cols>
@@ -7718,7 +7715,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="77" customHeight="1">
+    <row r="22" ht="110" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Week 9</t>
@@ -7767,6 +7764,9 @@
           <t>HOW TO READ IT.  Defects per unit audited, not the share of units with a defect — one contact can carry several. Same correction as the p′ chart and for the same reason: audit rates move more between weeks than sampling alone explains, and without it the chart cries wolf on the quiet weeks.
 SO:  A rate that trebles is a special cause: audit those weeks' contacts rather than re-training the team. And if sigma z is well above 1, say so when you report — the limits are wider than a plain chart would have drawn and that is the honest picture.</t>
         </is>
+      </c>
+      <c r="T22" s="23" t="n">
+        <v>9</v>
       </c>
       <c r="AD22" s="23">
         <f>IF($D22="",NA(),IF(OR($D22&gt;$K22,$D22&lt;$L22),$D22,NA()))</f>
@@ -8625,9 +8625,9 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="C7:I7"/>
-    <mergeCell ref="O22:W22"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="O22:S22"/>
     <mergeCell ref="C5:I5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/templates/27-control-charts.xlsx
+++ b/templates/27-control-charts.xlsx
@@ -4027,13 +4027,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="84" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Your data — one row per period, oldest first  ·  Key:
 • Moving range = the gap between this point and the one before it, always positive.
 • CL = centre line, the average the chart is drawn around
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line
+• UCL / LCL = upper and lower control limits, a fixed number of standard errors either side of the centre line — ±3 sigma where each point is plotted on its own, and narrower on EWMA or CUSUM, where the statistic already averages several periods and so varies less than a single point does
 • MR = moving range, the gap between one point and the one before it</t>
         </is>
       </c>
@@ -5570,13 +5570,13 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12" ht="72" customHeight="1">
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Your data — one row per day  ·  Key:
 • Sigma p = the standard deviation expected for THAT day's sample size, so a quiet day gets wider limits than a busy one.
 • z = your rate restated in standard deviations, so periods of different size compare
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line
+• UCL / LCL = upper and lower control limits, a fixed number of standard errors either side of the centre line — ±3 sigma where each point is plotted on its own, and narrower on EWMA or CUSUM, where the statistic already averages several periods and so varies less than a single point does
 • CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
@@ -7179,13 +7179,13 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
-    <row r="12" ht="72" customHeight="1">
+    <row r="12" ht="96" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Your data — one row per week  ·  Key:
 • Sigma u = the standard deviation expected for that week's exposure, so a week with more audited contacts gets tighter limits.
 • z = your rate restated in standard deviations, so periods of different size compare
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line
+• UCL / LCL = upper and lower control limits, a fixed number of standard errors either side of the centre line — ±3 sigma where each point is plotted on its own, and narrower on EWMA or CUSUM, where the statistic already averages several periods and so varies less than a single point does
 • CL = centre line, the average the chart is drawn around</t>
         </is>
       </c>
@@ -7715,7 +7715,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="110" customHeight="1">
+    <row r="22" ht="121" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Week 9</t>
@@ -7762,7 +7762,7 @@
       <c r="O22" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  Defects per unit audited, not the share of units with a defect — one contact can carry several. Same correction as the p′ chart and for the same reason: audit rates move more between weeks than sampling alone explains, and without it the chart cries wolf on the quiet weeks.
-SO:  A rate that trebles is a special cause: audit those weeks' contacts rather than re-training the team. And if sigma z is well above 1, say so when you report — the limits are wider than a plain chart would have drawn and that is the honest picture.</t>
+SO:  Two weeks above the upper limit is a special cause: audit those weeks' contacts rather than re-training the team. And if sigma z is well above 1, say so when you report — the limits are wider than a plain chart would have drawn and that is the honest picture.</t>
         </is>
       </c>
       <c r="T22" s="23" t="n">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>Sets the upper limit on the range chart: R-bar x D4. It is the only one of the three that is never zero.</t>
+          <t>Sets the upper limit on the range chart: R-bar x D4. Never zero at any n — D3 below is the only one of the three that ever is.</t>
         </is>
       </c>
     </row>
@@ -8846,13 +8846,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Your data — five observations per subgroup  ·  Key:
 • OBS 1..n are your individual measurements in one subgroup — one row per period
 • CL = centre line, the average the chart is drawn around
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+• UCL / LCL = upper and lower control limits, a fixed number of standard errors either side of the centre line — ±3 sigma where each point is plotted on its own, and narrower on EWMA or CUSUM, where the statistic already averages several periods and so varies less than a single point does</t>
         </is>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -10891,13 +10891,13 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14" ht="48" customHeight="1">
+    <row r="14" ht="72" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Your data — one row per period, oldest first  ·  Key:
 • Moving range = the gap between this point and the one before it, always positive.
 • CL = centre line, the average the chart is drawn around
-• UCL / LCL = upper and lower control limits, ±3 sigma from the centre line</t>
+• UCL / LCL = upper and lower control limits, a fixed number of standard errors either side of the centre line — ±3 sigma where each point is plotted on its own, and narrower on EWMA or CUSUM, where the statistic already averages several periods and so varies less than a single point does</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -12041,12 +12041,13 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="72" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Your data — one row per period, oldest first  ·  Key:
 • Moving range = the gap between this point and the one before it, always positive.
-• SL = service level, the share of contacts answered inside your target time</t>
+• SH (up) = the running sum of how far the process has drifted ABOVE target, counting only the part beyond the slack k, and held at zero otherwise
+• SL (down) = the running sum of how far the process has drifted BELOW target, counting only the part beyond the slack k, and held at zero otherwise</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
